--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1360934846" name="Picture">
+        <xdr:cNvPr id="1781062143" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -1962,7 +1962,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2027</t>
+            <t xml:space="preserve">10/09/2027</t>
           </r>
         </is>
       </c>
@@ -4411,7 +4411,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/06/2026</t>
+            <t xml:space="preserve">18/09/2027</t>
           </r>
         </is>
       </c>
@@ -14365,7 +14365,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -14681,7 +14681,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -16182,7 +16182,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">22/09/2027</t>
           </r>
         </is>
       </c>
@@ -18552,7 +18552,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2026</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -20211,7 +20211,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2026</t>
+            <t xml:space="preserve">15/09/2027</t>
           </r>
         </is>
       </c>
@@ -25631,7 +25631,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO AMANCIO ROSA</t>
+            <t xml:space="preserve">LARISSA SAMARA DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -25641,7 +25641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">063.242.856-26</t>
+            <t xml:space="preserve">130.312.456-44</t>
           </r>
         </is>
       </c>
@@ -25651,7 +25651,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23000101331182026</t>
+            <t xml:space="preserve">06360147584</t>
           </r>
         </is>
       </c>
@@ -25662,7 +25662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -25710,7 +25710,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO CORREA DE OLIVEIRA  </t>
+            <t xml:space="preserve">LEANDRO AMANCIO ROSA</t>
           </r>
         </is>
       </c>
@@ -25720,7 +25720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">102.927.847-40</t>
+            <t xml:space="preserve">063.242.856-26</t>
           </r>
         </is>
       </c>
@@ -25730,7 +25730,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03688215650</t>
+            <t xml:space="preserve">23000101331182026</t>
           </r>
         </is>
       </c>
@@ -25741,7 +25741,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -25789,7 +25789,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO DO CARMO NUNES</t>
+            <t xml:space="preserve">LEANDRO CORREA DE OLIVEIRA  </t>
           </r>
         </is>
       </c>
@@ -25799,7 +25799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.730.376-97</t>
+            <t xml:space="preserve">102.927.847-40</t>
           </r>
         </is>
       </c>
@@ -25809,7 +25809,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03147187110</t>
+            <t xml:space="preserve">03688215650</t>
           </r>
         </is>
       </c>
@@ -25820,7 +25820,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -25868,7 +25868,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO RODRIGUES DA SILVA</t>
+            <t xml:space="preserve">LEANDRO DO CARMO NUNES</t>
           </r>
         </is>
       </c>
@@ -25878,7 +25878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">321.301.738-88</t>
+            <t xml:space="preserve">067.730.376-97</t>
           </r>
         </is>
       </c>
@@ -25888,7 +25888,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03291564997</t>
+            <t xml:space="preserve">03147187110</t>
           </r>
         </is>
       </c>
@@ -25899,7 +25899,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -25947,7 +25947,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO SOUZA DA SILVA</t>
+            <t xml:space="preserve">LEANDRO RODRIGUES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -25957,7 +25957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">103.572.406-50</t>
+            <t xml:space="preserve">321.301.738-88</t>
           </r>
         </is>
       </c>
@@ -25967,7 +25967,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04542317313</t>
+            <t xml:space="preserve">03291564997</t>
           </r>
         </is>
       </c>
@@ -25978,7 +25978,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -26019,14 +26019,14 @@
       <c r="T327" s="12" t="inlineStr"/>
       <c r="U327" s="1" t="inlineStr"/>
     </row>
-    <row r="328" customHeight="1" ht="22">
+    <row r="328" customHeight="1" ht="21">
       <c r="A328" s="1" t="inlineStr"/>
       <c r="B328" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO WAGNER ZACARIAS OLIVEIRA</t>
+            <t xml:space="preserve">LEANDRO SOUZA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -26036,7 +26036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.744.036-70</t>
+            <t xml:space="preserve">103.572.406-50</t>
           </r>
         </is>
       </c>
@@ -26046,7 +26046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">2819007600</t>
+            <t xml:space="preserve">04542317313</t>
           </r>
         </is>
       </c>
@@ -26057,7 +26057,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -26098,14 +26098,14 @@
       <c r="T328" s="12" t="inlineStr"/>
       <c r="U328" s="1" t="inlineStr"/>
     </row>
-    <row r="329" customHeight="1" ht="21">
+    <row r="329" customHeight="1" ht="22">
       <c r="A329" s="1" t="inlineStr"/>
       <c r="B329" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEOCADIO DINIZ SILVA</t>
+            <t xml:space="preserve">LEANDRO WAGNER ZACARIAS OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -26115,7 +26115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">029.392.306-09</t>
+            <t xml:space="preserve">067.744.036-70</t>
           </r>
         </is>
       </c>
@@ -26125,7 +26125,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01279620953</t>
+            <t xml:space="preserve">2819007600</t>
           </r>
         </is>
       </c>
@@ -26184,7 +26184,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEONARDO LOURENCO DA SILVA</t>
+            <t xml:space="preserve">LEOCADIO DINIZ SILVA</t>
           </r>
         </is>
       </c>
@@ -26194,7 +26194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.288.766-20</t>
+            <t xml:space="preserve">029.392.306-09</t>
           </r>
         </is>
       </c>
@@ -26204,7 +26204,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03899458171</t>
+            <t xml:space="preserve">01279620953</t>
           </r>
         </is>
       </c>
@@ -26263,7 +26263,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEONEL HENRIQUE FERRÃO</t>
+            <t xml:space="preserve">LEONARDO LOURENCO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -26273,7 +26273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.263.116-45</t>
+            <t xml:space="preserve">079.288.766-20</t>
           </r>
         </is>
       </c>
@@ -26283,7 +26283,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05139720231</t>
+            <t xml:space="preserve">03899458171</t>
           </r>
         </is>
       </c>
@@ -26294,7 +26294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -26335,14 +26335,14 @@
       <c r="T331" s="12" t="inlineStr"/>
       <c r="U331" s="1" t="inlineStr"/>
     </row>
-    <row r="332" customHeight="1" ht="22">
+    <row r="332" customHeight="1" ht="21">
       <c r="A332" s="1" t="inlineStr"/>
       <c r="B332" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LETICIA LILIANE DE SOUZA BARBOSA </t>
+            <t xml:space="preserve">LEONEL HENRIQUE FERRÃO</t>
           </r>
         </is>
       </c>
@@ -26352,7 +26352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">064.598.096-07</t>
+            <t xml:space="preserve">122.263.116-45</t>
           </r>
         </is>
       </c>
@@ -26362,7 +26362,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04632836129</t>
+            <t xml:space="preserve">05139720231</t>
           </r>
         </is>
       </c>
@@ -26373,7 +26373,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/05/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -26414,14 +26414,14 @@
       <c r="T332" s="12" t="inlineStr"/>
       <c r="U332" s="1" t="inlineStr"/>
     </row>
-    <row r="333" customHeight="1" ht="21">
+    <row r="333" customHeight="1" ht="22">
       <c r="A333" s="1" t="inlineStr"/>
       <c r="B333" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LIDIANA APARECIDA CARNEIRO</t>
+            <t xml:space="preserve">LETICIA LILIANE DE SOUZA BARBOSA </t>
           </r>
         </is>
       </c>
@@ -26431,7 +26431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">118.771.816-50</t>
+            <t xml:space="preserve">064.598.096-07</t>
           </r>
         </is>
       </c>
@@ -26441,7 +26441,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06773280877</t>
+            <t xml:space="preserve">04632836129</t>
           </r>
         </is>
       </c>
@@ -26452,7 +26452,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/06/2026</t>
+            <t xml:space="preserve">30/05/2026</t>
           </r>
         </is>
       </c>
@@ -26493,14 +26493,14 @@
       <c r="T333" s="12" t="inlineStr"/>
       <c r="U333" s="1" t="inlineStr"/>
     </row>
-    <row r="334" customHeight="1" ht="22">
+    <row r="334" customHeight="1" ht="21">
       <c r="A334" s="1" t="inlineStr"/>
       <c r="B334" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LINDOLFO MENDONCA DOS SANTOS</t>
+            <t xml:space="preserve">LIDIANA APARECIDA CARNEIRO</t>
           </r>
         </is>
       </c>
@@ -26510,7 +26510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">529.408.706-59</t>
+            <t xml:space="preserve">118.771.816-50</t>
           </r>
         </is>
       </c>
@@ -26520,7 +26520,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00019756510</t>
+            <t xml:space="preserve">06773280877</t>
           </r>
         </is>
       </c>
@@ -26531,7 +26531,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -26572,14 +26572,14 @@
       <c r="T334" s="12" t="inlineStr"/>
       <c r="U334" s="1" t="inlineStr"/>
     </row>
-    <row r="335" customHeight="1" ht="21">
+    <row r="335" customHeight="1" ht="22">
       <c r="A335" s="1" t="inlineStr"/>
       <c r="B335" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUAN MARTINS MARCONDES</t>
+            <t xml:space="preserve">LINDOLFO MENDONCA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -26589,7 +26589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">096.277.976-85</t>
+            <t xml:space="preserve">529.408.706-59</t>
           </r>
         </is>
       </c>
@@ -26599,7 +26599,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289665375</t>
+            <t xml:space="preserve">00019756510</t>
           </r>
         </is>
       </c>
@@ -26610,7 +26610,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/02/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -26658,7 +26658,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS GONÇALVES MARTINS</t>
+            <t xml:space="preserve">LUAN MARTINS MARCONDES</t>
           </r>
         </is>
       </c>
@@ -26668,7 +26668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">085.552.436-70</t>
+            <t xml:space="preserve">096.277.976-85</t>
           </r>
         </is>
       </c>
@@ -26678,7 +26678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4693218713</t>
+            <t xml:space="preserve">04289665375</t>
           </r>
         </is>
       </c>
@@ -26689,7 +26689,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">11/02/2027</t>
           </r>
         </is>
       </c>
@@ -26737,7 +26737,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS LUIZ ALVES</t>
+            <t xml:space="preserve">LUCAS GONÇALVES MARTINS</t>
           </r>
         </is>
       </c>
@@ -26747,7 +26747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.062.856-91</t>
+            <t xml:space="preserve">085.552.436-70</t>
           </r>
         </is>
       </c>
@@ -26757,7 +26757,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01322002444</t>
+            <t xml:space="preserve">4693218713</t>
           </r>
         </is>
       </c>
@@ -26768,7 +26768,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -26816,7 +26816,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS SANTOS DE QUEIROZ</t>
+            <t xml:space="preserve">LUCAS LUIZ ALVES</t>
           </r>
         </is>
       </c>
@@ -26826,7 +26826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">113.927.196-23</t>
+            <t xml:space="preserve">819.062.856-91</t>
           </r>
         </is>
       </c>
@@ -26836,7 +26836,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05160627501</t>
+            <t xml:space="preserve">01322002444</t>
           </r>
         </is>
       </c>
@@ -26847,7 +26847,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -26895,7 +26895,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS SILVA FRANCA</t>
+            <t xml:space="preserve">LUCAS SANTOS DE QUEIROZ</t>
           </r>
         </is>
       </c>
@@ -26905,7 +26905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">013.991.046-83</t>
+            <t xml:space="preserve">113.927.196-23</t>
           </r>
         </is>
       </c>
@@ -26915,7 +26915,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02413059875</t>
+            <t xml:space="preserve">05160627501</t>
           </r>
         </is>
       </c>
@@ -26926,7 +26926,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -26974,7 +26974,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS VELOSO AMANCIO MACIEL</t>
+            <t xml:space="preserve">LUCAS SILVA FRANCA</t>
           </r>
         </is>
       </c>
@@ -26984,7 +26984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">135.218.266-19</t>
+            <t xml:space="preserve">013.991.046-83</t>
           </r>
         </is>
       </c>
@@ -26994,7 +26994,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06383476601</t>
+            <t xml:space="preserve">02413059875</t>
           </r>
         </is>
       </c>
@@ -27005,7 +27005,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2026</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -27046,14 +27046,14 @@
       <c r="T340" s="12" t="inlineStr"/>
       <c r="U340" s="1" t="inlineStr"/>
     </row>
-    <row r="341" customHeight="1" ht="22">
+    <row r="341" customHeight="1" ht="21">
       <c r="A341" s="1" t="inlineStr"/>
       <c r="B341" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIA FERNANDA PEREIRA DA COSTA</t>
+            <t xml:space="preserve">LUCAS VELOSO AMANCIO MACIEL</t>
           </r>
         </is>
       </c>
@@ -27063,7 +27063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">031.585.776-58</t>
+            <t xml:space="preserve">135.218.266-19</t>
           </r>
         </is>
       </c>
@@ -27073,7 +27073,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">053314624601</t>
+            <t xml:space="preserve">06383476601</t>
           </r>
         </is>
       </c>
@@ -27084,7 +27084,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">11/07/2026</t>
           </r>
         </is>
       </c>
@@ -27125,14 +27125,14 @@
       <c r="T341" s="12" t="inlineStr"/>
       <c r="U341" s="1" t="inlineStr"/>
     </row>
-    <row r="342" customHeight="1" ht="21">
+    <row r="342" customHeight="1" ht="22">
       <c r="A342" s="1" t="inlineStr"/>
       <c r="B342" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIANE DE FATIMA R. COSTA    </t>
+            <t xml:space="preserve">LUCIA FERNANDA PEREIRA DA COSTA</t>
           </r>
         </is>
       </c>
@@ -27142,7 +27142,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.763.156-69</t>
+            <t xml:space="preserve">031.585.776-58</t>
           </r>
         </is>
       </c>
@@ -27152,7 +27152,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04611449989</t>
+            <t xml:space="preserve">053314624601</t>
           </r>
         </is>
       </c>
@@ -27163,7 +27163,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -27211,7 +27211,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIANO PAULINO DA COSTA</t>
+            <t xml:space="preserve">LUCIANE DE FATIMA R. COSTA    </t>
           </r>
         </is>
       </c>
@@ -27221,7 +27221,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">050.130.496-79</t>
+            <t xml:space="preserve">093.763.156-69</t>
           </r>
         </is>
       </c>
@@ -27231,7 +27231,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03103773460</t>
+            <t xml:space="preserve">04611449989</t>
           </r>
         </is>
       </c>
@@ -27242,7 +27242,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -27290,7 +27290,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIO AURELIANO DA SILVA</t>
+            <t xml:space="preserve">LUCIANO PAULINO DA COSTA</t>
           </r>
         </is>
       </c>
@@ -27300,7 +27300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">047.703.276-17</t>
+            <t xml:space="preserve">050.130.496-79</t>
           </r>
         </is>
       </c>
@@ -27310,7 +27310,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04593463442</t>
+            <t xml:space="preserve">03103773460</t>
           </r>
         </is>
       </c>
@@ -27321,7 +27321,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -27369,7 +27369,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIO FABIO FERREIRA</t>
+            <t xml:space="preserve">LUCIO AURELIANO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -27379,7 +27379,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">006.683.332-94</t>
+            <t xml:space="preserve">047.703.276-17</t>
           </r>
         </is>
       </c>
@@ -27389,7 +27389,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04484954449</t>
+            <t xml:space="preserve">04593463442</t>
           </r>
         </is>
       </c>
@@ -27400,7 +27400,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2031</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -27448,7 +27448,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIS CARLOS VELOSO</t>
+            <t xml:space="preserve">LUCIO FABIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -27458,7 +27458,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">943.062.656-68</t>
+            <t xml:space="preserve">006.683.332-94</t>
           </r>
         </is>
       </c>
@@ -27468,7 +27468,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00863735779</t>
+            <t xml:space="preserve">04484954449</t>
           </r>
         </is>
       </c>
@@ -27479,7 +27479,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/01/2026</t>
+            <t xml:space="preserve">10/08/2031</t>
           </r>
         </is>
       </c>
@@ -27527,7 +27527,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ ANDRE BORGES CAIXETA</t>
+            <t xml:space="preserve">LUIS CARLOS VELOSO</t>
           </r>
         </is>
       </c>
@@ -27537,7 +27537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.942.196-77</t>
+            <t xml:space="preserve">943.062.656-68</t>
           </r>
         </is>
       </c>
@@ -27547,7 +27547,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01667588932</t>
+            <t xml:space="preserve">00863735779</t>
           </r>
         </is>
       </c>
@@ -27558,7 +27558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">14/01/2026</t>
           </r>
         </is>
       </c>
@@ -27606,7 +27606,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ ANTONIO DA SILVA</t>
+            <t xml:space="preserve">LUIZ ANDRE BORGES CAIXETA</t>
           </r>
         </is>
       </c>
@@ -27616,7 +27616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">778.833.066-34</t>
+            <t xml:space="preserve">046.942.196-77</t>
           </r>
         </is>
       </c>
@@ -27626,7 +27626,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02831837732</t>
+            <t xml:space="preserve">01667588932</t>
           </r>
         </is>
       </c>
@@ -27637,7 +27637,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -27685,7 +27685,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ CARLOS DE ASSIS</t>
+            <t xml:space="preserve">LUIZ ANTONIO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -27695,7 +27695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">063.432.686-42</t>
+            <t xml:space="preserve">778.833.066-34</t>
           </r>
         </is>
       </c>
@@ -27705,7 +27705,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02836643209</t>
+            <t xml:space="preserve">02831837732</t>
           </r>
         </is>
       </c>
@@ -27716,7 +27716,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/06/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -27764,7 +27764,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ FERNANDO GONCALVES</t>
+            <t xml:space="preserve">LUIZ CARLOS DE ASSIS</t>
           </r>
         </is>
       </c>
@@ -27774,7 +27774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">066.587.606-83</t>
+            <t xml:space="preserve">063.432.686-42</t>
           </r>
         </is>
       </c>
@@ -27784,7 +27784,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04319056439</t>
+            <t xml:space="preserve">02836643209</t>
           </r>
         </is>
       </c>
@@ -27795,7 +27795,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/10/2026</t>
+            <t xml:space="preserve">25/06/2027</t>
           </r>
         </is>
       </c>
@@ -27843,7 +27843,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ GONZAGA DA SILVA</t>
+            <t xml:space="preserve">LUIZ FERNANDO GONCALVES</t>
           </r>
         </is>
       </c>
@@ -27853,7 +27853,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">939.705.796-00</t>
+            <t xml:space="preserve">066.587.606-83</t>
           </r>
         </is>
       </c>
@@ -27863,7 +27863,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01099082690</t>
+            <t xml:space="preserve">04319056439</t>
           </r>
         </is>
       </c>
@@ -27874,7 +27874,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">09/10/2026</t>
           </r>
         </is>
       </c>
@@ -27922,7 +27922,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ GUSTAVO SANTOS LIMA</t>
+            <t xml:space="preserve">LUIZ GONZAGA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -27932,7 +27932,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">083.760.036-74</t>
+            <t xml:space="preserve">939.705.796-00</t>
           </r>
         </is>
       </c>
@@ -27942,7 +27942,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04424986322</t>
+            <t xml:space="preserve">01099082690</t>
           </r>
         </is>
       </c>
@@ -27953,7 +27953,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -28001,7 +28001,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ HENRIQUE E MARTINS VIEIRA  </t>
+            <t xml:space="preserve">LUIZ GUSTAVO SANTOS LIMA</t>
           </r>
         </is>
       </c>
@@ -28011,7 +28011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.281.616-04</t>
+            <t xml:space="preserve">083.760.036-74</t>
           </r>
         </is>
       </c>
@@ -28021,7 +28021,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04521971771</t>
+            <t xml:space="preserve">04424986322</t>
           </r>
         </is>
       </c>
@@ -28032,7 +28032,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -28080,7 +28080,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ RICARDO DE MELO</t>
+            <t xml:space="preserve">LUIZ HENRIQUE E MARTINS VIEIRA  </t>
           </r>
         </is>
       </c>
@@ -28090,7 +28090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.995.666-10</t>
+            <t xml:space="preserve">088.281.616-04</t>
           </r>
         </is>
       </c>
@@ -28100,7 +28100,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03344105706</t>
+            <t xml:space="preserve">04521971771</t>
           </r>
         </is>
       </c>
@@ -28111,7 +28111,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -28159,7 +28159,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUZIA MARIA DOS SANTOS</t>
+            <t xml:space="preserve">LUIZ RICARDO DE MELO</t>
           </r>
         </is>
       </c>
@@ -28169,7 +28169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.951.396-59</t>
+            <t xml:space="preserve">076.995.666-10</t>
           </r>
         </is>
       </c>
@@ -28179,7 +28179,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04148424907</t>
+            <t xml:space="preserve">03344105706</t>
           </r>
         </is>
       </c>
@@ -28190,7 +28190,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/12/2023</t>
+            <t xml:space="preserve">29/07/2027</t>
           </r>
         </is>
       </c>
@@ -28238,7 +28238,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAIKY SANTANA FERNANDES</t>
+            <t xml:space="preserve">LUZIA MARIA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -28248,7 +28248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">140.188.876-39</t>
+            <t xml:space="preserve">026.951.396-59</t>
           </r>
         </is>
       </c>
@@ -28258,7 +28258,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06777417203</t>
+            <t xml:space="preserve">04148424907</t>
           </r>
         </is>
       </c>
@@ -28269,7 +28269,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/07/2027</t>
+            <t xml:space="preserve">31/12/2023</t>
           </r>
         </is>
       </c>
@@ -28317,7 +28317,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MANOEL SANTOS MORAES</t>
+            <t xml:space="preserve">MAIKY SANTANA FERNANDES</t>
           </r>
         </is>
       </c>
@@ -28327,7 +28327,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">715.808.326-87</t>
+            <t xml:space="preserve">140.188.876-39</t>
           </r>
         </is>
       </c>
@@ -28337,7 +28337,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01155974255</t>
+            <t xml:space="preserve">06777417203</t>
           </r>
         </is>
       </c>
@@ -28348,7 +28348,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">24/07/2027</t>
           </r>
         </is>
       </c>
@@ -28396,7 +28396,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO BATISTA DOS SANTOS</t>
+            <t xml:space="preserve">MANOEL SANTOS MORAES</t>
           </r>
         </is>
       </c>
@@ -28406,7 +28406,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">043.142.726-78</t>
+            <t xml:space="preserve">715.808.326-87</t>
           </r>
         </is>
       </c>
@@ -28416,7 +28416,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02450313294</t>
+            <t xml:space="preserve">01155974255</t>
           </r>
         </is>
       </c>
@@ -28427,7 +28427,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -28475,7 +28475,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO HENRIQUE CAETANO</t>
+            <t xml:space="preserve">MARCELO BATISTA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -28485,7 +28485,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">034.939.999-92</t>
+            <t xml:space="preserve">043.142.726-78</t>
           </r>
         </is>
       </c>
@@ -28495,7 +28495,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02099361590</t>
+            <t xml:space="preserve">02450313294</t>
           </r>
         </is>
       </c>
@@ -28506,7 +28506,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -28547,14 +28547,14 @@
       <c r="T359" s="12" t="inlineStr"/>
       <c r="U359" s="1" t="inlineStr"/>
     </row>
-    <row r="360" customHeight="1" ht="22">
+    <row r="360" customHeight="1" ht="21">
       <c r="A360" s="1" t="inlineStr"/>
       <c r="B360" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO LUCIANO DE SOUZA OLIVEIRA</t>
+            <t xml:space="preserve">MARCELO HENRIQUE CAETANO</t>
           </r>
         </is>
       </c>
@@ -28564,7 +28564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">073.595.556-55</t>
+            <t xml:space="preserve">034.939.999-92</t>
           </r>
         </is>
       </c>
@@ -28574,7 +28574,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03641355881</t>
+            <t xml:space="preserve">02099361590</t>
           </r>
         </is>
       </c>
@@ -28585,7 +28585,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -28626,14 +28626,14 @@
       <c r="T360" s="12" t="inlineStr"/>
       <c r="U360" s="1" t="inlineStr"/>
     </row>
-    <row r="361" customHeight="1" ht="21">
+    <row r="361" customHeight="1" ht="22">
       <c r="A361" s="1" t="inlineStr"/>
       <c r="B361" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO MARTINS BORGES</t>
+            <t xml:space="preserve">MARCELO LUCIANO DE SOUZA OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -28643,7 +28643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">002.744.406-60</t>
+            <t xml:space="preserve">073.595.556-55</t>
           </r>
         </is>
       </c>
@@ -28653,7 +28653,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02783779084</t>
+            <t xml:space="preserve">03641355881</t>
           </r>
         </is>
       </c>
@@ -28664,7 +28664,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2025</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -28712,7 +28712,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO MENDES DOS SANTOS</t>
+            <t xml:space="preserve">MARCELO MARTINS BORGES</t>
           </r>
         </is>
       </c>
@@ -28722,7 +28722,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">901.945.276-20</t>
+            <t xml:space="preserve">002.744.406-60</t>
           </r>
         </is>
       </c>
@@ -28732,7 +28732,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04168367162</t>
+            <t xml:space="preserve">02783779084</t>
           </r>
         </is>
       </c>
@@ -28743,7 +28743,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">31/07/2025</t>
           </r>
         </is>
       </c>
@@ -28791,7 +28791,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO TADEU DE OLIVEIRA</t>
+            <t xml:space="preserve">MARCELO MENDES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -28801,7 +28801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">049.321.486-07</t>
+            <t xml:space="preserve">901.945.276-20</t>
           </r>
         </is>
       </c>
@@ -28811,7 +28811,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01620321495</t>
+            <t xml:space="preserve">04168367162</t>
           </r>
         </is>
       </c>
@@ -28822,7 +28822,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -28870,7 +28870,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ALAIR CORREA  </t>
+            <t xml:space="preserve">MARCELO TADEU DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -28880,7 +28880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">549.576.056-53</t>
+            <t xml:space="preserve">049.321.486-07</t>
           </r>
         </is>
       </c>
@@ -28890,7 +28890,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02871826370</t>
+            <t xml:space="preserve">01620321495</t>
           </r>
         </is>
       </c>
@@ -28901,7 +28901,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -28949,7 +28949,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ANTONIO FERREIRA</t>
+            <t xml:space="preserve">MARCIO ALAIR CORREA  </t>
           </r>
         </is>
       </c>
@@ -28959,7 +28959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">902.851.406-63</t>
+            <t xml:space="preserve">549.576.056-53</t>
           </r>
         </is>
       </c>
@@ -28969,7 +28969,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02516992442</t>
+            <t xml:space="preserve">02871826370</t>
           </r>
         </is>
       </c>
@@ -28980,7 +28980,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -29021,14 +29021,14 @@
       <c r="T365" s="12" t="inlineStr"/>
       <c r="U365" s="1" t="inlineStr"/>
     </row>
-    <row r="366" customHeight="1" ht="22">
+    <row r="366" customHeight="1" ht="21">
       <c r="A366" s="1" t="inlineStr"/>
       <c r="B366" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ANTONIO PARREIRAS DA PAZ</t>
+            <t xml:space="preserve">MARCIO ANTONIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -29038,7 +29038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">577.128.916-72</t>
+            <t xml:space="preserve">902.851.406-63</t>
           </r>
         </is>
       </c>
@@ -29048,7 +29048,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02890495585</t>
+            <t xml:space="preserve">02516992442</t>
           </r>
         </is>
       </c>
@@ -29059,7 +29059,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -29100,14 +29100,14 @@
       <c r="T366" s="12" t="inlineStr"/>
       <c r="U366" s="1" t="inlineStr"/>
     </row>
-    <row r="367" customHeight="1" ht="21">
+    <row r="367" customHeight="1" ht="22">
       <c r="A367" s="1" t="inlineStr"/>
       <c r="B367" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO DA SILVA OTTONI</t>
+            <t xml:space="preserve">MARCIO ANTONIO PARREIRAS DA PAZ</t>
           </r>
         </is>
       </c>
@@ -29117,7 +29117,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.607.566-51</t>
+            <t xml:space="preserve">577.128.916-72</t>
           </r>
         </is>
       </c>
@@ -29127,7 +29127,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01687919581</t>
+            <t xml:space="preserve">02890495585</t>
           </r>
         </is>
       </c>
@@ -29138,7 +29138,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/02/2026</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -29179,14 +29179,14 @@
       <c r="T367" s="12" t="inlineStr"/>
       <c r="U367" s="1" t="inlineStr"/>
     </row>
-    <row r="368" customHeight="1" ht="22">
+    <row r="368" customHeight="1" ht="21">
       <c r="A368" s="1" t="inlineStr"/>
       <c r="B368" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO FLAVIO ANDRADE ALMEIDA</t>
+            <t xml:space="preserve">MARCIO DA SILVA OTTONI</t>
           </r>
         </is>
       </c>
@@ -29196,7 +29196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.017.466-97</t>
+            <t xml:space="preserve">026.607.566-51</t>
           </r>
         </is>
       </c>
@@ -29206,7 +29206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289067720</t>
+            <t xml:space="preserve">01687919581</t>
           </r>
         </is>
       </c>
@@ -29217,7 +29217,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/07/2027</t>
+            <t xml:space="preserve">21/02/2026</t>
           </r>
         </is>
       </c>
@@ -29258,14 +29258,14 @@
       <c r="T368" s="12" t="inlineStr"/>
       <c r="U368" s="1" t="inlineStr"/>
     </row>
-    <row r="369" customHeight="1" ht="21">
+    <row r="369" customHeight="1" ht="22">
       <c r="A369" s="1" t="inlineStr"/>
       <c r="B369" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIONE APARECIDO MARTINS</t>
+            <t xml:space="preserve">MARCIO FLAVIO ANDRADE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -29275,7 +29275,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">041.411.046-39</t>
+            <t xml:space="preserve">040.017.466-97</t>
           </r>
         </is>
       </c>
@@ -29285,7 +29285,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03863886454</t>
+            <t xml:space="preserve">04289067720</t>
           </r>
         </is>
       </c>
@@ -29296,7 +29296,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">06/07/2027</t>
           </r>
         </is>
       </c>
@@ -29337,14 +29337,14 @@
       <c r="T369" s="12" t="inlineStr"/>
       <c r="U369" s="1" t="inlineStr"/>
     </row>
-    <row r="370" customHeight="1" ht="22">
+    <row r="370" customHeight="1" ht="21">
       <c r="A370" s="1" t="inlineStr"/>
       <c r="B370" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCO AURELIO HENRIQUE DOS SANTOS</t>
+            <t xml:space="preserve">MARCIONE APARECIDO MARTINS</t>
           </r>
         </is>
       </c>
@@ -29354,7 +29354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.690.426-50</t>
+            <t xml:space="preserve">041.411.046-39</t>
           </r>
         </is>
       </c>
@@ -29364,7 +29364,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05105181704</t>
+            <t xml:space="preserve">03863886454</t>
           </r>
         </is>
       </c>
@@ -29375,7 +29375,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -29416,14 +29416,14 @@
       <c r="T370" s="12" t="inlineStr"/>
       <c r="U370" s="1" t="inlineStr"/>
     </row>
-    <row r="371" customHeight="1" ht="21">
+    <row r="371" customHeight="1" ht="22">
       <c r="A371" s="1" t="inlineStr"/>
       <c r="B371" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANDRÉ DE ALMEIDA</t>
+            <t xml:space="preserve">MARCO AURELIO HENRIQUE DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -29433,7 +29433,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">056.770.516-16</t>
+            <t xml:space="preserve">110.690.426-50</t>
           </r>
         </is>
       </c>
@@ -29443,7 +29443,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03502926908</t>
+            <t xml:space="preserve">05105181704</t>
           </r>
         </is>
       </c>
@@ -29454,7 +29454,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -29495,14 +29495,14 @@
       <c r="T371" s="12" t="inlineStr"/>
       <c r="U371" s="1" t="inlineStr"/>
     </row>
-    <row r="372" customHeight="1" ht="22">
+    <row r="372" customHeight="1" ht="21">
       <c r="A372" s="1" t="inlineStr"/>
       <c r="B372" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANTONIO PEREIRA DA SILVA</t>
+            <t xml:space="preserve">MARCOS ANDRÉ DE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -29512,7 +29512,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">952.874.346-34</t>
+            <t xml:space="preserve">056.770.516-16</t>
           </r>
         </is>
       </c>
@@ -29522,7 +29522,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03056193881</t>
+            <t xml:space="preserve">03502926908</t>
           </r>
         </is>
       </c>
@@ -29533,7 +29533,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -29581,7 +29581,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS AURELIO BARBOSA</t>
+            <t xml:space="preserve">MARCOS ANTONIO COSTA</t>
           </r>
         </is>
       </c>
@@ -29591,7 +29591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.909.046-28</t>
+            <t xml:space="preserve">077.627.216-06</t>
           </r>
         </is>
       </c>
@@ -29601,7 +29601,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03480890822</t>
+            <t xml:space="preserve">05971763818</t>
           </r>
         </is>
       </c>
@@ -29612,7 +29612,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -29653,14 +29653,14 @@
       <c r="T373" s="12" t="inlineStr"/>
       <c r="U373" s="1" t="inlineStr"/>
     </row>
-    <row r="374" customHeight="1" ht="21">
+    <row r="374" customHeight="1" ht="22">
       <c r="A374" s="1" t="inlineStr"/>
       <c r="B374" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS DE ASSIS FERREIRA </t>
+            <t xml:space="preserve">MARCOS ANTONIO PEREIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -29670,7 +29670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">047.953.146-32</t>
+            <t xml:space="preserve">952.874.346-34</t>
           </r>
         </is>
       </c>
@@ -29680,7 +29680,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04407791869</t>
+            <t xml:space="preserve">03056193881</t>
           </r>
         </is>
       </c>
@@ -29691,7 +29691,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -29739,7 +29739,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS GUIMARAES CALDEIRA</t>
+            <t xml:space="preserve">MARCOS AURELIO BARBOSA</t>
           </r>
         </is>
       </c>
@@ -29749,7 +29749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.400.096-93</t>
+            <t xml:space="preserve">051.909.046-28</t>
           </r>
         </is>
       </c>
@@ -29759,7 +29759,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03689823277</t>
+            <t xml:space="preserve">03480890822</t>
           </r>
         </is>
       </c>
@@ -29770,7 +29770,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/08/2026</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -29818,7 +29818,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS HENRIQUE REIS</t>
+            <t xml:space="preserve">MARCOS DE ASSIS FERREIRA </t>
           </r>
         </is>
       </c>
@@ -29828,7 +29828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">089.960.066-29</t>
+            <t xml:space="preserve">047.953.146-32</t>
           </r>
         </is>
       </c>
@@ -29838,7 +29838,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04248770930</t>
+            <t xml:space="preserve">04407791869</t>
           </r>
         </is>
       </c>
@@ -29849,7 +29849,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -29897,7 +29897,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS JHONATAN ALVES</t>
+            <t xml:space="preserve">MARCOS GUIMARAES CALDEIRA</t>
           </r>
         </is>
       </c>
@@ -29907,7 +29907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">106.575.206-75</t>
+            <t xml:space="preserve">076.400.096-93</t>
           </r>
         </is>
       </c>
@@ -29917,7 +29917,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05470405595</t>
+            <t xml:space="preserve">03689823277</t>
           </r>
         </is>
       </c>
@@ -29928,7 +29928,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">28/08/2027</t>
           </r>
         </is>
       </c>
@@ -29976,7 +29976,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS JOSE TRIGUEIRO</t>
+            <t xml:space="preserve">MARCOS HENRIQUE REIS</t>
           </r>
         </is>
       </c>
@@ -29986,7 +29986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">721.730.416-49</t>
+            <t xml:space="preserve">089.960.066-29</t>
           </r>
         </is>
       </c>
@@ -29996,7 +29996,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01704730263</t>
+            <t xml:space="preserve">04248770930</t>
           </r>
         </is>
       </c>
@@ -30007,7 +30007,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/05/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -30055,7 +30055,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS VINICIUS SILVA GOMES</t>
+            <t xml:space="preserve">MARCOS JHONATAN ALVES</t>
           </r>
         </is>
       </c>
@@ -30065,7 +30065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">018.869.786-11</t>
+            <t xml:space="preserve">106.575.206-75</t>
           </r>
         </is>
       </c>
@@ -30075,7 +30075,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07590695960</t>
+            <t xml:space="preserve">05470405595</t>
           </r>
         </is>
       </c>
@@ -30086,7 +30086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2027</t>
+            <t xml:space="preserve">11/08/2026</t>
           </r>
         </is>
       </c>
@@ -30134,7 +30134,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCUS VINICIUS MOREIRA</t>
+            <t xml:space="preserve">MARCOS JOSE TRIGUEIRO</t>
           </r>
         </is>
       </c>
@@ -30144,7 +30144,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">582.830.726-68</t>
+            <t xml:space="preserve">721.730.416-49</t>
           </r>
         </is>
       </c>
@@ -30154,7 +30154,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01594136546</t>
+            <t xml:space="preserve">01704730263</t>
           </r>
         </is>
       </c>
@@ -30165,7 +30165,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">15/05/2026</t>
           </r>
         </is>
       </c>
@@ -30206,14 +30206,14 @@
       <c r="T380" s="12" t="inlineStr"/>
       <c r="U380" s="1" t="inlineStr"/>
     </row>
-    <row r="381" customHeight="1" ht="22">
+    <row r="381" customHeight="1" ht="21">
       <c r="A381" s="1" t="inlineStr"/>
       <c r="B381" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATHEUS MATIAS NOGUEIRA DOS SANTOS</t>
+            <t xml:space="preserve">MARCOS VINICIUS SILVA GOMES</t>
           </r>
         </is>
       </c>
@@ -30223,7 +30223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">105.075.596-06</t>
+            <t xml:space="preserve">018.869.786-11</t>
           </r>
         </is>
       </c>
@@ -30233,7 +30233,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06658773832</t>
+            <t xml:space="preserve">07590695960</t>
           </r>
         </is>
       </c>
@@ -30244,7 +30244,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">11/07/2027</t>
           </r>
         </is>
       </c>
@@ -30292,7 +30292,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATOSALEM NUNES DA CRUZ</t>
+            <t xml:space="preserve">MARCUS VINICIUS MOREIRA</t>
           </r>
         </is>
       </c>
@@ -30302,7 +30302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">936.443.376-91</t>
+            <t xml:space="preserve">582.830.726-68</t>
           </r>
         </is>
       </c>
@@ -30312,7 +30312,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02695434380</t>
+            <t xml:space="preserve">01594136546</t>
           </r>
         </is>
       </c>
@@ -30323,7 +30323,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -30364,14 +30364,14 @@
       <c r="T382" s="12" t="inlineStr"/>
       <c r="U382" s="1" t="inlineStr"/>
     </row>
-    <row r="383" customHeight="1" ht="21">
+    <row r="383" customHeight="1" ht="22">
       <c r="A383" s="1" t="inlineStr"/>
       <c r="B383" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATUSAEL PEREIRA DE SOUSA</t>
+            <t xml:space="preserve">MATHEUS MATIAS NOGUEIRA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -30381,7 +30381,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">702.247.496-68</t>
+            <t xml:space="preserve">105.075.596-06</t>
           </r>
         </is>
       </c>
@@ -30391,7 +30391,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02236242704</t>
+            <t xml:space="preserve">06658773832</t>
           </r>
         </is>
       </c>
@@ -30402,7 +30402,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/09/2025</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -30450,7 +30450,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO DOS SANTOS VIEIRA</t>
+            <t xml:space="preserve">MATOSALEM NUNES DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -30460,7 +30460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.860.416-69</t>
+            <t xml:space="preserve">936.443.376-91</t>
           </r>
         </is>
       </c>
@@ -30470,7 +30470,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01707561330</t>
+            <t xml:space="preserve">02695434380</t>
           </r>
         </is>
       </c>
@@ -30481,7 +30481,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/07/2025</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -30529,7 +30529,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO MONTEIRO</t>
+            <t xml:space="preserve">MATUSAEL PEREIRA DE SOUSA</t>
           </r>
         </is>
       </c>
@@ -30539,7 +30539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">631.406.596-87</t>
+            <t xml:space="preserve">702.247.496-68</t>
           </r>
         </is>
       </c>
@@ -30549,7 +30549,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04067779168</t>
+            <t xml:space="preserve">02236242704</t>
           </r>
         </is>
       </c>
@@ -30560,7 +30560,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/10/2025</t>
+            <t xml:space="preserve">20/09/2025</t>
           </r>
         </is>
       </c>
@@ -30608,7 +30608,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO RIBEIRO DE OLIVEIRA</t>
+            <t xml:space="preserve">MAURICIO DOS SANTOS VIEIRA</t>
           </r>
         </is>
       </c>
@@ -30618,7 +30618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.153.576-91</t>
+            <t xml:space="preserve">040.860.416-69</t>
           </r>
         </is>
       </c>
@@ -30628,7 +30628,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03578222825</t>
+            <t xml:space="preserve">01707561330</t>
           </r>
         </is>
       </c>
@@ -30639,7 +30639,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/05/2027</t>
+            <t xml:space="preserve">10/07/2025</t>
           </r>
         </is>
       </c>
@@ -30687,7 +30687,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO LÚCIO DO CARMO</t>
+            <t xml:space="preserve">MAURICIO MONTEIRO</t>
           </r>
         </is>
       </c>
@@ -30697,7 +30697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">925.340.316-00</t>
+            <t xml:space="preserve">631.406.596-87</t>
           </r>
         </is>
       </c>
@@ -30707,7 +30707,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00409168014</t>
+            <t xml:space="preserve">04067779168</t>
           </r>
         </is>
       </c>
@@ -30718,7 +30718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/03/2026</t>
+            <t xml:space="preserve">31/10/2025</t>
           </r>
         </is>
       </c>
@@ -30766,7 +30766,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO SOARES LEAO  </t>
+            <t xml:space="preserve">MAURICIO RIBEIRO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -30776,7 +30776,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">384.804.096-49</t>
+            <t xml:space="preserve">819.153.576-91</t>
           </r>
         </is>
       </c>
@@ -30786,7 +30786,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02582612080</t>
+            <t xml:space="preserve">03578222825</t>
           </r>
         </is>
       </c>
@@ -30797,7 +30797,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">26/05/2027</t>
           </r>
         </is>
       </c>
@@ -30845,7 +30845,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MICHELE FARIA DE CASTRO</t>
+            <t xml:space="preserve">MAURO LÚCIO DO CARMO</t>
           </r>
         </is>
       </c>
@@ -30855,7 +30855,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">083.973.226-04</t>
+            <t xml:space="preserve">925.340.316-00</t>
           </r>
         </is>
       </c>
@@ -30865,7 +30865,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03837467386</t>
+            <t xml:space="preserve">00409168014</t>
           </r>
         </is>
       </c>
@@ -30876,7 +30876,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/08/2027</t>
+            <t xml:space="preserve">21/03/2026</t>
           </r>
         </is>
       </c>
@@ -30924,7 +30924,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON DA SILVEIRA REZENDE</t>
+            <t xml:space="preserve">MAURO SOARES LEAO  </t>
           </r>
         </is>
       </c>
@@ -30934,7 +30934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">455.523.636-04</t>
+            <t xml:space="preserve">384.804.096-49</t>
           </r>
         </is>
       </c>
@@ -30944,7 +30944,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02118384033</t>
+            <t xml:space="preserve">02582612080</t>
           </r>
         </is>
       </c>
@@ -30955,7 +30955,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/11/2026</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -31003,7 +31003,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON FELIX DA CRUZ</t>
+            <t xml:space="preserve">MICHELE FARIA DE CASTRO</t>
           </r>
         </is>
       </c>
@@ -31013,7 +31013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">007.806.387-60</t>
+            <t xml:space="preserve">083.973.226-04</t>
           </r>
         </is>
       </c>
@@ -31023,7 +31023,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02901380541</t>
+            <t xml:space="preserve">03837467386</t>
           </r>
         </is>
       </c>
@@ -31034,7 +31034,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">26/08/2027</t>
           </r>
         </is>
       </c>
@@ -31082,7 +31082,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON LOURENCO   </t>
+            <t xml:space="preserve">MILTON DA SILVEIRA REZENDE</t>
           </r>
         </is>
       </c>
@@ -31092,7 +31092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">728.967.796-04</t>
+            <t xml:space="preserve">455.523.636-04</t>
           </r>
         </is>
       </c>
@@ -31102,7 +31102,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00967395628</t>
+            <t xml:space="preserve">02118384033</t>
           </r>
         </is>
       </c>
@@ -31113,7 +31113,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">20/11/2026</t>
           </r>
         </is>
       </c>
@@ -31161,7 +31161,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MIZAEL BABO AUGUSTO</t>
+            <t xml:space="preserve">MILTON FELIX DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -31171,7 +31171,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">097.718.576-14</t>
+            <t xml:space="preserve">007.806.387-60</t>
           </r>
         </is>
       </c>
@@ -31181,7 +31181,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07220573198</t>
+            <t xml:space="preserve">02901380541</t>
           </r>
         </is>
       </c>
@@ -31192,7 +31192,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/09/2025</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -31240,7 +31240,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MONALDO JULIO DA SILVA</t>
+            <t xml:space="preserve">MILTON LOURENCO   </t>
           </r>
         </is>
       </c>
@@ -31250,7 +31250,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">787.493.956-53</t>
+            <t xml:space="preserve">728.967.796-04</t>
           </r>
         </is>
       </c>
@@ -31260,7 +31260,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00710808596</t>
+            <t xml:space="preserve">00967395628</t>
           </r>
         </is>
       </c>
@@ -31271,7 +31271,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -31319,7 +31319,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MOZART JOSE DA SILVA</t>
+            <t xml:space="preserve">MIZAEL BABO AUGUSTO</t>
           </r>
         </is>
       </c>
@@ -31329,7 +31329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">411.500.586-68</t>
+            <t xml:space="preserve">097.718.576-14</t>
           </r>
         </is>
       </c>
@@ -31339,7 +31339,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02069316250</t>
+            <t xml:space="preserve">07220573198</t>
           </r>
         </is>
       </c>
@@ -31350,7 +31350,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2027</t>
+            <t xml:space="preserve">16/09/2025</t>
           </r>
         </is>
       </c>
@@ -31398,7 +31398,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NACIEL LEMOS PEREIRA</t>
+            <t xml:space="preserve">MONALDO JULIO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -31408,7 +31408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">113.971.196-24</t>
+            <t xml:space="preserve">787.493.956-53</t>
           </r>
         </is>
       </c>
@@ -31418,7 +31418,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05182091350</t>
+            <t xml:space="preserve">00710808596</t>
           </r>
         </is>
       </c>
@@ -31429,7 +31429,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -31477,7 +31477,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NASCIMENTO DOS REIS GONDIN</t>
+            <t xml:space="preserve">MOZART JOSE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -31487,7 +31487,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">761.988.636-20</t>
+            <t xml:space="preserve">411.500.586-68</t>
           </r>
         </is>
       </c>
@@ -31497,7 +31497,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00900948176</t>
+            <t xml:space="preserve">02069316250</t>
           </r>
         </is>
       </c>
@@ -31508,7 +31508,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">11/07/2027</t>
           </r>
         </is>
       </c>
@@ -31556,7 +31556,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NATALIA MARQUES CLEMENTE</t>
+            <t xml:space="preserve">NACIEL LEMOS PEREIRA</t>
           </r>
         </is>
       </c>
@@ -31566,7 +31566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">105.427.006-62</t>
+            <t xml:space="preserve">113.971.196-24</t>
           </r>
         </is>
       </c>
@@ -31576,7 +31576,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08144307204</t>
+            <t xml:space="preserve">05182091350</t>
           </r>
         </is>
       </c>
@@ -31587,7 +31587,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">11/08/2026</t>
           </r>
         </is>
       </c>
@@ -31635,7 +31635,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NAUBERT MARCELO SOUZA XAVIER</t>
+            <t xml:space="preserve">NASCIMENTO DOS REIS GONDIN</t>
           </r>
         </is>
       </c>
@@ -31645,7 +31645,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">102.231.886-11</t>
+            <t xml:space="preserve">761.988.636-20</t>
           </r>
         </is>
       </c>
@@ -31655,7 +31655,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06564062300</t>
+            <t xml:space="preserve">00900948176</t>
           </r>
         </is>
       </c>
@@ -31666,7 +31666,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -31707,14 +31707,14 @@
       <c r="T399" s="12" t="inlineStr"/>
       <c r="U399" s="1" t="inlineStr"/>
     </row>
-    <row r="400" customHeight="1" ht="22">
+    <row r="400" customHeight="1" ht="21">
       <c r="A400" s="1" t="inlineStr"/>
       <c r="B400" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NAYARA TARCIA PENIDO GUIMARAES</t>
+            <t xml:space="preserve">NATALIA MARQUES CLEMENTE</t>
           </r>
         </is>
       </c>
@@ -31724,7 +31724,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.418.096-47</t>
+            <t xml:space="preserve">105.427.006-62</t>
           </r>
         </is>
       </c>
@@ -31734,7 +31734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04386747420</t>
+            <t xml:space="preserve">08144307204</t>
           </r>
         </is>
       </c>
@@ -31745,7 +31745,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -31793,7 +31793,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NEIMAR RICARDO PEREIRA</t>
+            <t xml:space="preserve">NAUBERT MARCELO SOUZA XAVIER</t>
           </r>
         </is>
       </c>
@@ -31803,7 +31803,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">089.354.186-92</t>
+            <t xml:space="preserve">102.231.886-11</t>
           </r>
         </is>
       </c>
@@ -31813,7 +31813,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03994374484</t>
+            <t xml:space="preserve">06564062300</t>
           </r>
         </is>
       </c>
@@ -31824,7 +31824,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -31865,14 +31865,14 @@
       <c r="T401" s="12" t="inlineStr"/>
       <c r="U401" s="1" t="inlineStr"/>
     </row>
-    <row r="402" customHeight="1" ht="21">
+    <row r="402" customHeight="1" ht="22">
       <c r="A402" s="1" t="inlineStr"/>
       <c r="B402" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NELSON ESTEVAM CAETANO</t>
+            <t xml:space="preserve">NAYARA TARCIA PENIDO GUIMARAES</t>
           </r>
         </is>
       </c>
@@ -31882,7 +31882,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">786.778.316-49</t>
+            <t xml:space="preserve">088.418.096-47</t>
           </r>
         </is>
       </c>
@@ -31892,7 +31892,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00970062398</t>
+            <t xml:space="preserve">04386747420</t>
           </r>
         </is>
       </c>
@@ -31903,7 +31903,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -31951,7 +31951,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NERILTON RODRIGUES DE LIMA</t>
+            <t xml:space="preserve">NEIMAR RICARDO PEREIRA</t>
           </r>
         </is>
       </c>
@@ -31961,7 +31961,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">639.992.936-91</t>
+            <t xml:space="preserve">089.354.186-92</t>
           </r>
         </is>
       </c>
@@ -31971,7 +31971,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03027917140</t>
+            <t xml:space="preserve">03994374484</t>
           </r>
         </is>
       </c>
@@ -32030,7 +32030,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NILSON FERNANDES DE OLIVEIRA</t>
+            <t xml:space="preserve">NELSON ESTEVAM CAETANO</t>
           </r>
         </is>
       </c>
@@ -32040,7 +32040,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">968.600.146-87</t>
+            <t xml:space="preserve">786.778.316-49</t>
           </r>
         </is>
       </c>
@@ -32050,7 +32050,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00910443480</t>
+            <t xml:space="preserve">00970062398</t>
           </r>
         </is>
       </c>
@@ -32109,7 +32109,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NILTON CESAR DOS SANTOS</t>
+            <t xml:space="preserve">NERILTON RODRIGUES DE LIMA</t>
           </r>
         </is>
       </c>
@@ -32119,7 +32119,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">575.710.905-04</t>
+            <t xml:space="preserve">639.992.936-91</t>
           </r>
         </is>
       </c>
@@ -32129,7 +32129,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">005560025786</t>
+            <t xml:space="preserve">03027917140</t>
           </r>
         </is>
       </c>
@@ -32140,7 +32140,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -32188,7 +32188,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODAIR JOSE BELTOLDO</t>
+            <t xml:space="preserve">NILSON FERNANDES DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -32198,7 +32198,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">004.220.596-41</t>
+            <t xml:space="preserve">968.600.146-87</t>
           </r>
         </is>
       </c>
@@ -32208,7 +32208,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01148775390</t>
+            <t xml:space="preserve">00910443480</t>
           </r>
         </is>
       </c>
@@ -32219,7 +32219,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -32267,7 +32267,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODAIR JOSE DE ALMEIDA</t>
+            <t xml:space="preserve">NILTON CESAR DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -32277,7 +32277,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">000.451.336-38</t>
+            <t xml:space="preserve">575.710.905-04</t>
           </r>
         </is>
       </c>
@@ -32287,7 +32287,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03494010309</t>
+            <t xml:space="preserve">005560025786</t>
           </r>
         </is>
       </c>
@@ -32298,7 +32298,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -32346,7 +32346,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODICE DUTRA DOS REIS</t>
+            <t xml:space="preserve">ODAIR JOSE BELTOLDO</t>
           </r>
         </is>
       </c>
@@ -32356,7 +32356,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">754.948.256-04</t>
+            <t xml:space="preserve">004.220.596-41</t>
           </r>
         </is>
       </c>
@@ -32366,7 +32366,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01734148835</t>
+            <t xml:space="preserve">01148775390</t>
           </r>
         </is>
       </c>
@@ -32377,7 +32377,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -32425,7 +32425,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ORLANDO AGOSTINHO PINTO</t>
+            <t xml:space="preserve">ODAIR JOSE DE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -32435,7 +32435,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">006.413.446-60</t>
+            <t xml:space="preserve">000.451.336-38</t>
           </r>
         </is>
       </c>
@@ -32445,7 +32445,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02745787040</t>
+            <t xml:space="preserve">03494010309</t>
           </r>
         </is>
       </c>
@@ -32504,7 +32504,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALDO ARLINDO DE MEIRA</t>
+            <t xml:space="preserve">ODICE DUTRA DOS REIS</t>
           </r>
         </is>
       </c>
@@ -32514,7 +32514,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.805.766-60</t>
+            <t xml:space="preserve">754.948.256-04</t>
           </r>
         </is>
       </c>
@@ -32524,7 +32524,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03105139100</t>
+            <t xml:space="preserve">01734148835</t>
           </r>
         </is>
       </c>
@@ -32535,7 +32535,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -32583,7 +32583,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALDO COELHO DE MORAES</t>
+            <t xml:space="preserve">ORLANDO AGOSTINHO PINTO</t>
           </r>
         </is>
       </c>
@@ -32593,7 +32593,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">545.222.186-72</t>
+            <t xml:space="preserve">006.413.446-60</t>
           </r>
         </is>
       </c>
@@ -32603,7 +32603,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03759063307</t>
+            <t xml:space="preserve">02745787040</t>
           </r>
         </is>
       </c>
@@ -32614,7 +32614,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -32662,7 +32662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSWALDO DOS SANTOS JUNIOR</t>
+            <t xml:space="preserve">OSVALDO ARLINDO DE MEIRA</t>
           </r>
         </is>
       </c>
@@ -32672,7 +32672,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">892.492.326-91</t>
+            <t xml:space="preserve">051.805.766-60</t>
           </r>
         </is>
       </c>
@@ -32682,7 +32682,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00822357647</t>
+            <t xml:space="preserve">03105139100</t>
           </r>
         </is>
       </c>
@@ -32693,7 +32693,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -32741,7 +32741,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OTAVIO MOURA SILVA</t>
+            <t xml:space="preserve">OSVALDO COELHO DE MORAES</t>
           </r>
         </is>
       </c>
@@ -32751,7 +32751,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">116.799.556-24</t>
+            <t xml:space="preserve">545.222.186-72</t>
           </r>
         </is>
       </c>
@@ -32761,7 +32761,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06947671960</t>
+            <t xml:space="preserve">03759063307</t>
           </r>
         </is>
       </c>
@@ -32772,7 +32772,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02/07/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -32820,7 +32820,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OZIAS ROSA NUNES DA SILVA</t>
+            <t xml:space="preserve">OSWALDO DOS SANTOS JUNIOR</t>
           </r>
         </is>
       </c>
@@ -32830,7 +32830,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.717.456-17</t>
+            <t xml:space="preserve">892.492.326-91</t>
           </r>
         </is>
       </c>
@@ -32840,7 +32840,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02844195589</t>
+            <t xml:space="preserve">00822357647</t>
           </r>
         </is>
       </c>
@@ -32899,7 +32899,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PABLO NOE LANA</t>
+            <t xml:space="preserve">OTAVIO MOURA SILVA</t>
           </r>
         </is>
       </c>
@@ -32909,7 +32909,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.279.556-33</t>
+            <t xml:space="preserve">116.799.556-24</t>
           </r>
         </is>
       </c>
@@ -32919,7 +32919,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03371448607</t>
+            <t xml:space="preserve">06947671960</t>
           </r>
         </is>
       </c>
@@ -32930,7 +32930,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">02/07/2027</t>
           </r>
         </is>
       </c>
@@ -32978,7 +32978,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PABLO VINICIO MARQUES DA SILVA</t>
+            <t xml:space="preserve">OZIAS ROSA NUNES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -32988,7 +32988,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">125.648.656-66</t>
+            <t xml:space="preserve">051.717.456-17</t>
           </r>
         </is>
       </c>
@@ -32998,7 +32998,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06041166234</t>
+            <t xml:space="preserve">02844195589</t>
           </r>
         </is>
       </c>
@@ -33009,7 +33009,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -33057,7 +33057,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO FERNANDES MACHADO</t>
+            <t xml:space="preserve">PABLO NOE LANA</t>
           </r>
         </is>
       </c>
@@ -33067,7 +33067,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">646.984.836-20</t>
+            <t xml:space="preserve">040.279.556-33</t>
           </r>
         </is>
       </c>
@@ -33077,7 +33077,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00437370810</t>
+            <t xml:space="preserve">03371448607</t>
           </r>
         </is>
       </c>
@@ -33088,7 +33088,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -33136,7 +33136,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO HENRIQUE DA SILVA</t>
+            <t xml:space="preserve">PABLO VINICIO MARQUES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33146,7 +33146,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">145.560.786-01</t>
+            <t xml:space="preserve">125.648.656-66</t>
           </r>
         </is>
       </c>
@@ -33156,7 +33156,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06876540658</t>
+            <t xml:space="preserve">06041166234</t>
           </r>
         </is>
       </c>
@@ -33167,7 +33167,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/06/2026</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -33208,14 +33208,14 @@
       <c r="T418" s="12" t="inlineStr"/>
       <c r="U418" s="1" t="inlineStr"/>
     </row>
-    <row r="419" customHeight="1" ht="22">
+    <row r="419" customHeight="1" ht="21">
       <c r="A419" s="1" t="inlineStr"/>
       <c r="B419" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO HENRIQUE SILVA APOLINARIO</t>
+            <t xml:space="preserve">PAULO FERNANDES MACHADO</t>
           </r>
         </is>
       </c>
@@ -33225,7 +33225,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">078.119.326-52</t>
+            <t xml:space="preserve">646.984.836-20</t>
           </r>
         </is>
       </c>
@@ -33235,7 +33235,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04058607086</t>
+            <t xml:space="preserve">00437370810</t>
           </r>
         </is>
       </c>
@@ -33246,7 +33246,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/09/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -33294,7 +33294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO JOSE DO NASCIMENTO </t>
+            <t xml:space="preserve">PAULO HENRIQUE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33304,7 +33304,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">632.040.456-68</t>
+            <t xml:space="preserve">145.560.786-01</t>
           </r>
         </is>
       </c>
@@ -33314,7 +33314,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02867848381</t>
+            <t xml:space="preserve">06876540658</t>
           </r>
         </is>
       </c>
@@ -33325,7 +33325,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/07/2030</t>
+            <t xml:space="preserve">03/06/2026</t>
           </r>
         </is>
       </c>
@@ -33366,14 +33366,14 @@
       <c r="T420" s="12" t="inlineStr"/>
       <c r="U420" s="1" t="inlineStr"/>
     </row>
-    <row r="421" customHeight="1" ht="21">
+    <row r="421" customHeight="1" ht="22">
       <c r="A421" s="1" t="inlineStr"/>
       <c r="B421" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO MARCIO FERREIRA</t>
+            <t xml:space="preserve">PAULO HENRIQUE SILVA APOLINARIO</t>
           </r>
         </is>
       </c>
@@ -33383,7 +33383,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">927.606.946-15</t>
+            <t xml:space="preserve">078.119.326-52</t>
           </r>
         </is>
       </c>
@@ -33393,7 +33393,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02635238806</t>
+            <t xml:space="preserve">04058607086</t>
           </r>
         </is>
       </c>
@@ -33404,7 +33404,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">08/09/2027</t>
           </r>
         </is>
       </c>
@@ -33452,7 +33452,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO SERGIO DA CRUZ</t>
+            <t xml:space="preserve">PAULO JOSE DO NASCIMENTO </t>
           </r>
         </is>
       </c>
@@ -33462,7 +33462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">746.204.526-53</t>
+            <t xml:space="preserve">632.040.456-68</t>
           </r>
         </is>
       </c>
@@ -33472,7 +33472,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01934028430</t>
+            <t xml:space="preserve">02867848381</t>
           </r>
         </is>
       </c>
@@ -33483,7 +33483,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/07/2027</t>
+            <t xml:space="preserve">30/07/2030</t>
           </r>
         </is>
       </c>
@@ -33531,7 +33531,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO SERGIO DA CUNHA</t>
+            <t xml:space="preserve">PAULO MARCIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -33541,7 +33541,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">003.102.236-79</t>
+            <t xml:space="preserve">927.606.946-15</t>
           </r>
         </is>
       </c>
@@ -33551,7 +33551,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04344405135</t>
+            <t xml:space="preserve">02635238806</t>
           </r>
         </is>
       </c>
@@ -33562,7 +33562,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -33610,7 +33610,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO ANTONIO BENTO</t>
+            <t xml:space="preserve">PAULO SERGIO DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -33620,7 +33620,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">493.901.636-68</t>
+            <t xml:space="preserve">746.204.526-53</t>
           </r>
         </is>
       </c>
@@ -33630,7 +33630,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00694729250</t>
+            <t xml:space="preserve">01934028430</t>
           </r>
         </is>
       </c>
@@ -33641,7 +33641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2026</t>
+            <t xml:space="preserve">04/07/2027</t>
           </r>
         </is>
       </c>
@@ -33682,14 +33682,14 @@
       <c r="T424" s="12" t="inlineStr"/>
       <c r="U424" s="1" t="inlineStr"/>
     </row>
-    <row r="425" customHeight="1" ht="22">
+    <row r="425" customHeight="1" ht="21">
       <c r="A425" s="1" t="inlineStr"/>
       <c r="B425" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE ANTUNES MORAIS</t>
+            <t xml:space="preserve">PAULO SERGIO DA CUNHA</t>
           </r>
         </is>
       </c>
@@ -33699,7 +33699,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">124.819.026-29</t>
+            <t xml:space="preserve">003.102.236-79</t>
           </r>
         </is>
       </c>
@@ -33709,7 +33709,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06571602700</t>
+            <t xml:space="preserve">04344405135</t>
           </r>
         </is>
       </c>
@@ -33720,7 +33720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -33761,14 +33761,14 @@
       <c r="T425" s="12" t="inlineStr"/>
       <c r="U425" s="1" t="inlineStr"/>
     </row>
-    <row r="426" customHeight="1" ht="22">
+    <row r="426" customHeight="1" ht="21">
       <c r="A426" s="1" t="inlineStr"/>
       <c r="B426" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE RESENDE MAGALHAES FARINHA</t>
+            <t xml:space="preserve">PEDRO ANTONIO BENTO</t>
           </r>
         </is>
       </c>
@@ -33778,7 +33778,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.378.606-75</t>
+            <t xml:space="preserve">493.901.636-68</t>
           </r>
         </is>
       </c>
@@ -33788,7 +33788,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06845908627</t>
+            <t xml:space="preserve">00694729250</t>
           </r>
         </is>
       </c>
@@ -33799,7 +33799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">29/07/2026</t>
           </r>
         </is>
       </c>
@@ -33847,7 +33847,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE SILVERIO MARTINS VIEIRA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE ANTUNES MORAIS</t>
           </r>
         </is>
       </c>
@@ -33857,7 +33857,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.281.606-32</t>
+            <t xml:space="preserve">124.819.026-29</t>
           </r>
         </is>
       </c>
@@ -33867,7 +33867,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03691532816</t>
+            <t xml:space="preserve">06571602700</t>
           </r>
         </is>
       </c>
@@ -33878,7 +33878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -33926,7 +33926,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE TORRES MARTINS </t>
+            <t xml:space="preserve">PEDRO HENRIQUE RESENDE MAGALHAES FARINHA</t>
           </r>
         </is>
       </c>
@@ -33936,7 +33936,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">156.289.896-57</t>
+            <t xml:space="preserve">110.378.606-75</t>
           </r>
         </is>
       </c>
@@ -33946,7 +33946,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08127162566</t>
+            <t xml:space="preserve">06845908627</t>
           </r>
         </is>
       </c>
@@ -33957,7 +33957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -33998,14 +33998,14 @@
       <c r="T428" s="12" t="inlineStr"/>
       <c r="U428" s="1" t="inlineStr"/>
     </row>
-    <row r="429" customHeight="1" ht="21">
+    <row r="429" customHeight="1" ht="22">
       <c r="A429" s="1" t="inlineStr"/>
       <c r="B429" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO RODRIGUES DE PAULA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE SILVERIO MARTINS VIEIRA</t>
           </r>
         </is>
       </c>
@@ -34015,7 +34015,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">578.466.186-87</t>
+            <t xml:space="preserve">088.281.606-32</t>
           </r>
         </is>
       </c>
@@ -34025,7 +34025,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01168973776</t>
+            <t xml:space="preserve">03691532816</t>
           </r>
         </is>
       </c>
@@ -34036,7 +34036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2025</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -34077,14 +34077,14 @@
       <c r="T429" s="12" t="inlineStr"/>
       <c r="U429" s="1" t="inlineStr"/>
     </row>
-    <row r="430" customHeight="1" ht="21">
+    <row r="430" customHeight="1" ht="22">
       <c r="A430" s="1" t="inlineStr"/>
       <c r="B430" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO RODRIGUES PEREIRA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE TORRES MARTINS </t>
           </r>
         </is>
       </c>
@@ -34094,7 +34094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">095.236.816-13</t>
+            <t xml:space="preserve">156.289.896-57</t>
           </r>
         </is>
       </c>
@@ -34104,7 +34104,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04944405662</t>
+            <t xml:space="preserve">08127162566</t>
           </r>
         </is>
       </c>
@@ -34115,7 +34115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -34163,7 +34163,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PLINIO RAFAEL ANDRADE</t>
+            <t xml:space="preserve">PEDRO RODRIGUES DE PAULA</t>
           </r>
         </is>
       </c>
@@ -34173,7 +34173,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">098.676.626-79</t>
+            <t xml:space="preserve">578.466.186-87</t>
           </r>
         </is>
       </c>
@@ -34183,7 +34183,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04903258724</t>
+            <t xml:space="preserve">01168973776</t>
           </r>
         </is>
       </c>
@@ -34194,7 +34194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">31/07/2025</t>
           </r>
         </is>
       </c>
@@ -34242,7 +34242,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PRISCILA SILVA LACERDA</t>
+            <t xml:space="preserve">PEDRO RODRIGUES PEREIRA</t>
           </r>
         </is>
       </c>
@@ -34252,7 +34252,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">066.424.716-44</t>
+            <t xml:space="preserve">095.236.816-13</t>
           </r>
         </is>
       </c>
@@ -34262,7 +34262,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02895817906</t>
+            <t xml:space="preserve">04944405662</t>
           </r>
         </is>
       </c>
@@ -34273,7 +34273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/11/2026</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -34321,7 +34321,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAEL FERREIRA MARTINS</t>
+            <t xml:space="preserve">PLINIO RAFAEL ANDRADE</t>
           </r>
         </is>
       </c>
@@ -34331,7 +34331,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.733.626-84</t>
+            <t xml:space="preserve">098.676.626-79</t>
           </r>
         </is>
       </c>
@@ -34341,7 +34341,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05713407303</t>
+            <t xml:space="preserve">04903258724</t>
           </r>
         </is>
       </c>
@@ -34352,7 +34352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">28/07/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -34400,7 +34400,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL COIMBRA GONTIJO</t>
+            <t xml:space="preserve">PRISCILA SILVA LACERDA</t>
           </r>
         </is>
       </c>
@@ -34410,7 +34410,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.055.666-60</t>
+            <t xml:space="preserve">066.424.716-44</t>
           </r>
         </is>
       </c>
@@ -34420,7 +34420,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05538775609</t>
+            <t xml:space="preserve">02895817906</t>
           </r>
         </is>
       </c>
@@ -34431,7 +34431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">26/11/2026</t>
           </r>
         </is>
       </c>
@@ -34472,14 +34472,14 @@
       <c r="T434" s="12" t="inlineStr"/>
       <c r="U434" s="1" t="inlineStr"/>
     </row>
-    <row r="435" customHeight="1" ht="22">
+    <row r="435" customHeight="1" ht="21">
       <c r="A435" s="1" t="inlineStr"/>
       <c r="B435" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL MATHEUS MARTINS COELHO </t>
+            <t xml:space="preserve">RAEL FERREIRA MARTINS</t>
           </r>
         </is>
       </c>
@@ -34489,7 +34489,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">147.684.866-14</t>
+            <t xml:space="preserve">122.733.626-84</t>
           </r>
         </is>
       </c>
@@ -34499,7 +34499,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07093318680</t>
+            <t xml:space="preserve">05713407303</t>
           </r>
         </is>
       </c>
@@ -34510,7 +34510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">28/07/2026</t>
           </r>
         </is>
       </c>
@@ -34558,7 +34558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL MORAES BARBOSA</t>
+            <t xml:space="preserve">RAFAEL COIMBRA GONTIJO</t>
           </r>
         </is>
       </c>
@@ -34568,7 +34568,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.669.666-27</t>
+            <t xml:space="preserve">065.055.666-60</t>
           </r>
         </is>
       </c>
@@ -34578,7 +34578,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05783669254</t>
+            <t xml:space="preserve">05538775609</t>
           </r>
         </is>
       </c>
@@ -34589,7 +34589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/07/2027</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -34630,14 +34630,14 @@
       <c r="T436" s="12" t="inlineStr"/>
       <c r="U436" s="1" t="inlineStr"/>
     </row>
-    <row r="437" customHeight="1" ht="21">
+    <row r="437" customHeight="1" ht="22">
       <c r="A437" s="1" t="inlineStr"/>
       <c r="B437" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL SOUZA REZENDE ROCHA</t>
+            <t xml:space="preserve">RAFAEL MATHEUS MARTINS COELHO </t>
           </r>
         </is>
       </c>
@@ -34647,7 +34647,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.998.096-27</t>
+            <t xml:space="preserve">147.684.866-14</t>
           </r>
         </is>
       </c>
@@ -34657,7 +34657,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06443469242</t>
+            <t xml:space="preserve">07093318680</t>
           </r>
         </is>
       </c>
@@ -34668,7 +34668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/05/2026</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -34716,7 +34716,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAELA GONÇALVES DA SILVA</t>
+            <t xml:space="preserve">RAFAEL MORAES BARBOSA</t>
           </r>
         </is>
       </c>
@@ -34726,7 +34726,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">097.757.966-28</t>
+            <t xml:space="preserve">070.669.666-27</t>
           </r>
         </is>
       </c>
@@ -34736,7 +34736,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05193246932</t>
+            <t xml:space="preserve">05783669254</t>
           </r>
         </is>
       </c>
@@ -34747,7 +34747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">18/07/2027</t>
           </r>
         </is>
       </c>
@@ -34795,7 +34795,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAIMUNDO CAMILO DA SILVA NETO</t>
+            <t xml:space="preserve">RAFAEL SOUZA REZENDE ROCHA</t>
           </r>
         </is>
       </c>
@@ -34805,7 +34805,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">736.682.906-44</t>
+            <t xml:space="preserve">122.998.096-27</t>
           </r>
         </is>
       </c>
@@ -34815,7 +34815,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00628460620</t>
+            <t xml:space="preserve">06443469242</t>
           </r>
         </is>
       </c>
@@ -34826,7 +34826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">14/05/2026</t>
           </r>
         </is>
       </c>
@@ -34874,7 +34874,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAIMUNDO NONATO DOS REIS</t>
+            <t xml:space="preserve">RAFAELA GONÇALVES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -34884,7 +34884,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">520.482.176-72</t>
+            <t xml:space="preserve">097.757.966-28</t>
           </r>
         </is>
       </c>
@@ -34894,7 +34894,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02656000194</t>
+            <t xml:space="preserve">05193246932</t>
           </r>
         </is>
       </c>
@@ -34905,7 +34905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -34953,7 +34953,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAMON HENRIQUE DA SILVA</t>
+            <t xml:space="preserve">RAIMUNDO CAMILO DA SILVA NETO</t>
           </r>
         </is>
       </c>
@@ -34963,7 +34963,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.806.026-33</t>
+            <t xml:space="preserve">736.682.906-44</t>
           </r>
         </is>
       </c>
@@ -34973,7 +34973,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04113942460</t>
+            <t xml:space="preserve">00628460620</t>
           </r>
         </is>
       </c>
@@ -34984,7 +34984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/01/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -35025,14 +35025,14 @@
       <c r="T441" s="12" t="inlineStr"/>
       <c r="U441" s="1" t="inlineStr"/>
     </row>
-    <row r="442" customHeight="1" ht="22">
+    <row r="442" customHeight="1" ht="21">
       <c r="A442" s="1" t="inlineStr"/>
       <c r="B442" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAMON WEMERSON VELOSO TEIXEIRA</t>
+            <t xml:space="preserve">RAIMUNDO NONATO DOS REIS</t>
           </r>
         </is>
       </c>
@@ -35042,7 +35042,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">099.777.116-07</t>
+            <t xml:space="preserve">520.482.176-72</t>
           </r>
         </is>
       </c>
@@ -35052,7 +35052,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04970737232</t>
+            <t xml:space="preserve">02656000194</t>
           </r>
         </is>
       </c>
@@ -35063,7 +35063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -35104,14 +35104,14 @@
       <c r="T442" s="12" t="inlineStr"/>
       <c r="U442" s="1" t="inlineStr"/>
     </row>
-    <row r="443" customHeight="1" ht="22">
+    <row r="443" customHeight="1" ht="21">
       <c r="A443" s="1" t="inlineStr"/>
       <c r="B443" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RANIEL ROMERICK LIMA DE OLIVEIRA</t>
+            <t xml:space="preserve">RAMON HENRIQUE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -35121,7 +35121,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.580.076-05</t>
+            <t xml:space="preserve">079.806.026-33</t>
           </r>
         </is>
       </c>
@@ -35131,7 +35131,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05302294379</t>
+            <t xml:space="preserve">04113942460</t>
           </r>
         </is>
       </c>
@@ -35142,7 +35142,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">22/01/2027</t>
           </r>
         </is>
       </c>
@@ -35183,14 +35183,14 @@
       <c r="T443" s="12" t="inlineStr"/>
       <c r="U443" s="1" t="inlineStr"/>
     </row>
-    <row r="444" customHeight="1" ht="21">
+    <row r="444" customHeight="1" ht="22">
       <c r="A444" s="1" t="inlineStr"/>
       <c r="B444" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAPHAEL HENRIQUE ROCHA SILVA</t>
+            <t xml:space="preserve">RAMON WEMERSON VELOSO TEIXEIRA</t>
           </r>
         </is>
       </c>
@@ -35200,7 +35200,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">100.372.356-05</t>
+            <t xml:space="preserve">099.777.116-07</t>
           </r>
         </is>
       </c>
@@ -35210,7 +35210,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05480849132</t>
+            <t xml:space="preserve">04970737232</t>
           </r>
         </is>
       </c>
@@ -35221,7 +35221,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -35262,14 +35262,14 @@
       <c r="T444" s="12" t="inlineStr"/>
       <c r="U444" s="1" t="inlineStr"/>
     </row>
-    <row r="445" customHeight="1" ht="21">
+    <row r="445" customHeight="1" ht="22">
       <c r="A445" s="1" t="inlineStr"/>
       <c r="B445" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAVENGAR NUNES DE OLIVEIRA</t>
+            <t xml:space="preserve">RANIEL ROMERICK LIMA DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -35279,7 +35279,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">087.922.076-77</t>
+            <t xml:space="preserve">093.580.076-05</t>
           </r>
         </is>
       </c>
@@ -35289,7 +35289,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04161596624</t>
+            <t xml:space="preserve">05302294379</t>
           </r>
         </is>
       </c>
@@ -35300,7 +35300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/07/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -35348,7 +35348,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO EUSTAQUIO ALVES</t>
+            <t xml:space="preserve">RAPHAEL HENRIQUE ROCHA SILVA</t>
           </r>
         </is>
       </c>
@@ -35358,7 +35358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.746.886-98</t>
+            <t xml:space="preserve">100.372.356-05</t>
           </r>
         </is>
       </c>
@@ -35368,7 +35368,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02942466380</t>
+            <t xml:space="preserve">05480849132</t>
           </r>
         </is>
       </c>
@@ -35379,7 +35379,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -35427,7 +35427,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO GOMES DOS SANTOS</t>
+            <t xml:space="preserve">RAVENGAR NUNES DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -35437,7 +35437,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.934.616-71</t>
+            <t xml:space="preserve">087.922.076-77</t>
           </r>
         </is>
       </c>
@@ -35447,7 +35447,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03466250864</t>
+            <t xml:space="preserve">04161596624</t>
           </r>
         </is>
       </c>
@@ -35458,7 +35458,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/11/2026</t>
+            <t xml:space="preserve">21/07/2027</t>
           </r>
         </is>
       </c>
@@ -35506,7 +35506,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO VICENTINO DE PAULA</t>
+            <t xml:space="preserve">REGINALDO EUSTAQUIO ALVES</t>
           </r>
         </is>
       </c>
@@ -35516,7 +35516,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">062.303.156-61</t>
+            <t xml:space="preserve">046.746.886-98</t>
           </r>
         </is>
       </c>
@@ -35526,7 +35526,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07456908970</t>
+            <t xml:space="preserve">02942466380</t>
           </r>
         </is>
       </c>
@@ -35537,7 +35537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -35585,7 +35585,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RENAN REZENDE DA CRUZ</t>
+            <t xml:space="preserve">REGINALDO GOMES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -35595,7 +35595,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">068.003.286-00</t>
+            <t xml:space="preserve">061.934.616-71</t>
           </r>
         </is>
       </c>
@@ -35605,7 +35605,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04461438210</t>
+            <t xml:space="preserve">03466250864</t>
           </r>
         </is>
       </c>
@@ -35616,7 +35616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">25/11/2026</t>
           </r>
         </is>
       </c>
@@ -35657,14 +35657,14 @@
       <c r="T449" s="12" t="inlineStr"/>
       <c r="U449" s="1" t="inlineStr"/>
     </row>
-    <row r="450" customHeight="1" ht="22">
+    <row r="450" customHeight="1" ht="21">
       <c r="A450" s="1" t="inlineStr"/>
       <c r="B450" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RENATO MARTINS DA SILVA GOUVEIA</t>
+            <t xml:space="preserve">REGINALDO VICENTINO DE PAULA</t>
           </r>
         </is>
       </c>
@@ -35674,7 +35674,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">045.158.916-50</t>
+            <t xml:space="preserve">062.303.156-61</t>
           </r>
         </is>
       </c>
@@ -35684,7 +35684,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00796571668</t>
+            <t xml:space="preserve">07456908970</t>
           </r>
         </is>
       </c>
@@ -35695,7 +35695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/08/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -35743,7 +35743,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RICARDO SOUZA MARINHO</t>
+            <t xml:space="preserve">RENAN REZENDE DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -35753,7 +35753,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">683.789.476-53</t>
+            <t xml:space="preserve">068.003.286-00</t>
           </r>
         </is>
       </c>
@@ -35763,7 +35763,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02561487470</t>
+            <t xml:space="preserve">04461438210</t>
           </r>
         </is>
       </c>
@@ -35774,7 +35774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/12/2025</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -35822,7 +35822,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RICHARD HENRIQUE DE OLIVEIRA MACHADO</t>
+            <t xml:space="preserve">RENATO MARTINS DA SILVA GOUVEIA</t>
           </r>
         </is>
       </c>
@@ -35832,7 +35832,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">020.089.536-29</t>
+            <t xml:space="preserve">045.158.916-50</t>
           </r>
         </is>
       </c>
@@ -35842,7 +35842,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07127361656</t>
+            <t xml:space="preserve">00796571668</t>
           </r>
         </is>
       </c>
@@ -35853,7 +35853,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/11/2026</t>
+            <t xml:space="preserve">24/08/2027</t>
           </r>
         </is>
       </c>
@@ -35894,14 +35894,14 @@
       <c r="T452" s="12" t="inlineStr"/>
       <c r="U452" s="1" t="inlineStr"/>
     </row>
-    <row r="453" customHeight="1" ht="22">
+    <row r="453" customHeight="1" ht="21">
       <c r="A453" s="1" t="inlineStr"/>
       <c r="B453" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERT WILLIAM MARCELINO DE O PEREIRA </t>
+            <t xml:space="preserve">RICARDO SOUZA MARINHO</t>
           </r>
         </is>
       </c>
@@ -35911,7 +35911,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">143.991.156-88</t>
+            <t xml:space="preserve">683.789.476-53</t>
           </r>
         </is>
       </c>
@@ -35921,7 +35921,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06651427733</t>
+            <t xml:space="preserve">02561487470</t>
           </r>
         </is>
       </c>
@@ -35932,7 +35932,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">18/12/2025</t>
           </r>
         </is>
       </c>
@@ -35973,14 +35973,14 @@
       <c r="T453" s="12" t="inlineStr"/>
       <c r="U453" s="1" t="inlineStr"/>
     </row>
-    <row r="454" customHeight="1" ht="21">
+    <row r="454" customHeight="1" ht="22">
       <c r="A454" s="1" t="inlineStr"/>
       <c r="B454" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO CIRENO DE PAULA</t>
+            <t xml:space="preserve">RICHARD HENRIQUE DE OLIVEIRA MACHADO</t>
           </r>
         </is>
       </c>
@@ -35990,7 +35990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">673.187.626-72</t>
+            <t xml:space="preserve">020.089.536-29</t>
           </r>
         </is>
       </c>
@@ -36000,7 +36000,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01720717152</t>
+            <t xml:space="preserve">07127361656</t>
           </r>
         </is>
       </c>
@@ -36011,7 +36011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">25/11/2026</t>
           </r>
         </is>
       </c>
@@ -36052,14 +36052,14 @@
       <c r="T454" s="12" t="inlineStr"/>
       <c r="U454" s="1" t="inlineStr"/>
     </row>
-    <row r="455" customHeight="1" ht="21">
+    <row r="455" customHeight="1" ht="22">
       <c r="A455" s="1" t="inlineStr"/>
       <c r="B455" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO FLAVIO DA COSTA</t>
+            <t xml:space="preserve">ROBERT WILLIAM MARCELINO DE O PEREIRA </t>
           </r>
         </is>
       </c>
@@ -36069,7 +36069,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">610.846.036-91</t>
+            <t xml:space="preserve">143.991.156-88</t>
           </r>
         </is>
       </c>
@@ -36079,7 +36079,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02293916183</t>
+            <t xml:space="preserve">06651427733</t>
           </r>
         </is>
       </c>
@@ -36090,7 +36090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -36138,7 +36138,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO MOZART SANTANA</t>
+            <t xml:space="preserve">ROBERTO CIRENO DE PAULA</t>
           </r>
         </is>
       </c>
@@ -36148,7 +36148,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.939.556-34</t>
+            <t xml:space="preserve">673.187.626-72</t>
           </r>
         </is>
       </c>
@@ -36158,7 +36158,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02429053892</t>
+            <t xml:space="preserve">01720717152</t>
           </r>
         </is>
       </c>
@@ -36169,7 +36169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -36217,7 +36217,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON CAMILO DE OLIVEIRA</t>
+            <t xml:space="preserve">ROBERTO FLAVIO DA COSTA</t>
           </r>
         </is>
       </c>
@@ -36227,7 +36227,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.438.436-18</t>
+            <t xml:space="preserve">610.846.036-91</t>
           </r>
         </is>
       </c>
@@ -36237,7 +36237,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03133712661</t>
+            <t xml:space="preserve">02293916183</t>
           </r>
         </is>
       </c>
@@ -36248,7 +36248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -36289,14 +36289,14 @@
       <c r="T457" s="12" t="inlineStr"/>
       <c r="U457" s="1" t="inlineStr"/>
     </row>
-    <row r="458" customHeight="1" ht="22">
+    <row r="458" customHeight="1" ht="21">
       <c r="A458" s="1" t="inlineStr"/>
       <c r="B458" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON DOS SANTOS DE REZENDE</t>
+            <t xml:space="preserve">ROBERTO MOZART SANTANA</t>
           </r>
         </is>
       </c>
@@ -36306,7 +36306,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.387.886-66</t>
+            <t xml:space="preserve">868.939.556-34</t>
           </r>
         </is>
       </c>
@@ -36316,7 +36316,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04356240900</t>
+            <t xml:space="preserve">02429053892</t>
           </r>
         </is>
       </c>
@@ -36327,7 +36327,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -36375,7 +36375,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON FERREIRA COSTA</t>
+            <t xml:space="preserve">ROBSON CAMILO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -36385,7 +36385,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">986.658.396-15</t>
+            <t xml:space="preserve">070.438.436-18</t>
           </r>
         </is>
       </c>
@@ -36395,7 +36395,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">019790492230</t>
+            <t xml:space="preserve">03133712661</t>
           </r>
         </is>
       </c>
@@ -36406,7 +36406,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/12/2026</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -36447,14 +36447,14 @@
       <c r="T459" s="12" t="inlineStr"/>
       <c r="U459" s="1" t="inlineStr"/>
     </row>
-    <row r="460" customHeight="1" ht="21">
+    <row r="460" customHeight="1" ht="22">
       <c r="A460" s="1" t="inlineStr"/>
       <c r="B460" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO CESARIO DANTAS</t>
+            <t xml:space="preserve">ROBSON DOS SANTOS DE REZENDE</t>
           </r>
         </is>
       </c>
@@ -36464,7 +36464,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">062.821.666-16</t>
+            <t xml:space="preserve">077.387.886-66</t>
           </r>
         </is>
       </c>
@@ -36474,7 +36474,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02818805407</t>
+            <t xml:space="preserve">04356240900</t>
           </r>
         </is>
       </c>
@@ -36533,7 +36533,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO DA COSTA RAMOS</t>
+            <t xml:space="preserve">ROBSON FERREIRA COSTA</t>
           </r>
         </is>
       </c>
@@ -36543,7 +36543,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.330.686-85</t>
+            <t xml:space="preserve">986.658.396-15</t>
           </r>
         </is>
       </c>
@@ -36553,7 +36553,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03408753752</t>
+            <t xml:space="preserve">019790492230</t>
           </r>
         </is>
       </c>
@@ -36564,7 +36564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">12/12/2026</t>
           </r>
         </is>
       </c>
@@ -36612,7 +36612,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO DE SOUSA COELHO</t>
+            <t xml:space="preserve">RODRIGO CESARIO DANTAS</t>
           </r>
         </is>
       </c>
@@ -36622,7 +36622,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">071.019.256-85</t>
+            <t xml:space="preserve">062.821.666-16</t>
           </r>
         </is>
       </c>
@@ -36632,7 +36632,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03393047195</t>
+            <t xml:space="preserve">02818805407</t>
           </r>
         </is>
       </c>
@@ -36643,7 +36643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -36691,7 +36691,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO MACIEL XAVIER</t>
+            <t xml:space="preserve">RODRIGO DA COSTA RAMOS</t>
           </r>
         </is>
       </c>
@@ -36701,7 +36701,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">031.787.716-03</t>
+            <t xml:space="preserve">079.330.686-85</t>
           </r>
         </is>
       </c>
@@ -36711,7 +36711,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02992459933</t>
+            <t xml:space="preserve">03408753752</t>
           </r>
         </is>
       </c>
@@ -36722,7 +36722,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/03/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -36770,7 +36770,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO MOREIRA CORREA</t>
+            <t xml:space="preserve">RODRIGO DE SOUSA COELHO</t>
           </r>
         </is>
       </c>
@@ -36780,7 +36780,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">056.371.446-80</t>
+            <t xml:space="preserve">071.019.256-85</t>
           </r>
         </is>
       </c>
@@ -36790,7 +36790,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02338803674</t>
+            <t xml:space="preserve">03393047195</t>
           </r>
         </is>
       </c>
@@ -36801,7 +36801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -36849,7 +36849,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO WILLER DE OLIVEIRA</t>
+            <t xml:space="preserve">RODRIGO MACIEL XAVIER</t>
           </r>
         </is>
       </c>
@@ -36859,7 +36859,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">123.890.076-35</t>
+            <t xml:space="preserve">031.787.716-03</t>
           </r>
         </is>
       </c>
@@ -36869,7 +36869,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05732797762</t>
+            <t xml:space="preserve">02992459933</t>
           </r>
         </is>
       </c>
@@ -36880,7 +36880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2025</t>
+            <t xml:space="preserve">18/03/2027</t>
           </r>
         </is>
       </c>
@@ -36928,7 +36928,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGUES GERALDO DE SOUZA</t>
+            <t xml:space="preserve">RODRIGO MOREIRA CORREA</t>
           </r>
         </is>
       </c>
@@ -36938,7 +36938,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">036.160.136-07</t>
+            <t xml:space="preserve">056.371.446-80</t>
           </r>
         </is>
       </c>
@@ -36948,7 +36948,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05446425338</t>
+            <t xml:space="preserve">02338803674</t>
           </r>
         </is>
       </c>
@@ -36959,7 +36959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -37007,7 +37007,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGELIO DA CRUZ DOS SANTOS</t>
+            <t xml:space="preserve">RODRIGO WILLER DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -37017,7 +37017,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">043.086.985-10</t>
+            <t xml:space="preserve">123.890.076-35</t>
           </r>
         </is>
       </c>
@@ -37027,7 +37027,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04971758149</t>
+            <t xml:space="preserve">05732797762</t>
           </r>
         </is>
       </c>
@@ -37038,7 +37038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">03/07/2025</t>
           </r>
         </is>
       </c>
@@ -37086,7 +37086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGER MARCIO SIRIO    </t>
+            <t xml:space="preserve">RODRIGUES GERALDO DE SOUZA</t>
           </r>
         </is>
       </c>
@@ -37096,7 +37096,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">132.076.616-10</t>
+            <t xml:space="preserve">036.160.136-07</t>
           </r>
         </is>
       </c>
@@ -37106,7 +37106,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05572572958</t>
+            <t xml:space="preserve">05446425338</t>
           </r>
         </is>
       </c>
@@ -37117,7 +37117,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/01/2027</t>
           </r>
         </is>
       </c>
@@ -37165,7 +37165,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGERIO PEREIRA VARGAS</t>
+            <t xml:space="preserve">ROGELIO DA CRUZ DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -37175,7 +37175,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">032.158.106-70</t>
+            <t xml:space="preserve">043.086.985-10</t>
           </r>
         </is>
       </c>
@@ -37185,7 +37185,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03602334615</t>
+            <t xml:space="preserve">04971758149</t>
           </r>
         </is>
       </c>
@@ -37196,7 +37196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/11/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -37244,7 +37244,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROMERSON MANOEL DA SILVA</t>
+            <t xml:space="preserve">ROGER MARCIO SIRIO    </t>
           </r>
         </is>
       </c>
@@ -37254,7 +37254,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">932.654.096-00</t>
+            <t xml:space="preserve">132.076.616-10</t>
           </r>
         </is>
       </c>
@@ -37264,7 +37264,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4211589860</t>
+            <t xml:space="preserve">05572572958</t>
           </r>
         </is>
       </c>
@@ -37275,7 +37275,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/02/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -37323,7 +37323,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO BORGES MAGALHAES</t>
+            <t xml:space="preserve">ROGERIO PEREIRA VARGAS</t>
           </r>
         </is>
       </c>
@@ -37333,7 +37333,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">812.820.286-34</t>
+            <t xml:space="preserve">032.158.106-70</t>
           </r>
         </is>
       </c>
@@ -37343,7 +37343,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00574237295</t>
+            <t xml:space="preserve">03602334615</t>
           </r>
         </is>
       </c>
@@ -37354,7 +37354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/06/2026</t>
+            <t xml:space="preserve">03/11/2026</t>
           </r>
         </is>
       </c>
@@ -37402,7 +37402,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO ROSALVO DOS SANTOS</t>
+            <t xml:space="preserve">ROMERSON MANOEL DA SILVA</t>
           </r>
         </is>
       </c>
@@ -37412,7 +37412,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">035.607.284-36</t>
+            <t xml:space="preserve">932.654.096-00</t>
           </r>
         </is>
       </c>
@@ -37422,7 +37422,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03658415228</t>
+            <t xml:space="preserve">4211589860</t>
           </r>
         </is>
       </c>
@@ -37433,7 +37433,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">10/02/2027</t>
           </r>
         </is>
       </c>
@@ -37481,7 +37481,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO SILVA DE CARVALHO</t>
+            <t xml:space="preserve">RONALDO BORGES MAGALHAES</t>
           </r>
         </is>
       </c>
@@ -37491,7 +37491,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.120.046-62</t>
+            <t xml:space="preserve">812.820.286-34</t>
           </r>
         </is>
       </c>
@@ -37501,7 +37501,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05036941619</t>
+            <t xml:space="preserve">00574237295</t>
           </r>
         </is>
       </c>
@@ -37512,7 +37512,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">03/09/2027</t>
           </r>
         </is>
       </c>
@@ -37560,7 +37560,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONIE FERNANDO DA SILVA</t>
+            <t xml:space="preserve">RONALDO ROSALVO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -37570,7 +37570,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">052.060.286-22</t>
+            <t xml:space="preserve">035.607.284-36</t>
           </r>
         </is>
       </c>
@@ -37580,7 +37580,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06025263305</t>
+            <t xml:space="preserve">03658415228</t>
           </r>
         </is>
       </c>
@@ -37591,7 +37591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -37639,7 +37639,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONILDO OLIVEIRA CRUZ</t>
+            <t xml:space="preserve">RONALDO SILVA DE CARVALHO</t>
           </r>
         </is>
       </c>
@@ -37649,7 +37649,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">021.930.251-00</t>
+            <t xml:space="preserve">093.120.046-62</t>
           </r>
         </is>
       </c>
@@ -37659,7 +37659,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04883639482</t>
+            <t xml:space="preserve">05036941619</t>
           </r>
         </is>
       </c>
@@ -37670,7 +37670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -37718,7 +37718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONNY CARLOS DA SILVA</t>
+            <t xml:space="preserve">RONIE FERNANDO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -37728,7 +37728,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">947.454.126-49</t>
+            <t xml:space="preserve">052.060.286-22</t>
           </r>
         </is>
       </c>
@@ -37738,7 +37738,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03488127326</t>
+            <t xml:space="preserve">06025263305</t>
           </r>
         </is>
       </c>
@@ -37749,7 +37749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -37790,14 +37790,14 @@
       <c r="T476" s="12" t="inlineStr"/>
       <c r="U476" s="1" t="inlineStr"/>
     </row>
-    <row r="477" customHeight="1" ht="22">
+    <row r="477" customHeight="1" ht="21">
       <c r="A477" s="1" t="inlineStr"/>
       <c r="B477" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROSILENE DAS GRAÇAS DE O COSTA SIQUEIRA </t>
+            <t xml:space="preserve">RONILDO OLIVEIRA CRUZ</t>
           </r>
         </is>
       </c>
@@ -37807,7 +37807,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.324.136-93</t>
+            <t xml:space="preserve">021.930.251-00</t>
           </r>
         </is>
       </c>
@@ -37817,7 +37817,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04774059559</t>
+            <t xml:space="preserve">04883639482</t>
           </r>
         </is>
       </c>
@@ -37828,7 +37828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -37876,7 +37876,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROZEMAR SEMIAO PINTO</t>
+            <t xml:space="preserve">RONNY CARLOS DA SILVA</t>
           </r>
         </is>
       </c>
@@ -37886,7 +37886,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.531.246-95</t>
+            <t xml:space="preserve">947.454.126-49</t>
           </r>
         </is>
       </c>
@@ -37896,7 +37896,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04086354799</t>
+            <t xml:space="preserve">03488127326</t>
           </r>
         </is>
       </c>
@@ -37907,7 +37907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/08/2027</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -37948,14 +37948,14 @@
       <c r="T478" s="12" t="inlineStr"/>
       <c r="U478" s="1" t="inlineStr"/>
     </row>
-    <row r="479" customHeight="1" ht="21">
+    <row r="479" customHeight="1" ht="22">
       <c r="A479" s="1" t="inlineStr"/>
       <c r="B479" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RUBENS JOSE DA RO¿¿¿</t>
+            <t xml:space="preserve">ROSILENE DAS GRAÇAS DE O COSTA SIQUEIRA </t>
           </r>
         </is>
       </c>
@@ -37965,7 +37965,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">555.890.656-15</t>
+            <t xml:space="preserve">076.324.136-93</t>
           </r>
         </is>
       </c>
@@ -37975,7 +37975,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01136935529</t>
+            <t xml:space="preserve">04774059559</t>
           </r>
         </is>
       </c>
@@ -37986,7 +37986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -38034,7 +38034,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RUBENS LUIS CARNEIRO</t>
+            <t xml:space="preserve">ROZEMAR SEMIAO PINTO</t>
           </r>
         </is>
       </c>
@@ -38044,7 +38044,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">074.702.786-21</t>
+            <t xml:space="preserve">054.531.246-95</t>
           </r>
         </is>
       </c>
@@ -38054,7 +38054,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14163556</t>
+            <t xml:space="preserve">04086354799</t>
           </r>
         </is>
       </c>
@@ -38065,7 +38065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/08/2027</t>
+            <t xml:space="preserve">27/08/2027</t>
           </r>
         </is>
       </c>
@@ -38113,7 +38113,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SALATIEL GOMES DOS SANTOS</t>
+            <t xml:space="preserve">RUBENS JOSE DA RO¿¿¿</t>
           </r>
         </is>
       </c>
@@ -38123,7 +38123,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.278.946-32</t>
+            <t xml:space="preserve">555.890.656-15</t>
           </r>
         </is>
       </c>
@@ -38133,7 +38133,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05199034200</t>
+            <t xml:space="preserve">01136935529</t>
           </r>
         </is>
       </c>
@@ -38144,7 +38144,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -38192,7 +38192,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRA APARECIDA DE LACERDA</t>
+            <t xml:space="preserve">RUBENS LUIS CARNEIRO</t>
           </r>
         </is>
       </c>
@@ -38202,7 +38202,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.654.516-50</t>
+            <t xml:space="preserve">074.702.786-21</t>
           </r>
         </is>
       </c>
@@ -38212,7 +38212,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06112213773</t>
+            <t xml:space="preserve">14163556</t>
           </r>
         </is>
       </c>
@@ -38223,7 +38223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/03/2027</t>
+            <t xml:space="preserve">20/08/2027</t>
           </r>
         </is>
       </c>
@@ -38271,7 +38271,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRA MARA MARTINS</t>
+            <t xml:space="preserve">SALATIEL GOMES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -38281,7 +38281,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">038.635.206-29</t>
+            <t xml:space="preserve">120.278.946-32</t>
           </r>
         </is>
       </c>
@@ -38291,7 +38291,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04164944850</t>
+            <t xml:space="preserve">05199034200</t>
           </r>
         </is>
       </c>
@@ -38302,7 +38302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2026</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -38343,14 +38343,14 @@
       <c r="T483" s="12" t="inlineStr"/>
       <c r="U483" s="1" t="inlineStr"/>
     </row>
-    <row r="484" customHeight="1" ht="22">
+    <row r="484" customHeight="1" ht="21">
       <c r="A484" s="1" t="inlineStr"/>
       <c r="B484" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRO MARCOS DE FREITAS QUEIROS</t>
+            <t xml:space="preserve">SANDRA APARECIDA DE LACERDA</t>
           </r>
         </is>
       </c>
@@ -38360,7 +38360,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">977.080.206-97</t>
+            <t xml:space="preserve">067.654.516-50</t>
           </r>
         </is>
       </c>
@@ -38370,7 +38370,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01979048430</t>
+            <t xml:space="preserve">06112213773</t>
           </r>
         </is>
       </c>
@@ -38381,7 +38381,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">11/03/2027</t>
           </r>
         </is>
       </c>
@@ -38429,7 +38429,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SEBASTIAO EUSTAQUIO TEIXEIRA</t>
+            <t xml:space="preserve">SANDRA MARA MARTINS</t>
           </r>
         </is>
       </c>
@@ -38439,7 +38439,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">456.820.546-87</t>
+            <t xml:space="preserve">038.635.206-29</t>
           </r>
         </is>
       </c>
@@ -38449,7 +38449,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03016774844</t>
+            <t xml:space="preserve">04164944850</t>
           </r>
         </is>
       </c>
@@ -38460,7 +38460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">01/01/2026</t>
           </r>
         </is>
       </c>
@@ -38501,14 +38501,14 @@
       <c r="T485" s="12" t="inlineStr"/>
       <c r="U485" s="1" t="inlineStr"/>
     </row>
-    <row r="486" customHeight="1" ht="21">
+    <row r="486" customHeight="1" ht="22">
       <c r="A486" s="1" t="inlineStr"/>
       <c r="B486" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SEBASTIAO ROBERTO FRANCISCO</t>
+            <t xml:space="preserve">SANDRO MARCOS DE FREITAS QUEIROS</t>
           </r>
         </is>
       </c>
@@ -38518,7 +38518,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">032.171.546-22</t>
+            <t xml:space="preserve">977.080.206-97</t>
           </r>
         </is>
       </c>
@@ -38528,7 +38528,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01221024975</t>
+            <t xml:space="preserve">01979048430</t>
           </r>
         </is>
       </c>
@@ -38539,7 +38539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/07/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -38587,7 +38587,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO JESUS DE SENA</t>
+            <t xml:space="preserve">SEBASTIAO EUSTAQUIO TEIXEIRA</t>
           </r>
         </is>
       </c>
@@ -38597,7 +38597,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">703.152.481-49</t>
+            <t xml:space="preserve">456.820.546-87</t>
           </r>
         </is>
       </c>
@@ -38607,7 +38607,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01987693689</t>
+            <t xml:space="preserve">03016774844</t>
           </r>
         </is>
       </c>
@@ -38618,7 +38618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2026</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -38666,7 +38666,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO MARTINS CANDIDO</t>
+            <t xml:space="preserve">SEBASTIAO ROBERTO FRANCISCO</t>
           </r>
         </is>
       </c>
@@ -38676,7 +38676,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">055.992.066-02</t>
+            <t xml:space="preserve">032.171.546-22</t>
           </r>
         </is>
       </c>
@@ -38686,7 +38686,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01540143348</t>
+            <t xml:space="preserve">01221024975</t>
           </r>
         </is>
       </c>
@@ -38697,7 +38697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">01/07/2027</t>
           </r>
         </is>
       </c>
@@ -38745,7 +38745,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO SORA PEREIRA</t>
+            <t xml:space="preserve">SERGIO JESUS DE SENA</t>
           </r>
         </is>
       </c>
@@ -38755,7 +38755,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">116.201.246-37</t>
+            <t xml:space="preserve">703.152.481-49</t>
           </r>
         </is>
       </c>
@@ -38765,7 +38765,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05455543950</t>
+            <t xml:space="preserve">01987693689</t>
           </r>
         </is>
       </c>
@@ -38776,7 +38776,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2025</t>
+            <t xml:space="preserve">24/09/2026</t>
           </r>
         </is>
       </c>
@@ -38824,7 +38824,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEI EDERSON RODRIGUES</t>
+            <t xml:space="preserve">SERGIO MARTINS CANDIDO</t>
           </r>
         </is>
       </c>
@@ -38834,7 +38834,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">035.114.576-10</t>
+            <t xml:space="preserve">055.992.066-02</t>
           </r>
         </is>
       </c>
@@ -38844,7 +38844,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01367789491</t>
+            <t xml:space="preserve">01540143348</t>
           </r>
         </is>
       </c>
@@ -38855,7 +38855,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/06/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -38903,7 +38903,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEY JUSTINIANO DE CARVALHO  </t>
+            <t xml:space="preserve">SERGIO SORA PEREIRA</t>
           </r>
         </is>
       </c>
@@ -38913,7 +38913,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">933.213.766-87</t>
+            <t xml:space="preserve">116.201.246-37</t>
           </r>
         </is>
       </c>
@@ -38923,7 +38923,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00490361489</t>
+            <t xml:space="preserve">05455543950</t>
           </r>
         </is>
       </c>
@@ -38934,7 +38934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/01/2025</t>
+            <t xml:space="preserve">12/08/2025</t>
           </r>
         </is>
       </c>
@@ -38982,7 +38982,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEY LUCAS PEREIRA</t>
+            <t xml:space="preserve">SIDNEI EDERSON RODRIGUES</t>
           </r>
         </is>
       </c>
@@ -38992,7 +38992,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">003.086.236-14</t>
+            <t xml:space="preserve">035.114.576-10</t>
           </r>
         </is>
       </c>
@@ -39002,7 +39002,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01838999161</t>
+            <t xml:space="preserve">01367789491</t>
           </r>
         </is>
       </c>
@@ -39013,7 +39013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">12/06/2027</t>
           </r>
         </is>
       </c>
@@ -39061,7 +39061,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SINVAL DA SILVA VIGILATO</t>
+            <t xml:space="preserve">SIDNEY JUSTINIANO DE CARVALHO  </t>
           </r>
         </is>
       </c>
@@ -39071,7 +39071,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">875.211.056-72</t>
+            <t xml:space="preserve">933.213.766-87</t>
           </r>
         </is>
       </c>
@@ -39081,7 +39081,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02223241791</t>
+            <t xml:space="preserve">00490361489</t>
           </r>
         </is>
       </c>
@@ -39092,7 +39092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">27/01/2025</t>
           </r>
         </is>
       </c>
@@ -39140,7 +39140,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">STEFANY LUAN PEREIRA GUEDES</t>
+            <t xml:space="preserve">SIDNEY LUCAS PEREIRA</t>
           </r>
         </is>
       </c>
@@ -39150,7 +39150,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.806.076-13</t>
+            <t xml:space="preserve">003.086.236-14</t>
           </r>
         </is>
       </c>
@@ -39160,7 +39160,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04363860554</t>
+            <t xml:space="preserve">01838999161</t>
           </r>
         </is>
       </c>
@@ -39171,7 +39171,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/06/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -39219,7 +39219,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TALES VIEIRA DE SIQUEIRA</t>
+            <t xml:space="preserve">SINVAL DA SILVA VIGILATO</t>
           </r>
         </is>
       </c>
@@ -39229,7 +39229,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.981.346-46</t>
+            <t xml:space="preserve">875.211.056-72</t>
           </r>
         </is>
       </c>
@@ -39239,7 +39239,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05186360780</t>
+            <t xml:space="preserve">02223241791</t>
           </r>
         </is>
       </c>
@@ -39250,7 +39250,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -39298,7 +39298,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TATIANA CRISTINA DOS REIS</t>
+            <t xml:space="preserve">STEFANY LUAN PEREIRA GUEDES</t>
           </r>
         </is>
       </c>
@@ -39308,7 +39308,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.974.806-62</t>
+            <t xml:space="preserve">076.806.076-13</t>
           </r>
         </is>
       </c>
@@ -39318,7 +39318,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04699145123</t>
+            <t xml:space="preserve">04363860554</t>
           </r>
         </is>
       </c>
@@ -39329,7 +39329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">03/06/2027</t>
           </r>
         </is>
       </c>
@@ -39377,7 +39377,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TATIANE MARTINS DA CRUZ</t>
+            <t xml:space="preserve">TALES VIEIRA DE SIQUEIRA</t>
           </r>
         </is>
       </c>
@@ -39387,7 +39387,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.758.886-55</t>
+            <t xml:space="preserve">077.981.346-46</t>
           </r>
         </is>
       </c>
@@ -39397,7 +39397,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05838164206</t>
+            <t xml:space="preserve">05186360780</t>
           </r>
         </is>
       </c>
@@ -39408,7 +39408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/01/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -39449,14 +39449,14 @@
       <c r="T497" s="12" t="inlineStr"/>
       <c r="U497" s="1" t="inlineStr"/>
     </row>
-    <row r="498" customHeight="1" ht="22">
+    <row r="498" customHeight="1" ht="21">
       <c r="A498" s="1" t="inlineStr"/>
       <c r="B498" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THAISON BRUNO FERNANDO DOS SANTOS</t>
+            <t xml:space="preserve">TATIANA CRISTINA DOS REIS</t>
           </r>
         </is>
       </c>
@@ -39466,7 +39466,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">015.914.226-12</t>
+            <t xml:space="preserve">076.974.806-62</t>
           </r>
         </is>
       </c>
@@ -39476,7 +39476,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">0436952989</t>
+            <t xml:space="preserve">04699145123</t>
           </r>
         </is>
       </c>
@@ -39487,7 +39487,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/09/2027</t>
+            <t xml:space="preserve">13/01/2027</t>
           </r>
         </is>
       </c>
@@ -39535,7 +39535,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO ALVES FERREIRA</t>
+            <t xml:space="preserve">TATIANE MARTINS DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -39545,7 +39545,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.622.556-97</t>
+            <t xml:space="preserve">120.758.886-55</t>
           </r>
         </is>
       </c>
@@ -39555,7 +39555,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04151517893</t>
+            <t xml:space="preserve">05838164206</t>
           </r>
         </is>
       </c>
@@ -39566,7 +39566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/11/2026</t>
+            <t xml:space="preserve">27/01/2027</t>
           </r>
         </is>
       </c>
@@ -39607,14 +39607,14 @@
       <c r="T499" s="12" t="inlineStr"/>
       <c r="U499" s="1" t="inlineStr"/>
     </row>
-    <row r="500" customHeight="1" ht="21">
+    <row r="500" customHeight="1" ht="22">
       <c r="A500" s="1" t="inlineStr"/>
       <c r="B500" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO FARIA ROSA</t>
+            <t xml:space="preserve">THAISON BRUNO FERNANDO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -39624,7 +39624,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">101.801.956-11</t>
+            <t xml:space="preserve">015.914.226-12</t>
           </r>
         </is>
       </c>
@@ -39634,7 +39634,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05453493191</t>
+            <t xml:space="preserve">0436952989</t>
           </r>
         </is>
       </c>
@@ -39645,7 +39645,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">10/09/2027</t>
           </r>
         </is>
       </c>
@@ -39693,7 +39693,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO GONCALVES CARDOSO</t>
+            <t xml:space="preserve">THIAGO ALVES FERREIRA</t>
           </r>
         </is>
       </c>
@@ -39703,7 +39703,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">022.860.086-39</t>
+            <t xml:space="preserve">076.622.556-97</t>
           </r>
         </is>
       </c>
@@ -39713,7 +39713,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06955819327</t>
+            <t xml:space="preserve">04151517893</t>
           </r>
         </is>
       </c>
@@ -39724,7 +39724,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/12/2025</t>
+            <t xml:space="preserve">10/11/2026</t>
           </r>
         </is>
       </c>
@@ -39772,7 +39772,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TIAGO ANDRADE DOS PASSOS</t>
+            <t xml:space="preserve">THIAGO FARIA ROSA</t>
           </r>
         </is>
       </c>
@@ -39782,7 +39782,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">084.447.676-54</t>
+            <t xml:space="preserve">101.801.956-11</t>
           </r>
         </is>
       </c>
@@ -39792,7 +39792,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03945068162</t>
+            <t xml:space="preserve">05453493191</t>
           </r>
         </is>
       </c>
@@ -39803,7 +39803,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/06/2027</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -39851,7 +39851,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TIAGO DA SILVA LIMA</t>
+            <t xml:space="preserve">THIAGO GONCALVES CARDOSO</t>
           </r>
         </is>
       </c>
@@ -39861,7 +39861,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">075.518.336-33</t>
+            <t xml:space="preserve">022.860.086-39</t>
           </r>
         </is>
       </c>
@@ -39871,7 +39871,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03550506992</t>
+            <t xml:space="preserve">06955819327</t>
           </r>
         </is>
       </c>
@@ -39882,7 +39882,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/09/2027</t>
+            <t xml:space="preserve">11/12/2025</t>
           </r>
         </is>
       </c>
@@ -39930,7 +39930,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UENDERSON RONALD DA SILVA</t>
+            <t xml:space="preserve">TIAGO ANDRADE DOS PASSOS</t>
           </r>
         </is>
       </c>
@@ -39940,7 +39940,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.548.716-13</t>
+            <t xml:space="preserve">084.447.676-54</t>
           </r>
         </is>
       </c>
@@ -39950,7 +39950,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03399996765</t>
+            <t xml:space="preserve">03945068162</t>
           </r>
         </is>
       </c>
@@ -39961,7 +39961,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/07/2027</t>
+            <t xml:space="preserve">11/06/2027</t>
           </r>
         </is>
       </c>
@@ -40009,7 +40009,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ULISSES DE FREITAS MELO</t>
+            <t xml:space="preserve">TIAGO DA SILVA LIMA</t>
           </r>
         </is>
       </c>
@@ -40019,7 +40019,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">041.135.016-10</t>
+            <t xml:space="preserve">075.518.336-33</t>
           </r>
         </is>
       </c>
@@ -40029,7 +40029,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03364297306</t>
+            <t xml:space="preserve">03550506992</t>
           </r>
         </is>
       </c>
@@ -40040,7 +40040,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/09/2027</t>
+            <t xml:space="preserve">08/09/2027</t>
           </r>
         </is>
       </c>
@@ -40088,7 +40088,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">URBANO MORAIS LOURENCO</t>
+            <t xml:space="preserve">UENDERSON RONALD DA SILVA</t>
           </r>
         </is>
       </c>
@@ -40098,7 +40098,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">118.321.046-99</t>
+            <t xml:space="preserve">054.548.716-13</t>
           </r>
         </is>
       </c>
@@ -40108,7 +40108,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06455070312</t>
+            <t xml:space="preserve">03399996765</t>
           </r>
         </is>
       </c>
@@ -40119,7 +40119,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/04/2027</t>
+            <t xml:space="preserve">24/07/2027</t>
           </r>
         </is>
       </c>
@@ -40167,7 +40167,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VADIR BERNARDES DA SILVA</t>
+            <t xml:space="preserve">ULISSES DE FREITAS MELO</t>
           </r>
         </is>
       </c>
@@ -40177,7 +40177,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.330.718-66</t>
+            <t xml:space="preserve">041.135.016-10</t>
           </r>
         </is>
       </c>
@@ -40187,7 +40187,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01938461228</t>
+            <t xml:space="preserve">03364297306</t>
           </r>
         </is>
       </c>
@@ -40198,7 +40198,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2026</t>
+            <t xml:space="preserve">09/09/2027</t>
           </r>
         </is>
       </c>
@@ -40246,7 +40246,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALMIR GOMES RIBEIRO</t>
+            <t xml:space="preserve">URBANO MORAIS LOURENCO</t>
           </r>
         </is>
       </c>
@@ -40256,7 +40256,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.463.326-63</t>
+            <t xml:space="preserve">118.321.046-99</t>
           </r>
         </is>
       </c>
@@ -40266,7 +40266,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04922140128</t>
+            <t xml:space="preserve">06455070312</t>
           </r>
         </is>
       </c>
@@ -40277,7 +40277,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/01/2027</t>
+            <t xml:space="preserve">14/04/2027</t>
           </r>
         </is>
       </c>
@@ -40325,7 +40325,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALQUIRIA SANTOS COUTO</t>
+            <t xml:space="preserve">VADIR BERNARDES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -40335,7 +40335,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.378.626-09</t>
+            <t xml:space="preserve">046.330.718-66</t>
           </r>
         </is>
       </c>
@@ -40345,7 +40345,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05442378859</t>
+            <t xml:space="preserve">01938461228</t>
           </r>
         </is>
       </c>
@@ -40356,7 +40356,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/02/2026</t>
+            <t xml:space="preserve">23/07/2026</t>
           </r>
         </is>
       </c>
@@ -40404,7 +40404,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALTER DOMINGOS MEIRELES  </t>
+            <t xml:space="preserve">VALMIR GOMES RIBEIRO</t>
           </r>
         </is>
       </c>
@@ -40414,7 +40414,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.666.886-83</t>
+            <t xml:space="preserve">065.463.326-63</t>
           </r>
         </is>
       </c>
@@ -40424,7 +40424,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02232141549</t>
+            <t xml:space="preserve">04922140128</t>
           </r>
         </is>
       </c>
@@ -40435,7 +40435,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -40483,7 +40483,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALTER RAMOS DE LIMA</t>
+            <t xml:space="preserve">VALQUIRIA SANTOS COUTO</t>
           </r>
         </is>
       </c>
@@ -40493,7 +40493,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">832.376.746-72</t>
+            <t xml:space="preserve">077.378.626-09</t>
           </r>
         </is>
       </c>
@@ -40503,7 +40503,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01110738309</t>
+            <t xml:space="preserve">05442378859</t>
           </r>
         </is>
       </c>
@@ -40514,7 +40514,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">13/02/2026</t>
           </r>
         </is>
       </c>
@@ -40555,14 +40555,14 @@
       <c r="T511" s="12" t="inlineStr"/>
       <c r="U511" s="1" t="inlineStr"/>
     </row>
-    <row r="512" customHeight="1" ht="22">
+    <row r="512" customHeight="1" ht="21">
       <c r="A512" s="1" t="inlineStr"/>
       <c r="B512" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANDERCI BATISTA LEANDRO DOS SANTOS</t>
+            <t xml:space="preserve">VALTER DOMINGOS MEIRELES  </t>
           </r>
         </is>
       </c>
@@ -40572,7 +40572,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">939.681.836-49</t>
+            <t xml:space="preserve">040.666.886-83</t>
           </r>
         </is>
       </c>
@@ -40582,7 +40582,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02672395939</t>
+            <t xml:space="preserve">02232141549</t>
           </r>
         </is>
       </c>
@@ -40593,7 +40593,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/11/2026</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -40641,7 +40641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANDERSON TELES NASCIMENTO</t>
+            <t xml:space="preserve">VALTER RAMOS DE LIMA</t>
           </r>
         </is>
       </c>
@@ -40651,7 +40651,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.675.435-34</t>
+            <t xml:space="preserve">832.376.746-72</t>
           </r>
         </is>
       </c>
@@ -40661,7 +40661,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01845793756</t>
+            <t xml:space="preserve">01110738309</t>
           </r>
         </is>
       </c>
@@ -40672,7 +40672,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -40713,14 +40713,14 @@
       <c r="T513" s="12" t="inlineStr"/>
       <c r="U513" s="1" t="inlineStr"/>
     </row>
-    <row r="514" customHeight="1" ht="21">
+    <row r="514" customHeight="1" ht="22">
       <c r="A514" s="1" t="inlineStr"/>
       <c r="B514" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANEIALVES GUIMARAES</t>
+            <t xml:space="preserve">VANDERCI BATISTA LEANDRO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -40730,7 +40730,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.859.956-41</t>
+            <t xml:space="preserve">939.681.836-49</t>
           </r>
         </is>
       </c>
@@ -40740,7 +40740,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03607821769</t>
+            <t xml:space="preserve">02672395939</t>
           </r>
         </is>
       </c>
@@ -40751,7 +40751,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">26/11/2026</t>
           </r>
         </is>
       </c>
@@ -40799,7 +40799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANESSA CAROLINNE GONÇALVES</t>
+            <t xml:space="preserve">VANDERSON TELES NASCIMENTO</t>
           </r>
         </is>
       </c>
@@ -40809,7 +40809,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.868.326-80</t>
+            <t xml:space="preserve">819.675.435-34</t>
           </r>
         </is>
       </c>
@@ -40819,7 +40819,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06829001421</t>
+            <t xml:space="preserve">01845793756</t>
           </r>
         </is>
       </c>
@@ -40830,7 +40830,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/12/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -40878,7 +40878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE DE PAULO DA SILVA</t>
+            <t xml:space="preserve">VANEIALVES GUIMARAES</t>
           </r>
         </is>
       </c>
@@ -40888,7 +40888,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">731.778.146-00</t>
+            <t xml:space="preserve">026.859.956-41</t>
           </r>
         </is>
       </c>
@@ -40898,7 +40898,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02507810777</t>
+            <t xml:space="preserve">03607821769</t>
           </r>
         </is>
       </c>
@@ -40909,7 +40909,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -40957,7 +40957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE DOS REIS GOMES</t>
+            <t xml:space="preserve">VANESSA CAROLINNE GONÇALVES</t>
           </r>
         </is>
       </c>
@@ -40967,7 +40967,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">755.303.926-87</t>
+            <t xml:space="preserve">120.868.326-80</t>
           </r>
         </is>
       </c>
@@ -40977,7 +40977,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02525863238</t>
+            <t xml:space="preserve">06829001421</t>
           </r>
         </is>
       </c>
@@ -40988,7 +40988,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/08/2027</t>
+            <t xml:space="preserve">12/12/2026</t>
           </r>
         </is>
       </c>
@@ -41036,7 +41036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE ROBERTO ANGELO</t>
+            <t xml:space="preserve">VICENTE DE PAULO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -41046,7 +41046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">399.263.546-53</t>
+            <t xml:space="preserve">731.778.146-00</t>
           </r>
         </is>
       </c>
@@ -41056,7 +41056,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01030510930</t>
+            <t xml:space="preserve">02507810777</t>
           </r>
         </is>
       </c>
@@ -41067,7 +41067,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -41115,7 +41115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VILEIDE VAZ MOREIRA </t>
+            <t xml:space="preserve">VICENTE DOS REIS GOMES</t>
           </r>
         </is>
       </c>
@@ -41125,7 +41125,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">109.093.766-03</t>
+            <t xml:space="preserve">755.303.926-87</t>
           </r>
         </is>
       </c>
@@ -41135,7 +41135,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06087149441</t>
+            <t xml:space="preserve">02525863238</t>
           </r>
         </is>
       </c>
@@ -41146,7 +41146,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">26/08/2027</t>
           </r>
         </is>
       </c>
@@ -41194,7 +41194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VINICIO JOSE DOS SANTOS</t>
+            <t xml:space="preserve">VICENTE ROBERTO ANGELO</t>
           </r>
         </is>
       </c>
@@ -41204,7 +41204,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">048.389.316-11</t>
+            <t xml:space="preserve">399.263.546-53</t>
           </r>
         </is>
       </c>
@@ -41214,7 +41214,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01306809764</t>
+            <t xml:space="preserve">01030510930</t>
           </r>
         </is>
       </c>
@@ -41273,7 +41273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VINICIUS BORGES VALES</t>
+            <t xml:space="preserve">VILEIDE VAZ MOREIRA </t>
           </r>
         </is>
       </c>
@@ -41283,7 +41283,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">086.215.466-98</t>
+            <t xml:space="preserve">109.093.766-03</t>
           </r>
         </is>
       </c>
@@ -41293,7 +41293,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04262664653</t>
+            <t xml:space="preserve">06087149441</t>
           </r>
         </is>
       </c>
@@ -41304,7 +41304,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2024</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -41352,7 +41352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VITOR FERREIRA SANTOS</t>
+            <t xml:space="preserve">VINICIO JOSE DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -41362,7 +41362,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">136.025.886-88</t>
+            <t xml:space="preserve">048.389.316-11</t>
           </r>
         </is>
       </c>
@@ -41372,7 +41372,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07186400700</t>
+            <t xml:space="preserve">01306809764</t>
           </r>
         </is>
       </c>
@@ -41383,7 +41383,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -41431,7 +41431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VITOR GABRIEL GOMES CORREIA </t>
+            <t xml:space="preserve">VINICIUS BORGES VALES</t>
           </r>
         </is>
       </c>
@@ -41441,7 +41441,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">019.705.576-13</t>
+            <t xml:space="preserve">086.215.466-98</t>
           </r>
         </is>
       </c>
@@ -41451,7 +41451,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06930599950</t>
+            <t xml:space="preserve">04262664653</t>
           </r>
         </is>
       </c>
@@ -41462,7 +41462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">31/07/2024</t>
           </r>
         </is>
       </c>
@@ -41510,7 +41510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WAGNER FERNANDES DA SILVA</t>
+            <t xml:space="preserve">VITOR FERREIRA SANTOS</t>
           </r>
         </is>
       </c>
@@ -41520,7 +41520,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">012.597.906-14</t>
+            <t xml:space="preserve">136.025.886-88</t>
           </r>
         </is>
       </c>
@@ -41530,7 +41530,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03780457127</t>
+            <t xml:space="preserve">07186400700</t>
           </r>
         </is>
       </c>
@@ -41541,7 +41541,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -41589,7 +41589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WALMIR ALVES MEIRELES   </t>
+            <t xml:space="preserve">VITOR GABRIEL GOMES CORREIA </t>
           </r>
         </is>
       </c>
@@ -41599,7 +41599,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">001.214.386-35</t>
+            <t xml:space="preserve">019.705.576-13</t>
           </r>
         </is>
       </c>
@@ -41609,7 +41609,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00441481335</t>
+            <t xml:space="preserve">06930599950</t>
           </r>
         </is>
       </c>
@@ -41620,7 +41620,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/08/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -41668,7 +41668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WANDEIR HONORATO DE OLIVEIRA</t>
+            <t xml:space="preserve">WAGNER FERNANDES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -41678,7 +41678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">824.616.866-53</t>
+            <t xml:space="preserve">012.597.906-14</t>
           </r>
         </is>
       </c>
@@ -41688,7 +41688,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02755705481</t>
+            <t xml:space="preserve">03780457127</t>
           </r>
         </is>
       </c>
@@ -41699,7 +41699,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -41740,14 +41740,14 @@
       <c r="T526" s="12" t="inlineStr"/>
       <c r="U526" s="1" t="inlineStr"/>
     </row>
-    <row r="527" customHeight="1" ht="21">
+    <row r="527" customHeight="1" ht="22">
       <c r="A527" s="1" t="inlineStr"/>
       <c r="B527" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WANDERSON HENRIQUE FARAH</t>
+            <t xml:space="preserve">WALBER EVANGELISTA LONGO DO NASCIMENTO</t>
           </r>
         </is>
       </c>
@@ -41757,7 +41757,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.031.086-07</t>
+            <t xml:space="preserve">072.851.686-10</t>
           </r>
         </is>
       </c>
@@ -41767,7 +41767,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03551548436</t>
+            <t xml:space="preserve">03810941378</t>
           </r>
         </is>
       </c>
@@ -41778,7 +41778,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/05/2026</t>
+            <t xml:space="preserve">27/08/2027</t>
           </r>
         </is>
       </c>
@@ -41826,7 +41826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WARLEY TEODORO</t>
+            <t xml:space="preserve">WALMIR ALVES MEIRELES   </t>
           </r>
         </is>
       </c>
@@ -41836,7 +41836,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.096.156-09</t>
+            <t xml:space="preserve">001.214.386-35</t>
           </r>
         </is>
       </c>
@@ -41846,7 +41846,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03946495186</t>
+            <t xml:space="preserve">00441481335</t>
           </r>
         </is>
       </c>
@@ -41857,7 +41857,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">06/08/2027</t>
           </r>
         </is>
       </c>
@@ -41905,7 +41905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON ANTONIO DE AVILA</t>
+            <t xml:space="preserve">WANDEIR HONORATO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -41915,7 +41915,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">913.901.686-20</t>
+            <t xml:space="preserve">824.616.866-53</t>
           </r>
         </is>
       </c>
@@ -41925,7 +41925,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00562356548</t>
+            <t xml:space="preserve">02755705481</t>
           </r>
         </is>
       </c>
@@ -41936,7 +41936,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -41984,7 +41984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON BARBOSA VIEIRA</t>
+            <t xml:space="preserve">WANDERSON HENRIQUE FARAH</t>
           </r>
         </is>
       </c>
@@ -41994,7 +41994,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">094.176.466-48</t>
+            <t xml:space="preserve">070.031.086-07</t>
           </r>
         </is>
       </c>
@@ -42004,7 +42004,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">0412500611226</t>
+            <t xml:space="preserve">03551548436</t>
           </r>
         </is>
       </c>
@@ -42015,7 +42015,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">30/05/2026</t>
           </r>
         </is>
       </c>
@@ -42063,7 +42063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON WELLINGTON PINTO</t>
+            <t xml:space="preserve">WARLEY TEODORO</t>
           </r>
         </is>
       </c>
@@ -42073,7 +42073,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">092.920.176-08</t>
+            <t xml:space="preserve">061.096.156-09</t>
           </r>
         </is>
       </c>
@@ -42083,7 +42083,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04783305563</t>
+            <t xml:space="preserve">03946495186</t>
           </r>
         </is>
       </c>
@@ -42094,7 +42094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -42135,14 +42135,14 @@
       <c r="T531" s="12" t="inlineStr"/>
       <c r="U531" s="1" t="inlineStr"/>
     </row>
-    <row r="532" customHeight="1" ht="22">
+    <row r="532" customHeight="1" ht="21">
       <c r="A532" s="1" t="inlineStr"/>
       <c r="B532" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTONINACIO GOME DE REZENDE</t>
+            <t xml:space="preserve">WASHINGTON ANTONIO DE AVILA</t>
           </r>
         </is>
       </c>
@@ -42152,7 +42152,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">125.555.806-70</t>
+            <t xml:space="preserve">913.901.686-20</t>
           </r>
         </is>
       </c>
@@ -42162,7 +42162,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06093566794</t>
+            <t xml:space="preserve">00562356548</t>
           </r>
         </is>
       </c>
@@ -42173,7 +42173,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/07/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -42214,14 +42214,14 @@
       <c r="T532" s="12" t="inlineStr"/>
       <c r="U532" s="1" t="inlineStr"/>
     </row>
-    <row r="533" customHeight="1" ht="22">
+    <row r="533" customHeight="1" ht="21">
       <c r="A533" s="1" t="inlineStr"/>
       <c r="B533" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTHON FERNANDO FRANCISCO</t>
+            <t xml:space="preserve">WASHINGTON BARBOSA VIEIRA</t>
           </r>
         </is>
       </c>
@@ -42231,7 +42231,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.378.116-23</t>
+            <t xml:space="preserve">094.176.466-48</t>
           </r>
         </is>
       </c>
@@ -42241,7 +42241,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05042709980</t>
+            <t xml:space="preserve">0412500611226</t>
           </r>
         </is>
       </c>
@@ -42252,7 +42252,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/07/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -42293,14 +42293,14 @@
       <c r="T533" s="12" t="inlineStr"/>
       <c r="U533" s="1" t="inlineStr"/>
     </row>
-    <row r="534" customHeight="1" ht="22">
+    <row r="534" customHeight="1" ht="21">
       <c r="A534" s="1" t="inlineStr"/>
       <c r="B534" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON APARECIDO DO NASCIMENTOS</t>
+            <t xml:space="preserve">WASHINGTON WELLINGTON PINTO</t>
           </r>
         </is>
       </c>
@@ -42310,7 +42310,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">012.579.656-03</t>
+            <t xml:space="preserve">092.920.176-08</t>
           </r>
         </is>
       </c>
@@ -42320,7 +42320,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03357647398</t>
+            <t xml:space="preserve">04783305563</t>
           </r>
         </is>
       </c>
@@ -42331,7 +42331,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -42372,14 +42372,14 @@
       <c r="T534" s="12" t="inlineStr"/>
       <c r="U534" s="1" t="inlineStr"/>
     </row>
-    <row r="535" customHeight="1" ht="21">
+    <row r="535" customHeight="1" ht="22">
       <c r="A535" s="1" t="inlineStr"/>
       <c r="B535" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON PEREIRA SILVA</t>
+            <t xml:space="preserve">WASHINGTONINACIO GOME DE REZENDE</t>
           </r>
         </is>
       </c>
@@ -42389,7 +42389,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">052.481.486-42</t>
+            <t xml:space="preserve">125.555.806-70</t>
           </r>
         </is>
       </c>
@@ -42399,7 +42399,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02266389739</t>
+            <t xml:space="preserve">06093566794</t>
           </r>
         </is>
       </c>
@@ -42410,7 +42410,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">16/07/2027</t>
           </r>
         </is>
       </c>
@@ -42451,14 +42451,14 @@
       <c r="T535" s="12" t="inlineStr"/>
       <c r="U535" s="1" t="inlineStr"/>
     </row>
-    <row r="536" customHeight="1" ht="21">
+    <row r="536" customHeight="1" ht="22">
       <c r="A536" s="1" t="inlineStr"/>
       <c r="B536" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON TERTULIANO</t>
+            <t xml:space="preserve">WELLINGTHON FERNANDO FRANCISCO</t>
           </r>
         </is>
       </c>
@@ -42468,7 +42468,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">084.518.494-66</t>
+            <t xml:space="preserve">110.378.116-23</t>
           </r>
         </is>
       </c>
@@ -42478,7 +42478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04648920920</t>
+            <t xml:space="preserve">05042709980</t>
           </r>
         </is>
       </c>
@@ -42489,7 +42489,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">06/07/2027</t>
           </r>
         </is>
       </c>
@@ -42530,14 +42530,14 @@
       <c r="T536" s="12" t="inlineStr"/>
       <c r="U536" s="1" t="inlineStr"/>
     </row>
-    <row r="537" customHeight="1" ht="21">
+    <row r="537" customHeight="1" ht="22">
       <c r="A537" s="1" t="inlineStr"/>
       <c r="B537" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLISON FERREIRA RODRIGUES</t>
+            <t xml:space="preserve">WELLINGTON APARECIDO DO NASCIMENTOS</t>
           </r>
         </is>
       </c>
@@ -42547,7 +42547,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">060.332.916-03</t>
+            <t xml:space="preserve">012.579.656-03</t>
           </r>
         </is>
       </c>
@@ -42557,7 +42557,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04203957932</t>
+            <t xml:space="preserve">03357647398</t>
           </r>
         </is>
       </c>
@@ -42568,7 +42568,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2031</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -42616,7 +42616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WEMERSON DE SOUZA PIRES</t>
+            <t xml:space="preserve">WELLINGTON PEREIRA SILVA</t>
           </r>
         </is>
       </c>
@@ -42626,7 +42626,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">085.948.536-61</t>
+            <t xml:space="preserve">052.481.486-42</t>
           </r>
         </is>
       </c>
@@ -42636,7 +42636,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289760206</t>
+            <t xml:space="preserve">02266389739</t>
           </r>
         </is>
       </c>
@@ -42647,7 +42647,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -42695,7 +42695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEI FERNANDES DA COSTA</t>
+            <t xml:space="preserve">WELLINGTON TERTULIANO</t>
           </r>
         </is>
       </c>
@@ -42705,7 +42705,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.289.656-73</t>
+            <t xml:space="preserve">084.518.494-66</t>
           </r>
         </is>
       </c>
@@ -42715,7 +42715,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01357310210</t>
+            <t xml:space="preserve">04648920920</t>
           </r>
         </is>
       </c>
@@ -42726,7 +42726,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/01/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -42774,7 +42774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEY LARA DORNELAS VAZ</t>
+            <t xml:space="preserve">WELLINTON SOUSA NUNES</t>
           </r>
         </is>
       </c>
@@ -42784,7 +42784,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.926.946-20</t>
+            <t xml:space="preserve">868.631.261-68</t>
           </r>
         </is>
       </c>
@@ -42794,7 +42794,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01882616840</t>
+            <t xml:space="preserve">01601461581</t>
           </r>
         </is>
       </c>
@@ -42805,7 +42805,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -42846,14 +42846,14 @@
       <c r="T540" s="12" t="inlineStr"/>
       <c r="U540" s="1" t="inlineStr"/>
     </row>
-    <row r="541" customHeight="1" ht="22">
+    <row r="541" customHeight="1" ht="21">
       <c r="A541" s="1" t="inlineStr"/>
       <c r="B541" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILDENBERG DAYRELL BENEDITO DA SILVA</t>
+            <t xml:space="preserve">WELLISON FERREIRA RODRIGUES</t>
           </r>
         </is>
       </c>
@@ -42863,7 +42863,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">146.120.596-46</t>
+            <t xml:space="preserve">060.332.916-03</t>
           </r>
         </is>
       </c>
@@ -42873,7 +42873,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07394414462</t>
+            <t xml:space="preserve">04203957932</t>
           </r>
         </is>
       </c>
@@ -42884,7 +42884,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">29/07/2031</t>
           </r>
         </is>
       </c>
@@ -42932,7 +42932,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLER DIAS LADEIRA DA SILVA</t>
+            <t xml:space="preserve">WEMERSON DE SOUZA PIRES</t>
           </r>
         </is>
       </c>
@@ -42942,7 +42942,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.752.806-04</t>
+            <t xml:space="preserve">085.948.536-61</t>
           </r>
         </is>
       </c>
@@ -42952,7 +42952,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01225273506</t>
+            <t xml:space="preserve">04289760206</t>
           </r>
         </is>
       </c>
@@ -42963,7 +42963,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">18/09/2027</t>
           </r>
         </is>
       </c>
@@ -43011,7 +43011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLER RODRIGUES DUARTE   </t>
+            <t xml:space="preserve">WESLEI FERNANDES DA COSTA</t>
           </r>
         </is>
       </c>
@@ -43021,7 +43021,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">842.137.796-53</t>
+            <t xml:space="preserve">054.289.656-73</t>
           </r>
         </is>
       </c>
@@ -43031,7 +43031,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00718175645</t>
+            <t xml:space="preserve">01357310210</t>
           </r>
         </is>
       </c>
@@ -43042,7 +43042,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/11/2026</t>
+            <t xml:space="preserve">22/01/2027</t>
           </r>
         </is>
       </c>
@@ -43090,7 +43090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLIAN LOURENCO DA SILVA </t>
+            <t xml:space="preserve">WESLEY LARA DORNELAS VAZ</t>
           </r>
         </is>
       </c>
@@ -43100,7 +43100,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.769.226-39</t>
+            <t xml:space="preserve">051.926.946-20</t>
           </r>
         </is>
       </c>
@@ -43110,7 +43110,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04158429281</t>
+            <t xml:space="preserve">01882616840</t>
           </r>
         </is>
       </c>
@@ -43121,7 +43121,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/09/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -43169,7 +43169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILSON FRANCISCO MARZANO SILVEIRA </t>
+            <t xml:space="preserve">WILDENBERG DAYRELL BENEDITO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -43179,7 +43179,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">049.781.696-23</t>
+            <t xml:space="preserve">146.120.596-46</t>
           </r>
         </is>
       </c>
@@ -43189,7 +43189,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01673877203</t>
+            <t xml:space="preserve">07394414462</t>
           </r>
         </is>
       </c>
@@ -43241,14 +43241,14 @@
       <c r="T545" s="12" t="inlineStr"/>
       <c r="U545" s="1" t="inlineStr"/>
     </row>
-    <row r="546" customHeight="1" ht="22">
+    <row r="546" customHeight="1" ht="21">
       <c r="A546" s="1" t="inlineStr"/>
       <c r="B546" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ZENILSON MARCELINO DE CARVALHO</t>
+            <t xml:space="preserve">WILLER DIAS LADEIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -43258,7 +43258,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">039.291.734-33</t>
+            <t xml:space="preserve">868.752.806-04</t>
           </r>
         </is>
       </c>
@@ -43268,7 +43268,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04371720578</t>
+            <t xml:space="preserve">01225273506</t>
           </r>
         </is>
       </c>
@@ -43279,7 +43279,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -43320,41 +43320,357 @@
       <c r="T546" s="12" t="inlineStr"/>
       <c r="U546" s="1" t="inlineStr"/>
     </row>
-    <row r="547" customHeight="1" ht="15">
+    <row r="547" customHeight="1" ht="21">
       <c r="A547" s="1" t="inlineStr"/>
-      <c r="B547" s="1" t="inlineStr"/>
-      <c r="C547" s="14" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-       </rPr>
-            <t xml:space="preserve">Total Ativo: 540</t>
-          </r>
-        </is>
-      </c>
-      <c r="D547" s="15" t="inlineStr"/>
-      <c r="E547" s="1" t="inlineStr"/>
-      <c r="F547" s="1" t="inlineStr"/>
-      <c r="G547" s="1" t="inlineStr"/>
-      <c r="H547" s="1" t="inlineStr"/>
-      <c r="I547" s="1" t="inlineStr"/>
-      <c r="J547" s="1" t="inlineStr"/>
-      <c r="K547" s="1" t="inlineStr"/>
-      <c r="L547" s="1" t="inlineStr"/>
-      <c r="M547" s="1" t="inlineStr"/>
-      <c r="N547" s="1" t="inlineStr"/>
-      <c r="O547" s="1" t="inlineStr"/>
-      <c r="P547" s="1" t="inlineStr"/>
-      <c r="Q547" s="1" t="inlineStr"/>
-      <c r="R547" s="1" t="inlineStr"/>
-      <c r="S547" s="1" t="inlineStr"/>
-      <c r="T547" s="1" t="inlineStr"/>
+      <c r="B547" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">WILLER RODRIGUES DUARTE   </t>
+          </r>
+        </is>
+      </c>
+      <c r="C547" s="10" t="inlineStr"/>
+      <c r="D547" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">842.137.796-53</t>
+          </r>
+        </is>
+      </c>
+      <c r="E547" s="12" t="inlineStr"/>
+      <c r="F547" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">00718175645</t>
+          </r>
+        </is>
+      </c>
+      <c r="G547" s="12" t="inlineStr"/>
+      <c r="H547" s="12" t="inlineStr"/>
+      <c r="I547" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">17/11/2026</t>
+          </r>
+        </is>
+      </c>
+      <c r="J547" s="12" t="inlineStr"/>
+      <c r="K547" s="12" t="inlineStr"/>
+      <c r="L547" s="12" t="inlineStr"/>
+      <c r="M547" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N547" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O547" s="10" t="inlineStr"/>
+      <c r="P547" s="10" t="inlineStr"/>
+      <c r="Q547" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R547" s="12" t="inlineStr"/>
+      <c r="S547" s="12" t="inlineStr"/>
+      <c r="T547" s="12" t="inlineStr"/>
       <c r="U547" s="1" t="inlineStr"/>
     </row>
-    <row r="548" customHeight="1" ht="15">
+    <row r="548" customHeight="1" ht="21">
       <c r="A548" s="1" t="inlineStr"/>
-      <c r="B548" s="1" t="inlineStr"/>
-      <c r="C548" s="14" t="inlineStr">
+      <c r="B548" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">WILLIAN LOURENCO DA SILVA </t>
+          </r>
+        </is>
+      </c>
+      <c r="C548" s="10" t="inlineStr"/>
+      <c r="D548" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">065.769.226-39</t>
+          </r>
+        </is>
+      </c>
+      <c r="E548" s="12" t="inlineStr"/>
+      <c r="F548" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">04158429281</t>
+          </r>
+        </is>
+      </c>
+      <c r="G548" s="12" t="inlineStr"/>
+      <c r="H548" s="12" t="inlineStr"/>
+      <c r="I548" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">15/09/2027</t>
+          </r>
+        </is>
+      </c>
+      <c r="J548" s="12" t="inlineStr"/>
+      <c r="K548" s="12" t="inlineStr"/>
+      <c r="L548" s="12" t="inlineStr"/>
+      <c r="M548" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N548" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O548" s="10" t="inlineStr"/>
+      <c r="P548" s="10" t="inlineStr"/>
+      <c r="Q548" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R548" s="12" t="inlineStr"/>
+      <c r="S548" s="12" t="inlineStr"/>
+      <c r="T548" s="12" t="inlineStr"/>
+      <c r="U548" s="1" t="inlineStr"/>
+    </row>
+    <row r="549" customHeight="1" ht="22">
+      <c r="A549" s="1" t="inlineStr"/>
+      <c r="B549" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">WILSON FRANCISCO MARZANO SILVEIRA </t>
+          </r>
+        </is>
+      </c>
+      <c r="C549" s="10" t="inlineStr"/>
+      <c r="D549" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">049.781.696-23</t>
+          </r>
+        </is>
+      </c>
+      <c r="E549" s="12" t="inlineStr"/>
+      <c r="F549" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">01673877203</t>
+          </r>
+        </is>
+      </c>
+      <c r="G549" s="12" t="inlineStr"/>
+      <c r="H549" s="12" t="inlineStr"/>
+      <c r="I549" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">10/08/2027</t>
+          </r>
+        </is>
+      </c>
+      <c r="J549" s="12" t="inlineStr"/>
+      <c r="K549" s="12" t="inlineStr"/>
+      <c r="L549" s="12" t="inlineStr"/>
+      <c r="M549" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N549" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O549" s="10" t="inlineStr"/>
+      <c r="P549" s="10" t="inlineStr"/>
+      <c r="Q549" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R549" s="12" t="inlineStr"/>
+      <c r="S549" s="12" t="inlineStr"/>
+      <c r="T549" s="12" t="inlineStr"/>
+      <c r="U549" s="1" t="inlineStr"/>
+    </row>
+    <row r="550" customHeight="1" ht="22">
+      <c r="A550" s="1" t="inlineStr"/>
+      <c r="B550" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">ZENILSON MARCELINO DE CARVALHO</t>
+          </r>
+        </is>
+      </c>
+      <c r="C550" s="10" t="inlineStr"/>
+      <c r="D550" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">039.291.734-33</t>
+          </r>
+        </is>
+      </c>
+      <c r="E550" s="12" t="inlineStr"/>
+      <c r="F550" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">04371720578</t>
+          </r>
+        </is>
+      </c>
+      <c r="G550" s="12" t="inlineStr"/>
+      <c r="H550" s="12" t="inlineStr"/>
+      <c r="I550" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">13/01/2027</t>
+          </r>
+        </is>
+      </c>
+      <c r="J550" s="12" t="inlineStr"/>
+      <c r="K550" s="12" t="inlineStr"/>
+      <c r="L550" s="12" t="inlineStr"/>
+      <c r="M550" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N550" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O550" s="10" t="inlineStr"/>
+      <c r="P550" s="10" t="inlineStr"/>
+      <c r="Q550" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R550" s="12" t="inlineStr"/>
+      <c r="S550" s="12" t="inlineStr"/>
+      <c r="T550" s="12" t="inlineStr"/>
+      <c r="U550" s="1" t="inlineStr"/>
+    </row>
+    <row r="551" customHeight="1" ht="15">
+      <c r="A551" s="1" t="inlineStr"/>
+      <c r="B551" s="1" t="inlineStr"/>
+      <c r="C551" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Total Ativo: 544</t>
+          </r>
+        </is>
+      </c>
+      <c r="D551" s="15" t="inlineStr"/>
+      <c r="E551" s="1" t="inlineStr"/>
+      <c r="F551" s="1" t="inlineStr"/>
+      <c r="G551" s="1" t="inlineStr"/>
+      <c r="H551" s="1" t="inlineStr"/>
+      <c r="I551" s="1" t="inlineStr"/>
+      <c r="J551" s="1" t="inlineStr"/>
+      <c r="K551" s="1" t="inlineStr"/>
+      <c r="L551" s="1" t="inlineStr"/>
+      <c r="M551" s="1" t="inlineStr"/>
+      <c r="N551" s="1" t="inlineStr"/>
+      <c r="O551" s="1" t="inlineStr"/>
+      <c r="P551" s="1" t="inlineStr"/>
+      <c r="Q551" s="1" t="inlineStr"/>
+      <c r="R551" s="1" t="inlineStr"/>
+      <c r="S551" s="1" t="inlineStr"/>
+      <c r="T551" s="1" t="inlineStr"/>
+      <c r="U551" s="1" t="inlineStr"/>
+    </row>
+    <row r="552" customHeight="1" ht="15">
+      <c r="A552" s="1" t="inlineStr"/>
+      <c r="B552" s="1" t="inlineStr"/>
+      <c r="C552" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43363,75 +43679,75 @@
           </r>
         </is>
       </c>
-      <c r="D548" s="15" t="inlineStr"/>
-      <c r="E548" s="1" t="inlineStr"/>
-      <c r="F548" s="1" t="inlineStr"/>
-      <c r="G548" s="1" t="inlineStr"/>
-      <c r="H548" s="1" t="inlineStr"/>
-      <c r="I548" s="1" t="inlineStr"/>
-      <c r="J548" s="1" t="inlineStr"/>
-      <c r="K548" s="1" t="inlineStr"/>
-      <c r="L548" s="1" t="inlineStr"/>
-      <c r="M548" s="1" t="inlineStr"/>
-      <c r="N548" s="1" t="inlineStr"/>
-      <c r="O548" s="1" t="inlineStr"/>
-      <c r="P548" s="1" t="inlineStr"/>
-      <c r="Q548" s="1" t="inlineStr"/>
-      <c r="R548" s="1" t="inlineStr"/>
-      <c r="S548" s="1" t="inlineStr"/>
-      <c r="T548" s="1" t="inlineStr"/>
-      <c r="U548" s="1" t="inlineStr"/>
-    </row>
-    <row r="549" customHeight="1" ht="15">
-      <c r="A549" s="1" t="inlineStr"/>
-      <c r="B549" s="1" t="inlineStr"/>
-      <c r="C549" s="14" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-       </rPr>
-            <t xml:space="preserve">Total Geral: 540</t>
-          </r>
-        </is>
-      </c>
-      <c r="D549" s="15" t="inlineStr"/>
-      <c r="E549" s="1" t="inlineStr"/>
-      <c r="F549" s="1" t="inlineStr"/>
-      <c r="G549" s="1" t="inlineStr"/>
-      <c r="H549" s="1" t="inlineStr"/>
-      <c r="I549" s="1" t="inlineStr"/>
-      <c r="J549" s="1" t="inlineStr"/>
-      <c r="K549" s="1" t="inlineStr"/>
-      <c r="L549" s="1" t="inlineStr"/>
-      <c r="M549" s="1" t="inlineStr"/>
-      <c r="N549" s="1" t="inlineStr"/>
-      <c r="O549" s="1" t="inlineStr"/>
-      <c r="P549" s="1" t="inlineStr"/>
-      <c r="Q549" s="1" t="inlineStr"/>
-      <c r="R549" s="1" t="inlineStr"/>
-      <c r="S549" s="1" t="inlineStr"/>
-      <c r="T549" s="1" t="inlineStr"/>
-      <c r="U549" s="1" t="inlineStr"/>
-    </row>
-    <row r="550" customHeight="1" ht="15">
-      <c r="A550" s="1" t="inlineStr"/>
-      <c r="B550" s="1" t="inlineStr"/>
-      <c r="C550" s="1" t="inlineStr"/>
-      <c r="D550" s="1" t="inlineStr"/>
-      <c r="E550" s="1" t="inlineStr"/>
-      <c r="F550" s="1" t="inlineStr"/>
-      <c r="G550" s="1" t="inlineStr"/>
-      <c r="H550" s="1" t="inlineStr"/>
-      <c r="I550" s="1" t="inlineStr"/>
-      <c r="J550" s="1" t="inlineStr"/>
-      <c r="K550" s="1" t="inlineStr"/>
-      <c r="L550" s="1" t="inlineStr"/>
-      <c r="M550" s="1" t="inlineStr"/>
-      <c r="N550" s="1" t="inlineStr"/>
-      <c r="O550" s="1" t="inlineStr"/>
-      <c r="P550" s="1" t="inlineStr"/>
-      <c r="Q550" s="1" t="inlineStr"/>
-      <c r="R550" s="16" t="inlineStr">
+      <c r="D552" s="15" t="inlineStr"/>
+      <c r="E552" s="1" t="inlineStr"/>
+      <c r="F552" s="1" t="inlineStr"/>
+      <c r="G552" s="1" t="inlineStr"/>
+      <c r="H552" s="1" t="inlineStr"/>
+      <c r="I552" s="1" t="inlineStr"/>
+      <c r="J552" s="1" t="inlineStr"/>
+      <c r="K552" s="1" t="inlineStr"/>
+      <c r="L552" s="1" t="inlineStr"/>
+      <c r="M552" s="1" t="inlineStr"/>
+      <c r="N552" s="1" t="inlineStr"/>
+      <c r="O552" s="1" t="inlineStr"/>
+      <c r="P552" s="1" t="inlineStr"/>
+      <c r="Q552" s="1" t="inlineStr"/>
+      <c r="R552" s="1" t="inlineStr"/>
+      <c r="S552" s="1" t="inlineStr"/>
+      <c r="T552" s="1" t="inlineStr"/>
+      <c r="U552" s="1" t="inlineStr"/>
+    </row>
+    <row r="553" customHeight="1" ht="15">
+      <c r="A553" s="1" t="inlineStr"/>
+      <c r="B553" s="1" t="inlineStr"/>
+      <c r="C553" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Total Geral: 544</t>
+          </r>
+        </is>
+      </c>
+      <c r="D553" s="15" t="inlineStr"/>
+      <c r="E553" s="1" t="inlineStr"/>
+      <c r="F553" s="1" t="inlineStr"/>
+      <c r="G553" s="1" t="inlineStr"/>
+      <c r="H553" s="1" t="inlineStr"/>
+      <c r="I553" s="1" t="inlineStr"/>
+      <c r="J553" s="1" t="inlineStr"/>
+      <c r="K553" s="1" t="inlineStr"/>
+      <c r="L553" s="1" t="inlineStr"/>
+      <c r="M553" s="1" t="inlineStr"/>
+      <c r="N553" s="1" t="inlineStr"/>
+      <c r="O553" s="1" t="inlineStr"/>
+      <c r="P553" s="1" t="inlineStr"/>
+      <c r="Q553" s="1" t="inlineStr"/>
+      <c r="R553" s="1" t="inlineStr"/>
+      <c r="S553" s="1" t="inlineStr"/>
+      <c r="T553" s="1" t="inlineStr"/>
+      <c r="U553" s="1" t="inlineStr"/>
+    </row>
+    <row r="554" customHeight="1" ht="15">
+      <c r="A554" s="1" t="inlineStr"/>
+      <c r="B554" s="1" t="inlineStr"/>
+      <c r="C554" s="1" t="inlineStr"/>
+      <c r="D554" s="1" t="inlineStr"/>
+      <c r="E554" s="1" t="inlineStr"/>
+      <c r="F554" s="1" t="inlineStr"/>
+      <c r="G554" s="1" t="inlineStr"/>
+      <c r="H554" s="1" t="inlineStr"/>
+      <c r="I554" s="1" t="inlineStr"/>
+      <c r="J554" s="1" t="inlineStr"/>
+      <c r="K554" s="1" t="inlineStr"/>
+      <c r="L554" s="1" t="inlineStr"/>
+      <c r="M554" s="1" t="inlineStr"/>
+      <c r="N554" s="1" t="inlineStr"/>
+      <c r="O554" s="1" t="inlineStr"/>
+      <c r="P554" s="1" t="inlineStr"/>
+      <c r="Q554" s="1" t="inlineStr"/>
+      <c r="R554" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43440,8 +43756,8 @@
           </r>
         </is>
       </c>
-      <c r="S550" s="17" t="inlineStr"/>
-      <c r="T550" s="16" t="inlineStr">
+      <c r="S554" s="17" t="inlineStr"/>
+      <c r="T554" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43450,7 +43766,7 @@
           </r>
         </is>
       </c>
-      <c r="U550" s="1" t="inlineStr"/>
+      <c r="U554" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -46707,10 +47023,34 @@
     <mergeCell ref="I546:L546"/>
     <mergeCell ref="N546:P546"/>
     <mergeCell ref="Q546:T546"/>
-    <mergeCell ref="C547:D547"/>
-    <mergeCell ref="C548:D548"/>
-    <mergeCell ref="C549:D549"/>
-    <mergeCell ref="R550:S550"/>
+    <mergeCell ref="B547:C547"/>
+    <mergeCell ref="D547:E547"/>
+    <mergeCell ref="F547:H547"/>
+    <mergeCell ref="I547:L547"/>
+    <mergeCell ref="N547:P547"/>
+    <mergeCell ref="Q547:T547"/>
+    <mergeCell ref="B548:C548"/>
+    <mergeCell ref="D548:E548"/>
+    <mergeCell ref="F548:H548"/>
+    <mergeCell ref="I548:L548"/>
+    <mergeCell ref="N548:P548"/>
+    <mergeCell ref="Q548:T548"/>
+    <mergeCell ref="B549:C549"/>
+    <mergeCell ref="D549:E549"/>
+    <mergeCell ref="F549:H549"/>
+    <mergeCell ref="I549:L549"/>
+    <mergeCell ref="N549:P549"/>
+    <mergeCell ref="Q549:T549"/>
+    <mergeCell ref="B550:C550"/>
+    <mergeCell ref="D550:E550"/>
+    <mergeCell ref="F550:H550"/>
+    <mergeCell ref="I550:L550"/>
+    <mergeCell ref="N550:P550"/>
+    <mergeCell ref="Q550:T550"/>
+    <mergeCell ref="C551:D551"/>
+    <mergeCell ref="C552:D552"/>
+    <mergeCell ref="C553:D553"/>
+    <mergeCell ref="R554:S554"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rIdDr1"/>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1781062143" name="Picture">
+        <xdr:cNvPr id="101684751" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="101684751" name="Picture">
+        <xdr:cNvPr id="702001789" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -5438,7 +5438,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/07/2025</t>
+            <t xml:space="preserve">15/09/2027</t>
           </r>
         </is>
       </c>
@@ -24556,7 +24556,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">23/09/2027</t>
           </r>
         </is>
       </c>
@@ -42094,7 +42094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">23/09/2027</t>
           </r>
         </is>
       </c>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1218195581" name="Picture">
+        <xdr:cNvPr id="18069776" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -22107,7 +22107,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/12/2025</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -25473,7 +25473,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JULIO CESAR DA SILVA</t>
+            <t xml:space="preserve">JULIENE SILVA CAETANO</t>
           </r>
         </is>
       </c>
@@ -25483,7 +25483,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">082.425.056-75</t>
+            <t xml:space="preserve">134.303.206-74</t>
           </r>
         </is>
       </c>
@@ -25493,7 +25493,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04143152247</t>
+            <t xml:space="preserve">07294693707</t>
           </r>
         </is>
       </c>
@@ -25504,7 +25504,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -25552,7 +25552,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JUNIO AMADO GABRIEL FERREIRA</t>
+            <t xml:space="preserve">JULIO CESAR DA SILVA</t>
           </r>
         </is>
       </c>
@@ -25562,7 +25562,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">064.300.466-13</t>
+            <t xml:space="preserve">082.425.056-75</t>
           </r>
         </is>
       </c>
@@ -25572,7 +25572,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03448733822</t>
+            <t xml:space="preserve">04143152247</t>
           </r>
         </is>
       </c>
@@ -25583,7 +25583,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -25631,7 +25631,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JUNIOR SOARES SILVA</t>
+            <t xml:space="preserve">JUNIO AMADO GABRIEL FERREIRA</t>
           </r>
         </is>
       </c>
@@ -25641,7 +25641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">045.399.946-89</t>
+            <t xml:space="preserve">064.300.466-13</t>
           </r>
         </is>
       </c>
@@ -25651,7 +25651,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01058206100</t>
+            <t xml:space="preserve">03448733822</t>
           </r>
         </is>
       </c>
@@ -25662,7 +25662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -25710,7 +25710,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JURACY APARECIDO BENTO</t>
+            <t xml:space="preserve">JUNIOR SOARES SILVA</t>
           </r>
         </is>
       </c>
@@ -25720,7 +25720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">448.299.146-53</t>
+            <t xml:space="preserve">045.399.946-89</t>
           </r>
         </is>
       </c>
@@ -25730,7 +25730,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00773621945</t>
+            <t xml:space="preserve">01058206100</t>
           </r>
         </is>
       </c>
@@ -25789,7 +25789,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JUVENIL ANTONIO DE SOUZA</t>
+            <t xml:space="preserve">JURACY APARECIDO BENTO</t>
           </r>
         </is>
       </c>
@@ -25799,7 +25799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">030.929.956-00</t>
+            <t xml:space="preserve">448.299.146-53</t>
           </r>
         </is>
       </c>
@@ -25809,7 +25809,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02317748354</t>
+            <t xml:space="preserve">00773621945</t>
           </r>
         </is>
       </c>
@@ -25820,7 +25820,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -25868,7 +25868,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">KAIWAN VICTOR VIEIRA</t>
+            <t xml:space="preserve">JUVENIL ANTONIO DE SOUZA</t>
           </r>
         </is>
       </c>
@@ -25878,7 +25878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">114.962.086-25</t>
+            <t xml:space="preserve">030.929.956-00</t>
           </r>
         </is>
       </c>
@@ -25888,7 +25888,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06887718253</t>
+            <t xml:space="preserve">02317748354</t>
           </r>
         </is>
       </c>
@@ -25899,7 +25899,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -25940,14 +25940,14 @@
       <c r="T326" s="12" t="inlineStr"/>
       <c r="U326" s="1" t="inlineStr"/>
     </row>
-    <row r="327" customHeight="1" ht="22">
+    <row r="327" customHeight="1" ht="21">
       <c r="A327" s="1" t="inlineStr"/>
       <c r="B327" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">KLEITON DO BOMSSUCESSO MORAIS</t>
+            <t xml:space="preserve">KAIWAN VICTOR VIEIRA</t>
           </r>
         </is>
       </c>
@@ -25957,7 +25957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">059.718.396-16</t>
+            <t xml:space="preserve">114.962.086-25</t>
           </r>
         </is>
       </c>
@@ -25967,7 +25967,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03230201778</t>
+            <t xml:space="preserve">06887718253</t>
           </r>
         </is>
       </c>
@@ -25978,7 +25978,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -26019,14 +26019,14 @@
       <c r="T327" s="12" t="inlineStr"/>
       <c r="U327" s="1" t="inlineStr"/>
     </row>
-    <row r="328" customHeight="1" ht="21">
+    <row r="328" customHeight="1" ht="22">
       <c r="A328" s="1" t="inlineStr"/>
       <c r="B328" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">KRAUS LUIS FERREIRA</t>
+            <t xml:space="preserve">KLEITON DO BOMSSUCESSO MORAIS</t>
           </r>
         </is>
       </c>
@@ -26036,7 +26036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.304.466-17</t>
+            <t xml:space="preserve">059.718.396-16</t>
           </r>
         </is>
       </c>
@@ -26046,7 +26046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06905670380</t>
+            <t xml:space="preserve">03230201778</t>
           </r>
         </is>
       </c>
@@ -26057,7 +26057,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -26105,7 +26105,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LARISSA SAMARA DA CRUZ</t>
+            <t xml:space="preserve">KRAUS LUIS FERREIRA</t>
           </r>
         </is>
       </c>
@@ -26115,7 +26115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">130.312.456-44</t>
+            <t xml:space="preserve">067.304.466-17</t>
           </r>
         </is>
       </c>
@@ -26125,7 +26125,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06360147584</t>
+            <t xml:space="preserve">06905670380</t>
           </r>
         </is>
       </c>
@@ -26136,7 +26136,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -26184,7 +26184,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO AMANCIO ROSA</t>
+            <t xml:space="preserve">LARISSA SAMARA DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -26194,7 +26194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">063.242.856-26</t>
+            <t xml:space="preserve">130.312.456-44</t>
           </r>
         </is>
       </c>
@@ -26204,7 +26204,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23000101331182026</t>
+            <t xml:space="preserve">06360147584</t>
           </r>
         </is>
       </c>
@@ -26215,7 +26215,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -26263,7 +26263,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO CORREA DE OLIVEIRA  </t>
+            <t xml:space="preserve">LEANDRO AMANCIO ROSA</t>
           </r>
         </is>
       </c>
@@ -26273,7 +26273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">102.927.847-40</t>
+            <t xml:space="preserve">063.242.856-26</t>
           </r>
         </is>
       </c>
@@ -26283,7 +26283,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03688215650</t>
+            <t xml:space="preserve">23000101331182026</t>
           </r>
         </is>
       </c>
@@ -26294,7 +26294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -26342,7 +26342,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO DO CARMO NUNES</t>
+            <t xml:space="preserve">LEANDRO CORREA DE OLIVEIRA  </t>
           </r>
         </is>
       </c>
@@ -26352,7 +26352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.730.376-97</t>
+            <t xml:space="preserve">102.927.847-40</t>
           </r>
         </is>
       </c>
@@ -26362,7 +26362,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03147187110</t>
+            <t xml:space="preserve">03688215650</t>
           </r>
         </is>
       </c>
@@ -26373,7 +26373,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -26421,7 +26421,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO RODRIGUES DA SILVA</t>
+            <t xml:space="preserve">LEANDRO DO CARMO NUNES</t>
           </r>
         </is>
       </c>
@@ -26431,7 +26431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">321.301.738-88</t>
+            <t xml:space="preserve">067.730.376-97</t>
           </r>
         </is>
       </c>
@@ -26441,7 +26441,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03291564997</t>
+            <t xml:space="preserve">03147187110</t>
           </r>
         </is>
       </c>
@@ -26452,7 +26452,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -26500,7 +26500,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO SOUZA DA SILVA</t>
+            <t xml:space="preserve">LEANDRO RODRIGUES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -26510,7 +26510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">103.572.406-50</t>
+            <t xml:space="preserve">321.301.738-88</t>
           </r>
         </is>
       </c>
@@ -26520,7 +26520,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04542317313</t>
+            <t xml:space="preserve">03291564997</t>
           </r>
         </is>
       </c>
@@ -26531,7 +26531,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -26572,14 +26572,14 @@
       <c r="T334" s="12" t="inlineStr"/>
       <c r="U334" s="1" t="inlineStr"/>
     </row>
-    <row r="335" customHeight="1" ht="22">
+    <row r="335" customHeight="1" ht="21">
       <c r="A335" s="1" t="inlineStr"/>
       <c r="B335" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEANDRO WAGNER ZACARIAS OLIVEIRA</t>
+            <t xml:space="preserve">LEANDRO SOUZA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -26589,7 +26589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.744.036-70</t>
+            <t xml:space="preserve">103.572.406-50</t>
           </r>
         </is>
       </c>
@@ -26599,7 +26599,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">2819007600</t>
+            <t xml:space="preserve">04542317313</t>
           </r>
         </is>
       </c>
@@ -26610,7 +26610,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -26651,14 +26651,14 @@
       <c r="T335" s="12" t="inlineStr"/>
       <c r="U335" s="1" t="inlineStr"/>
     </row>
-    <row r="336" customHeight="1" ht="21">
+    <row r="336" customHeight="1" ht="22">
       <c r="A336" s="1" t="inlineStr"/>
       <c r="B336" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEOCADIO DINIZ SILVA</t>
+            <t xml:space="preserve">LEANDRO WAGNER ZACARIAS OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -26668,7 +26668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">029.392.306-09</t>
+            <t xml:space="preserve">067.744.036-70</t>
           </r>
         </is>
       </c>
@@ -26678,7 +26678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01279620953</t>
+            <t xml:space="preserve">2819007600</t>
           </r>
         </is>
       </c>
@@ -26737,7 +26737,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEONARDO LOURENCO DA SILVA</t>
+            <t xml:space="preserve">LEOCADIO DINIZ SILVA</t>
           </r>
         </is>
       </c>
@@ -26747,7 +26747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.288.766-20</t>
+            <t xml:space="preserve">029.392.306-09</t>
           </r>
         </is>
       </c>
@@ -26757,7 +26757,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03899458171</t>
+            <t xml:space="preserve">01279620953</t>
           </r>
         </is>
       </c>
@@ -26816,7 +26816,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LEONEL HENRIQUE FERRÃO</t>
+            <t xml:space="preserve">LEONARDO LOURENCO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -26826,7 +26826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.263.116-45</t>
+            <t xml:space="preserve">079.288.766-20</t>
           </r>
         </is>
       </c>
@@ -26836,7 +26836,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05139720231</t>
+            <t xml:space="preserve">03899458171</t>
           </r>
         </is>
       </c>
@@ -26847,7 +26847,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -26888,14 +26888,14 @@
       <c r="T338" s="12" t="inlineStr"/>
       <c r="U338" s="1" t="inlineStr"/>
     </row>
-    <row r="339" customHeight="1" ht="22">
+    <row r="339" customHeight="1" ht="21">
       <c r="A339" s="1" t="inlineStr"/>
       <c r="B339" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LETICIA LILIANE DE SOUZA BARBOSA </t>
+            <t xml:space="preserve">LEONEL HENRIQUE FERRÃO</t>
           </r>
         </is>
       </c>
@@ -26905,7 +26905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">064.598.096-07</t>
+            <t xml:space="preserve">122.263.116-45</t>
           </r>
         </is>
       </c>
@@ -26915,7 +26915,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04632836129</t>
+            <t xml:space="preserve">05139720231</t>
           </r>
         </is>
       </c>
@@ -26926,7 +26926,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/05/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -26967,14 +26967,14 @@
       <c r="T339" s="12" t="inlineStr"/>
       <c r="U339" s="1" t="inlineStr"/>
     </row>
-    <row r="340" customHeight="1" ht="21">
+    <row r="340" customHeight="1" ht="22">
       <c r="A340" s="1" t="inlineStr"/>
       <c r="B340" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LIDIANA APARECIDA CARNEIRO</t>
+            <t xml:space="preserve">LETICIA LILIANE DE SOUZA BARBOSA </t>
           </r>
         </is>
       </c>
@@ -26984,7 +26984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">118.771.816-50</t>
+            <t xml:space="preserve">064.598.096-07</t>
           </r>
         </is>
       </c>
@@ -26994,7 +26994,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06773280877</t>
+            <t xml:space="preserve">04632836129</t>
           </r>
         </is>
       </c>
@@ -27005,7 +27005,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -27046,14 +27046,14 @@
       <c r="T340" s="12" t="inlineStr"/>
       <c r="U340" s="1" t="inlineStr"/>
     </row>
-    <row r="341" customHeight="1" ht="22">
+    <row r="341" customHeight="1" ht="21">
       <c r="A341" s="1" t="inlineStr"/>
       <c r="B341" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LINDOLFO MENDONCA DOS SANTOS</t>
+            <t xml:space="preserve">LIDIANA APARECIDA CARNEIRO</t>
           </r>
         </is>
       </c>
@@ -27063,7 +27063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">529.408.706-59</t>
+            <t xml:space="preserve">118.771.816-50</t>
           </r>
         </is>
       </c>
@@ -27073,7 +27073,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00019756510</t>
+            <t xml:space="preserve">06773280877</t>
           </r>
         </is>
       </c>
@@ -27084,7 +27084,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -27125,14 +27125,14 @@
       <c r="T341" s="12" t="inlineStr"/>
       <c r="U341" s="1" t="inlineStr"/>
     </row>
-    <row r="342" customHeight="1" ht="21">
+    <row r="342" customHeight="1" ht="22">
       <c r="A342" s="1" t="inlineStr"/>
       <c r="B342" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUAN MARTINS MARCONDES</t>
+            <t xml:space="preserve">LINDOLFO MENDONCA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -27142,7 +27142,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">096.277.976-85</t>
+            <t xml:space="preserve">529.408.706-59</t>
           </r>
         </is>
       </c>
@@ -27152,7 +27152,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289665375</t>
+            <t xml:space="preserve">00019756510</t>
           </r>
         </is>
       </c>
@@ -27163,7 +27163,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/02/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -27211,7 +27211,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS GONÇALVES MARTINS</t>
+            <t xml:space="preserve">LUAN MARTINS MARCONDES</t>
           </r>
         </is>
       </c>
@@ -27221,7 +27221,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">085.552.436-70</t>
+            <t xml:space="preserve">096.277.976-85</t>
           </r>
         </is>
       </c>
@@ -27231,7 +27231,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4693218713</t>
+            <t xml:space="preserve">04289665375</t>
           </r>
         </is>
       </c>
@@ -27242,7 +27242,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">11/02/2027</t>
           </r>
         </is>
       </c>
@@ -27290,7 +27290,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS LUIZ ALVES</t>
+            <t xml:space="preserve">LUCAS GONÇALVES MARTINS</t>
           </r>
         </is>
       </c>
@@ -27300,7 +27300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.062.856-91</t>
+            <t xml:space="preserve">085.552.436-70</t>
           </r>
         </is>
       </c>
@@ -27310,7 +27310,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01322002444</t>
+            <t xml:space="preserve">4693218713</t>
           </r>
         </is>
       </c>
@@ -27321,7 +27321,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -27369,7 +27369,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS SANTOS DE QUEIROZ</t>
+            <t xml:space="preserve">LUCAS LUIZ ALVES</t>
           </r>
         </is>
       </c>
@@ -27379,7 +27379,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">113.927.196-23</t>
+            <t xml:space="preserve">819.062.856-91</t>
           </r>
         </is>
       </c>
@@ -27389,7 +27389,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05160627501</t>
+            <t xml:space="preserve">01322002444</t>
           </r>
         </is>
       </c>
@@ -27400,7 +27400,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -27448,7 +27448,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS SILVA FRANCA</t>
+            <t xml:space="preserve">LUCAS SANTOS DE QUEIROZ</t>
           </r>
         </is>
       </c>
@@ -27458,7 +27458,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">013.991.046-83</t>
+            <t xml:space="preserve">113.927.196-23</t>
           </r>
         </is>
       </c>
@@ -27468,7 +27468,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02413059875</t>
+            <t xml:space="preserve">05160627501</t>
           </r>
         </is>
       </c>
@@ -27479,7 +27479,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -27527,7 +27527,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS VELOSO AMANCIO MACIEL</t>
+            <t xml:space="preserve">LUCAS SILVA FRANCA</t>
           </r>
         </is>
       </c>
@@ -27537,7 +27537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">135.218.266-19</t>
+            <t xml:space="preserve">013.991.046-83</t>
           </r>
         </is>
       </c>
@@ -27547,7 +27547,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06383476601</t>
+            <t xml:space="preserve">02413059875</t>
           </r>
         </is>
       </c>
@@ -27558,7 +27558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2026</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -27599,14 +27599,14 @@
       <c r="T347" s="12" t="inlineStr"/>
       <c r="U347" s="1" t="inlineStr"/>
     </row>
-    <row r="348" customHeight="1" ht="22">
+    <row r="348" customHeight="1" ht="21">
       <c r="A348" s="1" t="inlineStr"/>
       <c r="B348" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIA FERNANDA PEREIRA DA COSTA</t>
+            <t xml:space="preserve">LUCAS VELOSO AMANCIO MACIEL</t>
           </r>
         </is>
       </c>
@@ -27616,7 +27616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">031.585.776-58</t>
+            <t xml:space="preserve">135.218.266-19</t>
           </r>
         </is>
       </c>
@@ -27626,7 +27626,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">053314624601</t>
+            <t xml:space="preserve">06383476601</t>
           </r>
         </is>
       </c>
@@ -27637,7 +27637,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">11/07/2026</t>
           </r>
         </is>
       </c>
@@ -27678,14 +27678,14 @@
       <c r="T348" s="12" t="inlineStr"/>
       <c r="U348" s="1" t="inlineStr"/>
     </row>
-    <row r="349" customHeight="1" ht="21">
+    <row r="349" customHeight="1" ht="22">
       <c r="A349" s="1" t="inlineStr"/>
       <c r="B349" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIANE DE FATIMA R. COSTA    </t>
+            <t xml:space="preserve">LUCIA FERNANDA PEREIRA DA COSTA</t>
           </r>
         </is>
       </c>
@@ -27695,7 +27695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.763.156-69</t>
+            <t xml:space="preserve">031.585.776-58</t>
           </r>
         </is>
       </c>
@@ -27705,7 +27705,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04611449989</t>
+            <t xml:space="preserve">053314624601</t>
           </r>
         </is>
       </c>
@@ -27716,7 +27716,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -27764,7 +27764,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIANO PAULINO DA COSTA</t>
+            <t xml:space="preserve">LUCIANE DE FATIMA R. COSTA    </t>
           </r>
         </is>
       </c>
@@ -27774,7 +27774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">050.130.496-79</t>
+            <t xml:space="preserve">093.763.156-69</t>
           </r>
         </is>
       </c>
@@ -27784,7 +27784,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03103773460</t>
+            <t xml:space="preserve">04611449989</t>
           </r>
         </is>
       </c>
@@ -27795,7 +27795,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -27843,7 +27843,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIO AURELIANO DA SILVA</t>
+            <t xml:space="preserve">LUCIANO PAULINO DA COSTA</t>
           </r>
         </is>
       </c>
@@ -27853,7 +27853,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">047.703.276-17</t>
+            <t xml:space="preserve">050.130.496-79</t>
           </r>
         </is>
       </c>
@@ -27863,7 +27863,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04593463442</t>
+            <t xml:space="preserve">03103773460</t>
           </r>
         </is>
       </c>
@@ -27874,7 +27874,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -27922,7 +27922,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIO FABIO FERREIRA</t>
+            <t xml:space="preserve">LUCIO AURELIANO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -27932,7 +27932,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">006.683.332-94</t>
+            <t xml:space="preserve">047.703.276-17</t>
           </r>
         </is>
       </c>
@@ -27942,7 +27942,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04484954449</t>
+            <t xml:space="preserve">04593463442</t>
           </r>
         </is>
       </c>
@@ -27953,7 +27953,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2031</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -28001,7 +28001,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIS CARLOS VELOSO</t>
+            <t xml:space="preserve">LUCIO FABIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -28011,7 +28011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">943.062.656-68</t>
+            <t xml:space="preserve">006.683.332-94</t>
           </r>
         </is>
       </c>
@@ -28021,7 +28021,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00863735779</t>
+            <t xml:space="preserve">04484954449</t>
           </r>
         </is>
       </c>
@@ -28032,7 +28032,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/01/2026</t>
+            <t xml:space="preserve">10/08/2031</t>
           </r>
         </is>
       </c>
@@ -28080,7 +28080,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ ANDRE BORGES CAIXETA</t>
+            <t xml:space="preserve">LUIS CARLOS VELOSO</t>
           </r>
         </is>
       </c>
@@ -28090,7 +28090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.942.196-77</t>
+            <t xml:space="preserve">943.062.656-68</t>
           </r>
         </is>
       </c>
@@ -28100,7 +28100,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01667588932</t>
+            <t xml:space="preserve">00863735779</t>
           </r>
         </is>
       </c>
@@ -28111,7 +28111,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -28159,7 +28159,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ ANTONIO DA SILVA</t>
+            <t xml:space="preserve">LUIZ ANDRE BORGES CAIXETA</t>
           </r>
         </is>
       </c>
@@ -28169,7 +28169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">778.833.066-34</t>
+            <t xml:space="preserve">046.942.196-77</t>
           </r>
         </is>
       </c>
@@ -28179,7 +28179,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02831837732</t>
+            <t xml:space="preserve">01667588932</t>
           </r>
         </is>
       </c>
@@ -28190,7 +28190,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -28238,7 +28238,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ CARLOS DE ASSIS</t>
+            <t xml:space="preserve">LUIZ ANTONIO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -28248,7 +28248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">063.432.686-42</t>
+            <t xml:space="preserve">778.833.066-34</t>
           </r>
         </is>
       </c>
@@ -28258,7 +28258,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02836643209</t>
+            <t xml:space="preserve">02831837732</t>
           </r>
         </is>
       </c>
@@ -28269,7 +28269,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/06/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -28317,7 +28317,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ FERNANDO GONCALVES</t>
+            <t xml:space="preserve">LUIZ CARLOS DE ASSIS</t>
           </r>
         </is>
       </c>
@@ -28327,7 +28327,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">066.587.606-83</t>
+            <t xml:space="preserve">063.432.686-42</t>
           </r>
         </is>
       </c>
@@ -28337,7 +28337,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04319056439</t>
+            <t xml:space="preserve">02836643209</t>
           </r>
         </is>
       </c>
@@ -28348,7 +28348,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/10/2026</t>
+            <t xml:space="preserve">25/06/2027</t>
           </r>
         </is>
       </c>
@@ -28396,7 +28396,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ GONZAGA DA SILVA</t>
+            <t xml:space="preserve">LUIZ FERNANDO GONCALVES</t>
           </r>
         </is>
       </c>
@@ -28406,7 +28406,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">939.705.796-00</t>
+            <t xml:space="preserve">066.587.606-83</t>
           </r>
         </is>
       </c>
@@ -28416,7 +28416,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01099082690</t>
+            <t xml:space="preserve">04319056439</t>
           </r>
         </is>
       </c>
@@ -28427,7 +28427,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">09/10/2026</t>
           </r>
         </is>
       </c>
@@ -28475,7 +28475,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ GUSTAVO SANTOS LIMA</t>
+            <t xml:space="preserve">LUIZ GONZAGA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -28485,7 +28485,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">083.760.036-74</t>
+            <t xml:space="preserve">939.705.796-00</t>
           </r>
         </is>
       </c>
@@ -28495,7 +28495,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04424986322</t>
+            <t xml:space="preserve">01099082690</t>
           </r>
         </is>
       </c>
@@ -28506,7 +28506,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -28554,7 +28554,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ HENRIQUE E MARTINS VIEIRA  </t>
+            <t xml:space="preserve">LUIZ GUSTAVO SANTOS LIMA</t>
           </r>
         </is>
       </c>
@@ -28564,7 +28564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.281.616-04</t>
+            <t xml:space="preserve">083.760.036-74</t>
           </r>
         </is>
       </c>
@@ -28574,7 +28574,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04521971771</t>
+            <t xml:space="preserve">04424986322</t>
           </r>
         </is>
       </c>
@@ -28585,7 +28585,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -28633,7 +28633,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ RICARDO DE MELO</t>
+            <t xml:space="preserve">LUIZ HENRIQUE E MARTINS VIEIRA  </t>
           </r>
         </is>
       </c>
@@ -28643,7 +28643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.995.666-10</t>
+            <t xml:space="preserve">088.281.616-04</t>
           </r>
         </is>
       </c>
@@ -28653,7 +28653,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03344105706</t>
+            <t xml:space="preserve">04521971771</t>
           </r>
         </is>
       </c>
@@ -28664,7 +28664,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -28712,7 +28712,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUZIA MARIA DOS SANTOS</t>
+            <t xml:space="preserve">LUIZ RICARDO DE MELO</t>
           </r>
         </is>
       </c>
@@ -28722,7 +28722,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.951.396-59</t>
+            <t xml:space="preserve">076.995.666-10</t>
           </r>
         </is>
       </c>
@@ -28732,7 +28732,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04148424907</t>
+            <t xml:space="preserve">03344105706</t>
           </r>
         </is>
       </c>
@@ -28743,7 +28743,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/12/2023</t>
+            <t xml:space="preserve">29/07/2027</t>
           </r>
         </is>
       </c>
@@ -28791,7 +28791,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAIKY SANTANA FERNANDES</t>
+            <t xml:space="preserve">LUZIA MARIA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -28801,7 +28801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">140.188.876-39</t>
+            <t xml:space="preserve">026.951.396-59</t>
           </r>
         </is>
       </c>
@@ -28811,7 +28811,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06777417203</t>
+            <t xml:space="preserve">04148424907</t>
           </r>
         </is>
       </c>
@@ -28822,7 +28822,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/07/2027</t>
+            <t xml:space="preserve">31/12/2023</t>
           </r>
         </is>
       </c>
@@ -28870,7 +28870,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MANOEL SANTOS MORAES</t>
+            <t xml:space="preserve">MAIKY SANTANA FERNANDES</t>
           </r>
         </is>
       </c>
@@ -28880,7 +28880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">715.808.326-87</t>
+            <t xml:space="preserve">140.188.876-39</t>
           </r>
         </is>
       </c>
@@ -28890,7 +28890,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01155974255</t>
+            <t xml:space="preserve">06777417203</t>
           </r>
         </is>
       </c>
@@ -28901,7 +28901,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">24/07/2027</t>
           </r>
         </is>
       </c>
@@ -28949,7 +28949,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO BATISTA DOS SANTOS</t>
+            <t xml:space="preserve">MANOEL SANTOS MORAES</t>
           </r>
         </is>
       </c>
@@ -28959,7 +28959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">043.142.726-78</t>
+            <t xml:space="preserve">715.808.326-87</t>
           </r>
         </is>
       </c>
@@ -28969,7 +28969,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02450313294</t>
+            <t xml:space="preserve">01155974255</t>
           </r>
         </is>
       </c>
@@ -28980,7 +28980,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -29028,7 +29028,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO HENRIQUE CAETANO</t>
+            <t xml:space="preserve">MARCELO BATISTA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -29038,7 +29038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">034.939.999-92</t>
+            <t xml:space="preserve">043.142.726-78</t>
           </r>
         </is>
       </c>
@@ -29048,7 +29048,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02099361590</t>
+            <t xml:space="preserve">02450313294</t>
           </r>
         </is>
       </c>
@@ -29059,7 +29059,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -29100,14 +29100,14 @@
       <c r="T366" s="12" t="inlineStr"/>
       <c r="U366" s="1" t="inlineStr"/>
     </row>
-    <row r="367" customHeight="1" ht="22">
+    <row r="367" customHeight="1" ht="21">
       <c r="A367" s="1" t="inlineStr"/>
       <c r="B367" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO LUCIANO DE SOUZA OLIVEIRA</t>
+            <t xml:space="preserve">MARCELO HENRIQUE CAETANO</t>
           </r>
         </is>
       </c>
@@ -29117,7 +29117,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">073.595.556-55</t>
+            <t xml:space="preserve">034.939.999-92</t>
           </r>
         </is>
       </c>
@@ -29127,7 +29127,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03641355881</t>
+            <t xml:space="preserve">02099361590</t>
           </r>
         </is>
       </c>
@@ -29138,7 +29138,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -29179,14 +29179,14 @@
       <c r="T367" s="12" t="inlineStr"/>
       <c r="U367" s="1" t="inlineStr"/>
     </row>
-    <row r="368" customHeight="1" ht="21">
+    <row r="368" customHeight="1" ht="22">
       <c r="A368" s="1" t="inlineStr"/>
       <c r="B368" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO MARTINS BORGES</t>
+            <t xml:space="preserve">MARCELO LUCIANO DE SOUZA OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -29196,7 +29196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">002.744.406-60</t>
+            <t xml:space="preserve">073.595.556-55</t>
           </r>
         </is>
       </c>
@@ -29206,7 +29206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02783779084</t>
+            <t xml:space="preserve">03641355881</t>
           </r>
         </is>
       </c>
@@ -29217,7 +29217,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2025</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -29265,7 +29265,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO MENDES DOS SANTOS</t>
+            <t xml:space="preserve">MARCELO MARTINS BORGES</t>
           </r>
         </is>
       </c>
@@ -29275,7 +29275,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">901.945.276-20</t>
+            <t xml:space="preserve">002.744.406-60</t>
           </r>
         </is>
       </c>
@@ -29285,7 +29285,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04168367162</t>
+            <t xml:space="preserve">02783779084</t>
           </r>
         </is>
       </c>
@@ -29296,7 +29296,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">31/07/2025</t>
           </r>
         </is>
       </c>
@@ -29344,7 +29344,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO TADEU DE OLIVEIRA</t>
+            <t xml:space="preserve">MARCELO MENDES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -29354,7 +29354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">049.321.486-07</t>
+            <t xml:space="preserve">901.945.276-20</t>
           </r>
         </is>
       </c>
@@ -29364,7 +29364,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01620321495</t>
+            <t xml:space="preserve">04168367162</t>
           </r>
         </is>
       </c>
@@ -29375,7 +29375,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -29423,7 +29423,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ALAIR CORREA  </t>
+            <t xml:space="preserve">MARCELO TADEU DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -29433,7 +29433,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">549.576.056-53</t>
+            <t xml:space="preserve">049.321.486-07</t>
           </r>
         </is>
       </c>
@@ -29443,7 +29443,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02871826370</t>
+            <t xml:space="preserve">01620321495</t>
           </r>
         </is>
       </c>
@@ -29454,7 +29454,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -29502,7 +29502,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ANTONIO FERREIRA</t>
+            <t xml:space="preserve">MARCIO ALAIR CORREA  </t>
           </r>
         </is>
       </c>
@@ -29512,7 +29512,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">902.851.406-63</t>
+            <t xml:space="preserve">549.576.056-53</t>
           </r>
         </is>
       </c>
@@ -29522,7 +29522,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02516992442</t>
+            <t xml:space="preserve">02871826370</t>
           </r>
         </is>
       </c>
@@ -29533,7 +29533,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -29574,14 +29574,14 @@
       <c r="T372" s="12" t="inlineStr"/>
       <c r="U372" s="1" t="inlineStr"/>
     </row>
-    <row r="373" customHeight="1" ht="22">
+    <row r="373" customHeight="1" ht="21">
       <c r="A373" s="1" t="inlineStr"/>
       <c r="B373" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ANTONIO PARREIRAS DA PAZ</t>
+            <t xml:space="preserve">MARCIO ANTONIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -29591,7 +29591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">577.128.916-72</t>
+            <t xml:space="preserve">902.851.406-63</t>
           </r>
         </is>
       </c>
@@ -29601,7 +29601,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02890495585</t>
+            <t xml:space="preserve">02516992442</t>
           </r>
         </is>
       </c>
@@ -29612,7 +29612,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -29653,14 +29653,14 @@
       <c r="T373" s="12" t="inlineStr"/>
       <c r="U373" s="1" t="inlineStr"/>
     </row>
-    <row r="374" customHeight="1" ht="21">
+    <row r="374" customHeight="1" ht="22">
       <c r="A374" s="1" t="inlineStr"/>
       <c r="B374" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO DA SILVA OTTONI</t>
+            <t xml:space="preserve">MARCIO ANTONIO PARREIRAS DA PAZ</t>
           </r>
         </is>
       </c>
@@ -29670,7 +29670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.607.566-51</t>
+            <t xml:space="preserve">577.128.916-72</t>
           </r>
         </is>
       </c>
@@ -29680,7 +29680,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01687919581</t>
+            <t xml:space="preserve">02890495585</t>
           </r>
         </is>
       </c>
@@ -29691,7 +29691,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/02/2026</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -29732,14 +29732,14 @@
       <c r="T374" s="12" t="inlineStr"/>
       <c r="U374" s="1" t="inlineStr"/>
     </row>
-    <row r="375" customHeight="1" ht="22">
+    <row r="375" customHeight="1" ht="21">
       <c r="A375" s="1" t="inlineStr"/>
       <c r="B375" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO FLAVIO ANDRADE ALMEIDA</t>
+            <t xml:space="preserve">MARCIO DA SILVA OTTONI</t>
           </r>
         </is>
       </c>
@@ -29749,7 +29749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.017.466-97</t>
+            <t xml:space="preserve">026.607.566-51</t>
           </r>
         </is>
       </c>
@@ -29759,7 +29759,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289067720</t>
+            <t xml:space="preserve">01687919581</t>
           </r>
         </is>
       </c>
@@ -29770,7 +29770,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/07/2027</t>
+            <t xml:space="preserve">21/02/2026</t>
           </r>
         </is>
       </c>
@@ -29811,14 +29811,14 @@
       <c r="T375" s="12" t="inlineStr"/>
       <c r="U375" s="1" t="inlineStr"/>
     </row>
-    <row r="376" customHeight="1" ht="21">
+    <row r="376" customHeight="1" ht="22">
       <c r="A376" s="1" t="inlineStr"/>
       <c r="B376" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIONE APARECIDO MARTINS</t>
+            <t xml:space="preserve">MARCIO FLAVIO ANDRADE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -29828,7 +29828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">041.411.046-39</t>
+            <t xml:space="preserve">040.017.466-97</t>
           </r>
         </is>
       </c>
@@ -29838,7 +29838,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03863886454</t>
+            <t xml:space="preserve">04289067720</t>
           </r>
         </is>
       </c>
@@ -29849,7 +29849,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">06/07/2027</t>
           </r>
         </is>
       </c>
@@ -29890,14 +29890,14 @@
       <c r="T376" s="12" t="inlineStr"/>
       <c r="U376" s="1" t="inlineStr"/>
     </row>
-    <row r="377" customHeight="1" ht="22">
+    <row r="377" customHeight="1" ht="21">
       <c r="A377" s="1" t="inlineStr"/>
       <c r="B377" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCO AURELIO HENRIQUE DOS SANTOS</t>
+            <t xml:space="preserve">MARCIONE APARECIDO MARTINS</t>
           </r>
         </is>
       </c>
@@ -29907,7 +29907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.690.426-50</t>
+            <t xml:space="preserve">041.411.046-39</t>
           </r>
         </is>
       </c>
@@ -29917,7 +29917,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05105181704</t>
+            <t xml:space="preserve">03863886454</t>
           </r>
         </is>
       </c>
@@ -29928,7 +29928,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -29969,14 +29969,14 @@
       <c r="T377" s="12" t="inlineStr"/>
       <c r="U377" s="1" t="inlineStr"/>
     </row>
-    <row r="378" customHeight="1" ht="21">
+    <row r="378" customHeight="1" ht="22">
       <c r="A378" s="1" t="inlineStr"/>
       <c r="B378" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANDRÉ DE ALMEIDA</t>
+            <t xml:space="preserve">MARCO AURELIO HENRIQUE DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -29986,7 +29986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">056.770.516-16</t>
+            <t xml:space="preserve">110.690.426-50</t>
           </r>
         </is>
       </c>
@@ -29996,7 +29996,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03502926908</t>
+            <t xml:space="preserve">05105181704</t>
           </r>
         </is>
       </c>
@@ -30007,7 +30007,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -30055,7 +30055,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANTONIO COSTA</t>
+            <t xml:space="preserve">MARCOS ANDRÉ DE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -30065,7 +30065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.627.216-06</t>
+            <t xml:space="preserve">056.770.516-16</t>
           </r>
         </is>
       </c>
@@ -30075,7 +30075,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05971763818</t>
+            <t xml:space="preserve">03502926908</t>
           </r>
         </is>
       </c>
@@ -30086,7 +30086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -30127,14 +30127,14 @@
       <c r="T379" s="12" t="inlineStr"/>
       <c r="U379" s="1" t="inlineStr"/>
     </row>
-    <row r="380" customHeight="1" ht="22">
+    <row r="380" customHeight="1" ht="21">
       <c r="A380" s="1" t="inlineStr"/>
       <c r="B380" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANTONIO PEREIRA DA SILVA</t>
+            <t xml:space="preserve">MARCOS ANTONIO COSTA</t>
           </r>
         </is>
       </c>
@@ -30144,7 +30144,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">952.874.346-34</t>
+            <t xml:space="preserve">077.627.216-06</t>
           </r>
         </is>
       </c>
@@ -30154,7 +30154,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03056193881</t>
+            <t xml:space="preserve">05971763818</t>
           </r>
         </is>
       </c>
@@ -30165,7 +30165,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -30206,14 +30206,14 @@
       <c r="T380" s="12" t="inlineStr"/>
       <c r="U380" s="1" t="inlineStr"/>
     </row>
-    <row r="381" customHeight="1" ht="21">
+    <row r="381" customHeight="1" ht="22">
       <c r="A381" s="1" t="inlineStr"/>
       <c r="B381" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS AURELIO BARBOSA</t>
+            <t xml:space="preserve">MARCOS ANTONIO PEREIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -30223,7 +30223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.909.046-28</t>
+            <t xml:space="preserve">952.874.346-34</t>
           </r>
         </is>
       </c>
@@ -30233,7 +30233,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03480890822</t>
+            <t xml:space="preserve">03056193881</t>
           </r>
         </is>
       </c>
@@ -30244,7 +30244,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -30292,7 +30292,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS DE ASSIS FERREIRA </t>
+            <t xml:space="preserve">MARCOS AURELIO BARBOSA</t>
           </r>
         </is>
       </c>
@@ -30302,7 +30302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">047.953.146-32</t>
+            <t xml:space="preserve">051.909.046-28</t>
           </r>
         </is>
       </c>
@@ -30312,7 +30312,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04407791869</t>
+            <t xml:space="preserve">03480890822</t>
           </r>
         </is>
       </c>
@@ -30323,7 +30323,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -30371,7 +30371,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS GUIMARAES CALDEIRA</t>
+            <t xml:space="preserve">MARCOS DE ASSIS FERREIRA </t>
           </r>
         </is>
       </c>
@@ -30381,7 +30381,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.400.096-93</t>
+            <t xml:space="preserve">047.953.146-32</t>
           </r>
         </is>
       </c>
@@ -30391,7 +30391,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03689823277</t>
+            <t xml:space="preserve">04407791869</t>
           </r>
         </is>
       </c>
@@ -30402,7 +30402,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">28/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -30450,7 +30450,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS HENRIQUE REIS</t>
+            <t xml:space="preserve">MARCOS GUIMARAES CALDEIRA</t>
           </r>
         </is>
       </c>
@@ -30460,7 +30460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">089.960.066-29</t>
+            <t xml:space="preserve">076.400.096-93</t>
           </r>
         </is>
       </c>
@@ -30470,7 +30470,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04248770930</t>
+            <t xml:space="preserve">03689823277</t>
           </r>
         </is>
       </c>
@@ -30481,7 +30481,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">28/08/2027</t>
           </r>
         </is>
       </c>
@@ -30529,7 +30529,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS JHONATAN ALVES</t>
+            <t xml:space="preserve">MARCOS HENRIQUE REIS</t>
           </r>
         </is>
       </c>
@@ -30539,7 +30539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">106.575.206-75</t>
+            <t xml:space="preserve">089.960.066-29</t>
           </r>
         </is>
       </c>
@@ -30549,7 +30549,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05470405595</t>
+            <t xml:space="preserve">04248770930</t>
           </r>
         </is>
       </c>
@@ -30560,7 +30560,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -30608,7 +30608,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS JOSE TRIGUEIRO</t>
+            <t xml:space="preserve">MARCOS JHONATAN ALVES</t>
           </r>
         </is>
       </c>
@@ -30618,7 +30618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">721.730.416-49</t>
+            <t xml:space="preserve">106.575.206-75</t>
           </r>
         </is>
       </c>
@@ -30628,7 +30628,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01704730263</t>
+            <t xml:space="preserve">05470405595</t>
           </r>
         </is>
       </c>
@@ -30639,7 +30639,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/05/2026</t>
+            <t xml:space="preserve">11/08/2026</t>
           </r>
         </is>
       </c>
@@ -30687,7 +30687,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS VINICIUS SILVA GOMES</t>
+            <t xml:space="preserve">MARCOS JOSE TRIGUEIRO</t>
           </r>
         </is>
       </c>
@@ -30697,7 +30697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">018.869.786-11</t>
+            <t xml:space="preserve">721.730.416-49</t>
           </r>
         </is>
       </c>
@@ -30707,7 +30707,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07590695960</t>
+            <t xml:space="preserve">01704730263</t>
           </r>
         </is>
       </c>
@@ -30718,7 +30718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2027</t>
+            <t xml:space="preserve">15/05/2026</t>
           </r>
         </is>
       </c>
@@ -30766,7 +30766,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCUS VINICIUS MOREIRA</t>
+            <t xml:space="preserve">MARCOS VINICIUS SILVA GOMES</t>
           </r>
         </is>
       </c>
@@ -30776,7 +30776,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">582.830.726-68</t>
+            <t xml:space="preserve">018.869.786-11</t>
           </r>
         </is>
       </c>
@@ -30786,7 +30786,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01594136546</t>
+            <t xml:space="preserve">07590695960</t>
           </r>
         </is>
       </c>
@@ -30797,7 +30797,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">11/07/2027</t>
           </r>
         </is>
       </c>
@@ -30838,14 +30838,14 @@
       <c r="T388" s="12" t="inlineStr"/>
       <c r="U388" s="1" t="inlineStr"/>
     </row>
-    <row r="389" customHeight="1" ht="22">
+    <row r="389" customHeight="1" ht="21">
       <c r="A389" s="1" t="inlineStr"/>
       <c r="B389" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATHEUS MATIAS NOGUEIRA DOS SANTOS</t>
+            <t xml:space="preserve">MARCUS VINICIUS MOREIRA</t>
           </r>
         </is>
       </c>
@@ -30855,7 +30855,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">105.075.596-06</t>
+            <t xml:space="preserve">582.830.726-68</t>
           </r>
         </is>
       </c>
@@ -30865,7 +30865,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06658773832</t>
+            <t xml:space="preserve">01594136546</t>
           </r>
         </is>
       </c>
@@ -30917,14 +30917,14 @@
       <c r="T389" s="12" t="inlineStr"/>
       <c r="U389" s="1" t="inlineStr"/>
     </row>
-    <row r="390" customHeight="1" ht="21">
+    <row r="390" customHeight="1" ht="22">
       <c r="A390" s="1" t="inlineStr"/>
       <c r="B390" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATOSALEM NUNES DA CRUZ</t>
+            <t xml:space="preserve">MATHEUS MATIAS NOGUEIRA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -30934,7 +30934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">936.443.376-91</t>
+            <t xml:space="preserve">105.075.596-06</t>
           </r>
         </is>
       </c>
@@ -30944,7 +30944,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02695434380</t>
+            <t xml:space="preserve">06658773832</t>
           </r>
         </is>
       </c>
@@ -30955,7 +30955,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -31003,7 +31003,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATUSAEL PEREIRA DE SOUSA</t>
+            <t xml:space="preserve">MATOSALEM NUNES DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -31013,7 +31013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">702.247.496-68</t>
+            <t xml:space="preserve">936.443.376-91</t>
           </r>
         </is>
       </c>
@@ -31023,7 +31023,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02236242704</t>
+            <t xml:space="preserve">02695434380</t>
           </r>
         </is>
       </c>
@@ -31034,7 +31034,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -31082,7 +31082,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO DOS SANTOS VIEIRA</t>
+            <t xml:space="preserve">MATUSAEL PEREIRA DE SOUSA</t>
           </r>
         </is>
       </c>
@@ -31092,7 +31092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.860.416-69</t>
+            <t xml:space="preserve">702.247.496-68</t>
           </r>
         </is>
       </c>
@@ -31102,7 +31102,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01707561330</t>
+            <t xml:space="preserve">02236242704</t>
           </r>
         </is>
       </c>
@@ -31113,7 +31113,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/07/2025</t>
+            <t xml:space="preserve">07/10/2027</t>
           </r>
         </is>
       </c>
@@ -31161,7 +31161,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO MONTEIRO</t>
+            <t xml:space="preserve">MAURICIO DOS SANTOS VIEIRA</t>
           </r>
         </is>
       </c>
@@ -31171,7 +31171,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">631.406.596-87</t>
+            <t xml:space="preserve">040.860.416-69</t>
           </r>
         </is>
       </c>
@@ -31181,7 +31181,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04067779168</t>
+            <t xml:space="preserve">01707561330</t>
           </r>
         </is>
       </c>
@@ -31192,7 +31192,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/10/2025</t>
+            <t xml:space="preserve">10/07/2025</t>
           </r>
         </is>
       </c>
@@ -31240,7 +31240,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO RIBEIRO DE OLIVEIRA</t>
+            <t xml:space="preserve">MAURICIO MONTEIRO</t>
           </r>
         </is>
       </c>
@@ -31250,7 +31250,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.153.576-91</t>
+            <t xml:space="preserve">631.406.596-87</t>
           </r>
         </is>
       </c>
@@ -31260,7 +31260,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03578222825</t>
+            <t xml:space="preserve">04067779168</t>
           </r>
         </is>
       </c>
@@ -31271,7 +31271,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/05/2027</t>
+            <t xml:space="preserve">31/10/2025</t>
           </r>
         </is>
       </c>
@@ -31319,7 +31319,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO LÚCIO DO CARMO</t>
+            <t xml:space="preserve">MAURICIO RIBEIRO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -31329,7 +31329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">925.340.316-00</t>
+            <t xml:space="preserve">819.153.576-91</t>
           </r>
         </is>
       </c>
@@ -31339,7 +31339,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00409168014</t>
+            <t xml:space="preserve">03578222825</t>
           </r>
         </is>
       </c>
@@ -31350,7 +31350,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/03/2026</t>
+            <t xml:space="preserve">26/05/2027</t>
           </r>
         </is>
       </c>
@@ -31398,7 +31398,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO SOARES LEAO  </t>
+            <t xml:space="preserve">MAURO LÚCIO DO CARMO</t>
           </r>
         </is>
       </c>
@@ -31408,7 +31408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">384.804.096-49</t>
+            <t xml:space="preserve">925.340.316-00</t>
           </r>
         </is>
       </c>
@@ -31418,7 +31418,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02582612080</t>
+            <t xml:space="preserve">00409168014</t>
           </r>
         </is>
       </c>
@@ -31429,7 +31429,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">21/03/2026</t>
           </r>
         </is>
       </c>
@@ -31477,7 +31477,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MICHELE FARIA DE CASTRO</t>
+            <t xml:space="preserve">MAURO SOARES LEAO  </t>
           </r>
         </is>
       </c>
@@ -31487,7 +31487,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">083.973.226-04</t>
+            <t xml:space="preserve">384.804.096-49</t>
           </r>
         </is>
       </c>
@@ -31497,7 +31497,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03837467386</t>
+            <t xml:space="preserve">02582612080</t>
           </r>
         </is>
       </c>
@@ -31508,7 +31508,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/08/2027</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -31556,7 +31556,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON DA SILVEIRA REZENDE</t>
+            <t xml:space="preserve">MICHELE FARIA DE CASTRO</t>
           </r>
         </is>
       </c>
@@ -31566,7 +31566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">455.523.636-04</t>
+            <t xml:space="preserve">083.973.226-04</t>
           </r>
         </is>
       </c>
@@ -31576,7 +31576,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02118384033</t>
+            <t xml:space="preserve">03837467386</t>
           </r>
         </is>
       </c>
@@ -31587,7 +31587,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/11/2026</t>
+            <t xml:space="preserve">26/08/2027</t>
           </r>
         </is>
       </c>
@@ -31635,7 +31635,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON FELIX DA CRUZ</t>
+            <t xml:space="preserve">MILTON DA SILVEIRA REZENDE</t>
           </r>
         </is>
       </c>
@@ -31645,7 +31645,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">007.806.387-60</t>
+            <t xml:space="preserve">455.523.636-04</t>
           </r>
         </is>
       </c>
@@ -31655,7 +31655,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02901380541</t>
+            <t xml:space="preserve">02118384033</t>
           </r>
         </is>
       </c>
@@ -31666,7 +31666,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">20/11/2026</t>
           </r>
         </is>
       </c>
@@ -31714,7 +31714,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON LOURENCO   </t>
+            <t xml:space="preserve">MILTON FELIX DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -31724,7 +31724,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">728.967.796-04</t>
+            <t xml:space="preserve">007.806.387-60</t>
           </r>
         </is>
       </c>
@@ -31734,7 +31734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00967395628</t>
+            <t xml:space="preserve">02901380541</t>
           </r>
         </is>
       </c>
@@ -31745,7 +31745,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -31793,7 +31793,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MIZAEL BABO AUGUSTO</t>
+            <t xml:space="preserve">MILTON LOURENCO   </t>
           </r>
         </is>
       </c>
@@ -31803,7 +31803,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">097.718.576-14</t>
+            <t xml:space="preserve">728.967.796-04</t>
           </r>
         </is>
       </c>
@@ -31813,7 +31813,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07220573198</t>
+            <t xml:space="preserve">00967395628</t>
           </r>
         </is>
       </c>
@@ -31824,7 +31824,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/09/2025</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -31872,7 +31872,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MONALDO JULIO DA SILVA</t>
+            <t xml:space="preserve">MIZAEL BABO AUGUSTO</t>
           </r>
         </is>
       </c>
@@ -31882,7 +31882,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">787.493.956-53</t>
+            <t xml:space="preserve">097.718.576-14</t>
           </r>
         </is>
       </c>
@@ -31892,7 +31892,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00710808596</t>
+            <t xml:space="preserve">07220573198</t>
           </r>
         </is>
       </c>
@@ -31903,7 +31903,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">16/09/2025</t>
           </r>
         </is>
       </c>
@@ -31951,7 +31951,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MOZART JOSE DA SILVA</t>
+            <t xml:space="preserve">MONALDO JULIO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -31961,7 +31961,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">411.500.586-68</t>
+            <t xml:space="preserve">787.493.956-53</t>
           </r>
         </is>
       </c>
@@ -31971,7 +31971,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02069316250</t>
+            <t xml:space="preserve">00710808596</t>
           </r>
         </is>
       </c>
@@ -31982,7 +31982,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -32030,7 +32030,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NACIEL LEMOS PEREIRA</t>
+            <t xml:space="preserve">MOZART JOSE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -32040,7 +32040,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">113.971.196-24</t>
+            <t xml:space="preserve">411.500.586-68</t>
           </r>
         </is>
       </c>
@@ -32050,7 +32050,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05182091350</t>
+            <t xml:space="preserve">02069316250</t>
           </r>
         </is>
       </c>
@@ -32061,7 +32061,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">11/07/2027</t>
           </r>
         </is>
       </c>
@@ -32109,7 +32109,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NASCIMENTO DOS REIS GONDIN</t>
+            <t xml:space="preserve">NACIEL LEMOS PEREIRA</t>
           </r>
         </is>
       </c>
@@ -32119,7 +32119,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">761.988.636-20</t>
+            <t xml:space="preserve">113.971.196-24</t>
           </r>
         </is>
       </c>
@@ -32129,7 +32129,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00900948176</t>
+            <t xml:space="preserve">05182091350</t>
           </r>
         </is>
       </c>
@@ -32140,7 +32140,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">11/08/2026</t>
           </r>
         </is>
       </c>
@@ -32188,7 +32188,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NATALIA MARQUES CLEMENTE</t>
+            <t xml:space="preserve">NASCIMENTO DOS REIS GONDIN</t>
           </r>
         </is>
       </c>
@@ -32198,7 +32198,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">105.427.006-62</t>
+            <t xml:space="preserve">761.988.636-20</t>
           </r>
         </is>
       </c>
@@ -32208,7 +32208,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08144307204</t>
+            <t xml:space="preserve">00900948176</t>
           </r>
         </is>
       </c>
@@ -32219,7 +32219,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -32267,7 +32267,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NAUBERT MARCELO SOUZA XAVIER</t>
+            <t xml:space="preserve">NATALIA MARQUES CLEMENTE</t>
           </r>
         </is>
       </c>
@@ -32277,7 +32277,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">102.231.886-11</t>
+            <t xml:space="preserve">105.427.006-62</t>
           </r>
         </is>
       </c>
@@ -32287,7 +32287,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06564062300</t>
+            <t xml:space="preserve">08144307204</t>
           </r>
         </is>
       </c>
@@ -32298,7 +32298,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -32339,14 +32339,14 @@
       <c r="T407" s="12" t="inlineStr"/>
       <c r="U407" s="1" t="inlineStr"/>
     </row>
-    <row r="408" customHeight="1" ht="22">
+    <row r="408" customHeight="1" ht="21">
       <c r="A408" s="1" t="inlineStr"/>
       <c r="B408" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NAYARA TARCIA PENIDO GUIMARAES</t>
+            <t xml:space="preserve">NAUBERT MARCELO SOUZA XAVIER</t>
           </r>
         </is>
       </c>
@@ -32356,7 +32356,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.418.096-47</t>
+            <t xml:space="preserve">102.231.886-11</t>
           </r>
         </is>
       </c>
@@ -32366,7 +32366,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04386747420</t>
+            <t xml:space="preserve">06564062300</t>
           </r>
         </is>
       </c>
@@ -32377,7 +32377,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -32418,14 +32418,14 @@
       <c r="T408" s="12" t="inlineStr"/>
       <c r="U408" s="1" t="inlineStr"/>
     </row>
-    <row r="409" customHeight="1" ht="21">
+    <row r="409" customHeight="1" ht="22">
       <c r="A409" s="1" t="inlineStr"/>
       <c r="B409" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NEIMAR RICARDO PEREIRA</t>
+            <t xml:space="preserve">NAYARA TARCIA PENIDO GUIMARAES</t>
           </r>
         </is>
       </c>
@@ -32435,7 +32435,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">089.354.186-92</t>
+            <t xml:space="preserve">088.418.096-47</t>
           </r>
         </is>
       </c>
@@ -32445,7 +32445,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03994374484</t>
+            <t xml:space="preserve">04386747420</t>
           </r>
         </is>
       </c>
@@ -32456,7 +32456,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -32504,7 +32504,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NELSON ESTEVAM CAETANO</t>
+            <t xml:space="preserve">NEIMAR RICARDO PEREIRA</t>
           </r>
         </is>
       </c>
@@ -32514,7 +32514,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">786.778.316-49</t>
+            <t xml:space="preserve">089.354.186-92</t>
           </r>
         </is>
       </c>
@@ -32524,7 +32524,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00970062398</t>
+            <t xml:space="preserve">03994374484</t>
           </r>
         </is>
       </c>
@@ -32535,7 +32535,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -32583,7 +32583,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NERILTON RODRIGUES DE LIMA</t>
+            <t xml:space="preserve">NELSON ESTEVAM CAETANO</t>
           </r>
         </is>
       </c>
@@ -32593,7 +32593,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">639.992.936-91</t>
+            <t xml:space="preserve">786.778.316-49</t>
           </r>
         </is>
       </c>
@@ -32603,7 +32603,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03027917140</t>
+            <t xml:space="preserve">00970062398</t>
           </r>
         </is>
       </c>
@@ -32614,7 +32614,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -32662,7 +32662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NILSON FERNANDES DE OLIVEIRA</t>
+            <t xml:space="preserve">NERILTON RODRIGUES DE LIMA</t>
           </r>
         </is>
       </c>
@@ -32672,7 +32672,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">968.600.146-87</t>
+            <t xml:space="preserve">639.992.936-91</t>
           </r>
         </is>
       </c>
@@ -32682,7 +32682,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00910443480</t>
+            <t xml:space="preserve">03027917140</t>
           </r>
         </is>
       </c>
@@ -32693,7 +32693,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -32741,7 +32741,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NILTON CESAR DOS SANTOS</t>
+            <t xml:space="preserve">NILSON FERNANDES DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -32751,7 +32751,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">575.710.905-04</t>
+            <t xml:space="preserve">968.600.146-87</t>
           </r>
         </is>
       </c>
@@ -32761,7 +32761,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">005560025786</t>
+            <t xml:space="preserve">00910443480</t>
           </r>
         </is>
       </c>
@@ -32772,7 +32772,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -32820,7 +32820,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODAIR JOSE BELTOLDO</t>
+            <t xml:space="preserve">NILTON CESAR DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -32830,7 +32830,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">004.220.596-41</t>
+            <t xml:space="preserve">575.710.905-04</t>
           </r>
         </is>
       </c>
@@ -32840,7 +32840,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01148775390</t>
+            <t xml:space="preserve">005560025786</t>
           </r>
         </is>
       </c>
@@ -32851,7 +32851,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -32899,7 +32899,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODAIR JOSE DE ALMEIDA</t>
+            <t xml:space="preserve">ODAIR JOSE BELTOLDO</t>
           </r>
         </is>
       </c>
@@ -32909,7 +32909,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">000.451.336-38</t>
+            <t xml:space="preserve">004.220.596-41</t>
           </r>
         </is>
       </c>
@@ -32919,7 +32919,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03494010309</t>
+            <t xml:space="preserve">01148775390</t>
           </r>
         </is>
       </c>
@@ -32930,7 +32930,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -32978,7 +32978,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODICE DUTRA DOS REIS</t>
+            <t xml:space="preserve">ODAIR JOSE DE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -32988,7 +32988,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">754.948.256-04</t>
+            <t xml:space="preserve">000.451.336-38</t>
           </r>
         </is>
       </c>
@@ -32998,7 +32998,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01734148835</t>
+            <t xml:space="preserve">03494010309</t>
           </r>
         </is>
       </c>
@@ -33009,7 +33009,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -33057,7 +33057,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ORLANDO AGOSTINHO PINTO</t>
+            <t xml:space="preserve">ODICE DUTRA DOS REIS</t>
           </r>
         </is>
       </c>
@@ -33067,7 +33067,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">006.413.446-60</t>
+            <t xml:space="preserve">754.948.256-04</t>
           </r>
         </is>
       </c>
@@ -33077,7 +33077,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02745787040</t>
+            <t xml:space="preserve">01734148835</t>
           </r>
         </is>
       </c>
@@ -33088,7 +33088,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -33136,7 +33136,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALDO ARLINDO DE MEIRA</t>
+            <t xml:space="preserve">ORLANDO AGOSTINHO PINTO</t>
           </r>
         </is>
       </c>
@@ -33146,7 +33146,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.805.766-60</t>
+            <t xml:space="preserve">006.413.446-60</t>
           </r>
         </is>
       </c>
@@ -33156,7 +33156,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03105139100</t>
+            <t xml:space="preserve">02745787040</t>
           </r>
         </is>
       </c>
@@ -33167,7 +33167,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -33215,7 +33215,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALDO COELHO DE MORAES</t>
+            <t xml:space="preserve">OSVALDO ARLINDO DE MEIRA</t>
           </r>
         </is>
       </c>
@@ -33225,7 +33225,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">545.222.186-72</t>
+            <t xml:space="preserve">051.805.766-60</t>
           </r>
         </is>
       </c>
@@ -33235,7 +33235,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03759063307</t>
+            <t xml:space="preserve">03105139100</t>
           </r>
         </is>
       </c>
@@ -33246,7 +33246,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -33294,7 +33294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSWALDO DOS SANTOS JUNIOR</t>
+            <t xml:space="preserve">OSVALDO COELHO DE MORAES</t>
           </r>
         </is>
       </c>
@@ -33304,7 +33304,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">892.492.326-91</t>
+            <t xml:space="preserve">545.222.186-72</t>
           </r>
         </is>
       </c>
@@ -33314,7 +33314,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00822357647</t>
+            <t xml:space="preserve">03759063307</t>
           </r>
         </is>
       </c>
@@ -33325,7 +33325,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -33373,7 +33373,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OTAVIO MOURA SILVA</t>
+            <t xml:space="preserve">OSVALMIR CLEITON GOMES</t>
           </r>
         </is>
       </c>
@@ -33383,7 +33383,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">116.799.556-24</t>
+            <t xml:space="preserve">126.795.126-50</t>
           </r>
         </is>
       </c>
@@ -33393,7 +33393,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06947671960</t>
+            <t xml:space="preserve">05485955266</t>
           </r>
         </is>
       </c>
@@ -33404,7 +33404,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02/07/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -33452,7 +33452,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OZIAS ROSA NUNES DA SILVA</t>
+            <t xml:space="preserve">OSWALDO DOS SANTOS JUNIOR</t>
           </r>
         </is>
       </c>
@@ -33462,7 +33462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.717.456-17</t>
+            <t xml:space="preserve">892.492.326-91</t>
           </r>
         </is>
       </c>
@@ -33472,7 +33472,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02844195589</t>
+            <t xml:space="preserve">00822357647</t>
           </r>
         </is>
       </c>
@@ -33531,7 +33531,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PABLO NOE LANA</t>
+            <t xml:space="preserve">OTAVIO MOURA SILVA</t>
           </r>
         </is>
       </c>
@@ -33541,7 +33541,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.279.556-33</t>
+            <t xml:space="preserve">116.799.556-24</t>
           </r>
         </is>
       </c>
@@ -33551,7 +33551,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03371448607</t>
+            <t xml:space="preserve">06947671960</t>
           </r>
         </is>
       </c>
@@ -33562,7 +33562,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">02/07/2027</t>
           </r>
         </is>
       </c>
@@ -33610,7 +33610,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PABLO VINICIO MARQUES DA SILVA</t>
+            <t xml:space="preserve">OZIAS ROSA NUNES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33620,7 +33620,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">125.648.656-66</t>
+            <t xml:space="preserve">051.717.456-17</t>
           </r>
         </is>
       </c>
@@ -33630,7 +33630,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06041166234</t>
+            <t xml:space="preserve">02844195589</t>
           </r>
         </is>
       </c>
@@ -33641,7 +33641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -33689,7 +33689,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO FERNANDES MACHADO</t>
+            <t xml:space="preserve">PABLO NOE LANA</t>
           </r>
         </is>
       </c>
@@ -33699,7 +33699,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">646.984.836-20</t>
+            <t xml:space="preserve">040.279.556-33</t>
           </r>
         </is>
       </c>
@@ -33709,7 +33709,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00437370810</t>
+            <t xml:space="preserve">03371448607</t>
           </r>
         </is>
       </c>
@@ -33720,7 +33720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -33768,7 +33768,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO HENRIQUE DA SILVA</t>
+            <t xml:space="preserve">PABLO VINICIO MARQUES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33778,7 +33778,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">145.560.786-01</t>
+            <t xml:space="preserve">125.648.656-66</t>
           </r>
         </is>
       </c>
@@ -33788,7 +33788,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06876540658</t>
+            <t xml:space="preserve">06041166234</t>
           </r>
         </is>
       </c>
@@ -33799,7 +33799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/10/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -33840,14 +33840,14 @@
       <c r="T426" s="12" t="inlineStr"/>
       <c r="U426" s="1" t="inlineStr"/>
     </row>
-    <row r="427" customHeight="1" ht="22">
+    <row r="427" customHeight="1" ht="21">
       <c r="A427" s="1" t="inlineStr"/>
       <c r="B427" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO HENRIQUE SILVA APOLINARIO</t>
+            <t xml:space="preserve">PAULO FERNANDES MACHADO</t>
           </r>
         </is>
       </c>
@@ -33857,7 +33857,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">078.119.326-52</t>
+            <t xml:space="preserve">646.984.836-20</t>
           </r>
         </is>
       </c>
@@ -33867,7 +33867,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04058607086</t>
+            <t xml:space="preserve">00437370810</t>
           </r>
         </is>
       </c>
@@ -33878,7 +33878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/09/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -33926,7 +33926,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO JOSE DO NASCIMENTO </t>
+            <t xml:space="preserve">PAULO HENRIQUE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33936,7 +33936,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">632.040.456-68</t>
+            <t xml:space="preserve">145.560.786-01</t>
           </r>
         </is>
       </c>
@@ -33946,7 +33946,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02867848381</t>
+            <t xml:space="preserve">06876540658</t>
           </r>
         </is>
       </c>
@@ -33957,7 +33957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/07/2030</t>
+            <t xml:space="preserve">05/10/2027</t>
           </r>
         </is>
       </c>
@@ -33998,14 +33998,14 @@
       <c r="T428" s="12" t="inlineStr"/>
       <c r="U428" s="1" t="inlineStr"/>
     </row>
-    <row r="429" customHeight="1" ht="21">
+    <row r="429" customHeight="1" ht="22">
       <c r="A429" s="1" t="inlineStr"/>
       <c r="B429" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO MARCIO FERREIRA</t>
+            <t xml:space="preserve">PAULO HENRIQUE SILVA APOLINARIO</t>
           </r>
         </is>
       </c>
@@ -34015,7 +34015,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">927.606.946-15</t>
+            <t xml:space="preserve">078.119.326-52</t>
           </r>
         </is>
       </c>
@@ -34025,7 +34025,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02635238806</t>
+            <t xml:space="preserve">04058607086</t>
           </r>
         </is>
       </c>
@@ -34036,7 +34036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">08/09/2027</t>
           </r>
         </is>
       </c>
@@ -34084,7 +34084,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO SERGIO DA CRUZ</t>
+            <t xml:space="preserve">PAULO JOSE DO NASCIMENTO </t>
           </r>
         </is>
       </c>
@@ -34094,7 +34094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">746.204.526-53</t>
+            <t xml:space="preserve">632.040.456-68</t>
           </r>
         </is>
       </c>
@@ -34104,7 +34104,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01934028430</t>
+            <t xml:space="preserve">02867848381</t>
           </r>
         </is>
       </c>
@@ -34115,7 +34115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/07/2027</t>
+            <t xml:space="preserve">30/07/2030</t>
           </r>
         </is>
       </c>
@@ -34163,7 +34163,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO SERGIO DA CUNHA</t>
+            <t xml:space="preserve">PAULO MARCIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -34173,7 +34173,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">003.102.236-79</t>
+            <t xml:space="preserve">927.606.946-15</t>
           </r>
         </is>
       </c>
@@ -34183,7 +34183,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04344405135</t>
+            <t xml:space="preserve">02635238806</t>
           </r>
         </is>
       </c>
@@ -34194,7 +34194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -34242,7 +34242,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO ANTONIO BENTO</t>
+            <t xml:space="preserve">PAULO SERGIO DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -34252,7 +34252,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">493.901.636-68</t>
+            <t xml:space="preserve">746.204.526-53</t>
           </r>
         </is>
       </c>
@@ -34262,7 +34262,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00694729250</t>
+            <t xml:space="preserve">01934028430</t>
           </r>
         </is>
       </c>
@@ -34273,7 +34273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2026</t>
+            <t xml:space="preserve">04/07/2027</t>
           </r>
         </is>
       </c>
@@ -34314,14 +34314,14 @@
       <c r="T432" s="12" t="inlineStr"/>
       <c r="U432" s="1" t="inlineStr"/>
     </row>
-    <row r="433" customHeight="1" ht="22">
+    <row r="433" customHeight="1" ht="21">
       <c r="A433" s="1" t="inlineStr"/>
       <c r="B433" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE ANTUNES MORAIS</t>
+            <t xml:space="preserve">PAULO SERGIO DA CUNHA</t>
           </r>
         </is>
       </c>
@@ -34331,7 +34331,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">124.819.026-29</t>
+            <t xml:space="preserve">003.102.236-79</t>
           </r>
         </is>
       </c>
@@ -34341,7 +34341,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06571602700</t>
+            <t xml:space="preserve">04344405135</t>
           </r>
         </is>
       </c>
@@ -34352,7 +34352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -34393,14 +34393,14 @@
       <c r="T433" s="12" t="inlineStr"/>
       <c r="U433" s="1" t="inlineStr"/>
     </row>
-    <row r="434" customHeight="1" ht="22">
+    <row r="434" customHeight="1" ht="21">
       <c r="A434" s="1" t="inlineStr"/>
       <c r="B434" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE RESENDE MAGALHAES FARINHA</t>
+            <t xml:space="preserve">PEDRO ANTONIO BENTO</t>
           </r>
         </is>
       </c>
@@ -34410,7 +34410,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.378.606-75</t>
+            <t xml:space="preserve">493.901.636-68</t>
           </r>
         </is>
       </c>
@@ -34420,7 +34420,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06845908627</t>
+            <t xml:space="preserve">00694729250</t>
           </r>
         </is>
       </c>
@@ -34431,7 +34431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">29/07/2026</t>
           </r>
         </is>
       </c>
@@ -34479,7 +34479,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE SILVERIO MARTINS VIEIRA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE ANTUNES MORAIS</t>
           </r>
         </is>
       </c>
@@ -34489,7 +34489,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.281.606-32</t>
+            <t xml:space="preserve">124.819.026-29</t>
           </r>
         </is>
       </c>
@@ -34499,7 +34499,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03691532816</t>
+            <t xml:space="preserve">06571602700</t>
           </r>
         </is>
       </c>
@@ -34510,7 +34510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -34558,7 +34558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE TORRES MARTINS </t>
+            <t xml:space="preserve">PEDRO HENRIQUE RESENDE MAGALHAES FARINHA</t>
           </r>
         </is>
       </c>
@@ -34568,7 +34568,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">156.289.896-57</t>
+            <t xml:space="preserve">110.378.606-75</t>
           </r>
         </is>
       </c>
@@ -34578,7 +34578,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08127162566</t>
+            <t xml:space="preserve">06845908627</t>
           </r>
         </is>
       </c>
@@ -34589,7 +34589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -34630,14 +34630,14 @@
       <c r="T436" s="12" t="inlineStr"/>
       <c r="U436" s="1" t="inlineStr"/>
     </row>
-    <row r="437" customHeight="1" ht="21">
+    <row r="437" customHeight="1" ht="22">
       <c r="A437" s="1" t="inlineStr"/>
       <c r="B437" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO RODRIGUES DE PAULA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE SILVERIO MARTINS VIEIRA</t>
           </r>
         </is>
       </c>
@@ -34647,7 +34647,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">578.466.186-87</t>
+            <t xml:space="preserve">088.281.606-32</t>
           </r>
         </is>
       </c>
@@ -34657,7 +34657,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01168973776</t>
+            <t xml:space="preserve">03691532816</t>
           </r>
         </is>
       </c>
@@ -34668,7 +34668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2025</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -34709,14 +34709,14 @@
       <c r="T437" s="12" t="inlineStr"/>
       <c r="U437" s="1" t="inlineStr"/>
     </row>
-    <row r="438" customHeight="1" ht="21">
+    <row r="438" customHeight="1" ht="22">
       <c r="A438" s="1" t="inlineStr"/>
       <c r="B438" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO RODRIGUES PEREIRA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE TORRES MARTINS </t>
           </r>
         </is>
       </c>
@@ -34726,7 +34726,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">095.236.816-13</t>
+            <t xml:space="preserve">156.289.896-57</t>
           </r>
         </is>
       </c>
@@ -34736,7 +34736,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04944405662</t>
+            <t xml:space="preserve">08127162566</t>
           </r>
         </is>
       </c>
@@ -34747,7 +34747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -34795,7 +34795,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PLINIO RAFAEL ANDRADE</t>
+            <t xml:space="preserve">PEDRO RODRIGUES DE PAULA</t>
           </r>
         </is>
       </c>
@@ -34805,7 +34805,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">098.676.626-79</t>
+            <t xml:space="preserve">578.466.186-87</t>
           </r>
         </is>
       </c>
@@ -34815,7 +34815,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04903258724</t>
+            <t xml:space="preserve">01168973776</t>
           </r>
         </is>
       </c>
@@ -34826,7 +34826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">31/07/2025</t>
           </r>
         </is>
       </c>
@@ -34874,7 +34874,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PRISCILA SILVA LACERDA</t>
+            <t xml:space="preserve">PEDRO RODRIGUES PEREIRA</t>
           </r>
         </is>
       </c>
@@ -34884,7 +34884,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">066.424.716-44</t>
+            <t xml:space="preserve">095.236.816-13</t>
           </r>
         </is>
       </c>
@@ -34894,7 +34894,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02895817906</t>
+            <t xml:space="preserve">04944405662</t>
           </r>
         </is>
       </c>
@@ -34905,7 +34905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/11/2026</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -34953,7 +34953,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAEL FERREIRA MARTINS</t>
+            <t xml:space="preserve">PLINIO RAFAEL ANDRADE</t>
           </r>
         </is>
       </c>
@@ -34963,7 +34963,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.733.626-84</t>
+            <t xml:space="preserve">098.676.626-79</t>
           </r>
         </is>
       </c>
@@ -34973,7 +34973,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05713407303</t>
+            <t xml:space="preserve">04903258724</t>
           </r>
         </is>
       </c>
@@ -34984,7 +34984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">28/07/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -35032,7 +35032,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL COIMBRA GONTIJO</t>
+            <t xml:space="preserve">PRISCILA SILVA LACERDA</t>
           </r>
         </is>
       </c>
@@ -35042,7 +35042,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.055.666-60</t>
+            <t xml:space="preserve">066.424.716-44</t>
           </r>
         </is>
       </c>
@@ -35052,7 +35052,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05538775609</t>
+            <t xml:space="preserve">02895817906</t>
           </r>
         </is>
       </c>
@@ -35063,7 +35063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">26/11/2026</t>
           </r>
         </is>
       </c>
@@ -35104,14 +35104,14 @@
       <c r="T442" s="12" t="inlineStr"/>
       <c r="U442" s="1" t="inlineStr"/>
     </row>
-    <row r="443" customHeight="1" ht="22">
+    <row r="443" customHeight="1" ht="21">
       <c r="A443" s="1" t="inlineStr"/>
       <c r="B443" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL MATHEUS MARTINS COELHO </t>
+            <t xml:space="preserve">RAEL FERREIRA MARTINS</t>
           </r>
         </is>
       </c>
@@ -35121,7 +35121,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">147.684.866-14</t>
+            <t xml:space="preserve">122.733.626-84</t>
           </r>
         </is>
       </c>
@@ -35131,7 +35131,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07093318680</t>
+            <t xml:space="preserve">05713407303</t>
           </r>
         </is>
       </c>
@@ -35142,7 +35142,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">28/07/2026</t>
           </r>
         </is>
       </c>
@@ -35190,7 +35190,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL MORAES BARBOSA</t>
+            <t xml:space="preserve">RAFAEL COIMBRA GONTIJO</t>
           </r>
         </is>
       </c>
@@ -35200,7 +35200,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.669.666-27</t>
+            <t xml:space="preserve">065.055.666-60</t>
           </r>
         </is>
       </c>
@@ -35210,7 +35210,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05783669254</t>
+            <t xml:space="preserve">05538775609</t>
           </r>
         </is>
       </c>
@@ -35221,7 +35221,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/07/2027</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -35262,14 +35262,14 @@
       <c r="T444" s="12" t="inlineStr"/>
       <c r="U444" s="1" t="inlineStr"/>
     </row>
-    <row r="445" customHeight="1" ht="21">
+    <row r="445" customHeight="1" ht="22">
       <c r="A445" s="1" t="inlineStr"/>
       <c r="B445" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL SOUZA REZENDE ROCHA</t>
+            <t xml:space="preserve">RAFAEL MATHEUS MARTINS COELHO </t>
           </r>
         </is>
       </c>
@@ -35279,7 +35279,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.998.096-27</t>
+            <t xml:space="preserve">147.684.866-14</t>
           </r>
         </is>
       </c>
@@ -35289,7 +35289,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06443469242</t>
+            <t xml:space="preserve">07093318680</t>
           </r>
         </is>
       </c>
@@ -35300,7 +35300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/05/2026</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -35348,7 +35348,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAELA GONÇALVES DA SILVA</t>
+            <t xml:space="preserve">RAFAEL MORAES BARBOSA</t>
           </r>
         </is>
       </c>
@@ -35358,7 +35358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">097.757.966-28</t>
+            <t xml:space="preserve">070.669.666-27</t>
           </r>
         </is>
       </c>
@@ -35368,7 +35368,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05193246932</t>
+            <t xml:space="preserve">05783669254</t>
           </r>
         </is>
       </c>
@@ -35379,7 +35379,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">18/07/2027</t>
           </r>
         </is>
       </c>
@@ -35427,7 +35427,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAIMUNDO CAMILO DA SILVA NETO</t>
+            <t xml:space="preserve">RAFAEL SOUZA REZENDE ROCHA</t>
           </r>
         </is>
       </c>
@@ -35437,7 +35437,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">736.682.906-44</t>
+            <t xml:space="preserve">122.998.096-27</t>
           </r>
         </is>
       </c>
@@ -35447,7 +35447,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00628460620</t>
+            <t xml:space="preserve">06443469242</t>
           </r>
         </is>
       </c>
@@ -35458,7 +35458,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">14/05/2026</t>
           </r>
         </is>
       </c>
@@ -35506,7 +35506,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAIMUNDO NONATO DOS REIS</t>
+            <t xml:space="preserve">RAFAELA GONÇALVES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -35516,7 +35516,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">520.482.176-72</t>
+            <t xml:space="preserve">097.757.966-28</t>
           </r>
         </is>
       </c>
@@ -35526,7 +35526,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02656000194</t>
+            <t xml:space="preserve">05193246932</t>
           </r>
         </is>
       </c>
@@ -35537,7 +35537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -35585,7 +35585,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAMON HENRIQUE DA SILVA</t>
+            <t xml:space="preserve">RAIMUNDO CAMILO DA SILVA NETO</t>
           </r>
         </is>
       </c>
@@ -35595,7 +35595,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.806.026-33</t>
+            <t xml:space="preserve">736.682.906-44</t>
           </r>
         </is>
       </c>
@@ -35605,7 +35605,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04113942460</t>
+            <t xml:space="preserve">00628460620</t>
           </r>
         </is>
       </c>
@@ -35616,7 +35616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/01/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -35657,14 +35657,14 @@
       <c r="T449" s="12" t="inlineStr"/>
       <c r="U449" s="1" t="inlineStr"/>
     </row>
-    <row r="450" customHeight="1" ht="22">
+    <row r="450" customHeight="1" ht="21">
       <c r="A450" s="1" t="inlineStr"/>
       <c r="B450" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAMON WEMERSON VELOSO TEIXEIRA</t>
+            <t xml:space="preserve">RAIMUNDO NONATO DOS REIS</t>
           </r>
         </is>
       </c>
@@ -35674,7 +35674,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">099.777.116-07</t>
+            <t xml:space="preserve">520.482.176-72</t>
           </r>
         </is>
       </c>
@@ -35684,7 +35684,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04970737232</t>
+            <t xml:space="preserve">02656000194</t>
           </r>
         </is>
       </c>
@@ -35695,7 +35695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -35736,14 +35736,14 @@
       <c r="T450" s="12" t="inlineStr"/>
       <c r="U450" s="1" t="inlineStr"/>
     </row>
-    <row r="451" customHeight="1" ht="22">
+    <row r="451" customHeight="1" ht="21">
       <c r="A451" s="1" t="inlineStr"/>
       <c r="B451" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RANIEL ROMERICK LIMA DE OLIVEIRA</t>
+            <t xml:space="preserve">RAMON HENRIQUE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -35753,7 +35753,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.580.076-05</t>
+            <t xml:space="preserve">079.806.026-33</t>
           </r>
         </is>
       </c>
@@ -35763,7 +35763,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05302294379</t>
+            <t xml:space="preserve">04113942460</t>
           </r>
         </is>
       </c>
@@ -35774,7 +35774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">22/01/2027</t>
           </r>
         </is>
       </c>
@@ -35815,14 +35815,14 @@
       <c r="T451" s="12" t="inlineStr"/>
       <c r="U451" s="1" t="inlineStr"/>
     </row>
-    <row r="452" customHeight="1" ht="21">
+    <row r="452" customHeight="1" ht="22">
       <c r="A452" s="1" t="inlineStr"/>
       <c r="B452" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAPHAEL HENRIQUE ROCHA SILVA</t>
+            <t xml:space="preserve">RAMON WEMERSON VELOSO TEIXEIRA</t>
           </r>
         </is>
       </c>
@@ -35832,7 +35832,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">100.372.356-05</t>
+            <t xml:space="preserve">099.777.116-07</t>
           </r>
         </is>
       </c>
@@ -35842,7 +35842,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05480849132</t>
+            <t xml:space="preserve">04970737232</t>
           </r>
         </is>
       </c>
@@ -35853,7 +35853,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -35894,14 +35894,14 @@
       <c r="T452" s="12" t="inlineStr"/>
       <c r="U452" s="1" t="inlineStr"/>
     </row>
-    <row r="453" customHeight="1" ht="21">
+    <row r="453" customHeight="1" ht="22">
       <c r="A453" s="1" t="inlineStr"/>
       <c r="B453" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAVENGAR NUNES DE OLIVEIRA</t>
+            <t xml:space="preserve">RANIEL ROMERICK LIMA DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -35911,7 +35911,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">087.922.076-77</t>
+            <t xml:space="preserve">093.580.076-05</t>
           </r>
         </is>
       </c>
@@ -35921,7 +35921,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04161596624</t>
+            <t xml:space="preserve">05302294379</t>
           </r>
         </is>
       </c>
@@ -35932,7 +35932,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/07/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -35980,7 +35980,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO EUSTAQUIO ALVES</t>
+            <t xml:space="preserve">RAPHAEL HENRIQUE ROCHA SILVA</t>
           </r>
         </is>
       </c>
@@ -35990,7 +35990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.746.886-98</t>
+            <t xml:space="preserve">100.372.356-05</t>
           </r>
         </is>
       </c>
@@ -36000,7 +36000,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02942466380</t>
+            <t xml:space="preserve">05480849132</t>
           </r>
         </is>
       </c>
@@ -36011,7 +36011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -36059,7 +36059,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO GOMES DOS SANTOS</t>
+            <t xml:space="preserve">RAVENGAR NUNES DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -36069,7 +36069,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.934.616-71</t>
+            <t xml:space="preserve">087.922.076-77</t>
           </r>
         </is>
       </c>
@@ -36079,7 +36079,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03466250864</t>
+            <t xml:space="preserve">04161596624</t>
           </r>
         </is>
       </c>
@@ -36090,7 +36090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/11/2026</t>
+            <t xml:space="preserve">21/07/2027</t>
           </r>
         </is>
       </c>
@@ -36138,7 +36138,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO VICENTINO DE PAULA</t>
+            <t xml:space="preserve">REGINALDO EUSTAQUIO ALVES</t>
           </r>
         </is>
       </c>
@@ -36148,7 +36148,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">062.303.156-61</t>
+            <t xml:space="preserve">046.746.886-98</t>
           </r>
         </is>
       </c>
@@ -36158,7 +36158,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07456908970</t>
+            <t xml:space="preserve">02942466380</t>
           </r>
         </is>
       </c>
@@ -36169,7 +36169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -36217,7 +36217,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RENAN REZENDE DA CRUZ</t>
+            <t xml:space="preserve">REGINALDO GOMES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -36227,7 +36227,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">068.003.286-00</t>
+            <t xml:space="preserve">061.934.616-71</t>
           </r>
         </is>
       </c>
@@ -36237,7 +36237,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04461438210</t>
+            <t xml:space="preserve">03466250864</t>
           </r>
         </is>
       </c>
@@ -36248,7 +36248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">25/11/2026</t>
           </r>
         </is>
       </c>
@@ -36289,14 +36289,14 @@
       <c r="T457" s="12" t="inlineStr"/>
       <c r="U457" s="1" t="inlineStr"/>
     </row>
-    <row r="458" customHeight="1" ht="22">
+    <row r="458" customHeight="1" ht="21">
       <c r="A458" s="1" t="inlineStr"/>
       <c r="B458" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RENATO MARTINS DA SILVA GOUVEIA</t>
+            <t xml:space="preserve">REGINALDO VICENTINO DE PAULA</t>
           </r>
         </is>
       </c>
@@ -36306,7 +36306,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">045.158.916-50</t>
+            <t xml:space="preserve">062.303.156-61</t>
           </r>
         </is>
       </c>
@@ -36316,7 +36316,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00796571668</t>
+            <t xml:space="preserve">07456908970</t>
           </r>
         </is>
       </c>
@@ -36327,7 +36327,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/08/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -36375,7 +36375,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RICARDO SOUZA MARINHO</t>
+            <t xml:space="preserve">RENAN REZENDE DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -36385,7 +36385,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">683.789.476-53</t>
+            <t xml:space="preserve">068.003.286-00</t>
           </r>
         </is>
       </c>
@@ -36395,7 +36395,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02561487470</t>
+            <t xml:space="preserve">04461438210</t>
           </r>
         </is>
       </c>
@@ -36406,7 +36406,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/12/2025</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -36454,7 +36454,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RICHARD HENRIQUE DE OLIVEIRA MACHADO</t>
+            <t xml:space="preserve">RENATO MARTINS DA SILVA GOUVEIA</t>
           </r>
         </is>
       </c>
@@ -36464,7 +36464,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">020.089.536-29</t>
+            <t xml:space="preserve">045.158.916-50</t>
           </r>
         </is>
       </c>
@@ -36474,7 +36474,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07127361656</t>
+            <t xml:space="preserve">00796571668</t>
           </r>
         </is>
       </c>
@@ -36485,7 +36485,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/11/2026</t>
+            <t xml:space="preserve">24/08/2027</t>
           </r>
         </is>
       </c>
@@ -36526,14 +36526,14 @@
       <c r="T460" s="12" t="inlineStr"/>
       <c r="U460" s="1" t="inlineStr"/>
     </row>
-    <row r="461" customHeight="1" ht="22">
+    <row r="461" customHeight="1" ht="21">
       <c r="A461" s="1" t="inlineStr"/>
       <c r="B461" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERT WILLIAM MARCELINO DE O PEREIRA </t>
+            <t xml:space="preserve">RICARDO SOUZA MARINHO</t>
           </r>
         </is>
       </c>
@@ -36543,7 +36543,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">143.991.156-88</t>
+            <t xml:space="preserve">683.789.476-53</t>
           </r>
         </is>
       </c>
@@ -36553,7 +36553,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06651427733</t>
+            <t xml:space="preserve">02561487470</t>
           </r>
         </is>
       </c>
@@ -36564,7 +36564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">18/12/2025</t>
           </r>
         </is>
       </c>
@@ -36605,14 +36605,14 @@
       <c r="T461" s="12" t="inlineStr"/>
       <c r="U461" s="1" t="inlineStr"/>
     </row>
-    <row r="462" customHeight="1" ht="21">
+    <row r="462" customHeight="1" ht="22">
       <c r="A462" s="1" t="inlineStr"/>
       <c r="B462" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO CIRENO DE PAULA</t>
+            <t xml:space="preserve">RICHARD HENRIQUE DE OLIVEIRA MACHADO</t>
           </r>
         </is>
       </c>
@@ -36622,7 +36622,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">673.187.626-72</t>
+            <t xml:space="preserve">020.089.536-29</t>
           </r>
         </is>
       </c>
@@ -36632,7 +36632,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01720717152</t>
+            <t xml:space="preserve">07127361656</t>
           </r>
         </is>
       </c>
@@ -36643,7 +36643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">25/11/2026</t>
           </r>
         </is>
       </c>
@@ -36684,14 +36684,14 @@
       <c r="T462" s="12" t="inlineStr"/>
       <c r="U462" s="1" t="inlineStr"/>
     </row>
-    <row r="463" customHeight="1" ht="21">
+    <row r="463" customHeight="1" ht="22">
       <c r="A463" s="1" t="inlineStr"/>
       <c r="B463" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO FLAVIO DA COSTA</t>
+            <t xml:space="preserve">ROBERT WILLIAM MARCELINO DE O PEREIRA </t>
           </r>
         </is>
       </c>
@@ -36701,7 +36701,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">610.846.036-91</t>
+            <t xml:space="preserve">143.991.156-88</t>
           </r>
         </is>
       </c>
@@ -36711,7 +36711,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02293916183</t>
+            <t xml:space="preserve">06651427733</t>
           </r>
         </is>
       </c>
@@ -36722,7 +36722,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -36770,7 +36770,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO MOZART SANTANA</t>
+            <t xml:space="preserve">ROBERTO CIRENO DE PAULA</t>
           </r>
         </is>
       </c>
@@ -36780,7 +36780,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.939.556-34</t>
+            <t xml:space="preserve">673.187.626-72</t>
           </r>
         </is>
       </c>
@@ -36790,7 +36790,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02429053892</t>
+            <t xml:space="preserve">01720717152</t>
           </r>
         </is>
       </c>
@@ -36801,7 +36801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -36849,7 +36849,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON CAMILO DE OLIVEIRA</t>
+            <t xml:space="preserve">ROBERTO FLAVIO DA COSTA</t>
           </r>
         </is>
       </c>
@@ -36859,7 +36859,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.438.436-18</t>
+            <t xml:space="preserve">610.846.036-91</t>
           </r>
         </is>
       </c>
@@ -36869,7 +36869,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03133712661</t>
+            <t xml:space="preserve">02293916183</t>
           </r>
         </is>
       </c>
@@ -36880,7 +36880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -36921,14 +36921,14 @@
       <c r="T465" s="12" t="inlineStr"/>
       <c r="U465" s="1" t="inlineStr"/>
     </row>
-    <row r="466" customHeight="1" ht="22">
+    <row r="466" customHeight="1" ht="21">
       <c r="A466" s="1" t="inlineStr"/>
       <c r="B466" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON DOS SANTOS DE REZENDE</t>
+            <t xml:space="preserve">ROBERTO MOZART SANTANA</t>
           </r>
         </is>
       </c>
@@ -36938,7 +36938,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.387.886-66</t>
+            <t xml:space="preserve">868.939.556-34</t>
           </r>
         </is>
       </c>
@@ -36948,7 +36948,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04356240900</t>
+            <t xml:space="preserve">02429053892</t>
           </r>
         </is>
       </c>
@@ -36959,7 +36959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -37007,7 +37007,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON FERREIRA COSTA</t>
+            <t xml:space="preserve">ROBSON CAMILO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -37017,7 +37017,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">986.658.396-15</t>
+            <t xml:space="preserve">070.438.436-18</t>
           </r>
         </is>
       </c>
@@ -37027,7 +37027,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">019790492230</t>
+            <t xml:space="preserve">03133712661</t>
           </r>
         </is>
       </c>
@@ -37038,7 +37038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/12/2026</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -37079,14 +37079,14 @@
       <c r="T467" s="12" t="inlineStr"/>
       <c r="U467" s="1" t="inlineStr"/>
     </row>
-    <row r="468" customHeight="1" ht="21">
+    <row r="468" customHeight="1" ht="22">
       <c r="A468" s="1" t="inlineStr"/>
       <c r="B468" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO CESARIO DANTAS</t>
+            <t xml:space="preserve">ROBSON DOS SANTOS DE REZENDE</t>
           </r>
         </is>
       </c>
@@ -37096,7 +37096,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">062.821.666-16</t>
+            <t xml:space="preserve">077.387.886-66</t>
           </r>
         </is>
       </c>
@@ -37106,7 +37106,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02818805407</t>
+            <t xml:space="preserve">04356240900</t>
           </r>
         </is>
       </c>
@@ -37165,7 +37165,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO DA COSTA RAMOS</t>
+            <t xml:space="preserve">ROBSON FERREIRA COSTA</t>
           </r>
         </is>
       </c>
@@ -37175,7 +37175,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.330.686-85</t>
+            <t xml:space="preserve">986.658.396-15</t>
           </r>
         </is>
       </c>
@@ -37185,7 +37185,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03408753752</t>
+            <t xml:space="preserve">019790492230</t>
           </r>
         </is>
       </c>
@@ -37196,7 +37196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">12/12/2026</t>
           </r>
         </is>
       </c>
@@ -37244,7 +37244,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO DE SOUSA COELHO</t>
+            <t xml:space="preserve">RODRIGO CESARIO DANTAS</t>
           </r>
         </is>
       </c>
@@ -37254,7 +37254,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">071.019.256-85</t>
+            <t xml:space="preserve">062.821.666-16</t>
           </r>
         </is>
       </c>
@@ -37264,7 +37264,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03393047195</t>
+            <t xml:space="preserve">02818805407</t>
           </r>
         </is>
       </c>
@@ -37275,7 +37275,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -37323,7 +37323,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO MACIEL XAVIER</t>
+            <t xml:space="preserve">RODRIGO DA COSTA RAMOS</t>
           </r>
         </is>
       </c>
@@ -37333,7 +37333,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">031.787.716-03</t>
+            <t xml:space="preserve">079.330.686-85</t>
           </r>
         </is>
       </c>
@@ -37343,7 +37343,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02992459933</t>
+            <t xml:space="preserve">03408753752</t>
           </r>
         </is>
       </c>
@@ -37354,7 +37354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/03/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -37402,7 +37402,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO MOREIRA CORREA</t>
+            <t xml:space="preserve">RODRIGO DE SOUSA COELHO</t>
           </r>
         </is>
       </c>
@@ -37412,7 +37412,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">056.371.446-80</t>
+            <t xml:space="preserve">071.019.256-85</t>
           </r>
         </is>
       </c>
@@ -37422,7 +37422,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02338803674</t>
+            <t xml:space="preserve">03393047195</t>
           </r>
         </is>
       </c>
@@ -37433,7 +37433,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -37481,7 +37481,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO WILLER DE OLIVEIRA</t>
+            <t xml:space="preserve">RODRIGO MACIEL XAVIER</t>
           </r>
         </is>
       </c>
@@ -37491,7 +37491,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">123.890.076-35</t>
+            <t xml:space="preserve">031.787.716-03</t>
           </r>
         </is>
       </c>
@@ -37501,7 +37501,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05732797762</t>
+            <t xml:space="preserve">02992459933</t>
           </r>
         </is>
       </c>
@@ -37512,7 +37512,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2025</t>
+            <t xml:space="preserve">18/03/2027</t>
           </r>
         </is>
       </c>
@@ -37560,7 +37560,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGUES GERALDO DE SOUZA</t>
+            <t xml:space="preserve">RODRIGO MOREIRA CORREA</t>
           </r>
         </is>
       </c>
@@ -37570,7 +37570,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">036.160.136-07</t>
+            <t xml:space="preserve">056.371.446-80</t>
           </r>
         </is>
       </c>
@@ -37580,7 +37580,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05446425338</t>
+            <t xml:space="preserve">02338803674</t>
           </r>
         </is>
       </c>
@@ -37591,7 +37591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -37639,7 +37639,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGELIO DA CRUZ DOS SANTOS</t>
+            <t xml:space="preserve">RODRIGO WILLER DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -37649,7 +37649,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">043.086.985-10</t>
+            <t xml:space="preserve">123.890.076-35</t>
           </r>
         </is>
       </c>
@@ -37659,7 +37659,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04971758149</t>
+            <t xml:space="preserve">05732797762</t>
           </r>
         </is>
       </c>
@@ -37670,7 +37670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">03/07/2025</t>
           </r>
         </is>
       </c>
@@ -37718,7 +37718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGER MARCIO SIRIO    </t>
+            <t xml:space="preserve">RODRIGUES GERALDO DE SOUZA</t>
           </r>
         </is>
       </c>
@@ -37728,7 +37728,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">132.076.616-10</t>
+            <t xml:space="preserve">036.160.136-07</t>
           </r>
         </is>
       </c>
@@ -37738,7 +37738,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05572572958</t>
+            <t xml:space="preserve">05446425338</t>
           </r>
         </is>
       </c>
@@ -37749,7 +37749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/01/2027</t>
           </r>
         </is>
       </c>
@@ -37797,7 +37797,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGERIO PEREIRA VARGAS</t>
+            <t xml:space="preserve">ROGELIO DA CRUZ DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -37807,7 +37807,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">032.158.106-70</t>
+            <t xml:space="preserve">043.086.985-10</t>
           </r>
         </is>
       </c>
@@ -37817,7 +37817,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03602334615</t>
+            <t xml:space="preserve">04971758149</t>
           </r>
         </is>
       </c>
@@ -37828,7 +37828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/11/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -37876,7 +37876,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROMERSON MANOEL DA SILVA</t>
+            <t xml:space="preserve">ROGER MARCIO SIRIO    </t>
           </r>
         </is>
       </c>
@@ -37886,7 +37886,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">932.654.096-00</t>
+            <t xml:space="preserve">132.076.616-10</t>
           </r>
         </is>
       </c>
@@ -37896,7 +37896,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4211589860</t>
+            <t xml:space="preserve">05572572958</t>
           </r>
         </is>
       </c>
@@ -37907,7 +37907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/02/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -37955,7 +37955,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO BORGES MAGALHAES</t>
+            <t xml:space="preserve">ROGERIO PEREIRA VARGAS</t>
           </r>
         </is>
       </c>
@@ -37965,7 +37965,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">812.820.286-34</t>
+            <t xml:space="preserve">032.158.106-70</t>
           </r>
         </is>
       </c>
@@ -37975,7 +37975,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00574237295</t>
+            <t xml:space="preserve">03602334615</t>
           </r>
         </is>
       </c>
@@ -37986,7 +37986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/09/2027</t>
+            <t xml:space="preserve">03/11/2026</t>
           </r>
         </is>
       </c>
@@ -38034,7 +38034,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO ROSALVO DOS SANTOS</t>
+            <t xml:space="preserve">ROMERSON MANOEL DA SILVA</t>
           </r>
         </is>
       </c>
@@ -38044,7 +38044,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">035.607.284-36</t>
+            <t xml:space="preserve">932.654.096-00</t>
           </r>
         </is>
       </c>
@@ -38054,7 +38054,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03658415228</t>
+            <t xml:space="preserve">4211589860</t>
           </r>
         </is>
       </c>
@@ -38065,7 +38065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">10/02/2027</t>
           </r>
         </is>
       </c>
@@ -38113,7 +38113,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO SILVA DE CARVALHO</t>
+            <t xml:space="preserve">RONALDO BORGES MAGALHAES</t>
           </r>
         </is>
       </c>
@@ -38123,7 +38123,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.120.046-62</t>
+            <t xml:space="preserve">812.820.286-34</t>
           </r>
         </is>
       </c>
@@ -38133,7 +38133,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05036941619</t>
+            <t xml:space="preserve">00574237295</t>
           </r>
         </is>
       </c>
@@ -38144,7 +38144,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">03/09/2027</t>
           </r>
         </is>
       </c>
@@ -38192,7 +38192,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONIE FERNANDO DA SILVA</t>
+            <t xml:space="preserve">RONALDO ROSALVO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -38202,7 +38202,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">052.060.286-22</t>
+            <t xml:space="preserve">035.607.284-36</t>
           </r>
         </is>
       </c>
@@ -38212,7 +38212,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06025263305</t>
+            <t xml:space="preserve">03658415228</t>
           </r>
         </is>
       </c>
@@ -38223,7 +38223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -38271,7 +38271,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONILDO OLIVEIRA CRUZ</t>
+            <t xml:space="preserve">RONALDO SILVA DE CARVALHO</t>
           </r>
         </is>
       </c>
@@ -38281,7 +38281,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">021.930.251-00</t>
+            <t xml:space="preserve">093.120.046-62</t>
           </r>
         </is>
       </c>
@@ -38291,7 +38291,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04883639482</t>
+            <t xml:space="preserve">05036941619</t>
           </r>
         </is>
       </c>
@@ -38302,7 +38302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -38350,7 +38350,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONNY CARLOS DA SILVA</t>
+            <t xml:space="preserve">RONIE FERNANDO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -38360,7 +38360,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">947.454.126-49</t>
+            <t xml:space="preserve">052.060.286-22</t>
           </r>
         </is>
       </c>
@@ -38370,7 +38370,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03488127326</t>
+            <t xml:space="preserve">06025263305</t>
           </r>
         </is>
       </c>
@@ -38381,7 +38381,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -38422,14 +38422,14 @@
       <c r="T484" s="12" t="inlineStr"/>
       <c r="U484" s="1" t="inlineStr"/>
     </row>
-    <row r="485" customHeight="1" ht="22">
+    <row r="485" customHeight="1" ht="21">
       <c r="A485" s="1" t="inlineStr"/>
       <c r="B485" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROSILENE DAS GRAÇAS DE O COSTA SIQUEIRA </t>
+            <t xml:space="preserve">RONILDO OLIVEIRA CRUZ</t>
           </r>
         </is>
       </c>
@@ -38439,7 +38439,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.324.136-93</t>
+            <t xml:space="preserve">021.930.251-00</t>
           </r>
         </is>
       </c>
@@ -38449,7 +38449,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04774059559</t>
+            <t xml:space="preserve">04883639482</t>
           </r>
         </is>
       </c>
@@ -38460,7 +38460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -38508,7 +38508,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROZEMAR SEMIAO PINTO</t>
+            <t xml:space="preserve">RONNY CARLOS DA SILVA</t>
           </r>
         </is>
       </c>
@@ -38518,7 +38518,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.531.246-95</t>
+            <t xml:space="preserve">947.454.126-49</t>
           </r>
         </is>
       </c>
@@ -38528,7 +38528,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04086354799</t>
+            <t xml:space="preserve">03488127326</t>
           </r>
         </is>
       </c>
@@ -38539,7 +38539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/08/2027</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -38580,14 +38580,14 @@
       <c r="T486" s="12" t="inlineStr"/>
       <c r="U486" s="1" t="inlineStr"/>
     </row>
-    <row r="487" customHeight="1" ht="21">
+    <row r="487" customHeight="1" ht="22">
       <c r="A487" s="1" t="inlineStr"/>
       <c r="B487" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RUBENS JOSE DA RO¿¿¿</t>
+            <t xml:space="preserve">ROSILENE DAS GRAÇAS DE O COSTA SIQUEIRA </t>
           </r>
         </is>
       </c>
@@ -38597,7 +38597,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">555.890.656-15</t>
+            <t xml:space="preserve">076.324.136-93</t>
           </r>
         </is>
       </c>
@@ -38607,7 +38607,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01136935529</t>
+            <t xml:space="preserve">04774059559</t>
           </r>
         </is>
       </c>
@@ -38618,7 +38618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -38666,7 +38666,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RUBENS LUIS CARNEIRO</t>
+            <t xml:space="preserve">ROZEMAR SEMIAO PINTO</t>
           </r>
         </is>
       </c>
@@ -38676,7 +38676,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">074.702.786-21</t>
+            <t xml:space="preserve">054.531.246-95</t>
           </r>
         </is>
       </c>
@@ -38686,7 +38686,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14163556</t>
+            <t xml:space="preserve">04086354799</t>
           </r>
         </is>
       </c>
@@ -38697,7 +38697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/08/2027</t>
+            <t xml:space="preserve">27/08/2027</t>
           </r>
         </is>
       </c>
@@ -38745,7 +38745,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SALATIEL GOMES DOS SANTOS</t>
+            <t xml:space="preserve">RUBENS JOSE DA RO¿¿¿</t>
           </r>
         </is>
       </c>
@@ -38755,7 +38755,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.278.946-32</t>
+            <t xml:space="preserve">555.890.656-15</t>
           </r>
         </is>
       </c>
@@ -38765,7 +38765,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05199034200</t>
+            <t xml:space="preserve">01136935529</t>
           </r>
         </is>
       </c>
@@ -38776,7 +38776,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -38824,7 +38824,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRA APARECIDA DE LACERDA</t>
+            <t xml:space="preserve">RUBENS LUIS CARNEIRO</t>
           </r>
         </is>
       </c>
@@ -38834,7 +38834,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.654.516-50</t>
+            <t xml:space="preserve">074.702.786-21</t>
           </r>
         </is>
       </c>
@@ -38844,7 +38844,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06112213773</t>
+            <t xml:space="preserve">14163556</t>
           </r>
         </is>
       </c>
@@ -38855,7 +38855,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/03/2027</t>
+            <t xml:space="preserve">20/08/2027</t>
           </r>
         </is>
       </c>
@@ -38903,7 +38903,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRA MARA MARTINS</t>
+            <t xml:space="preserve">SALATIEL GOMES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -38913,7 +38913,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">038.635.206-29</t>
+            <t xml:space="preserve">120.278.946-32</t>
           </r>
         </is>
       </c>
@@ -38923,7 +38923,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04164944850</t>
+            <t xml:space="preserve">05199034200</t>
           </r>
         </is>
       </c>
@@ -38934,7 +38934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2026</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -38975,14 +38975,14 @@
       <c r="T491" s="12" t="inlineStr"/>
       <c r="U491" s="1" t="inlineStr"/>
     </row>
-    <row r="492" customHeight="1" ht="22">
+    <row r="492" customHeight="1" ht="21">
       <c r="A492" s="1" t="inlineStr"/>
       <c r="B492" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRO MARCOS DE FREITAS QUEIROS</t>
+            <t xml:space="preserve">SANDRA APARECIDA DE LACERDA</t>
           </r>
         </is>
       </c>
@@ -38992,7 +38992,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">977.080.206-97</t>
+            <t xml:space="preserve">067.654.516-50</t>
           </r>
         </is>
       </c>
@@ -39002,7 +39002,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01979048430</t>
+            <t xml:space="preserve">06112213773</t>
           </r>
         </is>
       </c>
@@ -39013,7 +39013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">11/03/2027</t>
           </r>
         </is>
       </c>
@@ -39061,7 +39061,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SEBASTIAO EUSTAQUIO TEIXEIRA</t>
+            <t xml:space="preserve">SANDRA MARA MARTINS</t>
           </r>
         </is>
       </c>
@@ -39071,7 +39071,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">456.820.546-87</t>
+            <t xml:space="preserve">038.635.206-29</t>
           </r>
         </is>
       </c>
@@ -39081,7 +39081,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03016774844</t>
+            <t xml:space="preserve">04164944850</t>
           </r>
         </is>
       </c>
@@ -39092,7 +39092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">01/01/2026</t>
           </r>
         </is>
       </c>
@@ -39133,14 +39133,14 @@
       <c r="T493" s="12" t="inlineStr"/>
       <c r="U493" s="1" t="inlineStr"/>
     </row>
-    <row r="494" customHeight="1" ht="21">
+    <row r="494" customHeight="1" ht="22">
       <c r="A494" s="1" t="inlineStr"/>
       <c r="B494" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SEBASTIAO ROBERTO FRANCISCO</t>
+            <t xml:space="preserve">SANDRO MARCOS DE FREITAS QUEIROS</t>
           </r>
         </is>
       </c>
@@ -39150,7 +39150,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">032.171.546-22</t>
+            <t xml:space="preserve">977.080.206-97</t>
           </r>
         </is>
       </c>
@@ -39160,7 +39160,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01221024975</t>
+            <t xml:space="preserve">01979048430</t>
           </r>
         </is>
       </c>
@@ -39171,7 +39171,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/07/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -39219,7 +39219,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO JESUS DE SENA</t>
+            <t xml:space="preserve">SEBASTIAO EUSTAQUIO TEIXEIRA</t>
           </r>
         </is>
       </c>
@@ -39229,7 +39229,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">703.152.481-49</t>
+            <t xml:space="preserve">456.820.546-87</t>
           </r>
         </is>
       </c>
@@ -39239,7 +39239,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01987693689</t>
+            <t xml:space="preserve">03016774844</t>
           </r>
         </is>
       </c>
@@ -39250,7 +39250,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2026</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -39298,7 +39298,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO MARTINS CANDIDO</t>
+            <t xml:space="preserve">SEBASTIAO ROBERTO FRANCISCO</t>
           </r>
         </is>
       </c>
@@ -39308,7 +39308,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">055.992.066-02</t>
+            <t xml:space="preserve">032.171.546-22</t>
           </r>
         </is>
       </c>
@@ -39318,7 +39318,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01540143348</t>
+            <t xml:space="preserve">01221024975</t>
           </r>
         </is>
       </c>
@@ -39329,7 +39329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">01/07/2027</t>
           </r>
         </is>
       </c>
@@ -39377,7 +39377,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO SORA PEREIRA</t>
+            <t xml:space="preserve">SERGIO JESUS DE SENA</t>
           </r>
         </is>
       </c>
@@ -39387,7 +39387,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">116.201.246-37</t>
+            <t xml:space="preserve">703.152.481-49</t>
           </r>
         </is>
       </c>
@@ -39397,7 +39397,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05455543950</t>
+            <t xml:space="preserve">01987693689</t>
           </r>
         </is>
       </c>
@@ -39408,7 +39408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2025</t>
+            <t xml:space="preserve">24/09/2026</t>
           </r>
         </is>
       </c>
@@ -39456,7 +39456,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEI EDERSON RODRIGUES</t>
+            <t xml:space="preserve">SERGIO MARTINS CANDIDO</t>
           </r>
         </is>
       </c>
@@ -39466,7 +39466,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">035.114.576-10</t>
+            <t xml:space="preserve">055.992.066-02</t>
           </r>
         </is>
       </c>
@@ -39476,7 +39476,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01367789491</t>
+            <t xml:space="preserve">01540143348</t>
           </r>
         </is>
       </c>
@@ -39487,7 +39487,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/06/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -39535,7 +39535,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEY JUSTINIANO DE CARVALHO  </t>
+            <t xml:space="preserve">SERGIO SORA PEREIRA</t>
           </r>
         </is>
       </c>
@@ -39545,7 +39545,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">933.213.766-87</t>
+            <t xml:space="preserve">116.201.246-37</t>
           </r>
         </is>
       </c>
@@ -39555,7 +39555,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00490361489</t>
+            <t xml:space="preserve">05455543950</t>
           </r>
         </is>
       </c>
@@ -39566,7 +39566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/01/2025</t>
+            <t xml:space="preserve">12/08/2025</t>
           </r>
         </is>
       </c>
@@ -39614,7 +39614,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEY LUCAS PEREIRA</t>
+            <t xml:space="preserve">SIDNEI EDERSON RODRIGUES</t>
           </r>
         </is>
       </c>
@@ -39624,7 +39624,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">003.086.236-14</t>
+            <t xml:space="preserve">035.114.576-10</t>
           </r>
         </is>
       </c>
@@ -39634,7 +39634,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01838999161</t>
+            <t xml:space="preserve">01367789491</t>
           </r>
         </is>
       </c>
@@ -39645,7 +39645,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">12/06/2027</t>
           </r>
         </is>
       </c>
@@ -39693,7 +39693,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SINVAL DA SILVA VIGILATO</t>
+            <t xml:space="preserve">SIDNEY JUSTINIANO DE CARVALHO  </t>
           </r>
         </is>
       </c>
@@ -39703,7 +39703,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">875.211.056-72</t>
+            <t xml:space="preserve">933.213.766-87</t>
           </r>
         </is>
       </c>
@@ -39713,7 +39713,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02223241791</t>
+            <t xml:space="preserve">00490361489</t>
           </r>
         </is>
       </c>
@@ -39724,7 +39724,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">27/01/2025</t>
           </r>
         </is>
       </c>
@@ -39772,7 +39772,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">STEFANY LUAN PEREIRA GUEDES</t>
+            <t xml:space="preserve">SIDNEY LUCAS PEREIRA</t>
           </r>
         </is>
       </c>
@@ -39782,7 +39782,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.806.076-13</t>
+            <t xml:space="preserve">003.086.236-14</t>
           </r>
         </is>
       </c>
@@ -39792,7 +39792,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04363860554</t>
+            <t xml:space="preserve">01838999161</t>
           </r>
         </is>
       </c>
@@ -39803,7 +39803,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/06/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -39851,7 +39851,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TALES VIEIRA DE SIQUEIRA</t>
+            <t xml:space="preserve">SINVAL DA SILVA VIGILATO</t>
           </r>
         </is>
       </c>
@@ -39861,7 +39861,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.981.346-46</t>
+            <t xml:space="preserve">875.211.056-72</t>
           </r>
         </is>
       </c>
@@ -39871,7 +39871,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05186360780</t>
+            <t xml:space="preserve">02223241791</t>
           </r>
         </is>
       </c>
@@ -39882,7 +39882,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -39930,7 +39930,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TATIANA CRISTINA DOS REIS</t>
+            <t xml:space="preserve">STEFANY LUAN PEREIRA GUEDES</t>
           </r>
         </is>
       </c>
@@ -39940,7 +39940,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.974.806-62</t>
+            <t xml:space="preserve">076.806.076-13</t>
           </r>
         </is>
       </c>
@@ -39950,7 +39950,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04699145123</t>
+            <t xml:space="preserve">04363860554</t>
           </r>
         </is>
       </c>
@@ -39961,7 +39961,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">03/06/2027</t>
           </r>
         </is>
       </c>
@@ -40009,7 +40009,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TATIANE MARTINS DA CRUZ</t>
+            <t xml:space="preserve">TALES VIEIRA DE SIQUEIRA</t>
           </r>
         </is>
       </c>
@@ -40019,7 +40019,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.758.886-55</t>
+            <t xml:space="preserve">077.981.346-46</t>
           </r>
         </is>
       </c>
@@ -40029,7 +40029,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05838164206</t>
+            <t xml:space="preserve">05186360780</t>
           </r>
         </is>
       </c>
@@ -40040,7 +40040,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/01/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -40081,14 +40081,14 @@
       <c r="T505" s="12" t="inlineStr"/>
       <c r="U505" s="1" t="inlineStr"/>
     </row>
-    <row r="506" customHeight="1" ht="22">
+    <row r="506" customHeight="1" ht="21">
       <c r="A506" s="1" t="inlineStr"/>
       <c r="B506" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THAISON BRUNO FERNANDO DOS SANTOS</t>
+            <t xml:space="preserve">TATIANA CRISTINA DOS REIS</t>
           </r>
         </is>
       </c>
@@ -40098,7 +40098,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">015.914.226-12</t>
+            <t xml:space="preserve">076.974.806-62</t>
           </r>
         </is>
       </c>
@@ -40108,7 +40108,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">0436952989</t>
+            <t xml:space="preserve">04699145123</t>
           </r>
         </is>
       </c>
@@ -40119,7 +40119,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/09/2027</t>
+            <t xml:space="preserve">13/01/2027</t>
           </r>
         </is>
       </c>
@@ -40167,7 +40167,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO ALVES FERREIRA</t>
+            <t xml:space="preserve">TATIANE MARTINS DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -40177,7 +40177,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.622.556-97</t>
+            <t xml:space="preserve">120.758.886-55</t>
           </r>
         </is>
       </c>
@@ -40187,7 +40187,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04151517893</t>
+            <t xml:space="preserve">05838164206</t>
           </r>
         </is>
       </c>
@@ -40198,7 +40198,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/11/2026</t>
+            <t xml:space="preserve">27/01/2027</t>
           </r>
         </is>
       </c>
@@ -40239,14 +40239,14 @@
       <c r="T507" s="12" t="inlineStr"/>
       <c r="U507" s="1" t="inlineStr"/>
     </row>
-    <row r="508" customHeight="1" ht="21">
+    <row r="508" customHeight="1" ht="22">
       <c r="A508" s="1" t="inlineStr"/>
       <c r="B508" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO FARIA ROSA</t>
+            <t xml:space="preserve">THAISON BRUNO FERNANDO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -40256,7 +40256,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">101.801.956-11</t>
+            <t xml:space="preserve">015.914.226-12</t>
           </r>
         </is>
       </c>
@@ -40266,7 +40266,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05453493191</t>
+            <t xml:space="preserve">0436952989</t>
           </r>
         </is>
       </c>
@@ -40277,7 +40277,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">10/09/2027</t>
           </r>
         </is>
       </c>
@@ -40325,7 +40325,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO GONCALVES CARDOSO</t>
+            <t xml:space="preserve">THIAGO ALVES FERREIRA</t>
           </r>
         </is>
       </c>
@@ -40335,7 +40335,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">022.860.086-39</t>
+            <t xml:space="preserve">076.622.556-97</t>
           </r>
         </is>
       </c>
@@ -40345,7 +40345,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06955819327</t>
+            <t xml:space="preserve">04151517893</t>
           </r>
         </is>
       </c>
@@ -40356,7 +40356,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/12/2025</t>
+            <t xml:space="preserve">10/11/2026</t>
           </r>
         </is>
       </c>
@@ -40404,7 +40404,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TIAGO ANDRADE DOS PASSOS</t>
+            <t xml:space="preserve">THIAGO FARIA ROSA</t>
           </r>
         </is>
       </c>
@@ -40414,7 +40414,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">084.447.676-54</t>
+            <t xml:space="preserve">101.801.956-11</t>
           </r>
         </is>
       </c>
@@ -40424,7 +40424,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03945068162</t>
+            <t xml:space="preserve">05453493191</t>
           </r>
         </is>
       </c>
@@ -40435,7 +40435,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/06/2027</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -40483,7 +40483,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TIAGO DA SILVA LIMA</t>
+            <t xml:space="preserve">THIAGO GONCALVES CARDOSO</t>
           </r>
         </is>
       </c>
@@ -40493,7 +40493,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">075.518.336-33</t>
+            <t xml:space="preserve">022.860.086-39</t>
           </r>
         </is>
       </c>
@@ -40503,7 +40503,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03550506992</t>
+            <t xml:space="preserve">06955819327</t>
           </r>
         </is>
       </c>
@@ -40514,7 +40514,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/09/2027</t>
+            <t xml:space="preserve">11/12/2025</t>
           </r>
         </is>
       </c>
@@ -40562,7 +40562,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UENDERSON RONALD DA SILVA</t>
+            <t xml:space="preserve">TIAGO ANDRADE DOS PASSOS</t>
           </r>
         </is>
       </c>
@@ -40572,7 +40572,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.548.716-13</t>
+            <t xml:space="preserve">084.447.676-54</t>
           </r>
         </is>
       </c>
@@ -40582,7 +40582,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03399996765</t>
+            <t xml:space="preserve">03945068162</t>
           </r>
         </is>
       </c>
@@ -40593,7 +40593,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/07/2027</t>
+            <t xml:space="preserve">11/06/2027</t>
           </r>
         </is>
       </c>
@@ -40641,7 +40641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ULISSES DE FREITAS MELO</t>
+            <t xml:space="preserve">TIAGO DA SILVA LIMA</t>
           </r>
         </is>
       </c>
@@ -40651,7 +40651,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">041.135.016-10</t>
+            <t xml:space="preserve">075.518.336-33</t>
           </r>
         </is>
       </c>
@@ -40661,7 +40661,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03364297306</t>
+            <t xml:space="preserve">03550506992</t>
           </r>
         </is>
       </c>
@@ -40672,7 +40672,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/09/2027</t>
+            <t xml:space="preserve">08/09/2027</t>
           </r>
         </is>
       </c>
@@ -40720,7 +40720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">URBANO MORAIS LOURENCO</t>
+            <t xml:space="preserve">UENDERSON RONALD DA SILVA</t>
           </r>
         </is>
       </c>
@@ -40730,7 +40730,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">118.321.046-99</t>
+            <t xml:space="preserve">054.548.716-13</t>
           </r>
         </is>
       </c>
@@ -40740,7 +40740,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06455070312</t>
+            <t xml:space="preserve">03399996765</t>
           </r>
         </is>
       </c>
@@ -40751,7 +40751,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/04/2027</t>
+            <t xml:space="preserve">24/07/2027</t>
           </r>
         </is>
       </c>
@@ -40799,7 +40799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VADIR BERNARDES DA SILVA</t>
+            <t xml:space="preserve">ULISSES DE FREITAS MELO</t>
           </r>
         </is>
       </c>
@@ -40809,7 +40809,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.330.718-66</t>
+            <t xml:space="preserve">041.135.016-10</t>
           </r>
         </is>
       </c>
@@ -40819,7 +40819,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01938461228</t>
+            <t xml:space="preserve">03364297306</t>
           </r>
         </is>
       </c>
@@ -40830,7 +40830,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2026</t>
+            <t xml:space="preserve">09/09/2027</t>
           </r>
         </is>
       </c>
@@ -40878,7 +40878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALMIR GOMES RIBEIRO</t>
+            <t xml:space="preserve">URBANO MORAIS LOURENCO</t>
           </r>
         </is>
       </c>
@@ -40888,7 +40888,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.463.326-63</t>
+            <t xml:space="preserve">118.321.046-99</t>
           </r>
         </is>
       </c>
@@ -40898,7 +40898,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04922140128</t>
+            <t xml:space="preserve">06455070312</t>
           </r>
         </is>
       </c>
@@ -40909,7 +40909,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/01/2027</t>
+            <t xml:space="preserve">14/04/2027</t>
           </r>
         </is>
       </c>
@@ -40957,7 +40957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALQUIRIA SANTOS COUTO</t>
+            <t xml:space="preserve">VADIR BERNARDES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -40967,7 +40967,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.378.626-09</t>
+            <t xml:space="preserve">046.330.718-66</t>
           </r>
         </is>
       </c>
@@ -40977,7 +40977,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05442378859</t>
+            <t xml:space="preserve">01938461228</t>
           </r>
         </is>
       </c>
@@ -40988,7 +40988,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/02/2026</t>
+            <t xml:space="preserve">23/07/2026</t>
           </r>
         </is>
       </c>
@@ -41036,7 +41036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALTER DOMINGOS MEIRELES  </t>
+            <t xml:space="preserve">VALMIR GOMES RIBEIRO</t>
           </r>
         </is>
       </c>
@@ -41046,7 +41046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.666.886-83</t>
+            <t xml:space="preserve">065.463.326-63</t>
           </r>
         </is>
       </c>
@@ -41056,7 +41056,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02232141549</t>
+            <t xml:space="preserve">04922140128</t>
           </r>
         </is>
       </c>
@@ -41067,7 +41067,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -41115,7 +41115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALTER RAMOS DE LIMA</t>
+            <t xml:space="preserve">VALQUIRIA SANTOS COUTO</t>
           </r>
         </is>
       </c>
@@ -41125,7 +41125,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">832.376.746-72</t>
+            <t xml:space="preserve">077.378.626-09</t>
           </r>
         </is>
       </c>
@@ -41135,7 +41135,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01110738309</t>
+            <t xml:space="preserve">05442378859</t>
           </r>
         </is>
       </c>
@@ -41146,7 +41146,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">13/02/2026</t>
           </r>
         </is>
       </c>
@@ -41187,14 +41187,14 @@
       <c r="T519" s="12" t="inlineStr"/>
       <c r="U519" s="1" t="inlineStr"/>
     </row>
-    <row r="520" customHeight="1" ht="22">
+    <row r="520" customHeight="1" ht="21">
       <c r="A520" s="1" t="inlineStr"/>
       <c r="B520" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANDERCI BATISTA LEANDRO DOS SANTOS</t>
+            <t xml:space="preserve">VALTER DOMINGOS MEIRELES  </t>
           </r>
         </is>
       </c>
@@ -41204,7 +41204,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">939.681.836-49</t>
+            <t xml:space="preserve">040.666.886-83</t>
           </r>
         </is>
       </c>
@@ -41214,7 +41214,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02672395939</t>
+            <t xml:space="preserve">02232141549</t>
           </r>
         </is>
       </c>
@@ -41225,7 +41225,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/11/2026</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -41273,7 +41273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANDERSON TELES NASCIMENTO</t>
+            <t xml:space="preserve">VALTER RAMOS DE LIMA</t>
           </r>
         </is>
       </c>
@@ -41283,7 +41283,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.675.435-34</t>
+            <t xml:space="preserve">832.376.746-72</t>
           </r>
         </is>
       </c>
@@ -41293,7 +41293,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01845793756</t>
+            <t xml:space="preserve">01110738309</t>
           </r>
         </is>
       </c>
@@ -41304,7 +41304,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -41345,14 +41345,14 @@
       <c r="T521" s="12" t="inlineStr"/>
       <c r="U521" s="1" t="inlineStr"/>
     </row>
-    <row r="522" customHeight="1" ht="21">
+    <row r="522" customHeight="1" ht="22">
       <c r="A522" s="1" t="inlineStr"/>
       <c r="B522" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANEIALVES GUIMARAES</t>
+            <t xml:space="preserve">VANDERCI BATISTA LEANDRO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -41362,7 +41362,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.859.956-41</t>
+            <t xml:space="preserve">939.681.836-49</t>
           </r>
         </is>
       </c>
@@ -41372,7 +41372,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03607821769</t>
+            <t xml:space="preserve">02672395939</t>
           </r>
         </is>
       </c>
@@ -41383,7 +41383,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">26/11/2026</t>
           </r>
         </is>
       </c>
@@ -41431,7 +41431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANESSA CAROLINNE GONÇALVES</t>
+            <t xml:space="preserve">VANDERSON TELES NASCIMENTO</t>
           </r>
         </is>
       </c>
@@ -41441,7 +41441,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.868.326-80</t>
+            <t xml:space="preserve">819.675.435-34</t>
           </r>
         </is>
       </c>
@@ -41451,7 +41451,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06829001421</t>
+            <t xml:space="preserve">01845793756</t>
           </r>
         </is>
       </c>
@@ -41462,7 +41462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/12/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -41510,7 +41510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE DE PAULO DA SILVA</t>
+            <t xml:space="preserve">VANEIALVES GUIMARAES</t>
           </r>
         </is>
       </c>
@@ -41520,7 +41520,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">731.778.146-00</t>
+            <t xml:space="preserve">026.859.956-41</t>
           </r>
         </is>
       </c>
@@ -41530,7 +41530,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02507810777</t>
+            <t xml:space="preserve">03607821769</t>
           </r>
         </is>
       </c>
@@ -41541,7 +41541,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -41589,7 +41589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE DOS REIS GOMES</t>
+            <t xml:space="preserve">VANESSA CAROLINNE GONÇALVES</t>
           </r>
         </is>
       </c>
@@ -41599,7 +41599,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">755.303.926-87</t>
+            <t xml:space="preserve">120.868.326-80</t>
           </r>
         </is>
       </c>
@@ -41609,7 +41609,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02525863238</t>
+            <t xml:space="preserve">06829001421</t>
           </r>
         </is>
       </c>
@@ -41620,7 +41620,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/08/2027</t>
+            <t xml:space="preserve">12/12/2026</t>
           </r>
         </is>
       </c>
@@ -41668,7 +41668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE ROBERTO ANGELO</t>
+            <t xml:space="preserve">VICENTE DE PAULO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -41678,7 +41678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">399.263.546-53</t>
+            <t xml:space="preserve">731.778.146-00</t>
           </r>
         </is>
       </c>
@@ -41688,7 +41688,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01030510930</t>
+            <t xml:space="preserve">02507810777</t>
           </r>
         </is>
       </c>
@@ -41699,7 +41699,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -41747,7 +41747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VILEIDE VAZ MOREIRA </t>
+            <t xml:space="preserve">VICENTE DOS REIS GOMES</t>
           </r>
         </is>
       </c>
@@ -41757,7 +41757,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">109.093.766-03</t>
+            <t xml:space="preserve">755.303.926-87</t>
           </r>
         </is>
       </c>
@@ -41767,7 +41767,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06087149441</t>
+            <t xml:space="preserve">02525863238</t>
           </r>
         </is>
       </c>
@@ -41778,7 +41778,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">26/08/2027</t>
           </r>
         </is>
       </c>
@@ -41826,7 +41826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VINICIO JOSE DOS SANTOS</t>
+            <t xml:space="preserve">VICENTE ROBERTO ANGELO</t>
           </r>
         </is>
       </c>
@@ -41836,7 +41836,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">048.389.316-11</t>
+            <t xml:space="preserve">399.263.546-53</t>
           </r>
         </is>
       </c>
@@ -41846,7 +41846,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01306809764</t>
+            <t xml:space="preserve">01030510930</t>
           </r>
         </is>
       </c>
@@ -41905,7 +41905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VINICIUS BORGES VALES</t>
+            <t xml:space="preserve">VILEIDE VAZ MOREIRA </t>
           </r>
         </is>
       </c>
@@ -41915,7 +41915,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">086.215.466-98</t>
+            <t xml:space="preserve">109.093.766-03</t>
           </r>
         </is>
       </c>
@@ -41925,7 +41925,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04262664653</t>
+            <t xml:space="preserve">06087149441</t>
           </r>
         </is>
       </c>
@@ -41936,7 +41936,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2024</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -41984,7 +41984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VITOR FERREIRA SANTOS</t>
+            <t xml:space="preserve">VINICIO JOSE DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -41994,7 +41994,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">136.025.886-88</t>
+            <t xml:space="preserve">048.389.316-11</t>
           </r>
         </is>
       </c>
@@ -42004,7 +42004,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07186400700</t>
+            <t xml:space="preserve">01306809764</t>
           </r>
         </is>
       </c>
@@ -42015,7 +42015,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -42063,7 +42063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VITOR GABRIEL GOMES CORREIA </t>
+            <t xml:space="preserve">VINICIUS BORGES VALES</t>
           </r>
         </is>
       </c>
@@ -42073,7 +42073,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">019.705.576-13</t>
+            <t xml:space="preserve">086.215.466-98</t>
           </r>
         </is>
       </c>
@@ -42083,7 +42083,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06930599950</t>
+            <t xml:space="preserve">04262664653</t>
           </r>
         </is>
       </c>
@@ -42094,7 +42094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">31/07/2024</t>
           </r>
         </is>
       </c>
@@ -42142,7 +42142,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WAGNER FERNANDES DA SILVA</t>
+            <t xml:space="preserve">VITOR FERREIRA SANTOS</t>
           </r>
         </is>
       </c>
@@ -42152,7 +42152,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">012.597.906-14</t>
+            <t xml:space="preserve">136.025.886-88</t>
           </r>
         </is>
       </c>
@@ -42162,7 +42162,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03780457127</t>
+            <t xml:space="preserve">07186400700</t>
           </r>
         </is>
       </c>
@@ -42173,7 +42173,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -42214,14 +42214,14 @@
       <c r="T532" s="12" t="inlineStr"/>
       <c r="U532" s="1" t="inlineStr"/>
     </row>
-    <row r="533" customHeight="1" ht="22">
+    <row r="533" customHeight="1" ht="21">
       <c r="A533" s="1" t="inlineStr"/>
       <c r="B533" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WALBER EVANGELISTA LONGO DO NASCIMENTO</t>
+            <t xml:space="preserve">VITOR GABRIEL GOMES CORREIA </t>
           </r>
         </is>
       </c>
@@ -42231,7 +42231,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">072.851.686-10</t>
+            <t xml:space="preserve">019.705.576-13</t>
           </r>
         </is>
       </c>
@@ -42241,7 +42241,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03810941378</t>
+            <t xml:space="preserve">06930599950</t>
           </r>
         </is>
       </c>
@@ -42252,7 +42252,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/08/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -42300,7 +42300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WALMIR ALVES MEIRELES   </t>
+            <t xml:space="preserve">WAGNER FERNANDES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -42310,7 +42310,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">001.214.386-35</t>
+            <t xml:space="preserve">012.597.906-14</t>
           </r>
         </is>
       </c>
@@ -42320,7 +42320,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00441481335</t>
+            <t xml:space="preserve">03780457127</t>
           </r>
         </is>
       </c>
@@ -42331,7 +42331,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -42372,14 +42372,14 @@
       <c r="T534" s="12" t="inlineStr"/>
       <c r="U534" s="1" t="inlineStr"/>
     </row>
-    <row r="535" customHeight="1" ht="21">
+    <row r="535" customHeight="1" ht="22">
       <c r="A535" s="1" t="inlineStr"/>
       <c r="B535" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WANDEIR HONORATO DE OLIVEIRA</t>
+            <t xml:space="preserve">WALBER EVANGELISTA LONGO DO NASCIMENTO</t>
           </r>
         </is>
       </c>
@@ -42389,7 +42389,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">824.616.866-53</t>
+            <t xml:space="preserve">072.851.686-10</t>
           </r>
         </is>
       </c>
@@ -42399,7 +42399,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02755705481</t>
+            <t xml:space="preserve">03810941378</t>
           </r>
         </is>
       </c>
@@ -42410,7 +42410,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">27/08/2027</t>
           </r>
         </is>
       </c>
@@ -42458,7 +42458,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WANDERSON HENRIQUE FARAH</t>
+            <t xml:space="preserve">WALMIR ALVES MEIRELES   </t>
           </r>
         </is>
       </c>
@@ -42468,7 +42468,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.031.086-07</t>
+            <t xml:space="preserve">001.214.386-35</t>
           </r>
         </is>
       </c>
@@ -42478,7 +42478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03551548436</t>
+            <t xml:space="preserve">00441481335</t>
           </r>
         </is>
       </c>
@@ -42489,7 +42489,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/05/2026</t>
+            <t xml:space="preserve">06/08/2027</t>
           </r>
         </is>
       </c>
@@ -42537,7 +42537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WARLEY TEODORO</t>
+            <t xml:space="preserve">WANDEIR HONORATO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -42547,7 +42547,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.096.156-09</t>
+            <t xml:space="preserve">824.616.866-53</t>
           </r>
         </is>
       </c>
@@ -42557,7 +42557,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03946495186</t>
+            <t xml:space="preserve">02755705481</t>
           </r>
         </is>
       </c>
@@ -42568,7 +42568,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/09/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -42616,7 +42616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON ANTONIO DE AVILA</t>
+            <t xml:space="preserve">WANDERSON HENRIQUE FARAH</t>
           </r>
         </is>
       </c>
@@ -42626,7 +42626,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">913.901.686-20</t>
+            <t xml:space="preserve">070.031.086-07</t>
           </r>
         </is>
       </c>
@@ -42636,7 +42636,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00562356548</t>
+            <t xml:space="preserve">03551548436</t>
           </r>
         </is>
       </c>
@@ -42647,7 +42647,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">30/05/2026</t>
           </r>
         </is>
       </c>
@@ -42695,7 +42695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON BARBOSA VIEIRA</t>
+            <t xml:space="preserve">WARLEY TEODORO</t>
           </r>
         </is>
       </c>
@@ -42705,7 +42705,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">094.176.466-48</t>
+            <t xml:space="preserve">061.096.156-09</t>
           </r>
         </is>
       </c>
@@ -42715,7 +42715,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">0412500611226</t>
+            <t xml:space="preserve">03946495186</t>
           </r>
         </is>
       </c>
@@ -42726,7 +42726,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">23/09/2027</t>
           </r>
         </is>
       </c>
@@ -42774,7 +42774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON WELLINGTON PINTO</t>
+            <t xml:space="preserve">WASHINGTON ANTONIO DE AVILA</t>
           </r>
         </is>
       </c>
@@ -42784,7 +42784,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">092.920.176-08</t>
+            <t xml:space="preserve">913.901.686-20</t>
           </r>
         </is>
       </c>
@@ -42794,7 +42794,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04783305563</t>
+            <t xml:space="preserve">00562356548</t>
           </r>
         </is>
       </c>
@@ -42805,7 +42805,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -42846,14 +42846,14 @@
       <c r="T540" s="12" t="inlineStr"/>
       <c r="U540" s="1" t="inlineStr"/>
     </row>
-    <row r="541" customHeight="1" ht="22">
+    <row r="541" customHeight="1" ht="21">
       <c r="A541" s="1" t="inlineStr"/>
       <c r="B541" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTONINACIO GOME DE REZENDE</t>
+            <t xml:space="preserve">WASHINGTON BARBOSA VIEIRA</t>
           </r>
         </is>
       </c>
@@ -42863,7 +42863,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">125.555.806-70</t>
+            <t xml:space="preserve">094.176.466-48</t>
           </r>
         </is>
       </c>
@@ -42873,7 +42873,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06093566794</t>
+            <t xml:space="preserve">0412500611226</t>
           </r>
         </is>
       </c>
@@ -42884,7 +42884,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/07/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -42925,14 +42925,14 @@
       <c r="T541" s="12" t="inlineStr"/>
       <c r="U541" s="1" t="inlineStr"/>
     </row>
-    <row r="542" customHeight="1" ht="22">
+    <row r="542" customHeight="1" ht="21">
       <c r="A542" s="1" t="inlineStr"/>
       <c r="B542" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTHON FERNANDO FRANCISCO</t>
+            <t xml:space="preserve">WASHINGTON WELLINGTON PINTO</t>
           </r>
         </is>
       </c>
@@ -42942,7 +42942,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.378.116-23</t>
+            <t xml:space="preserve">092.920.176-08</t>
           </r>
         </is>
       </c>
@@ -42952,7 +42952,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05042709980</t>
+            <t xml:space="preserve">04783305563</t>
           </r>
         </is>
       </c>
@@ -42963,7 +42963,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/07/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -43011,7 +43011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON APARECIDO DO NASCIMENTOS</t>
+            <t xml:space="preserve">WASHINGTONINACIO GOME DE REZENDE</t>
           </r>
         </is>
       </c>
@@ -43021,7 +43021,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">012.579.656-03</t>
+            <t xml:space="preserve">125.555.806-70</t>
           </r>
         </is>
       </c>
@@ -43031,7 +43031,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03357647398</t>
+            <t xml:space="preserve">06093566794</t>
           </r>
         </is>
       </c>
@@ -43042,7 +43042,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">16/07/2027</t>
           </r>
         </is>
       </c>
@@ -43083,14 +43083,14 @@
       <c r="T543" s="12" t="inlineStr"/>
       <c r="U543" s="1" t="inlineStr"/>
     </row>
-    <row r="544" customHeight="1" ht="21">
+    <row r="544" customHeight="1" ht="22">
       <c r="A544" s="1" t="inlineStr"/>
       <c r="B544" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON PEREIRA SILVA</t>
+            <t xml:space="preserve">WELLINGTHON FERNANDO FRANCISCO</t>
           </r>
         </is>
       </c>
@@ -43100,7 +43100,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">052.481.486-42</t>
+            <t xml:space="preserve">110.378.116-23</t>
           </r>
         </is>
       </c>
@@ -43110,7 +43110,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02266389739</t>
+            <t xml:space="preserve">05042709980</t>
           </r>
         </is>
       </c>
@@ -43121,7 +43121,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">06/07/2027</t>
           </r>
         </is>
       </c>
@@ -43162,14 +43162,14 @@
       <c r="T544" s="12" t="inlineStr"/>
       <c r="U544" s="1" t="inlineStr"/>
     </row>
-    <row r="545" customHeight="1" ht="21">
+    <row r="545" customHeight="1" ht="22">
       <c r="A545" s="1" t="inlineStr"/>
       <c r="B545" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON TERTULIANO</t>
+            <t xml:space="preserve">WELLINGTON APARECIDO DO NASCIMENTOS</t>
           </r>
         </is>
       </c>
@@ -43179,7 +43179,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">084.518.494-66</t>
+            <t xml:space="preserve">012.579.656-03</t>
           </r>
         </is>
       </c>
@@ -43189,7 +43189,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04648920920</t>
+            <t xml:space="preserve">03357647398</t>
           </r>
         </is>
       </c>
@@ -43200,7 +43200,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -43248,7 +43248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINTON SOUSA NUNES</t>
+            <t xml:space="preserve">WELLINGTON PEREIRA SILVA</t>
           </r>
         </is>
       </c>
@@ -43258,7 +43258,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.631.261-68</t>
+            <t xml:space="preserve">052.481.486-42</t>
           </r>
         </is>
       </c>
@@ -43268,7 +43268,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01601461581</t>
+            <t xml:space="preserve">02266389739</t>
           </r>
         </is>
       </c>
@@ -43279,7 +43279,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -43327,7 +43327,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLISON FERREIRA RODRIGUES</t>
+            <t xml:space="preserve">WELLINGTON TERTULIANO</t>
           </r>
         </is>
       </c>
@@ -43337,7 +43337,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">060.332.916-03</t>
+            <t xml:space="preserve">084.518.494-66</t>
           </r>
         </is>
       </c>
@@ -43347,7 +43347,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04203957932</t>
+            <t xml:space="preserve">04648920920</t>
           </r>
         </is>
       </c>
@@ -43358,7 +43358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2031</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -43406,7 +43406,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WEMERSON DE SOUZA PIRES</t>
+            <t xml:space="preserve">WELLINTON SOUSA NUNES</t>
           </r>
         </is>
       </c>
@@ -43416,7 +43416,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">085.948.536-61</t>
+            <t xml:space="preserve">868.631.261-68</t>
           </r>
         </is>
       </c>
@@ -43426,7 +43426,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289760206</t>
+            <t xml:space="preserve">01601461581</t>
           </r>
         </is>
       </c>
@@ -43437,7 +43437,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/09/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -43485,7 +43485,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEI FERNANDES DA COSTA</t>
+            <t xml:space="preserve">WELLISON FERREIRA RODRIGUES</t>
           </r>
         </is>
       </c>
@@ -43495,7 +43495,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.289.656-73</t>
+            <t xml:space="preserve">060.332.916-03</t>
           </r>
         </is>
       </c>
@@ -43505,7 +43505,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01357310210</t>
+            <t xml:space="preserve">04203957932</t>
           </r>
         </is>
       </c>
@@ -43516,7 +43516,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/01/2027</t>
+            <t xml:space="preserve">29/07/2031</t>
           </r>
         </is>
       </c>
@@ -43564,7 +43564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEY LARA DORNELAS VAZ</t>
+            <t xml:space="preserve">WEMERSON DE SOUZA PIRES</t>
           </r>
         </is>
       </c>
@@ -43574,7 +43574,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.926.946-20</t>
+            <t xml:space="preserve">085.948.536-61</t>
           </r>
         </is>
       </c>
@@ -43584,7 +43584,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01882616840</t>
+            <t xml:space="preserve">04289760206</t>
           </r>
         </is>
       </c>
@@ -43595,7 +43595,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">18/09/2027</t>
           </r>
         </is>
       </c>
@@ -43643,7 +43643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEY PEREIRA DA SILVA</t>
+            <t xml:space="preserve">WESLEI FERNANDES DA COSTA</t>
           </r>
         </is>
       </c>
@@ -43653,7 +43653,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">080.589.316-40</t>
+            <t xml:space="preserve">054.289.656-73</t>
           </r>
         </is>
       </c>
@@ -43663,7 +43663,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04884904684</t>
+            <t xml:space="preserve">01357310210</t>
           </r>
         </is>
       </c>
@@ -43674,7 +43674,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2027</t>
+            <t xml:space="preserve">22/01/2027</t>
           </r>
         </is>
       </c>
@@ -43715,14 +43715,14 @@
       <c r="T551" s="12" t="inlineStr"/>
       <c r="U551" s="1" t="inlineStr"/>
     </row>
-    <row r="552" customHeight="1" ht="22">
+    <row r="552" customHeight="1" ht="21">
       <c r="A552" s="1" t="inlineStr"/>
       <c r="B552" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILDENBERG DAYRELL BENEDITO DA SILVA</t>
+            <t xml:space="preserve">WESLEY LARA DORNELAS VAZ</t>
           </r>
         </is>
       </c>
@@ -43732,7 +43732,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">146.120.596-46</t>
+            <t xml:space="preserve">051.926.946-20</t>
           </r>
         </is>
       </c>
@@ -43742,7 +43742,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07394414462</t>
+            <t xml:space="preserve">01882616840</t>
           </r>
         </is>
       </c>
@@ -43753,7 +43753,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -43801,7 +43801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLER DIAS LADEIRA DA SILVA</t>
+            <t xml:space="preserve">WESLEY PEREIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -43811,7 +43811,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.752.806-04</t>
+            <t xml:space="preserve">080.589.316-40</t>
           </r>
         </is>
       </c>
@@ -43821,7 +43821,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01225273506</t>
+            <t xml:space="preserve">04884904684</t>
           </r>
         </is>
       </c>
@@ -43832,7 +43832,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/10/2027</t>
+            <t xml:space="preserve">07/10/2027</t>
           </r>
         </is>
       </c>
@@ -43873,14 +43873,14 @@
       <c r="T553" s="12" t="inlineStr"/>
       <c r="U553" s="1" t="inlineStr"/>
     </row>
-    <row r="554" customHeight="1" ht="21">
+    <row r="554" customHeight="1" ht="22">
       <c r="A554" s="1" t="inlineStr"/>
       <c r="B554" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLER RODRIGUES DUARTE   </t>
+            <t xml:space="preserve">WILDENBERG DAYRELL BENEDITO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -43890,7 +43890,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">842.137.796-53</t>
+            <t xml:space="preserve">146.120.596-46</t>
           </r>
         </is>
       </c>
@@ -43900,7 +43900,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00718175645</t>
+            <t xml:space="preserve">07394414462</t>
           </r>
         </is>
       </c>
@@ -43911,7 +43911,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/11/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -43959,7 +43959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLIAN LOURENCO DA SILVA </t>
+            <t xml:space="preserve">WILLER DIAS LADEIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -43969,7 +43969,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.769.226-39</t>
+            <t xml:space="preserve">868.752.806-04</t>
           </r>
         </is>
       </c>
@@ -43979,7 +43979,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04158429281</t>
+            <t xml:space="preserve">01225273506</t>
           </r>
         </is>
       </c>
@@ -43990,7 +43990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/09/2027</t>
+            <t xml:space="preserve">05/10/2027</t>
           </r>
         </is>
       </c>
@@ -44031,14 +44031,14 @@
       <c r="T555" s="12" t="inlineStr"/>
       <c r="U555" s="1" t="inlineStr"/>
     </row>
-    <row r="556" customHeight="1" ht="22">
+    <row r="556" customHeight="1" ht="21">
       <c r="A556" s="1" t="inlineStr"/>
       <c r="B556" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILSON FRANCISCO MARZANO SILVEIRA </t>
+            <t xml:space="preserve">WILLER RODRIGUES DUARTE   </t>
           </r>
         </is>
       </c>
@@ -44048,7 +44048,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">049.781.696-23</t>
+            <t xml:space="preserve">842.137.796-53</t>
           </r>
         </is>
       </c>
@@ -44058,7 +44058,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01673877203</t>
+            <t xml:space="preserve">00718175645</t>
           </r>
         </is>
       </c>
@@ -44069,7 +44069,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">17/11/2026</t>
           </r>
         </is>
       </c>
@@ -44110,14 +44110,14 @@
       <c r="T556" s="12" t="inlineStr"/>
       <c r="U556" s="1" t="inlineStr"/>
     </row>
-    <row r="557" customHeight="1" ht="22">
+    <row r="557" customHeight="1" ht="21">
       <c r="A557" s="1" t="inlineStr"/>
       <c r="B557" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ZENILSON MARCELINO DE CARVALHO</t>
+            <t xml:space="preserve">WILLIAN LOURENCO DA SILVA </t>
           </r>
         </is>
       </c>
@@ -44127,7 +44127,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">039.291.734-33</t>
+            <t xml:space="preserve">065.769.226-39</t>
           </r>
         </is>
       </c>
@@ -44137,7 +44137,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04371720578</t>
+            <t xml:space="preserve">04158429281</t>
           </r>
         </is>
       </c>
@@ -44148,7 +44148,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">15/09/2027</t>
           </r>
         </is>
       </c>
@@ -44189,66 +44189,162 @@
       <c r="T557" s="12" t="inlineStr"/>
       <c r="U557" s="1" t="inlineStr"/>
     </row>
-    <row r="558" customHeight="1" ht="15">
+    <row r="558" customHeight="1" ht="22">
       <c r="A558" s="1" t="inlineStr"/>
-      <c r="B558" s="1" t="inlineStr"/>
-      <c r="C558" s="14" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-       </rPr>
-            <t xml:space="preserve">Total Ativo: 551</t>
-          </r>
-        </is>
-      </c>
-      <c r="D558" s="15" t="inlineStr"/>
-      <c r="E558" s="1" t="inlineStr"/>
-      <c r="F558" s="1" t="inlineStr"/>
-      <c r="G558" s="1" t="inlineStr"/>
-      <c r="H558" s="1" t="inlineStr"/>
-      <c r="I558" s="1" t="inlineStr"/>
-      <c r="J558" s="1" t="inlineStr"/>
-      <c r="K558" s="1" t="inlineStr"/>
-      <c r="L558" s="1" t="inlineStr"/>
-      <c r="M558" s="1" t="inlineStr"/>
-      <c r="N558" s="1" t="inlineStr"/>
-      <c r="O558" s="1" t="inlineStr"/>
-      <c r="P558" s="1" t="inlineStr"/>
-      <c r="Q558" s="1" t="inlineStr"/>
-      <c r="R558" s="1" t="inlineStr"/>
-      <c r="S558" s="1" t="inlineStr"/>
-      <c r="T558" s="1" t="inlineStr"/>
+      <c r="B558" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">WILSON FRANCISCO MARZANO SILVEIRA </t>
+          </r>
+        </is>
+      </c>
+      <c r="C558" s="10" t="inlineStr"/>
+      <c r="D558" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">049.781.696-23</t>
+          </r>
+        </is>
+      </c>
+      <c r="E558" s="12" t="inlineStr"/>
+      <c r="F558" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">01673877203</t>
+          </r>
+        </is>
+      </c>
+      <c r="G558" s="12" t="inlineStr"/>
+      <c r="H558" s="12" t="inlineStr"/>
+      <c r="I558" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">10/08/2027</t>
+          </r>
+        </is>
+      </c>
+      <c r="J558" s="12" t="inlineStr"/>
+      <c r="K558" s="12" t="inlineStr"/>
+      <c r="L558" s="12" t="inlineStr"/>
+      <c r="M558" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N558" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O558" s="10" t="inlineStr"/>
+      <c r="P558" s="10" t="inlineStr"/>
+      <c r="Q558" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R558" s="12" t="inlineStr"/>
+      <c r="S558" s="12" t="inlineStr"/>
+      <c r="T558" s="12" t="inlineStr"/>
       <c r="U558" s="1" t="inlineStr"/>
     </row>
-    <row r="559" customHeight="1" ht="15">
+    <row r="559" customHeight="1" ht="22">
       <c r="A559" s="1" t="inlineStr"/>
-      <c r="B559" s="1" t="inlineStr"/>
-      <c r="C559" s="14" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-       </rPr>
-            <t xml:space="preserve">Total Inativo: 0</t>
-          </r>
-        </is>
-      </c>
-      <c r="D559" s="15" t="inlineStr"/>
-      <c r="E559" s="1" t="inlineStr"/>
-      <c r="F559" s="1" t="inlineStr"/>
-      <c r="G559" s="1" t="inlineStr"/>
-      <c r="H559" s="1" t="inlineStr"/>
-      <c r="I559" s="1" t="inlineStr"/>
-      <c r="J559" s="1" t="inlineStr"/>
-      <c r="K559" s="1" t="inlineStr"/>
-      <c r="L559" s="1" t="inlineStr"/>
-      <c r="M559" s="1" t="inlineStr"/>
-      <c r="N559" s="1" t="inlineStr"/>
-      <c r="O559" s="1" t="inlineStr"/>
-      <c r="P559" s="1" t="inlineStr"/>
-      <c r="Q559" s="1" t="inlineStr"/>
-      <c r="R559" s="1" t="inlineStr"/>
-      <c r="S559" s="1" t="inlineStr"/>
-      <c r="T559" s="1" t="inlineStr"/>
+      <c r="B559" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">ZENILSON MARCELINO DE CARVALHO</t>
+          </r>
+        </is>
+      </c>
+      <c r="C559" s="10" t="inlineStr"/>
+      <c r="D559" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">039.291.734-33</t>
+          </r>
+        </is>
+      </c>
+      <c r="E559" s="12" t="inlineStr"/>
+      <c r="F559" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">04371720578</t>
+          </r>
+        </is>
+      </c>
+      <c r="G559" s="12" t="inlineStr"/>
+      <c r="H559" s="12" t="inlineStr"/>
+      <c r="I559" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">13/01/2027</t>
+          </r>
+        </is>
+      </c>
+      <c r="J559" s="12" t="inlineStr"/>
+      <c r="K559" s="12" t="inlineStr"/>
+      <c r="L559" s="12" t="inlineStr"/>
+      <c r="M559" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N559" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O559" s="10" t="inlineStr"/>
+      <c r="P559" s="10" t="inlineStr"/>
+      <c r="Q559" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R559" s="12" t="inlineStr"/>
+      <c r="S559" s="12" t="inlineStr"/>
+      <c r="T559" s="12" t="inlineStr"/>
       <c r="U559" s="1" t="inlineStr"/>
     </row>
     <row r="560" customHeight="1" ht="15">
@@ -44259,7 +44355,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">Total Geral: 551</t>
+            <t xml:space="preserve">Total Ativo: 553</t>
           </r>
         </is>
       </c>
@@ -44285,8 +44381,16 @@
     <row r="561" customHeight="1" ht="15">
       <c r="A561" s="1" t="inlineStr"/>
       <c r="B561" s="1" t="inlineStr"/>
-      <c r="C561" s="1" t="inlineStr"/>
-      <c r="D561" s="1" t="inlineStr"/>
+      <c r="C561" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Total Inativo: 0</t>
+          </r>
+        </is>
+      </c>
+      <c r="D561" s="15" t="inlineStr"/>
       <c r="E561" s="1" t="inlineStr"/>
       <c r="F561" s="1" t="inlineStr"/>
       <c r="G561" s="1" t="inlineStr"/>
@@ -44300,7 +44404,61 @@
       <c r="O561" s="1" t="inlineStr"/>
       <c r="P561" s="1" t="inlineStr"/>
       <c r="Q561" s="1" t="inlineStr"/>
-      <c r="R561" s="16" t="inlineStr">
+      <c r="R561" s="1" t="inlineStr"/>
+      <c r="S561" s="1" t="inlineStr"/>
+      <c r="T561" s="1" t="inlineStr"/>
+      <c r="U561" s="1" t="inlineStr"/>
+    </row>
+    <row r="562" customHeight="1" ht="15">
+      <c r="A562" s="1" t="inlineStr"/>
+      <c r="B562" s="1" t="inlineStr"/>
+      <c r="C562" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Total Geral: 553</t>
+          </r>
+        </is>
+      </c>
+      <c r="D562" s="15" t="inlineStr"/>
+      <c r="E562" s="1" t="inlineStr"/>
+      <c r="F562" s="1" t="inlineStr"/>
+      <c r="G562" s="1" t="inlineStr"/>
+      <c r="H562" s="1" t="inlineStr"/>
+      <c r="I562" s="1" t="inlineStr"/>
+      <c r="J562" s="1" t="inlineStr"/>
+      <c r="K562" s="1" t="inlineStr"/>
+      <c r="L562" s="1" t="inlineStr"/>
+      <c r="M562" s="1" t="inlineStr"/>
+      <c r="N562" s="1" t="inlineStr"/>
+      <c r="O562" s="1" t="inlineStr"/>
+      <c r="P562" s="1" t="inlineStr"/>
+      <c r="Q562" s="1" t="inlineStr"/>
+      <c r="R562" s="1" t="inlineStr"/>
+      <c r="S562" s="1" t="inlineStr"/>
+      <c r="T562" s="1" t="inlineStr"/>
+      <c r="U562" s="1" t="inlineStr"/>
+    </row>
+    <row r="563" customHeight="1" ht="15">
+      <c r="A563" s="1" t="inlineStr"/>
+      <c r="B563" s="1" t="inlineStr"/>
+      <c r="C563" s="1" t="inlineStr"/>
+      <c r="D563" s="1" t="inlineStr"/>
+      <c r="E563" s="1" t="inlineStr"/>
+      <c r="F563" s="1" t="inlineStr"/>
+      <c r="G563" s="1" t="inlineStr"/>
+      <c r="H563" s="1" t="inlineStr"/>
+      <c r="I563" s="1" t="inlineStr"/>
+      <c r="J563" s="1" t="inlineStr"/>
+      <c r="K563" s="1" t="inlineStr"/>
+      <c r="L563" s="1" t="inlineStr"/>
+      <c r="M563" s="1" t="inlineStr"/>
+      <c r="N563" s="1" t="inlineStr"/>
+      <c r="O563" s="1" t="inlineStr"/>
+      <c r="P563" s="1" t="inlineStr"/>
+      <c r="Q563" s="1" t="inlineStr"/>
+      <c r="R563" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44309,8 +44467,8 @@
           </r>
         </is>
       </c>
-      <c r="S561" s="17" t="inlineStr"/>
-      <c r="T561" s="16" t="inlineStr">
+      <c r="S563" s="17" t="inlineStr"/>
+      <c r="T563" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44319,7 +44477,7 @@
           </r>
         </is>
       </c>
-      <c r="U561" s="1" t="inlineStr"/>
+      <c r="U563" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -47642,10 +47800,22 @@
     <mergeCell ref="I557:L557"/>
     <mergeCell ref="N557:P557"/>
     <mergeCell ref="Q557:T557"/>
-    <mergeCell ref="C558:D558"/>
-    <mergeCell ref="C559:D559"/>
+    <mergeCell ref="B558:C558"/>
+    <mergeCell ref="D558:E558"/>
+    <mergeCell ref="F558:H558"/>
+    <mergeCell ref="I558:L558"/>
+    <mergeCell ref="N558:P558"/>
+    <mergeCell ref="Q558:T558"/>
+    <mergeCell ref="B559:C559"/>
+    <mergeCell ref="D559:E559"/>
+    <mergeCell ref="F559:H559"/>
+    <mergeCell ref="I559:L559"/>
+    <mergeCell ref="N559:P559"/>
+    <mergeCell ref="Q559:T559"/>
     <mergeCell ref="C560:D560"/>
-    <mergeCell ref="R561:S561"/>
+    <mergeCell ref="C561:D561"/>
+    <mergeCell ref="C562:D562"/>
+    <mergeCell ref="R563:S563"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rIdDr1"/>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="597332770" name="Picture">
+        <xdr:cNvPr id="1378179387" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1378179387" name="Picture">
+        <xdr:cNvPr id="878250374" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -3226,7 +3226,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/11/2026</t>
+            <t xml:space="preserve">20/10/2027</t>
           </r>
         </is>
       </c>
@@ -6781,7 +6781,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2026</t>
+            <t xml:space="preserve">14/10/2027</t>
           </r>
         </is>
       </c>
@@ -19184,7 +19184,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/09/2026</t>
+            <t xml:space="preserve">14/10/2027</t>
           </r>
         </is>
       </c>
@@ -27637,7 +27637,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">14/10/2027</t>
           </r>
         </is>
       </c>
@@ -30007,7 +30007,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">02/10/2027</t>
           </r>
         </is>
       </c>
@@ -45728,7 +45728,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/11/2026</t>
+            <t xml:space="preserve">20/10/2027</t>
           </r>
         </is>
       </c>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="512137061" name="Picture">
+        <xdr:cNvPr id="1065174443" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -5438,7 +5438,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/10/2027</t>
+            <t xml:space="preserve">27/10/2027</t>
           </r>
         </is>
       </c>
@@ -23292,7 +23292,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -28791,7 +28791,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS GONÇALVES MARTINS</t>
+            <t xml:space="preserve">LUCAS DO ROSARIO SANTOS</t>
           </r>
         </is>
       </c>
@@ -28801,7 +28801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">085.552.436-70</t>
+            <t xml:space="preserve">112.127.256-89</t>
           </r>
         </is>
       </c>
@@ -28811,7 +28811,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4693218713</t>
+            <t xml:space="preserve">06718162157</t>
           </r>
         </is>
       </c>
@@ -28822,7 +28822,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">16/10/2027</t>
           </r>
         </is>
       </c>
@@ -28870,7 +28870,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS LUIZ ALVES</t>
+            <t xml:space="preserve">LUCAS GONÇALVES MARTINS</t>
           </r>
         </is>
       </c>
@@ -28880,7 +28880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.062.856-91</t>
+            <t xml:space="preserve">085.552.436-70</t>
           </r>
         </is>
       </c>
@@ -28890,7 +28890,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01322002444</t>
+            <t xml:space="preserve">4693218713</t>
           </r>
         </is>
       </c>
@@ -28901,7 +28901,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -28949,7 +28949,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS SANTOS DE QUEIROZ</t>
+            <t xml:space="preserve">LUCAS LUIZ ALVES</t>
           </r>
         </is>
       </c>
@@ -28959,7 +28959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">113.927.196-23</t>
+            <t xml:space="preserve">819.062.856-91</t>
           </r>
         </is>
       </c>
@@ -28969,7 +28969,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05160627501</t>
+            <t xml:space="preserve">01322002444</t>
           </r>
         </is>
       </c>
@@ -28980,7 +28980,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -29028,7 +29028,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS SILVA FRANCA</t>
+            <t xml:space="preserve">LUCAS SANTOS DE QUEIROZ</t>
           </r>
         </is>
       </c>
@@ -29038,7 +29038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">013.991.046-83</t>
+            <t xml:space="preserve">113.927.196-23</t>
           </r>
         </is>
       </c>
@@ -29048,7 +29048,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02413059875</t>
+            <t xml:space="preserve">05160627501</t>
           </r>
         </is>
       </c>
@@ -29059,7 +29059,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -29107,7 +29107,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCAS VELOSO AMANCIO MACIEL</t>
+            <t xml:space="preserve">LUCAS SILVA FRANCA</t>
           </r>
         </is>
       </c>
@@ -29117,7 +29117,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">135.218.266-19</t>
+            <t xml:space="preserve">013.991.046-83</t>
           </r>
         </is>
       </c>
@@ -29127,7 +29127,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06383476601</t>
+            <t xml:space="preserve">02413059875</t>
           </r>
         </is>
       </c>
@@ -29138,7 +29138,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2026</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -29179,14 +29179,14 @@
       <c r="T367" s="12" t="inlineStr"/>
       <c r="U367" s="1" t="inlineStr"/>
     </row>
-    <row r="368" customHeight="1" ht="22">
+    <row r="368" customHeight="1" ht="21">
       <c r="A368" s="1" t="inlineStr"/>
       <c r="B368" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIA FERNANDA PEREIRA DA COSTA</t>
+            <t xml:space="preserve">LUCAS VELOSO AMANCIO MACIEL</t>
           </r>
         </is>
       </c>
@@ -29196,7 +29196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">031.585.776-58</t>
+            <t xml:space="preserve">135.218.266-19</t>
           </r>
         </is>
       </c>
@@ -29206,7 +29206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">053314624601</t>
+            <t xml:space="preserve">06383476601</t>
           </r>
         </is>
       </c>
@@ -29217,7 +29217,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">11/07/2026</t>
           </r>
         </is>
       </c>
@@ -29258,14 +29258,14 @@
       <c r="T368" s="12" t="inlineStr"/>
       <c r="U368" s="1" t="inlineStr"/>
     </row>
-    <row r="369" customHeight="1" ht="21">
+    <row r="369" customHeight="1" ht="22">
       <c r="A369" s="1" t="inlineStr"/>
       <c r="B369" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIANE DE FATIMA R. COSTA    </t>
+            <t xml:space="preserve">LUCIA FERNANDA PEREIRA DA COSTA</t>
           </r>
         </is>
       </c>
@@ -29275,7 +29275,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.763.156-69</t>
+            <t xml:space="preserve">031.585.776-58</t>
           </r>
         </is>
       </c>
@@ -29285,7 +29285,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04611449989</t>
+            <t xml:space="preserve">053314624601</t>
           </r>
         </is>
       </c>
@@ -29296,7 +29296,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -29344,7 +29344,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIANO PAULINO DA COSTA</t>
+            <t xml:space="preserve">LUCIANE DE FATIMA R. COSTA    </t>
           </r>
         </is>
       </c>
@@ -29354,7 +29354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">050.130.496-79</t>
+            <t xml:space="preserve">093.763.156-69</t>
           </r>
         </is>
       </c>
@@ -29364,7 +29364,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03103773460</t>
+            <t xml:space="preserve">04611449989</t>
           </r>
         </is>
       </c>
@@ -29375,7 +29375,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/10/2027</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -29423,7 +29423,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIO AURELIANO DA SILVA</t>
+            <t xml:space="preserve">LUCIANO PAULINO DA COSTA</t>
           </r>
         </is>
       </c>
@@ -29433,7 +29433,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">047.703.276-17</t>
+            <t xml:space="preserve">050.130.496-79</t>
           </r>
         </is>
       </c>
@@ -29443,7 +29443,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04593463442</t>
+            <t xml:space="preserve">03103773460</t>
           </r>
         </is>
       </c>
@@ -29454,7 +29454,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -29502,7 +29502,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUCIO FABIO FERREIRA</t>
+            <t xml:space="preserve">LUCIO AURELIANO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -29512,7 +29512,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">006.683.332-94</t>
+            <t xml:space="preserve">047.703.276-17</t>
           </r>
         </is>
       </c>
@@ -29522,7 +29522,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04484954449</t>
+            <t xml:space="preserve">04593463442</t>
           </r>
         </is>
       </c>
@@ -29533,7 +29533,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2031</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -29581,7 +29581,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIS CARLOS VELOSO</t>
+            <t xml:space="preserve">LUCIO FABIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -29591,7 +29591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">943.062.656-68</t>
+            <t xml:space="preserve">006.683.332-94</t>
           </r>
         </is>
       </c>
@@ -29601,7 +29601,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00863735779</t>
+            <t xml:space="preserve">04484954449</t>
           </r>
         </is>
       </c>
@@ -29612,7 +29612,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/10/2027</t>
+            <t xml:space="preserve">10/08/2031</t>
           </r>
         </is>
       </c>
@@ -29660,7 +29660,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ ANDRE BORGES CAIXETA</t>
+            <t xml:space="preserve">LUIS CARLOS VELOSO</t>
           </r>
         </is>
       </c>
@@ -29670,7 +29670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.942.196-77</t>
+            <t xml:space="preserve">943.062.656-68</t>
           </r>
         </is>
       </c>
@@ -29680,7 +29680,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01667588932</t>
+            <t xml:space="preserve">00863735779</t>
           </r>
         </is>
       </c>
@@ -29691,7 +29691,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -29739,7 +29739,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ ANTONIO DA SILVA</t>
+            <t xml:space="preserve">LUIZ ANDRE BORGES CAIXETA</t>
           </r>
         </is>
       </c>
@@ -29749,7 +29749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">778.833.066-34</t>
+            <t xml:space="preserve">046.942.196-77</t>
           </r>
         </is>
       </c>
@@ -29759,7 +29759,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02831837732</t>
+            <t xml:space="preserve">01667588932</t>
           </r>
         </is>
       </c>
@@ -29770,7 +29770,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -29818,7 +29818,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ CARLOS DE ASSIS</t>
+            <t xml:space="preserve">LUIZ ANTONIO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -29828,7 +29828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">063.432.686-42</t>
+            <t xml:space="preserve">778.833.066-34</t>
           </r>
         </is>
       </c>
@@ -29838,7 +29838,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02836643209</t>
+            <t xml:space="preserve">02831837732</t>
           </r>
         </is>
       </c>
@@ -29849,7 +29849,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/06/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -29897,7 +29897,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ FERNANDO GONCALVES</t>
+            <t xml:space="preserve">LUIZ CARLOS DE ASSIS</t>
           </r>
         </is>
       </c>
@@ -29907,7 +29907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">066.587.606-83</t>
+            <t xml:space="preserve">063.432.686-42</t>
           </r>
         </is>
       </c>
@@ -29917,7 +29917,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04319056439</t>
+            <t xml:space="preserve">02836643209</t>
           </r>
         </is>
       </c>
@@ -29928,7 +29928,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/10/2026</t>
+            <t xml:space="preserve">25/06/2027</t>
           </r>
         </is>
       </c>
@@ -29976,7 +29976,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ GONZAGA DA SILVA</t>
+            <t xml:space="preserve">LUIZ FERNANDO GONCALVES</t>
           </r>
         </is>
       </c>
@@ -29986,7 +29986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">939.705.796-00</t>
+            <t xml:space="preserve">066.587.606-83</t>
           </r>
         </is>
       </c>
@@ -29996,7 +29996,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01099082690</t>
+            <t xml:space="preserve">04319056439</t>
           </r>
         </is>
       </c>
@@ -30007,7 +30007,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">09/10/2026</t>
           </r>
         </is>
       </c>
@@ -30055,7 +30055,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ GUSTAVO SANTOS LIMA</t>
+            <t xml:space="preserve">LUIZ GONZAGA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -30065,7 +30065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">083.760.036-74</t>
+            <t xml:space="preserve">939.705.796-00</t>
           </r>
         </is>
       </c>
@@ -30075,7 +30075,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04424986322</t>
+            <t xml:space="preserve">01099082690</t>
           </r>
         </is>
       </c>
@@ -30086,7 +30086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -30134,7 +30134,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ HENRIQUE E MARTINS VIEIRA  </t>
+            <t xml:space="preserve">LUIZ GUSTAVO SANTOS LIMA</t>
           </r>
         </is>
       </c>
@@ -30144,7 +30144,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.281.616-04</t>
+            <t xml:space="preserve">083.760.036-74</t>
           </r>
         </is>
       </c>
@@ -30154,7 +30154,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04521971771</t>
+            <t xml:space="preserve">04424986322</t>
           </r>
         </is>
       </c>
@@ -30165,7 +30165,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -30213,7 +30213,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUIZ RICARDO DE MELO</t>
+            <t xml:space="preserve">LUIZ HENRIQUE E MARTINS VIEIRA  </t>
           </r>
         </is>
       </c>
@@ -30223,7 +30223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.995.666-10</t>
+            <t xml:space="preserve">088.281.616-04</t>
           </r>
         </is>
       </c>
@@ -30233,7 +30233,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03344105706</t>
+            <t xml:space="preserve">04521971771</t>
           </r>
         </is>
       </c>
@@ -30244,7 +30244,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -30292,7 +30292,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LUZIA MARIA DOS SANTOS</t>
+            <t xml:space="preserve">LUIZ RICARDO DE MELO</t>
           </r>
         </is>
       </c>
@@ -30302,7 +30302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.951.396-59</t>
+            <t xml:space="preserve">076.995.666-10</t>
           </r>
         </is>
       </c>
@@ -30312,7 +30312,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04148424907</t>
+            <t xml:space="preserve">03344105706</t>
           </r>
         </is>
       </c>
@@ -30323,7 +30323,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/12/2023</t>
+            <t xml:space="preserve">29/07/2027</t>
           </r>
         </is>
       </c>
@@ -30371,7 +30371,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAIKY SANTANA FERNANDES</t>
+            <t xml:space="preserve">LUZIA MARIA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -30381,7 +30381,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">140.188.876-39</t>
+            <t xml:space="preserve">026.951.396-59</t>
           </r>
         </is>
       </c>
@@ -30391,7 +30391,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06777417203</t>
+            <t xml:space="preserve">04148424907</t>
           </r>
         </is>
       </c>
@@ -30402,7 +30402,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/07/2027</t>
+            <t xml:space="preserve">31/12/2023</t>
           </r>
         </is>
       </c>
@@ -30450,7 +30450,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MANOEL SANTOS MORAES</t>
+            <t xml:space="preserve">MAIKY SANTANA FERNANDES</t>
           </r>
         </is>
       </c>
@@ -30460,7 +30460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">715.808.326-87</t>
+            <t xml:space="preserve">140.188.876-39</t>
           </r>
         </is>
       </c>
@@ -30470,7 +30470,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01155974255</t>
+            <t xml:space="preserve">06777417203</t>
           </r>
         </is>
       </c>
@@ -30481,7 +30481,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02/10/2027</t>
+            <t xml:space="preserve">24/07/2027</t>
           </r>
         </is>
       </c>
@@ -30529,7 +30529,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO BATISTA DOS SANTOS</t>
+            <t xml:space="preserve">MANOEL SANTOS MORAES</t>
           </r>
         </is>
       </c>
@@ -30539,7 +30539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">043.142.726-78</t>
+            <t xml:space="preserve">715.808.326-87</t>
           </r>
         </is>
       </c>
@@ -30549,7 +30549,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02450313294</t>
+            <t xml:space="preserve">01155974255</t>
           </r>
         </is>
       </c>
@@ -30560,7 +30560,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">02/10/2027</t>
           </r>
         </is>
       </c>
@@ -30608,7 +30608,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO HENRIQUE CAETANO</t>
+            <t xml:space="preserve">MARCELO BATISTA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -30618,7 +30618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">034.939.999-92</t>
+            <t xml:space="preserve">043.142.726-78</t>
           </r>
         </is>
       </c>
@@ -30628,7 +30628,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02099361590</t>
+            <t xml:space="preserve">02450313294</t>
           </r>
         </is>
       </c>
@@ -30639,7 +30639,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -30680,14 +30680,14 @@
       <c r="T386" s="12" t="inlineStr"/>
       <c r="U386" s="1" t="inlineStr"/>
     </row>
-    <row r="387" customHeight="1" ht="22">
+    <row r="387" customHeight="1" ht="21">
       <c r="A387" s="1" t="inlineStr"/>
       <c r="B387" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO LUCIANO DE SOUZA OLIVEIRA</t>
+            <t xml:space="preserve">MARCELO HENRIQUE CAETANO</t>
           </r>
         </is>
       </c>
@@ -30697,7 +30697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">073.595.556-55</t>
+            <t xml:space="preserve">034.939.999-92</t>
           </r>
         </is>
       </c>
@@ -30707,7 +30707,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03641355881</t>
+            <t xml:space="preserve">02099361590</t>
           </r>
         </is>
       </c>
@@ -30718,7 +30718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -30759,14 +30759,14 @@
       <c r="T387" s="12" t="inlineStr"/>
       <c r="U387" s="1" t="inlineStr"/>
     </row>
-    <row r="388" customHeight="1" ht="21">
+    <row r="388" customHeight="1" ht="22">
       <c r="A388" s="1" t="inlineStr"/>
       <c r="B388" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO MARTINS BORGES</t>
+            <t xml:space="preserve">MARCELO LUCIANO DE SOUZA OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -30776,7 +30776,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">002.744.406-60</t>
+            <t xml:space="preserve">073.595.556-55</t>
           </r>
         </is>
       </c>
@@ -30786,7 +30786,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02783779084</t>
+            <t xml:space="preserve">03641355881</t>
           </r>
         </is>
       </c>
@@ -30797,7 +30797,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2025</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -30845,7 +30845,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO MENDES DOS SANTOS</t>
+            <t xml:space="preserve">MARCELO MARTINS BORGES</t>
           </r>
         </is>
       </c>
@@ -30855,7 +30855,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">901.945.276-20</t>
+            <t xml:space="preserve">002.744.406-60</t>
           </r>
         </is>
       </c>
@@ -30865,7 +30865,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04168367162</t>
+            <t xml:space="preserve">02783779084</t>
           </r>
         </is>
       </c>
@@ -30876,7 +30876,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">31/07/2025</t>
           </r>
         </is>
       </c>
@@ -30924,7 +30924,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCELO TADEU DE OLIVEIRA</t>
+            <t xml:space="preserve">MARCELO MENDES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -30934,7 +30934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">049.321.486-07</t>
+            <t xml:space="preserve">901.945.276-20</t>
           </r>
         </is>
       </c>
@@ -30944,7 +30944,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01620321495</t>
+            <t xml:space="preserve">04168367162</t>
           </r>
         </is>
       </c>
@@ -30955,7 +30955,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -31003,7 +31003,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ALAIR CORREA  </t>
+            <t xml:space="preserve">MARCELO TADEU DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -31013,7 +31013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">549.576.056-53</t>
+            <t xml:space="preserve">049.321.486-07</t>
           </r>
         </is>
       </c>
@@ -31023,7 +31023,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02871826370</t>
+            <t xml:space="preserve">01620321495</t>
           </r>
         </is>
       </c>
@@ -31034,7 +31034,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -31082,7 +31082,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ANTONIO FERREIRA</t>
+            <t xml:space="preserve">MARCIO ALAIR CORREA  </t>
           </r>
         </is>
       </c>
@@ -31092,7 +31092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">902.851.406-63</t>
+            <t xml:space="preserve">549.576.056-53</t>
           </r>
         </is>
       </c>
@@ -31102,7 +31102,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02516992442</t>
+            <t xml:space="preserve">02871826370</t>
           </r>
         </is>
       </c>
@@ -31113,7 +31113,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -31154,14 +31154,14 @@
       <c r="T392" s="12" t="inlineStr"/>
       <c r="U392" s="1" t="inlineStr"/>
     </row>
-    <row r="393" customHeight="1" ht="22">
+    <row r="393" customHeight="1" ht="21">
       <c r="A393" s="1" t="inlineStr"/>
       <c r="B393" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO ANTONIO PARREIRAS DA PAZ</t>
+            <t xml:space="preserve">MARCIO ANTONIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -31171,7 +31171,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">577.128.916-72</t>
+            <t xml:space="preserve">902.851.406-63</t>
           </r>
         </is>
       </c>
@@ -31181,7 +31181,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02890495585</t>
+            <t xml:space="preserve">02516992442</t>
           </r>
         </is>
       </c>
@@ -31192,7 +31192,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -31233,14 +31233,14 @@
       <c r="T393" s="12" t="inlineStr"/>
       <c r="U393" s="1" t="inlineStr"/>
     </row>
-    <row r="394" customHeight="1" ht="21">
+    <row r="394" customHeight="1" ht="22">
       <c r="A394" s="1" t="inlineStr"/>
       <c r="B394" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO DA SILVA OTTONI</t>
+            <t xml:space="preserve">MARCIO ANTONIO PARREIRAS DA PAZ</t>
           </r>
         </is>
       </c>
@@ -31250,7 +31250,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.607.566-51</t>
+            <t xml:space="preserve">577.128.916-72</t>
           </r>
         </is>
       </c>
@@ -31260,7 +31260,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01687919581</t>
+            <t xml:space="preserve">02890495585</t>
           </r>
         </is>
       </c>
@@ -31271,7 +31271,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/02/2026</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -31312,14 +31312,14 @@
       <c r="T394" s="12" t="inlineStr"/>
       <c r="U394" s="1" t="inlineStr"/>
     </row>
-    <row r="395" customHeight="1" ht="22">
+    <row r="395" customHeight="1" ht="21">
       <c r="A395" s="1" t="inlineStr"/>
       <c r="B395" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIO FLAVIO ANDRADE ALMEIDA</t>
+            <t xml:space="preserve">MARCIO DA SILVA OTTONI</t>
           </r>
         </is>
       </c>
@@ -31329,7 +31329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.017.466-97</t>
+            <t xml:space="preserve">026.607.566-51</t>
           </r>
         </is>
       </c>
@@ -31339,7 +31339,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289067720</t>
+            <t xml:space="preserve">01687919581</t>
           </r>
         </is>
       </c>
@@ -31350,7 +31350,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/07/2027</t>
+            <t xml:space="preserve">21/02/2026</t>
           </r>
         </is>
       </c>
@@ -31391,14 +31391,14 @@
       <c r="T395" s="12" t="inlineStr"/>
       <c r="U395" s="1" t="inlineStr"/>
     </row>
-    <row r="396" customHeight="1" ht="21">
+    <row r="396" customHeight="1" ht="22">
       <c r="A396" s="1" t="inlineStr"/>
       <c r="B396" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCIONE APARECIDO MARTINS</t>
+            <t xml:space="preserve">MARCIO FLAVIO ANDRADE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -31408,7 +31408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">041.411.046-39</t>
+            <t xml:space="preserve">040.017.466-97</t>
           </r>
         </is>
       </c>
@@ -31418,7 +31418,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03863886454</t>
+            <t xml:space="preserve">04289067720</t>
           </r>
         </is>
       </c>
@@ -31429,7 +31429,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">06/07/2027</t>
           </r>
         </is>
       </c>
@@ -31470,14 +31470,14 @@
       <c r="T396" s="12" t="inlineStr"/>
       <c r="U396" s="1" t="inlineStr"/>
     </row>
-    <row r="397" customHeight="1" ht="22">
+    <row r="397" customHeight="1" ht="21">
       <c r="A397" s="1" t="inlineStr"/>
       <c r="B397" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCO AURELIO HENRIQUE DOS SANTOS</t>
+            <t xml:space="preserve">MARCIONE APARECIDO MARTINS</t>
           </r>
         </is>
       </c>
@@ -31487,7 +31487,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.690.426-50</t>
+            <t xml:space="preserve">041.411.046-39</t>
           </r>
         </is>
       </c>
@@ -31497,7 +31497,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05105181704</t>
+            <t xml:space="preserve">03863886454</t>
           </r>
         </is>
       </c>
@@ -31508,7 +31508,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -31549,14 +31549,14 @@
       <c r="T397" s="12" t="inlineStr"/>
       <c r="U397" s="1" t="inlineStr"/>
     </row>
-    <row r="398" customHeight="1" ht="21">
+    <row r="398" customHeight="1" ht="22">
       <c r="A398" s="1" t="inlineStr"/>
       <c r="B398" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANDRÉ DE ALMEIDA</t>
+            <t xml:space="preserve">MARCO AURELIO HENRIQUE DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -31566,7 +31566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">056.770.516-16</t>
+            <t xml:space="preserve">110.690.426-50</t>
           </r>
         </is>
       </c>
@@ -31576,7 +31576,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03502926908</t>
+            <t xml:space="preserve">05105181704</t>
           </r>
         </is>
       </c>
@@ -31587,7 +31587,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -31635,7 +31635,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANTONIO COSTA</t>
+            <t xml:space="preserve">MARCOS ANDRÉ DE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -31645,7 +31645,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.627.216-06</t>
+            <t xml:space="preserve">056.770.516-16</t>
           </r>
         </is>
       </c>
@@ -31655,7 +31655,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05971763818</t>
+            <t xml:space="preserve">03502926908</t>
           </r>
         </is>
       </c>
@@ -31666,7 +31666,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -31707,14 +31707,14 @@
       <c r="T399" s="12" t="inlineStr"/>
       <c r="U399" s="1" t="inlineStr"/>
     </row>
-    <row r="400" customHeight="1" ht="22">
+    <row r="400" customHeight="1" ht="21">
       <c r="A400" s="1" t="inlineStr"/>
       <c r="B400" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS ANTONIO PEREIRA DA SILVA</t>
+            <t xml:space="preserve">MARCOS ANTONIO COSTA</t>
           </r>
         </is>
       </c>
@@ -31724,7 +31724,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">952.874.346-34</t>
+            <t xml:space="preserve">077.627.216-06</t>
           </r>
         </is>
       </c>
@@ -31734,7 +31734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03056193881</t>
+            <t xml:space="preserve">05971763818</t>
           </r>
         </is>
       </c>
@@ -31745,7 +31745,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -31786,14 +31786,14 @@
       <c r="T400" s="12" t="inlineStr"/>
       <c r="U400" s="1" t="inlineStr"/>
     </row>
-    <row r="401" customHeight="1" ht="21">
+    <row r="401" customHeight="1" ht="22">
       <c r="A401" s="1" t="inlineStr"/>
       <c r="B401" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS AURELIO BARBOSA</t>
+            <t xml:space="preserve">MARCOS ANTONIO PEREIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -31803,7 +31803,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.909.046-28</t>
+            <t xml:space="preserve">952.874.346-34</t>
           </r>
         </is>
       </c>
@@ -31813,7 +31813,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03480890822</t>
+            <t xml:space="preserve">03056193881</t>
           </r>
         </is>
       </c>
@@ -31824,7 +31824,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -31872,7 +31872,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS DE ASSIS FERREIRA </t>
+            <t xml:space="preserve">MARCOS AURELIO BARBOSA</t>
           </r>
         </is>
       </c>
@@ -31882,7 +31882,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">047.953.146-32</t>
+            <t xml:space="preserve">051.909.046-28</t>
           </r>
         </is>
       </c>
@@ -31892,7 +31892,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04407791869</t>
+            <t xml:space="preserve">03480890822</t>
           </r>
         </is>
       </c>
@@ -31903,7 +31903,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -31951,7 +31951,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS GUIMARAES CALDEIRA</t>
+            <t xml:space="preserve">MARCOS DE ASSIS FERREIRA </t>
           </r>
         </is>
       </c>
@@ -31961,7 +31961,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.400.096-93</t>
+            <t xml:space="preserve">047.953.146-32</t>
           </r>
         </is>
       </c>
@@ -31971,7 +31971,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03689823277</t>
+            <t xml:space="preserve">04407791869</t>
           </r>
         </is>
       </c>
@@ -31982,7 +31982,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">28/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -32030,7 +32030,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS HENRIQUE REIS</t>
+            <t xml:space="preserve">MARCOS GUIMARAES CALDEIRA</t>
           </r>
         </is>
       </c>
@@ -32040,7 +32040,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">089.960.066-29</t>
+            <t xml:space="preserve">076.400.096-93</t>
           </r>
         </is>
       </c>
@@ -32050,7 +32050,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04248770930</t>
+            <t xml:space="preserve">03689823277</t>
           </r>
         </is>
       </c>
@@ -32061,7 +32061,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">28/08/2027</t>
           </r>
         </is>
       </c>
@@ -32109,7 +32109,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS JHONATAN ALVES</t>
+            <t xml:space="preserve">MARCOS HENRIQUE REIS</t>
           </r>
         </is>
       </c>
@@ -32119,7 +32119,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">106.575.206-75</t>
+            <t xml:space="preserve">089.960.066-29</t>
           </r>
         </is>
       </c>
@@ -32129,7 +32129,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05470405595</t>
+            <t xml:space="preserve">04248770930</t>
           </r>
         </is>
       </c>
@@ -32140,7 +32140,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -32188,7 +32188,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS JOSE TRIGUEIRO</t>
+            <t xml:space="preserve">MARCOS JHONATAN ALVES</t>
           </r>
         </is>
       </c>
@@ -32198,7 +32198,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">721.730.416-49</t>
+            <t xml:space="preserve">106.575.206-75</t>
           </r>
         </is>
       </c>
@@ -32208,7 +32208,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01704730263</t>
+            <t xml:space="preserve">05470405595</t>
           </r>
         </is>
       </c>
@@ -32219,7 +32219,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/05/2026</t>
+            <t xml:space="preserve">11/08/2026</t>
           </r>
         </is>
       </c>
@@ -32267,7 +32267,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCOS VINICIUS SILVA GOMES</t>
+            <t xml:space="preserve">MARCOS JOSE TRIGUEIRO</t>
           </r>
         </is>
       </c>
@@ -32277,7 +32277,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">018.869.786-11</t>
+            <t xml:space="preserve">721.730.416-49</t>
           </r>
         </is>
       </c>
@@ -32287,7 +32287,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07590695960</t>
+            <t xml:space="preserve">01704730263</t>
           </r>
         </is>
       </c>
@@ -32298,7 +32298,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2027</t>
+            <t xml:space="preserve">15/05/2026</t>
           </r>
         </is>
       </c>
@@ -32346,7 +32346,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARCUS VINICIUS MOREIRA</t>
+            <t xml:space="preserve">MARCOS VINICIUS SILVA GOMES</t>
           </r>
         </is>
       </c>
@@ -32356,7 +32356,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">582.830.726-68</t>
+            <t xml:space="preserve">018.869.786-11</t>
           </r>
         </is>
       </c>
@@ -32366,7 +32366,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01594136546</t>
+            <t xml:space="preserve">07590695960</t>
           </r>
         </is>
       </c>
@@ -32377,7 +32377,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">11/07/2027</t>
           </r>
         </is>
       </c>
@@ -32425,7 +32425,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MARLI VIEIRA DA SILVA</t>
+            <t xml:space="preserve">MARCUS VINICIUS MOREIRA</t>
           </r>
         </is>
       </c>
@@ -32435,7 +32435,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">002.368.206-05</t>
+            <t xml:space="preserve">582.830.726-68</t>
           </r>
         </is>
       </c>
@@ -32445,7 +32445,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03711793571</t>
+            <t xml:space="preserve">01594136546</t>
           </r>
         </is>
       </c>
@@ -32456,7 +32456,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -32497,14 +32497,14 @@
       <c r="T409" s="12" t="inlineStr"/>
       <c r="U409" s="1" t="inlineStr"/>
     </row>
-    <row r="410" customHeight="1" ht="22">
+    <row r="410" customHeight="1" ht="21">
       <c r="A410" s="1" t="inlineStr"/>
       <c r="B410" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATHEUS MATIAS NOGUEIRA DOS SANTOS</t>
+            <t xml:space="preserve">MARLI VIEIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -32514,7 +32514,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">105.075.596-06</t>
+            <t xml:space="preserve">002.368.206-05</t>
           </r>
         </is>
       </c>
@@ -32524,7 +32524,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06658773832</t>
+            <t xml:space="preserve">03711793571</t>
           </r>
         </is>
       </c>
@@ -32535,7 +32535,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">16/10/2027</t>
           </r>
         </is>
       </c>
@@ -32576,14 +32576,14 @@
       <c r="T410" s="12" t="inlineStr"/>
       <c r="U410" s="1" t="inlineStr"/>
     </row>
-    <row r="411" customHeight="1" ht="21">
+    <row r="411" customHeight="1" ht="22">
       <c r="A411" s="1" t="inlineStr"/>
       <c r="B411" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATOSALEM NUNES DA CRUZ</t>
+            <t xml:space="preserve">MATHEUS MATIAS NOGUEIRA DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -32593,7 +32593,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">936.443.376-91</t>
+            <t xml:space="preserve">105.075.596-06</t>
           </r>
         </is>
       </c>
@@ -32603,7 +32603,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02695434380</t>
+            <t xml:space="preserve">06658773832</t>
           </r>
         </is>
       </c>
@@ -32614,7 +32614,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -32662,7 +32662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MATUSAEL PEREIRA DE SOUSA</t>
+            <t xml:space="preserve">MATOSALEM NUNES DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -32672,7 +32672,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">702.247.496-68</t>
+            <t xml:space="preserve">936.443.376-91</t>
           </r>
         </is>
       </c>
@@ -32682,7 +32682,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02236242704</t>
+            <t xml:space="preserve">02695434380</t>
           </r>
         </is>
       </c>
@@ -32693,7 +32693,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -32741,7 +32741,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO DOS SANTOS VIEIRA</t>
+            <t xml:space="preserve">MATUSAEL PEREIRA DE SOUSA</t>
           </r>
         </is>
       </c>
@@ -32751,7 +32751,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.860.416-69</t>
+            <t xml:space="preserve">702.247.496-68</t>
           </r>
         </is>
       </c>
@@ -32761,7 +32761,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01707561330</t>
+            <t xml:space="preserve">02236242704</t>
           </r>
         </is>
       </c>
@@ -32772,7 +32772,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/10/2027</t>
+            <t xml:space="preserve">07/10/2027</t>
           </r>
         </is>
       </c>
@@ -32820,7 +32820,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO MONTEIRO</t>
+            <t xml:space="preserve">MAURICIO DOS SANTOS VIEIRA</t>
           </r>
         </is>
       </c>
@@ -32830,7 +32830,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">631.406.596-87</t>
+            <t xml:space="preserve">040.860.416-69</t>
           </r>
         </is>
       </c>
@@ -32840,7 +32840,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04067779168</t>
+            <t xml:space="preserve">01707561330</t>
           </r>
         </is>
       </c>
@@ -32851,7 +32851,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/10/2025</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -32899,7 +32899,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURICIO RIBEIRO DE OLIVEIRA</t>
+            <t xml:space="preserve">MAURICIO MONTEIRO</t>
           </r>
         </is>
       </c>
@@ -32909,7 +32909,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.153.576-91</t>
+            <t xml:space="preserve">631.406.596-87</t>
           </r>
         </is>
       </c>
@@ -32919,7 +32919,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03578222825</t>
+            <t xml:space="preserve">04067779168</t>
           </r>
         </is>
       </c>
@@ -32930,7 +32930,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/05/2027</t>
+            <t xml:space="preserve">31/10/2025</t>
           </r>
         </is>
       </c>
@@ -32978,7 +32978,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO ADRIANO SAMPAIO LEAL</t>
+            <t xml:space="preserve">MAURICIO RIBEIRO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -32988,7 +32988,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">988.222.176-91</t>
+            <t xml:space="preserve">819.153.576-91</t>
           </r>
         </is>
       </c>
@@ -32998,7 +32998,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02386109509</t>
+            <t xml:space="preserve">03578222825</t>
           </r>
         </is>
       </c>
@@ -33009,7 +33009,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2027</t>
+            <t xml:space="preserve">26/05/2027</t>
           </r>
         </is>
       </c>
@@ -33057,7 +33057,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO LÚCIO DO CARMO</t>
+            <t xml:space="preserve">MAURO ADRIANO SAMPAIO LEAL</t>
           </r>
         </is>
       </c>
@@ -33067,7 +33067,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">925.340.316-00</t>
+            <t xml:space="preserve">988.222.176-91</t>
           </r>
         </is>
       </c>
@@ -33077,7 +33077,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00409168014</t>
+            <t xml:space="preserve">02386109509</t>
           </r>
         </is>
       </c>
@@ -33088,7 +33088,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/03/2026</t>
+            <t xml:space="preserve">16/10/2027</t>
           </r>
         </is>
       </c>
@@ -33136,7 +33136,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MAURO SOARES LEAO  </t>
+            <t xml:space="preserve">MAURO LÚCIO DO CARMO</t>
           </r>
         </is>
       </c>
@@ -33146,7 +33146,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">384.804.096-49</t>
+            <t xml:space="preserve">925.340.316-00</t>
           </r>
         </is>
       </c>
@@ -33156,7 +33156,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02582612080</t>
+            <t xml:space="preserve">00409168014</t>
           </r>
         </is>
       </c>
@@ -33167,7 +33167,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">21/03/2026</t>
           </r>
         </is>
       </c>
@@ -33215,7 +33215,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MICHELE FARIA DE CASTRO</t>
+            <t xml:space="preserve">MAURO SOARES LEAO  </t>
           </r>
         </is>
       </c>
@@ -33225,7 +33225,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">083.973.226-04</t>
+            <t xml:space="preserve">384.804.096-49</t>
           </r>
         </is>
       </c>
@@ -33235,7 +33235,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03837467386</t>
+            <t xml:space="preserve">02582612080</t>
           </r>
         </is>
       </c>
@@ -33246,7 +33246,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/08/2027</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -33294,7 +33294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON DA SILVEIRA REZENDE</t>
+            <t xml:space="preserve">MICHELE FARIA DE CASTRO</t>
           </r>
         </is>
       </c>
@@ -33304,7 +33304,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">455.523.636-04</t>
+            <t xml:space="preserve">083.973.226-04</t>
           </r>
         </is>
       </c>
@@ -33314,7 +33314,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02118384033</t>
+            <t xml:space="preserve">03837467386</t>
           </r>
         </is>
       </c>
@@ -33325,7 +33325,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/11/2026</t>
+            <t xml:space="preserve">26/08/2027</t>
           </r>
         </is>
       </c>
@@ -33373,7 +33373,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON FELIX DA CRUZ</t>
+            <t xml:space="preserve">MILTON DA SILVEIRA REZENDE</t>
           </r>
         </is>
       </c>
@@ -33383,7 +33383,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">007.806.387-60</t>
+            <t xml:space="preserve">455.523.636-04</t>
           </r>
         </is>
       </c>
@@ -33393,7 +33393,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02901380541</t>
+            <t xml:space="preserve">02118384033</t>
           </r>
         </is>
       </c>
@@ -33404,7 +33404,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">20/11/2026</t>
           </r>
         </is>
       </c>
@@ -33452,7 +33452,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MILTON LOURENCO   </t>
+            <t xml:space="preserve">MILTON FELIX DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -33462,7 +33462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">728.967.796-04</t>
+            <t xml:space="preserve">007.806.387-60</t>
           </r>
         </is>
       </c>
@@ -33472,7 +33472,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00967395628</t>
+            <t xml:space="preserve">02901380541</t>
           </r>
         </is>
       </c>
@@ -33483,7 +33483,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -33531,7 +33531,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MIZAEL BABO AUGUSTO</t>
+            <t xml:space="preserve">MILTON LOURENCO   </t>
           </r>
         </is>
       </c>
@@ -33541,7 +33541,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">097.718.576-14</t>
+            <t xml:space="preserve">728.967.796-04</t>
           </r>
         </is>
       </c>
@@ -33551,7 +33551,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07220573198</t>
+            <t xml:space="preserve">00967395628</t>
           </r>
         </is>
       </c>
@@ -33562,7 +33562,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -33610,7 +33610,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MONALDO JULIO DA SILVA</t>
+            <t xml:space="preserve">MIZAEL BABO AUGUSTO</t>
           </r>
         </is>
       </c>
@@ -33620,7 +33620,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">787.493.956-53</t>
+            <t xml:space="preserve">097.718.576-14</t>
           </r>
         </is>
       </c>
@@ -33630,7 +33630,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00710808596</t>
+            <t xml:space="preserve">07220573198</t>
           </r>
         </is>
       </c>
@@ -33641,7 +33641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -33689,7 +33689,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MOZART JOSE DA SILVA</t>
+            <t xml:space="preserve">MONALDO JULIO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33699,7 +33699,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">411.500.586-68</t>
+            <t xml:space="preserve">787.493.956-53</t>
           </r>
         </is>
       </c>
@@ -33709,7 +33709,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02069316250</t>
+            <t xml:space="preserve">00710808596</t>
           </r>
         </is>
       </c>
@@ -33720,7 +33720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/07/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -33768,7 +33768,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NACIEL LEMOS PEREIRA</t>
+            <t xml:space="preserve">MOZART JOSE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -33778,7 +33778,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">113.971.196-24</t>
+            <t xml:space="preserve">411.500.586-68</t>
           </r>
         </is>
       </c>
@@ -33788,7 +33788,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05182091350</t>
+            <t xml:space="preserve">02069316250</t>
           </r>
         </is>
       </c>
@@ -33799,7 +33799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">11/07/2027</t>
           </r>
         </is>
       </c>
@@ -33847,7 +33847,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NASCIMENTO DOS REIS GONDIN</t>
+            <t xml:space="preserve">NACIEL LEMOS PEREIRA</t>
           </r>
         </is>
       </c>
@@ -33857,7 +33857,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">761.988.636-20</t>
+            <t xml:space="preserve">113.971.196-24</t>
           </r>
         </is>
       </c>
@@ -33867,7 +33867,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00900948176</t>
+            <t xml:space="preserve">05182091350</t>
           </r>
         </is>
       </c>
@@ -33878,7 +33878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -33926,7 +33926,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NATALIA MARQUES CLEMENTE</t>
+            <t xml:space="preserve">NASCIMENTO DOS REIS GONDIN</t>
           </r>
         </is>
       </c>
@@ -33936,7 +33936,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">105.427.006-62</t>
+            <t xml:space="preserve">761.988.636-20</t>
           </r>
         </is>
       </c>
@@ -33946,7 +33946,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08144307204</t>
+            <t xml:space="preserve">00900948176</t>
           </r>
         </is>
       </c>
@@ -33957,7 +33957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -34005,7 +34005,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NAUBERT MARCELO SOUZA XAVIER</t>
+            <t xml:space="preserve">NATALIA MARQUES CLEMENTE</t>
           </r>
         </is>
       </c>
@@ -34015,7 +34015,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">102.231.886-11</t>
+            <t xml:space="preserve">105.427.006-62</t>
           </r>
         </is>
       </c>
@@ -34025,7 +34025,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06564062300</t>
+            <t xml:space="preserve">08144307204</t>
           </r>
         </is>
       </c>
@@ -34036,7 +34036,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -34077,14 +34077,14 @@
       <c r="T429" s="12" t="inlineStr"/>
       <c r="U429" s="1" t="inlineStr"/>
     </row>
-    <row r="430" customHeight="1" ht="22">
+    <row r="430" customHeight="1" ht="21">
       <c r="A430" s="1" t="inlineStr"/>
       <c r="B430" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NAYARA TARCIA PENIDO GUIMARAES</t>
+            <t xml:space="preserve">NAUBERT MARCELO SOUZA XAVIER</t>
           </r>
         </is>
       </c>
@@ -34094,7 +34094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.418.096-47</t>
+            <t xml:space="preserve">102.231.886-11</t>
           </r>
         </is>
       </c>
@@ -34104,7 +34104,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04386747420</t>
+            <t xml:space="preserve">06564062300</t>
           </r>
         </is>
       </c>
@@ -34115,7 +34115,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/02/2027</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -34156,14 +34156,14 @@
       <c r="T430" s="12" t="inlineStr"/>
       <c r="U430" s="1" t="inlineStr"/>
     </row>
-    <row r="431" customHeight="1" ht="21">
+    <row r="431" customHeight="1" ht="22">
       <c r="A431" s="1" t="inlineStr"/>
       <c r="B431" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NEIMAR RICARDO PEREIRA</t>
+            <t xml:space="preserve">NAYARA TARCIA PENIDO GUIMARAES</t>
           </r>
         </is>
       </c>
@@ -34173,7 +34173,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">089.354.186-92</t>
+            <t xml:space="preserve">088.418.096-47</t>
           </r>
         </is>
       </c>
@@ -34183,7 +34183,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03994374484</t>
+            <t xml:space="preserve">04386747420</t>
           </r>
         </is>
       </c>
@@ -34194,7 +34194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">03/02/2027</t>
           </r>
         </is>
       </c>
@@ -34242,7 +34242,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NELSON ESTEVAM CAETANO</t>
+            <t xml:space="preserve">NEIMAR RICARDO PEREIRA</t>
           </r>
         </is>
       </c>
@@ -34252,7 +34252,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">786.778.316-49</t>
+            <t xml:space="preserve">089.354.186-92</t>
           </r>
         </is>
       </c>
@@ -34262,7 +34262,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00970062398</t>
+            <t xml:space="preserve">03994374484</t>
           </r>
         </is>
       </c>
@@ -34273,7 +34273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -34321,7 +34321,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NERILTON RODRIGUES DE LIMA</t>
+            <t xml:space="preserve">NELSON ESTEVAM CAETANO</t>
           </r>
         </is>
       </c>
@@ -34331,7 +34331,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">639.992.936-91</t>
+            <t xml:space="preserve">786.778.316-49</t>
           </r>
         </is>
       </c>
@@ -34341,7 +34341,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03027917140</t>
+            <t xml:space="preserve">00970062398</t>
           </r>
         </is>
       </c>
@@ -34352,7 +34352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -34400,7 +34400,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NILSON FERNANDES DE OLIVEIRA</t>
+            <t xml:space="preserve">NERILTON RODRIGUES DE LIMA</t>
           </r>
         </is>
       </c>
@@ -34410,7 +34410,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">968.600.146-87</t>
+            <t xml:space="preserve">639.992.936-91</t>
           </r>
         </is>
       </c>
@@ -34420,7 +34420,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00910443480</t>
+            <t xml:space="preserve">03027917140</t>
           </r>
         </is>
       </c>
@@ -34431,7 +34431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -34479,7 +34479,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NILTON CESAR DOS SANTOS</t>
+            <t xml:space="preserve">NILSON FERNANDES DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -34489,7 +34489,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">575.710.905-04</t>
+            <t xml:space="preserve">968.600.146-87</t>
           </r>
         </is>
       </c>
@@ -34499,7 +34499,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">005560025786</t>
+            <t xml:space="preserve">00910443480</t>
           </r>
         </is>
       </c>
@@ -34510,7 +34510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -34558,7 +34558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODAIR JOSE BELTOLDO</t>
+            <t xml:space="preserve">NILTON CESAR DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -34568,7 +34568,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">004.220.596-41</t>
+            <t xml:space="preserve">575.710.905-04</t>
           </r>
         </is>
       </c>
@@ -34578,7 +34578,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01148775390</t>
+            <t xml:space="preserve">005560025786</t>
           </r>
         </is>
       </c>
@@ -34589,7 +34589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -34637,7 +34637,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODAIR JOSE DE ALMEIDA</t>
+            <t xml:space="preserve">ODAIR JOSE BELTOLDO</t>
           </r>
         </is>
       </c>
@@ -34647,7 +34647,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">000.451.336-38</t>
+            <t xml:space="preserve">004.220.596-41</t>
           </r>
         </is>
       </c>
@@ -34657,7 +34657,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03494010309</t>
+            <t xml:space="preserve">01148775390</t>
           </r>
         </is>
       </c>
@@ -34668,7 +34668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -34716,7 +34716,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ODICE DUTRA DOS REIS</t>
+            <t xml:space="preserve">ODAIR JOSE DE ALMEIDA</t>
           </r>
         </is>
       </c>
@@ -34726,7 +34726,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">754.948.256-04</t>
+            <t xml:space="preserve">000.451.336-38</t>
           </r>
         </is>
       </c>
@@ -34736,7 +34736,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01734148835</t>
+            <t xml:space="preserve">03494010309</t>
           </r>
         </is>
       </c>
@@ -34747,7 +34747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -34795,7 +34795,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ORLANDO AGOSTINHO PINTO</t>
+            <t xml:space="preserve">ODICE DUTRA DOS REIS</t>
           </r>
         </is>
       </c>
@@ -34805,7 +34805,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">006.413.446-60</t>
+            <t xml:space="preserve">754.948.256-04</t>
           </r>
         </is>
       </c>
@@ -34815,7 +34815,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02745787040</t>
+            <t xml:space="preserve">01734148835</t>
           </r>
         </is>
       </c>
@@ -34826,7 +34826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -34874,7 +34874,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALDO ARLINDO DE MEIRA</t>
+            <t xml:space="preserve">ORLANDO AGOSTINHO PINTO</t>
           </r>
         </is>
       </c>
@@ -34884,7 +34884,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.805.766-60</t>
+            <t xml:space="preserve">006.413.446-60</t>
           </r>
         </is>
       </c>
@@ -34894,7 +34894,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03105139100</t>
+            <t xml:space="preserve">02745787040</t>
           </r>
         </is>
       </c>
@@ -34905,7 +34905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -34953,7 +34953,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALDO COELHO DE MORAES</t>
+            <t xml:space="preserve">OSVALDO ARLINDO DE MEIRA</t>
           </r>
         </is>
       </c>
@@ -34963,7 +34963,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">545.222.186-72</t>
+            <t xml:space="preserve">051.805.766-60</t>
           </r>
         </is>
       </c>
@@ -34973,7 +34973,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03759063307</t>
+            <t xml:space="preserve">03105139100</t>
           </r>
         </is>
       </c>
@@ -34984,7 +34984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/06/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -35032,7 +35032,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSVALMIR CLEITON GOMES</t>
+            <t xml:space="preserve">OSVALDO COELHO DE MORAES</t>
           </r>
         </is>
       </c>
@@ -35042,7 +35042,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">126.795.126-50</t>
+            <t xml:space="preserve">545.222.186-72</t>
           </r>
         </is>
       </c>
@@ -35052,7 +35052,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05485955266</t>
+            <t xml:space="preserve">03759063307</t>
           </r>
         </is>
       </c>
@@ -35063,7 +35063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/10/2027</t>
+            <t xml:space="preserve">26/06/2027</t>
           </r>
         </is>
       </c>
@@ -35111,7 +35111,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OSWALDO DOS SANTOS JUNIOR</t>
+            <t xml:space="preserve">OSVALMIR CLEITON GOMES</t>
           </r>
         </is>
       </c>
@@ -35121,7 +35121,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">892.492.326-91</t>
+            <t xml:space="preserve">126.795.126-50</t>
           </r>
         </is>
       </c>
@@ -35131,7 +35131,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00822357647</t>
+            <t xml:space="preserve">05485955266</t>
           </r>
         </is>
       </c>
@@ -35142,7 +35142,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">13/10/2027</t>
           </r>
         </is>
       </c>
@@ -35190,7 +35190,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OTAVIO MOURA SILVA</t>
+            <t xml:space="preserve">OSWALDO DOS SANTOS JUNIOR</t>
           </r>
         </is>
       </c>
@@ -35200,7 +35200,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">116.799.556-24</t>
+            <t xml:space="preserve">892.492.326-91</t>
           </r>
         </is>
       </c>
@@ -35210,7 +35210,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06947671960</t>
+            <t xml:space="preserve">00822357647</t>
           </r>
         </is>
       </c>
@@ -35221,7 +35221,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02/07/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -35269,7 +35269,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">OZIAS ROSA NUNES DA SILVA</t>
+            <t xml:space="preserve">OTAVIO MOURA SILVA</t>
           </r>
         </is>
       </c>
@@ -35279,7 +35279,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.717.456-17</t>
+            <t xml:space="preserve">116.799.556-24</t>
           </r>
         </is>
       </c>
@@ -35289,7 +35289,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02844195589</t>
+            <t xml:space="preserve">06947671960</t>
           </r>
         </is>
       </c>
@@ -35300,7 +35300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">02/07/2027</t>
           </r>
         </is>
       </c>
@@ -35348,7 +35348,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PABLO NOE LANA</t>
+            <t xml:space="preserve">OZIAS ROSA NUNES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -35358,7 +35358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.279.556-33</t>
+            <t xml:space="preserve">051.717.456-17</t>
           </r>
         </is>
       </c>
@@ -35368,7 +35368,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03371448607</t>
+            <t xml:space="preserve">02844195589</t>
           </r>
         </is>
       </c>
@@ -35379,7 +35379,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -35427,7 +35427,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PABLO VINICIO MARQUES DA SILVA</t>
+            <t xml:space="preserve">PABLO NOE LANA</t>
           </r>
         </is>
       </c>
@@ -35437,7 +35437,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">125.648.656-66</t>
+            <t xml:space="preserve">040.279.556-33</t>
           </r>
         </is>
       </c>
@@ -35447,7 +35447,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06041166234</t>
+            <t xml:space="preserve">03371448607</t>
           </r>
         </is>
       </c>
@@ -35506,7 +35506,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO FERNANDES MACHADO</t>
+            <t xml:space="preserve">PABLO VINICIO MARQUES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -35516,7 +35516,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">646.984.836-20</t>
+            <t xml:space="preserve">125.648.656-66</t>
           </r>
         </is>
       </c>
@@ -35526,7 +35526,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00437370810</t>
+            <t xml:space="preserve">06041166234</t>
           </r>
         </is>
       </c>
@@ -35537,7 +35537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -35585,7 +35585,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO HENRIQUE DA SILVA</t>
+            <t xml:space="preserve">PAULO FERNANDES MACHADO</t>
           </r>
         </is>
       </c>
@@ -35595,7 +35595,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">145.560.786-01</t>
+            <t xml:space="preserve">646.984.836-20</t>
           </r>
         </is>
       </c>
@@ -35605,7 +35605,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06876540658</t>
+            <t xml:space="preserve">00437370810</t>
           </r>
         </is>
       </c>
@@ -35616,7 +35616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/10/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -35657,14 +35657,14 @@
       <c r="T449" s="12" t="inlineStr"/>
       <c r="U449" s="1" t="inlineStr"/>
     </row>
-    <row r="450" customHeight="1" ht="22">
+    <row r="450" customHeight="1" ht="21">
       <c r="A450" s="1" t="inlineStr"/>
       <c r="B450" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO HENRIQUE SILVA APOLINARIO</t>
+            <t xml:space="preserve">PAULO HENRIQUE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -35674,7 +35674,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">078.119.326-52</t>
+            <t xml:space="preserve">145.560.786-01</t>
           </r>
         </is>
       </c>
@@ -35684,7 +35684,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04058607086</t>
+            <t xml:space="preserve">06876540658</t>
           </r>
         </is>
       </c>
@@ -35695,7 +35695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/09/2027</t>
+            <t xml:space="preserve">05/10/2027</t>
           </r>
         </is>
       </c>
@@ -35736,14 +35736,14 @@
       <c r="T450" s="12" t="inlineStr"/>
       <c r="U450" s="1" t="inlineStr"/>
     </row>
-    <row r="451" customHeight="1" ht="21">
+    <row r="451" customHeight="1" ht="22">
       <c r="A451" s="1" t="inlineStr"/>
       <c r="B451" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO JOSE DO NASCIMENTO </t>
+            <t xml:space="preserve">PAULO HENRIQUE SILVA APOLINARIO</t>
           </r>
         </is>
       </c>
@@ -35753,7 +35753,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">632.040.456-68</t>
+            <t xml:space="preserve">078.119.326-52</t>
           </r>
         </is>
       </c>
@@ -35763,7 +35763,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02867848381</t>
+            <t xml:space="preserve">04058607086</t>
           </r>
         </is>
       </c>
@@ -35774,7 +35774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/07/2030</t>
+            <t xml:space="preserve">08/09/2027</t>
           </r>
         </is>
       </c>
@@ -35822,7 +35822,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO MARCIO FERREIRA</t>
+            <t xml:space="preserve">PAULO JOSE DO NASCIMENTO </t>
           </r>
         </is>
       </c>
@@ -35832,7 +35832,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">927.606.946-15</t>
+            <t xml:space="preserve">632.040.456-68</t>
           </r>
         </is>
       </c>
@@ -35842,7 +35842,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02635238806</t>
+            <t xml:space="preserve">02867848381</t>
           </r>
         </is>
       </c>
@@ -35853,7 +35853,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">30/07/2030</t>
           </r>
         </is>
       </c>
@@ -35901,7 +35901,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO SERGIO DA CRUZ</t>
+            <t xml:space="preserve">PAULO MARCIO FERREIRA</t>
           </r>
         </is>
       </c>
@@ -35911,7 +35911,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">746.204.526-53</t>
+            <t xml:space="preserve">927.606.946-15</t>
           </r>
         </is>
       </c>
@@ -35921,7 +35921,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01934028430</t>
+            <t xml:space="preserve">02635238806</t>
           </r>
         </is>
       </c>
@@ -35932,7 +35932,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/07/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -35980,7 +35980,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PAULO SERGIO DA CUNHA</t>
+            <t xml:space="preserve">PAULO SERGIO DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -35990,7 +35990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">003.102.236-79</t>
+            <t xml:space="preserve">746.204.526-53</t>
           </r>
         </is>
       </c>
@@ -36000,7 +36000,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04344405135</t>
+            <t xml:space="preserve">01934028430</t>
           </r>
         </is>
       </c>
@@ -36011,7 +36011,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">04/07/2027</t>
           </r>
         </is>
       </c>
@@ -36059,7 +36059,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO ANTONIO BENTO</t>
+            <t xml:space="preserve">PAULO SERGIO DA CUNHA</t>
           </r>
         </is>
       </c>
@@ -36069,7 +36069,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">493.901.636-68</t>
+            <t xml:space="preserve">003.102.236-79</t>
           </r>
         </is>
       </c>
@@ -36079,7 +36079,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00694729250</t>
+            <t xml:space="preserve">04344405135</t>
           </r>
         </is>
       </c>
@@ -36090,7 +36090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -36131,14 +36131,14 @@
       <c r="T455" s="12" t="inlineStr"/>
       <c r="U455" s="1" t="inlineStr"/>
     </row>
-    <row r="456" customHeight="1" ht="22">
+    <row r="456" customHeight="1" ht="21">
       <c r="A456" s="1" t="inlineStr"/>
       <c r="B456" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE ANTUNES MORAIS</t>
+            <t xml:space="preserve">PEDRO ANTONIO BENTO</t>
           </r>
         </is>
       </c>
@@ -36148,7 +36148,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">124.819.026-29</t>
+            <t xml:space="preserve">493.901.636-68</t>
           </r>
         </is>
       </c>
@@ -36158,7 +36158,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06571602700</t>
+            <t xml:space="preserve">00694729250</t>
           </r>
         </is>
       </c>
@@ -36169,7 +36169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/07/2027</t>
+            <t xml:space="preserve">21/10/2027</t>
           </r>
         </is>
       </c>
@@ -36217,7 +36217,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE RESENDE MAGALHAES FARINHA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE ANTUNES MORAIS</t>
           </r>
         </is>
       </c>
@@ -36227,7 +36227,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.378.606-75</t>
+            <t xml:space="preserve">124.819.026-29</t>
           </r>
         </is>
       </c>
@@ -36237,7 +36237,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06845908627</t>
+            <t xml:space="preserve">06571602700</t>
           </r>
         </is>
       </c>
@@ -36248,7 +36248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">17/07/2027</t>
           </r>
         </is>
       </c>
@@ -36296,7 +36296,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE SILVERIO MARTINS VIEIRA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE RESENDE MAGALHAES FARINHA</t>
           </r>
         </is>
       </c>
@@ -36306,7 +36306,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">088.281.606-32</t>
+            <t xml:space="preserve">110.378.606-75</t>
           </r>
         </is>
       </c>
@@ -36316,7 +36316,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03691532816</t>
+            <t xml:space="preserve">06845908627</t>
           </r>
         </is>
       </c>
@@ -36327,7 +36327,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -36375,7 +36375,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO HENRIQUE TORRES MARTINS </t>
+            <t xml:space="preserve">PEDRO HENRIQUE SILVERIO MARTINS VIEIRA</t>
           </r>
         </is>
       </c>
@@ -36385,7 +36385,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">156.289.896-57</t>
+            <t xml:space="preserve">088.281.606-32</t>
           </r>
         </is>
       </c>
@@ -36395,7 +36395,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08127162566</t>
+            <t xml:space="preserve">03691532816</t>
           </r>
         </is>
       </c>
@@ -36406,7 +36406,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -36447,14 +36447,14 @@
       <c r="T459" s="12" t="inlineStr"/>
       <c r="U459" s="1" t="inlineStr"/>
     </row>
-    <row r="460" customHeight="1" ht="21">
+    <row r="460" customHeight="1" ht="22">
       <c r="A460" s="1" t="inlineStr"/>
       <c r="B460" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO RODRIGUES DE PAULA</t>
+            <t xml:space="preserve">PEDRO HENRIQUE TORRES MARTINS </t>
           </r>
         </is>
       </c>
@@ -36464,7 +36464,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">578.466.186-87</t>
+            <t xml:space="preserve">156.289.896-57</t>
           </r>
         </is>
       </c>
@@ -36474,7 +36474,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01168973776</t>
+            <t xml:space="preserve">08127162566</t>
           </r>
         </is>
       </c>
@@ -36485,7 +36485,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2025</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -36533,7 +36533,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PEDRO RODRIGUES PEREIRA</t>
+            <t xml:space="preserve">PEDRO RODRIGUES DE PAULA</t>
           </r>
         </is>
       </c>
@@ -36543,7 +36543,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">095.236.816-13</t>
+            <t xml:space="preserve">578.466.186-87</t>
           </r>
         </is>
       </c>
@@ -36553,7 +36553,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04944405662</t>
+            <t xml:space="preserve">01168973776</t>
           </r>
         </is>
       </c>
@@ -36564,7 +36564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">31/07/2025</t>
           </r>
         </is>
       </c>
@@ -36612,7 +36612,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PLINIO RAFAEL ANDRADE</t>
+            <t xml:space="preserve">PEDRO RODRIGUES PEREIRA</t>
           </r>
         </is>
       </c>
@@ -36622,7 +36622,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">098.676.626-79</t>
+            <t xml:space="preserve">095.236.816-13</t>
           </r>
         </is>
       </c>
@@ -36632,7 +36632,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04903258724</t>
+            <t xml:space="preserve">04944405662</t>
           </r>
         </is>
       </c>
@@ -36643,7 +36643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -36691,7 +36691,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PRISCILA SILVA LACERDA</t>
+            <t xml:space="preserve">PLINIO RAFAEL ANDRADE</t>
           </r>
         </is>
       </c>
@@ -36701,7 +36701,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">066.424.716-44</t>
+            <t xml:space="preserve">098.676.626-79</t>
           </r>
         </is>
       </c>
@@ -36711,7 +36711,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02895817906</t>
+            <t xml:space="preserve">04903258724</t>
           </r>
         </is>
       </c>
@@ -36722,7 +36722,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/11/2026</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -36770,7 +36770,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAEL FERREIRA MARTINS</t>
+            <t xml:space="preserve">PRISCILA SILVA LACERDA</t>
           </r>
         </is>
       </c>
@@ -36780,7 +36780,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.733.626-84</t>
+            <t xml:space="preserve">066.424.716-44</t>
           </r>
         </is>
       </c>
@@ -36790,7 +36790,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05713407303</t>
+            <t xml:space="preserve">02895817906</t>
           </r>
         </is>
       </c>
@@ -36801,7 +36801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">28/07/2026</t>
+            <t xml:space="preserve">26/11/2026</t>
           </r>
         </is>
       </c>
@@ -36849,7 +36849,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL COIMBRA GONTIJO</t>
+            <t xml:space="preserve">RAEL FERREIRA MARTINS</t>
           </r>
         </is>
       </c>
@@ -36859,7 +36859,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.055.666-60</t>
+            <t xml:space="preserve">122.733.626-84</t>
           </r>
         </is>
       </c>
@@ -36869,7 +36869,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05538775609</t>
+            <t xml:space="preserve">05713407303</t>
           </r>
         </is>
       </c>
@@ -36880,7 +36880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">28/07/2026</t>
           </r>
         </is>
       </c>
@@ -36921,14 +36921,14 @@
       <c r="T465" s="12" t="inlineStr"/>
       <c r="U465" s="1" t="inlineStr"/>
     </row>
-    <row r="466" customHeight="1" ht="22">
+    <row r="466" customHeight="1" ht="21">
       <c r="A466" s="1" t="inlineStr"/>
       <c r="B466" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL MATHEUS MARTINS COELHO </t>
+            <t xml:space="preserve">RAFAEL COIMBRA GONTIJO</t>
           </r>
         </is>
       </c>
@@ -36938,7 +36938,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">147.684.866-14</t>
+            <t xml:space="preserve">065.055.666-60</t>
           </r>
         </is>
       </c>
@@ -36948,7 +36948,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07093318680</t>
+            <t xml:space="preserve">05538775609</t>
           </r>
         </is>
       </c>
@@ -36959,7 +36959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/09/2026</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -37000,14 +37000,14 @@
       <c r="T466" s="12" t="inlineStr"/>
       <c r="U466" s="1" t="inlineStr"/>
     </row>
-    <row r="467" customHeight="1" ht="21">
+    <row r="467" customHeight="1" ht="22">
       <c r="A467" s="1" t="inlineStr"/>
       <c r="B467" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL MORAES BARBOSA</t>
+            <t xml:space="preserve">RAFAEL MATHEUS MARTINS COELHO </t>
           </r>
         </is>
       </c>
@@ -37017,7 +37017,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.669.666-27</t>
+            <t xml:space="preserve">147.684.866-14</t>
           </r>
         </is>
       </c>
@@ -37027,7 +37027,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05783669254</t>
+            <t xml:space="preserve">07093318680</t>
           </r>
         </is>
       </c>
@@ -37038,7 +37038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/07/2027</t>
+            <t xml:space="preserve">19/09/2026</t>
           </r>
         </is>
       </c>
@@ -37086,7 +37086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAEL SOUZA REZENDE ROCHA</t>
+            <t xml:space="preserve">RAFAEL MORAES BARBOSA</t>
           </r>
         </is>
       </c>
@@ -37096,7 +37096,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">122.998.096-27</t>
+            <t xml:space="preserve">070.669.666-27</t>
           </r>
         </is>
       </c>
@@ -37106,7 +37106,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06443469242</t>
+            <t xml:space="preserve">05783669254</t>
           </r>
         </is>
       </c>
@@ -37117,7 +37117,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/05/2026</t>
+            <t xml:space="preserve">18/07/2027</t>
           </r>
         </is>
       </c>
@@ -37165,7 +37165,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAFAELA GONÇALVES DA SILVA</t>
+            <t xml:space="preserve">RAFAEL SOUZA REZENDE ROCHA</t>
           </r>
         </is>
       </c>
@@ -37175,7 +37175,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">097.757.966-28</t>
+            <t xml:space="preserve">122.998.096-27</t>
           </r>
         </is>
       </c>
@@ -37185,7 +37185,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05193246932</t>
+            <t xml:space="preserve">06443469242</t>
           </r>
         </is>
       </c>
@@ -37196,7 +37196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">14/05/2026</t>
           </r>
         </is>
       </c>
@@ -37244,7 +37244,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAIMUNDO CAMILO DA SILVA NETO</t>
+            <t xml:space="preserve">RAFAELA GONÇALVES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -37254,7 +37254,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">736.682.906-44</t>
+            <t xml:space="preserve">097.757.966-28</t>
           </r>
         </is>
       </c>
@@ -37264,7 +37264,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00628460620</t>
+            <t xml:space="preserve">05193246932</t>
           </r>
         </is>
       </c>
@@ -37323,7 +37323,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAIMUNDO NONATO DOS REIS</t>
+            <t xml:space="preserve">RAIMUNDO CAMILO DA SILVA NETO</t>
           </r>
         </is>
       </c>
@@ -37333,7 +37333,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">520.482.176-72</t>
+            <t xml:space="preserve">736.682.906-44</t>
           </r>
         </is>
       </c>
@@ -37343,7 +37343,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02656000194</t>
+            <t xml:space="preserve">00628460620</t>
           </r>
         </is>
       </c>
@@ -37354,7 +37354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -37402,7 +37402,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAMON HENRIQUE DA SILVA</t>
+            <t xml:space="preserve">RAIMUNDO NONATO DOS REIS</t>
           </r>
         </is>
       </c>
@@ -37412,7 +37412,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.806.026-33</t>
+            <t xml:space="preserve">520.482.176-72</t>
           </r>
         </is>
       </c>
@@ -37422,7 +37422,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04113942460</t>
+            <t xml:space="preserve">02656000194</t>
           </r>
         </is>
       </c>
@@ -37433,7 +37433,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/01/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -37474,14 +37474,14 @@
       <c r="T472" s="12" t="inlineStr"/>
       <c r="U472" s="1" t="inlineStr"/>
     </row>
-    <row r="473" customHeight="1" ht="22">
+    <row r="473" customHeight="1" ht="21">
       <c r="A473" s="1" t="inlineStr"/>
       <c r="B473" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAMON WEMERSON VELOSO TEIXEIRA</t>
+            <t xml:space="preserve">RAMON HENRIQUE DA SILVA</t>
           </r>
         </is>
       </c>
@@ -37491,7 +37491,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">099.777.116-07</t>
+            <t xml:space="preserve">079.806.026-33</t>
           </r>
         </is>
       </c>
@@ -37501,7 +37501,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04970737232</t>
+            <t xml:space="preserve">04113942460</t>
           </r>
         </is>
       </c>
@@ -37512,7 +37512,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/08/2027</t>
+            <t xml:space="preserve">22/01/2027</t>
           </r>
         </is>
       </c>
@@ -37560,7 +37560,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RANIEL ROMERICK LIMA DE OLIVEIRA</t>
+            <t xml:space="preserve">RAMON WEMERSON VELOSO TEIXEIRA</t>
           </r>
         </is>
       </c>
@@ -37570,7 +37570,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.580.076-05</t>
+            <t xml:space="preserve">099.777.116-07</t>
           </r>
         </is>
       </c>
@@ -37580,7 +37580,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05302294379</t>
+            <t xml:space="preserve">04970737232</t>
           </r>
         </is>
       </c>
@@ -37591,7 +37591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">04/08/2027</t>
           </r>
         </is>
       </c>
@@ -37632,14 +37632,14 @@
       <c r="T474" s="12" t="inlineStr"/>
       <c r="U474" s="1" t="inlineStr"/>
     </row>
-    <row r="475" customHeight="1" ht="21">
+    <row r="475" customHeight="1" ht="22">
       <c r="A475" s="1" t="inlineStr"/>
       <c r="B475" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAPHAEL HENRIQUE ROCHA SILVA</t>
+            <t xml:space="preserve">RANIEL ROMERICK LIMA DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -37649,7 +37649,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">100.372.356-05</t>
+            <t xml:space="preserve">093.580.076-05</t>
           </r>
         </is>
       </c>
@@ -37659,7 +37659,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05480849132</t>
+            <t xml:space="preserve">05302294379</t>
           </r>
         </is>
       </c>
@@ -37670,7 +37670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/08/2027</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -37718,7 +37718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RAVENGAR NUNES DE OLIVEIRA</t>
+            <t xml:space="preserve">RAPHAEL HENRIQUE ROCHA SILVA</t>
           </r>
         </is>
       </c>
@@ -37728,7 +37728,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">087.922.076-77</t>
+            <t xml:space="preserve">100.372.356-05</t>
           </r>
         </is>
       </c>
@@ -37738,7 +37738,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04161596624</t>
+            <t xml:space="preserve">05480849132</t>
           </r>
         </is>
       </c>
@@ -37749,7 +37749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/07/2027</t>
+            <t xml:space="preserve">05/08/2027</t>
           </r>
         </is>
       </c>
@@ -37797,7 +37797,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO EUSTAQUIO ALVES</t>
+            <t xml:space="preserve">RAVENGAR NUNES DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -37807,7 +37807,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.746.886-98</t>
+            <t xml:space="preserve">087.922.076-77</t>
           </r>
         </is>
       </c>
@@ -37817,7 +37817,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02942466380</t>
+            <t xml:space="preserve">04161596624</t>
           </r>
         </is>
       </c>
@@ -37828,7 +37828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/08/2027</t>
+            <t xml:space="preserve">21/07/2027</t>
           </r>
         </is>
       </c>
@@ -37876,7 +37876,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO GOMES DOS SANTOS</t>
+            <t xml:space="preserve">REGINALDO EUSTAQUIO ALVES</t>
           </r>
         </is>
       </c>
@@ -37886,7 +37886,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.934.616-71</t>
+            <t xml:space="preserve">046.746.886-98</t>
           </r>
         </is>
       </c>
@@ -37896,7 +37896,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03466250864</t>
+            <t xml:space="preserve">02942466380</t>
           </r>
         </is>
       </c>
@@ -37907,7 +37907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/11/2026</t>
+            <t xml:space="preserve">17/08/2027</t>
           </r>
         </is>
       </c>
@@ -37955,7 +37955,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">REGINALDO VICENTINO DE PAULA</t>
+            <t xml:space="preserve">REGINALDO GOMES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -37965,7 +37965,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">062.303.156-61</t>
+            <t xml:space="preserve">061.934.616-71</t>
           </r>
         </is>
       </c>
@@ -37975,7 +37975,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07456908970</t>
+            <t xml:space="preserve">03466250864</t>
           </r>
         </is>
       </c>
@@ -37986,7 +37986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">25/11/2026</t>
           </r>
         </is>
       </c>
@@ -38034,7 +38034,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RENAN REZENDE DA CRUZ</t>
+            <t xml:space="preserve">REGINALDO VICENTINO DE PAULA</t>
           </r>
         </is>
       </c>
@@ -38044,7 +38044,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">068.003.286-00</t>
+            <t xml:space="preserve">062.303.156-61</t>
           </r>
         </is>
       </c>
@@ -38054,7 +38054,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04461438210</t>
+            <t xml:space="preserve">07456908970</t>
           </r>
         </is>
       </c>
@@ -38065,7 +38065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -38106,14 +38106,14 @@
       <c r="T480" s="12" t="inlineStr"/>
       <c r="U480" s="1" t="inlineStr"/>
     </row>
-    <row r="481" customHeight="1" ht="22">
+    <row r="481" customHeight="1" ht="21">
       <c r="A481" s="1" t="inlineStr"/>
       <c r="B481" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RENATO MARTINS DA SILVA GOUVEIA</t>
+            <t xml:space="preserve">RENAN REZENDE DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -38123,7 +38123,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">045.158.916-50</t>
+            <t xml:space="preserve">068.003.286-00</t>
           </r>
         </is>
       </c>
@@ -38133,7 +38133,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00796571668</t>
+            <t xml:space="preserve">04461438210</t>
           </r>
         </is>
       </c>
@@ -38144,7 +38144,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/08/2027</t>
+            <t xml:space="preserve">12/08/2027</t>
           </r>
         </is>
       </c>
@@ -38185,14 +38185,14 @@
       <c r="T481" s="12" t="inlineStr"/>
       <c r="U481" s="1" t="inlineStr"/>
     </row>
-    <row r="482" customHeight="1" ht="21">
+    <row r="482" customHeight="1" ht="22">
       <c r="A482" s="1" t="inlineStr"/>
       <c r="B482" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RICARDO SOUZA MARINHO</t>
+            <t xml:space="preserve">RENATO MARTINS DA SILVA GOUVEIA</t>
           </r>
         </is>
       </c>
@@ -38202,7 +38202,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">683.789.476-53</t>
+            <t xml:space="preserve">045.158.916-50</t>
           </r>
         </is>
       </c>
@@ -38212,7 +38212,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02561487470</t>
+            <t xml:space="preserve">00796571668</t>
           </r>
         </is>
       </c>
@@ -38223,7 +38223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/12/2025</t>
+            <t xml:space="preserve">24/08/2027</t>
           </r>
         </is>
       </c>
@@ -38264,14 +38264,14 @@
       <c r="T482" s="12" t="inlineStr"/>
       <c r="U482" s="1" t="inlineStr"/>
     </row>
-    <row r="483" customHeight="1" ht="22">
+    <row r="483" customHeight="1" ht="21">
       <c r="A483" s="1" t="inlineStr"/>
       <c r="B483" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RICHARD HENRIQUE DE OLIVEIRA MACHADO</t>
+            <t xml:space="preserve">RICARDO SOUZA MARINHO</t>
           </r>
         </is>
       </c>
@@ -38281,7 +38281,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">020.089.536-29</t>
+            <t xml:space="preserve">683.789.476-53</t>
           </r>
         </is>
       </c>
@@ -38291,7 +38291,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07127361656</t>
+            <t xml:space="preserve">02561487470</t>
           </r>
         </is>
       </c>
@@ -38302,7 +38302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/11/2026</t>
+            <t xml:space="preserve">18/12/2025</t>
           </r>
         </is>
       </c>
@@ -38350,7 +38350,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERT WILLIAM MARCELINO DE O PEREIRA </t>
+            <t xml:space="preserve">RICHARD HENRIQUE DE OLIVEIRA MACHADO</t>
           </r>
         </is>
       </c>
@@ -38360,7 +38360,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">143.991.156-88</t>
+            <t xml:space="preserve">020.089.536-29</t>
           </r>
         </is>
       </c>
@@ -38370,7 +38370,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06651427733</t>
+            <t xml:space="preserve">07127361656</t>
           </r>
         </is>
       </c>
@@ -38381,7 +38381,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">25/11/2026</t>
           </r>
         </is>
       </c>
@@ -38422,14 +38422,14 @@
       <c r="T484" s="12" t="inlineStr"/>
       <c r="U484" s="1" t="inlineStr"/>
     </row>
-    <row r="485" customHeight="1" ht="21">
+    <row r="485" customHeight="1" ht="22">
       <c r="A485" s="1" t="inlineStr"/>
       <c r="B485" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO CIRENO DE PAULA</t>
+            <t xml:space="preserve">ROBERT WILLIAM MARCELINO DE O PEREIRA </t>
           </r>
         </is>
       </c>
@@ -38439,7 +38439,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">673.187.626-72</t>
+            <t xml:space="preserve">143.991.156-88</t>
           </r>
         </is>
       </c>
@@ -38449,7 +38449,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01720717152</t>
+            <t xml:space="preserve">06651427733</t>
           </r>
         </is>
       </c>
@@ -38460,7 +38460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -38508,7 +38508,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO FLAVIO DA COSTA</t>
+            <t xml:space="preserve">ROBERTO CIRENO DE PAULA</t>
           </r>
         </is>
       </c>
@@ -38518,7 +38518,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">610.846.036-91</t>
+            <t xml:space="preserve">673.187.626-72</t>
           </r>
         </is>
       </c>
@@ -38528,7 +38528,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02293916183</t>
+            <t xml:space="preserve">01720717152</t>
           </r>
         </is>
       </c>
@@ -38539,7 +38539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -38587,7 +38587,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBERTO MOZART SANTANA</t>
+            <t xml:space="preserve">ROBERTO FLAVIO DA COSTA</t>
           </r>
         </is>
       </c>
@@ -38597,7 +38597,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.939.556-34</t>
+            <t xml:space="preserve">610.846.036-91</t>
           </r>
         </is>
       </c>
@@ -38607,7 +38607,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02429053892</t>
+            <t xml:space="preserve">02293916183</t>
           </r>
         </is>
       </c>
@@ -38618,7 +38618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -38666,7 +38666,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON CAMILO DE OLIVEIRA</t>
+            <t xml:space="preserve">ROBERTO MOZART SANTANA</t>
           </r>
         </is>
       </c>
@@ -38676,7 +38676,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.438.436-18</t>
+            <t xml:space="preserve">868.939.556-34</t>
           </r>
         </is>
       </c>
@@ -38686,7 +38686,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03133712661</t>
+            <t xml:space="preserve">02429053892</t>
           </r>
         </is>
       </c>
@@ -38697,7 +38697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/08/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -38738,14 +38738,14 @@
       <c r="T488" s="12" t="inlineStr"/>
       <c r="U488" s="1" t="inlineStr"/>
     </row>
-    <row r="489" customHeight="1" ht="22">
+    <row r="489" customHeight="1" ht="21">
       <c r="A489" s="1" t="inlineStr"/>
       <c r="B489" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON DOS SANTOS DE REZENDE</t>
+            <t xml:space="preserve">ROBSON CAMILO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -38755,7 +38755,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.387.886-66</t>
+            <t xml:space="preserve">070.438.436-18</t>
           </r>
         </is>
       </c>
@@ -38765,7 +38765,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04356240900</t>
+            <t xml:space="preserve">03133712661</t>
           </r>
         </is>
       </c>
@@ -38776,7 +38776,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">03/08/2027</t>
           </r>
         </is>
       </c>
@@ -38817,14 +38817,14 @@
       <c r="T489" s="12" t="inlineStr"/>
       <c r="U489" s="1" t="inlineStr"/>
     </row>
-    <row r="490" customHeight="1" ht="21">
+    <row r="490" customHeight="1" ht="22">
       <c r="A490" s="1" t="inlineStr"/>
       <c r="B490" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROBSON FERREIRA COSTA</t>
+            <t xml:space="preserve">ROBSON DOS SANTOS DE REZENDE</t>
           </r>
         </is>
       </c>
@@ -38834,7 +38834,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">986.658.396-15</t>
+            <t xml:space="preserve">077.387.886-66</t>
           </r>
         </is>
       </c>
@@ -38844,7 +38844,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">019790492230</t>
+            <t xml:space="preserve">04356240900</t>
           </r>
         </is>
       </c>
@@ -38855,7 +38855,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/12/2026</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -38903,7 +38903,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO CESARIO DANTAS</t>
+            <t xml:space="preserve">ROBSON FERREIRA COSTA</t>
           </r>
         </is>
       </c>
@@ -38913,7 +38913,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">062.821.666-16</t>
+            <t xml:space="preserve">986.658.396-15</t>
           </r>
         </is>
       </c>
@@ -38923,7 +38923,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02818805407</t>
+            <t xml:space="preserve">019790492230</t>
           </r>
         </is>
       </c>
@@ -38934,7 +38934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">12/12/2026</t>
           </r>
         </is>
       </c>
@@ -38982,7 +38982,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO DA COSTA RAMOS</t>
+            <t xml:space="preserve">RODRIGO CESARIO DANTAS</t>
           </r>
         </is>
       </c>
@@ -38992,7 +38992,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">079.330.686-85</t>
+            <t xml:space="preserve">062.821.666-16</t>
           </r>
         </is>
       </c>
@@ -39002,7 +39002,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03408753752</t>
+            <t xml:space="preserve">02818805407</t>
           </r>
         </is>
       </c>
@@ -39013,7 +39013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -39061,7 +39061,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO DE SOUSA COELHO</t>
+            <t xml:space="preserve">RODRIGO DA COSTA RAMOS</t>
           </r>
         </is>
       </c>
@@ -39071,7 +39071,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">071.019.256-85</t>
+            <t xml:space="preserve">079.330.686-85</t>
           </r>
         </is>
       </c>
@@ -39081,7 +39081,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03393047195</t>
+            <t xml:space="preserve">03408753752</t>
           </r>
         </is>
       </c>
@@ -39092,7 +39092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -39140,7 +39140,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO MACIEL XAVIER</t>
+            <t xml:space="preserve">RODRIGO DE SOUSA COELHO</t>
           </r>
         </is>
       </c>
@@ -39150,7 +39150,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">031.787.716-03</t>
+            <t xml:space="preserve">071.019.256-85</t>
           </r>
         </is>
       </c>
@@ -39160,7 +39160,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02992459933</t>
+            <t xml:space="preserve">03393047195</t>
           </r>
         </is>
       </c>
@@ -39171,7 +39171,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/03/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -39219,7 +39219,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO MOREIRA CORREA</t>
+            <t xml:space="preserve">RODRIGO MACIEL XAVIER</t>
           </r>
         </is>
       </c>
@@ -39229,7 +39229,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">056.371.446-80</t>
+            <t xml:space="preserve">031.787.716-03</t>
           </r>
         </is>
       </c>
@@ -39239,7 +39239,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02338803674</t>
+            <t xml:space="preserve">02992459933</t>
           </r>
         </is>
       </c>
@@ -39250,7 +39250,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">18/03/2027</t>
           </r>
         </is>
       </c>
@@ -39298,7 +39298,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGO WILLER DE OLIVEIRA</t>
+            <t xml:space="preserve">RODRIGO MOREIRA CORREA</t>
           </r>
         </is>
       </c>
@@ -39308,7 +39308,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">123.890.076-35</t>
+            <t xml:space="preserve">056.371.446-80</t>
           </r>
         </is>
       </c>
@@ -39318,7 +39318,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05732797762</t>
+            <t xml:space="preserve">02338803674</t>
           </r>
         </is>
       </c>
@@ -39329,7 +39329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2025</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -39377,7 +39377,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RODRIGUES GERALDO DE SOUZA</t>
+            <t xml:space="preserve">RODRIGO WILLER DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -39387,7 +39387,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">036.160.136-07</t>
+            <t xml:space="preserve">123.890.076-35</t>
           </r>
         </is>
       </c>
@@ -39397,7 +39397,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05446425338</t>
+            <t xml:space="preserve">05732797762</t>
           </r>
         </is>
       </c>
@@ -39408,7 +39408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">03/07/2025</t>
           </r>
         </is>
       </c>
@@ -39456,7 +39456,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGELIO DA CRUZ DOS SANTOS</t>
+            <t xml:space="preserve">RODRIGUES GERALDO DE SOUZA</t>
           </r>
         </is>
       </c>
@@ -39466,7 +39466,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">043.086.985-10</t>
+            <t xml:space="preserve">036.160.136-07</t>
           </r>
         </is>
       </c>
@@ -39476,7 +39476,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04971758149</t>
+            <t xml:space="preserve">05446425338</t>
           </r>
         </is>
       </c>
@@ -39487,7 +39487,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">13/01/2027</t>
           </r>
         </is>
       </c>
@@ -39535,7 +39535,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGER MARCIO SIRIO    </t>
+            <t xml:space="preserve">ROGELIO DA CRUZ DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -39545,7 +39545,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">132.076.616-10</t>
+            <t xml:space="preserve">043.086.985-10</t>
           </r>
         </is>
       </c>
@@ -39555,7 +39555,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05572572958</t>
+            <t xml:space="preserve">04971758149</t>
           </r>
         </is>
       </c>
@@ -39614,7 +39614,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGERIO PEREIRA VARGAS</t>
+            <t xml:space="preserve">ROGER MARCIO SIRIO    </t>
           </r>
         </is>
       </c>
@@ -39624,7 +39624,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">032.158.106-70</t>
+            <t xml:space="preserve">132.076.616-10</t>
           </r>
         </is>
       </c>
@@ -39634,7 +39634,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03602334615</t>
+            <t xml:space="preserve">05572572958</t>
           </r>
         </is>
       </c>
@@ -39645,7 +39645,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -39693,7 +39693,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROGERIO SILVA ARAUJO</t>
+            <t xml:space="preserve">ROGERIO PEREIRA VARGAS</t>
           </r>
         </is>
       </c>
@@ -39703,7 +39703,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.071.636-03</t>
+            <t xml:space="preserve">032.158.106-70</t>
           </r>
         </is>
       </c>
@@ -39713,7 +39713,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03090082407</t>
+            <t xml:space="preserve">03602334615</t>
           </r>
         </is>
       </c>
@@ -39724,7 +39724,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/10/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -39772,7 +39772,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROMERSON MANOEL DA SILVA</t>
+            <t xml:space="preserve">ROGERIO SILVA ARAUJO</t>
           </r>
         </is>
       </c>
@@ -39782,7 +39782,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">932.654.096-00</t>
+            <t xml:space="preserve">061.071.636-03</t>
           </r>
         </is>
       </c>
@@ -39792,7 +39792,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4211589860</t>
+            <t xml:space="preserve">03090082407</t>
           </r>
         </is>
       </c>
@@ -39803,7 +39803,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/02/2027</t>
+            <t xml:space="preserve">09/10/2027</t>
           </r>
         </is>
       </c>
@@ -39851,7 +39851,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROMILDA JOSILEIA SOUSA</t>
+            <t xml:space="preserve">ROMERSON MANOEL DA SILVA</t>
           </r>
         </is>
       </c>
@@ -39861,7 +39861,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.632.306-89</t>
+            <t xml:space="preserve">932.654.096-00</t>
           </r>
         </is>
       </c>
@@ -39871,7 +39871,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05001455978</t>
+            <t xml:space="preserve">4211589860</t>
           </r>
         </is>
       </c>
@@ -39882,7 +39882,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">10/02/2027</t>
           </r>
         </is>
       </c>
@@ -39923,14 +39923,14 @@
       <c r="T503" s="12" t="inlineStr"/>
       <c r="U503" s="1" t="inlineStr"/>
     </row>
-    <row r="504" customHeight="1" ht="22">
+    <row r="504" customHeight="1" ht="21">
       <c r="A504" s="1" t="inlineStr"/>
       <c r="B504" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROMILSON FREDERICO DE AZEVEDO</t>
+            <t xml:space="preserve">ROMILDA JOSILEIA SOUSA</t>
           </r>
         </is>
       </c>
@@ -39940,7 +39940,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">129.360.716-90</t>
+            <t xml:space="preserve">070.632.306-89</t>
           </r>
         </is>
       </c>
@@ -39950,7 +39950,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06438884446</t>
+            <t xml:space="preserve">05001455978</t>
           </r>
         </is>
       </c>
@@ -39961,7 +39961,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -40002,14 +40002,14 @@
       <c r="T504" s="12" t="inlineStr"/>
       <c r="U504" s="1" t="inlineStr"/>
     </row>
-    <row r="505" customHeight="1" ht="21">
+    <row r="505" customHeight="1" ht="22">
       <c r="A505" s="1" t="inlineStr"/>
       <c r="B505" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO BORGES MAGALHAES</t>
+            <t xml:space="preserve">ROMILSON FREDERICO DE AZEVEDO</t>
           </r>
         </is>
       </c>
@@ -40019,7 +40019,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">812.820.286-34</t>
+            <t xml:space="preserve">129.360.716-90</t>
           </r>
         </is>
       </c>
@@ -40029,7 +40029,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00574237295</t>
+            <t xml:space="preserve">06438884446</t>
           </r>
         </is>
       </c>
@@ -40040,7 +40040,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/09/2027</t>
+            <t xml:space="preserve">16/10/2027</t>
           </r>
         </is>
       </c>
@@ -40088,7 +40088,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO ROSALVO DOS SANTOS</t>
+            <t xml:space="preserve">RONALDO BORGES MAGALHAES</t>
           </r>
         </is>
       </c>
@@ -40098,7 +40098,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">035.607.284-36</t>
+            <t xml:space="preserve">812.820.286-34</t>
           </r>
         </is>
       </c>
@@ -40108,7 +40108,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03658415228</t>
+            <t xml:space="preserve">00574237295</t>
           </r>
         </is>
       </c>
@@ -40119,7 +40119,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">03/09/2027</t>
           </r>
         </is>
       </c>
@@ -40167,7 +40167,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONALDO SILVA DE CARVALHO</t>
+            <t xml:space="preserve">RONALDO ROSALVO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -40177,7 +40177,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">093.120.046-62</t>
+            <t xml:space="preserve">035.607.284-36</t>
           </r>
         </is>
       </c>
@@ -40187,7 +40187,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05036941619</t>
+            <t xml:space="preserve">03658415228</t>
           </r>
         </is>
       </c>
@@ -40198,7 +40198,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -40246,7 +40246,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONIE FERNANDO DA SILVA</t>
+            <t xml:space="preserve">RONALDO SILVA DE CARVALHO</t>
           </r>
         </is>
       </c>
@@ -40256,7 +40256,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">052.060.286-22</t>
+            <t xml:space="preserve">093.120.046-62</t>
           </r>
         </is>
       </c>
@@ -40266,7 +40266,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06025263305</t>
+            <t xml:space="preserve">05036941619</t>
           </r>
         </is>
       </c>
@@ -40277,7 +40277,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/07/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -40325,7 +40325,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONILDO OLIVEIRA CRUZ</t>
+            <t xml:space="preserve">RONIE FERNANDO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -40335,7 +40335,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">021.930.251-00</t>
+            <t xml:space="preserve">052.060.286-22</t>
           </r>
         </is>
       </c>
@@ -40345,7 +40345,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04883639482</t>
+            <t xml:space="preserve">06025263305</t>
           </r>
         </is>
       </c>
@@ -40356,7 +40356,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/08/2027</t>
+            <t xml:space="preserve">03/07/2027</t>
           </r>
         </is>
       </c>
@@ -40404,7 +40404,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RONNY CARLOS DA SILVA</t>
+            <t xml:space="preserve">RONILDO OLIVEIRA CRUZ</t>
           </r>
         </is>
       </c>
@@ -40414,7 +40414,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">947.454.126-49</t>
+            <t xml:space="preserve">021.930.251-00</t>
           </r>
         </is>
       </c>
@@ -40424,7 +40424,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03488127326</t>
+            <t xml:space="preserve">04883639482</t>
           </r>
         </is>
       </c>
@@ -40435,7 +40435,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">25/08/2027</t>
           </r>
         </is>
       </c>
@@ -40476,14 +40476,14 @@
       <c r="T510" s="12" t="inlineStr"/>
       <c r="U510" s="1" t="inlineStr"/>
     </row>
-    <row r="511" customHeight="1" ht="22">
+    <row r="511" customHeight="1" ht="21">
       <c r="A511" s="1" t="inlineStr"/>
       <c r="B511" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROSILENE DAS GRAÇAS DE O COSTA SIQUEIRA </t>
+            <t xml:space="preserve">RONNY CARLOS DA SILVA</t>
           </r>
         </is>
       </c>
@@ -40493,7 +40493,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.324.136-93</t>
+            <t xml:space="preserve">947.454.126-49</t>
           </r>
         </is>
       </c>
@@ -40503,7 +40503,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04774059559</t>
+            <t xml:space="preserve">03488127326</t>
           </r>
         </is>
       </c>
@@ -40514,7 +40514,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -40555,14 +40555,14 @@
       <c r="T511" s="12" t="inlineStr"/>
       <c r="U511" s="1" t="inlineStr"/>
     </row>
-    <row r="512" customHeight="1" ht="21">
+    <row r="512" customHeight="1" ht="22">
       <c r="A512" s="1" t="inlineStr"/>
       <c r="B512" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ROZEMAR SEMIAO PINTO</t>
+            <t xml:space="preserve">ROSILENE DAS GRAÇAS DE O COSTA SIQUEIRA </t>
           </r>
         </is>
       </c>
@@ -40572,7 +40572,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.531.246-95</t>
+            <t xml:space="preserve">076.324.136-93</t>
           </r>
         </is>
       </c>
@@ -40582,7 +40582,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04086354799</t>
+            <t xml:space="preserve">04774059559</t>
           </r>
         </is>
       </c>
@@ -40593,7 +40593,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -40641,7 +40641,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RUBENS JOSE DA RO¿¿¿</t>
+            <t xml:space="preserve">ROZEMAR SEMIAO PINTO</t>
           </r>
         </is>
       </c>
@@ -40651,7 +40651,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">555.890.656-15</t>
+            <t xml:space="preserve">054.531.246-95</t>
           </r>
         </is>
       </c>
@@ -40661,7 +40661,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01136935529</t>
+            <t xml:space="preserve">04086354799</t>
           </r>
         </is>
       </c>
@@ -40672,7 +40672,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/07/2027</t>
+            <t xml:space="preserve">27/08/2027</t>
           </r>
         </is>
       </c>
@@ -40720,7 +40720,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RUBENS LUIS CARNEIRO</t>
+            <t xml:space="preserve">RUBENS JOSE DA RO¿¿¿</t>
           </r>
         </is>
       </c>
@@ -40730,7 +40730,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">074.702.786-21</t>
+            <t xml:space="preserve">555.890.656-15</t>
           </r>
         </is>
       </c>
@@ -40740,7 +40740,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14163556</t>
+            <t xml:space="preserve">01136935529</t>
           </r>
         </is>
       </c>
@@ -40751,7 +40751,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/08/2027</t>
+            <t xml:space="preserve">13/07/2027</t>
           </r>
         </is>
       </c>
@@ -40799,7 +40799,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SALATIEL GOMES DOS SANTOS</t>
+            <t xml:space="preserve">RUBENS LUIS CARNEIRO</t>
           </r>
         </is>
       </c>
@@ -40809,7 +40809,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.278.946-32</t>
+            <t xml:space="preserve">074.702.786-21</t>
           </r>
         </is>
       </c>
@@ -40819,7 +40819,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05199034200</t>
+            <t xml:space="preserve">14163556</t>
           </r>
         </is>
       </c>
@@ -40830,7 +40830,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/02/2027</t>
+            <t xml:space="preserve">20/08/2027</t>
           </r>
         </is>
       </c>
@@ -40878,7 +40878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRA APARECIDA DE LACERDA</t>
+            <t xml:space="preserve">SALATIEL GOMES DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -40888,7 +40888,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">067.654.516-50</t>
+            <t xml:space="preserve">120.278.946-32</t>
           </r>
         </is>
       </c>
@@ -40898,7 +40898,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06112213773</t>
+            <t xml:space="preserve">05199034200</t>
           </r>
         </is>
       </c>
@@ -40909,7 +40909,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/03/2027</t>
+            <t xml:space="preserve">19/02/2027</t>
           </r>
         </is>
       </c>
@@ -40957,7 +40957,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRA MARA MARTINS</t>
+            <t xml:space="preserve">SANDRA APARECIDA DE LACERDA</t>
           </r>
         </is>
       </c>
@@ -40967,7 +40967,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">038.635.206-29</t>
+            <t xml:space="preserve">067.654.516-50</t>
           </r>
         </is>
       </c>
@@ -40977,7 +40977,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04164944850</t>
+            <t xml:space="preserve">06112213773</t>
           </r>
         </is>
       </c>
@@ -40988,7 +40988,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2026</t>
+            <t xml:space="preserve">11/03/2027</t>
           </r>
         </is>
       </c>
@@ -41029,14 +41029,14 @@
       <c r="T517" s="12" t="inlineStr"/>
       <c r="U517" s="1" t="inlineStr"/>
     </row>
-    <row r="518" customHeight="1" ht="22">
+    <row r="518" customHeight="1" ht="21">
       <c r="A518" s="1" t="inlineStr"/>
       <c r="B518" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SANDRO MARCOS DE FREITAS QUEIROS</t>
+            <t xml:space="preserve">SANDRA MARA MARTINS</t>
           </r>
         </is>
       </c>
@@ -41046,7 +41046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">977.080.206-97</t>
+            <t xml:space="preserve">038.635.206-29</t>
           </r>
         </is>
       </c>
@@ -41056,7 +41056,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01979048430</t>
+            <t xml:space="preserve">04164944850</t>
           </r>
         </is>
       </c>
@@ -41067,7 +41067,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">01/01/2026</t>
           </r>
         </is>
       </c>
@@ -41108,14 +41108,14 @@
       <c r="T518" s="12" t="inlineStr"/>
       <c r="U518" s="1" t="inlineStr"/>
     </row>
-    <row r="519" customHeight="1" ht="21">
+    <row r="519" customHeight="1" ht="22">
       <c r="A519" s="1" t="inlineStr"/>
       <c r="B519" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SEBASTIAO EUSTAQUIO TEIXEIRA</t>
+            <t xml:space="preserve">SANDRO MARCOS DE FREITAS QUEIROS</t>
           </r>
         </is>
       </c>
@@ -41125,7 +41125,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">456.820.546-87</t>
+            <t xml:space="preserve">977.080.206-97</t>
           </r>
         </is>
       </c>
@@ -41135,7 +41135,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03016774844</t>
+            <t xml:space="preserve">01979048430</t>
           </r>
         </is>
       </c>
@@ -41146,7 +41146,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -41194,7 +41194,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SEBASTIAO ROBERTO FRANCISCO</t>
+            <t xml:space="preserve">SEBASTIAO EUSTAQUIO TEIXEIRA</t>
           </r>
         </is>
       </c>
@@ -41204,7 +41204,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">032.171.546-22</t>
+            <t xml:space="preserve">456.820.546-87</t>
           </r>
         </is>
       </c>
@@ -41214,7 +41214,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01221024975</t>
+            <t xml:space="preserve">03016774844</t>
           </r>
         </is>
       </c>
@@ -41225,7 +41225,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/07/2027</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -41273,7 +41273,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO JESUS DE SENA</t>
+            <t xml:space="preserve">SEBASTIAO ROBERTO FRANCISCO</t>
           </r>
         </is>
       </c>
@@ -41283,7 +41283,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">703.152.481-49</t>
+            <t xml:space="preserve">032.171.546-22</t>
           </r>
         </is>
       </c>
@@ -41293,7 +41293,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01987693689</t>
+            <t xml:space="preserve">01221024975</t>
           </r>
         </is>
       </c>
@@ -41304,7 +41304,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2026</t>
+            <t xml:space="preserve">01/07/2027</t>
           </r>
         </is>
       </c>
@@ -41352,7 +41352,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO MARTINS CANDIDO</t>
+            <t xml:space="preserve">SERGIO JESUS DE SENA</t>
           </r>
         </is>
       </c>
@@ -41362,7 +41362,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">055.992.066-02</t>
+            <t xml:space="preserve">703.152.481-49</t>
           </r>
         </is>
       </c>
@@ -41372,7 +41372,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01540143348</t>
+            <t xml:space="preserve">01987693689</t>
           </r>
         </is>
       </c>
@@ -41383,7 +41383,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">24/09/2026</t>
           </r>
         </is>
       </c>
@@ -41431,7 +41431,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SERGIO SORA PEREIRA</t>
+            <t xml:space="preserve">SERGIO MARTINS CANDIDO</t>
           </r>
         </is>
       </c>
@@ -41441,7 +41441,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">116.201.246-37</t>
+            <t xml:space="preserve">055.992.066-02</t>
           </r>
         </is>
       </c>
@@ -41451,7 +41451,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05455543950</t>
+            <t xml:space="preserve">01540143348</t>
           </r>
         </is>
       </c>
@@ -41462,7 +41462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/08/2025</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -41510,7 +41510,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEI EDERSON RODRIGUES</t>
+            <t xml:space="preserve">SERGIO SORA PEREIRA</t>
           </r>
         </is>
       </c>
@@ -41520,7 +41520,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">035.114.576-10</t>
+            <t xml:space="preserve">116.201.246-37</t>
           </r>
         </is>
       </c>
@@ -41530,7 +41530,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01367789491</t>
+            <t xml:space="preserve">05455543950</t>
           </r>
         </is>
       </c>
@@ -41541,7 +41541,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/06/2027</t>
+            <t xml:space="preserve">12/08/2025</t>
           </r>
         </is>
       </c>
@@ -41589,7 +41589,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEY JUSTINIANO DE CARVALHO  </t>
+            <t xml:space="preserve">SIDNEI EDERSON RODRIGUES</t>
           </r>
         </is>
       </c>
@@ -41599,7 +41599,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">933.213.766-87</t>
+            <t xml:space="preserve">035.114.576-10</t>
           </r>
         </is>
       </c>
@@ -41609,7 +41609,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00490361489</t>
+            <t xml:space="preserve">01367789491</t>
           </r>
         </is>
       </c>
@@ -41620,7 +41620,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/01/2025</t>
+            <t xml:space="preserve">12/06/2027</t>
           </r>
         </is>
       </c>
@@ -41668,7 +41668,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SIDNEY LUCAS PEREIRA</t>
+            <t xml:space="preserve">SIDNEY JUSTINIANO DE CARVALHO  </t>
           </r>
         </is>
       </c>
@@ -41678,7 +41678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">003.086.236-14</t>
+            <t xml:space="preserve">933.213.766-87</t>
           </r>
         </is>
       </c>
@@ -41688,7 +41688,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01838999161</t>
+            <t xml:space="preserve">00490361489</t>
           </r>
         </is>
       </c>
@@ -41699,7 +41699,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/08/2027</t>
+            <t xml:space="preserve">27/01/2025</t>
           </r>
         </is>
       </c>
@@ -41747,7 +41747,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SINVAL DA SILVA VIGILATO</t>
+            <t xml:space="preserve">SIDNEY LUCAS PEREIRA</t>
           </r>
         </is>
       </c>
@@ -41757,7 +41757,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">875.211.056-72</t>
+            <t xml:space="preserve">003.086.236-14</t>
           </r>
         </is>
       </c>
@@ -41767,7 +41767,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02223241791</t>
+            <t xml:space="preserve">01838999161</t>
           </r>
         </is>
       </c>
@@ -41778,7 +41778,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">07/08/2027</t>
           </r>
         </is>
       </c>
@@ -41826,7 +41826,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">STEFANY LUAN PEREIRA GUEDES</t>
+            <t xml:space="preserve">SINVAL DA SILVA VIGILATO</t>
           </r>
         </is>
       </c>
@@ -41836,7 +41836,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.806.076-13</t>
+            <t xml:space="preserve">875.211.056-72</t>
           </r>
         </is>
       </c>
@@ -41846,7 +41846,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04363860554</t>
+            <t xml:space="preserve">02223241791</t>
           </r>
         </is>
       </c>
@@ -41857,7 +41857,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03/06/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -41905,7 +41905,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TALES VIEIRA DE SIQUEIRA</t>
+            <t xml:space="preserve">STEFANY LUAN PEREIRA GUEDES</t>
           </r>
         </is>
       </c>
@@ -41915,7 +41915,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.981.346-46</t>
+            <t xml:space="preserve">076.806.076-13</t>
           </r>
         </is>
       </c>
@@ -41925,7 +41925,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05186360780</t>
+            <t xml:space="preserve">04363860554</t>
           </r>
         </is>
       </c>
@@ -41936,7 +41936,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">03/06/2027</t>
           </r>
         </is>
       </c>
@@ -41984,7 +41984,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TATIANA CRISTINA DOS REIS</t>
+            <t xml:space="preserve">TALES VIEIRA DE SIQUEIRA</t>
           </r>
         </is>
       </c>
@@ -41994,7 +41994,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.974.806-62</t>
+            <t xml:space="preserve">077.981.346-46</t>
           </r>
         </is>
       </c>
@@ -42004,7 +42004,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04699145123</t>
+            <t xml:space="preserve">05186360780</t>
           </r>
         </is>
       </c>
@@ -42015,7 +42015,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -42063,7 +42063,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TATIANE MARTINS DA CRUZ</t>
+            <t xml:space="preserve">TATIANA CRISTINA DOS REIS</t>
           </r>
         </is>
       </c>
@@ -42073,7 +42073,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.758.886-55</t>
+            <t xml:space="preserve">076.974.806-62</t>
           </r>
         </is>
       </c>
@@ -42083,7 +42083,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05838164206</t>
+            <t xml:space="preserve">04699145123</t>
           </r>
         </is>
       </c>
@@ -42094,7 +42094,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/01/2027</t>
+            <t xml:space="preserve">13/01/2027</t>
           </r>
         </is>
       </c>
@@ -42135,14 +42135,14 @@
       <c r="T531" s="12" t="inlineStr"/>
       <c r="U531" s="1" t="inlineStr"/>
     </row>
-    <row r="532" customHeight="1" ht="22">
+    <row r="532" customHeight="1" ht="21">
       <c r="A532" s="1" t="inlineStr"/>
       <c r="B532" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THAISON BRUNO FERNANDO DOS SANTOS</t>
+            <t xml:space="preserve">TATIANE MARTINS DA CRUZ</t>
           </r>
         </is>
       </c>
@@ -42152,7 +42152,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">015.914.226-12</t>
+            <t xml:space="preserve">120.758.886-55</t>
           </r>
         </is>
       </c>
@@ -42162,7 +42162,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">0436952989</t>
+            <t xml:space="preserve">05838164206</t>
           </r>
         </is>
       </c>
@@ -42173,7 +42173,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/09/2027</t>
+            <t xml:space="preserve">27/01/2027</t>
           </r>
         </is>
       </c>
@@ -42214,14 +42214,14 @@
       <c r="T532" s="12" t="inlineStr"/>
       <c r="U532" s="1" t="inlineStr"/>
     </row>
-    <row r="533" customHeight="1" ht="21">
+    <row r="533" customHeight="1" ht="22">
       <c r="A533" s="1" t="inlineStr"/>
       <c r="B533" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO ALVES FERREIRA</t>
+            <t xml:space="preserve">THAISON BRUNO FERNANDO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -42231,7 +42231,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">076.622.556-97</t>
+            <t xml:space="preserve">015.914.226-12</t>
           </r>
         </is>
       </c>
@@ -42241,7 +42241,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04151517893</t>
+            <t xml:space="preserve">0436952989</t>
           </r>
         </is>
       </c>
@@ -42252,7 +42252,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/11/2026</t>
+            <t xml:space="preserve">10/09/2027</t>
           </r>
         </is>
       </c>
@@ -42300,7 +42300,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO FARIA ROSA</t>
+            <t xml:space="preserve">THIAGO ALVES FERREIRA</t>
           </r>
         </is>
       </c>
@@ -42310,7 +42310,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">101.801.956-11</t>
+            <t xml:space="preserve">076.622.556-97</t>
           </r>
         </is>
       </c>
@@ -42320,7 +42320,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05453493191</t>
+            <t xml:space="preserve">04151517893</t>
           </r>
         </is>
       </c>
@@ -42331,7 +42331,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/07/2027</t>
+            <t xml:space="preserve">10/11/2026</t>
           </r>
         </is>
       </c>
@@ -42379,7 +42379,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">THIAGO GONCALVES CARDOSO</t>
+            <t xml:space="preserve">THIAGO FARIA ROSA</t>
           </r>
         </is>
       </c>
@@ -42389,7 +42389,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">022.860.086-39</t>
+            <t xml:space="preserve">101.801.956-11</t>
           </r>
         </is>
       </c>
@@ -42399,7 +42399,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06955819327</t>
+            <t xml:space="preserve">05453493191</t>
           </r>
         </is>
       </c>
@@ -42410,7 +42410,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/12/2025</t>
+            <t xml:space="preserve">14/07/2027</t>
           </r>
         </is>
       </c>
@@ -42458,7 +42458,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TIAGO ANDRADE DOS PASSOS</t>
+            <t xml:space="preserve">THIAGO GONCALVES CARDOSO</t>
           </r>
         </is>
       </c>
@@ -42468,7 +42468,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">084.447.676-54</t>
+            <t xml:space="preserve">022.860.086-39</t>
           </r>
         </is>
       </c>
@@ -42478,7 +42478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03945068162</t>
+            <t xml:space="preserve">06955819327</t>
           </r>
         </is>
       </c>
@@ -42489,7 +42489,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/06/2027</t>
+            <t xml:space="preserve">11/12/2025</t>
           </r>
         </is>
       </c>
@@ -42537,7 +42537,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TIAGO DA SILVA LIMA</t>
+            <t xml:space="preserve">TIAGO ANDRADE DOS PASSOS</t>
           </r>
         </is>
       </c>
@@ -42547,7 +42547,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">075.518.336-33</t>
+            <t xml:space="preserve">084.447.676-54</t>
           </r>
         </is>
       </c>
@@ -42557,7 +42557,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03550506992</t>
+            <t xml:space="preserve">03945068162</t>
           </r>
         </is>
       </c>
@@ -42568,7 +42568,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/09/2027</t>
+            <t xml:space="preserve">11/06/2027</t>
           </r>
         </is>
       </c>
@@ -42616,7 +42616,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UENDERSON RONALD DA SILVA</t>
+            <t xml:space="preserve">TIAGO DA SILVA LIMA</t>
           </r>
         </is>
       </c>
@@ -42626,7 +42626,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.548.716-13</t>
+            <t xml:space="preserve">075.518.336-33</t>
           </r>
         </is>
       </c>
@@ -42636,7 +42636,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03399996765</t>
+            <t xml:space="preserve">03550506992</t>
           </r>
         </is>
       </c>
@@ -42647,7 +42647,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/07/2027</t>
+            <t xml:space="preserve">08/09/2027</t>
           </r>
         </is>
       </c>
@@ -42695,7 +42695,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ULISSES DE FREITAS MELO</t>
+            <t xml:space="preserve">UENDERSON RONALD DA SILVA</t>
           </r>
         </is>
       </c>
@@ -42705,7 +42705,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">041.135.016-10</t>
+            <t xml:space="preserve">054.548.716-13</t>
           </r>
         </is>
       </c>
@@ -42715,7 +42715,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03364297306</t>
+            <t xml:space="preserve">03399996765</t>
           </r>
         </is>
       </c>
@@ -42726,7 +42726,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/09/2027</t>
+            <t xml:space="preserve">24/07/2027</t>
           </r>
         </is>
       </c>
@@ -42774,7 +42774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">URBANO MORAIS LOURENCO</t>
+            <t xml:space="preserve">ULISSES DE FREITAS MELO</t>
           </r>
         </is>
       </c>
@@ -42784,7 +42784,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">118.321.046-99</t>
+            <t xml:space="preserve">041.135.016-10</t>
           </r>
         </is>
       </c>
@@ -42794,7 +42794,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06455070312</t>
+            <t xml:space="preserve">03364297306</t>
           </r>
         </is>
       </c>
@@ -42805,7 +42805,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">14/04/2027</t>
+            <t xml:space="preserve">09/09/2027</t>
           </r>
         </is>
       </c>
@@ -42853,7 +42853,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VADIR BERNARDES DA SILVA</t>
+            <t xml:space="preserve">URBANO MORAIS LOURENCO</t>
           </r>
         </is>
       </c>
@@ -42863,7 +42863,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">046.330.718-66</t>
+            <t xml:space="preserve">118.321.046-99</t>
           </r>
         </is>
       </c>
@@ -42873,7 +42873,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01938461228</t>
+            <t xml:space="preserve">06455070312</t>
           </r>
         </is>
       </c>
@@ -42884,7 +42884,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2026</t>
+            <t xml:space="preserve">14/04/2027</t>
           </r>
         </is>
       </c>
@@ -42925,14 +42925,14 @@
       <c r="T541" s="12" t="inlineStr"/>
       <c r="U541" s="1" t="inlineStr"/>
     </row>
-    <row r="542" customHeight="1" ht="22">
+    <row r="542" customHeight="1" ht="21">
       <c r="A542" s="1" t="inlineStr"/>
       <c r="B542" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALERIANO ALEX VIEIRA DE OLIVEIRA</t>
+            <t xml:space="preserve">VADIR BERNARDES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -42942,7 +42942,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">086.507.656-10</t>
+            <t xml:space="preserve">046.330.718-66</t>
           </r>
         </is>
       </c>
@@ -42952,7 +42952,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04705449109</t>
+            <t xml:space="preserve">01938461228</t>
           </r>
         </is>
       </c>
@@ -42963,7 +42963,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">23/07/2026</t>
           </r>
         </is>
       </c>
@@ -43004,14 +43004,14 @@
       <c r="T542" s="12" t="inlineStr"/>
       <c r="U542" s="1" t="inlineStr"/>
     </row>
-    <row r="543" customHeight="1" ht="21">
+    <row r="543" customHeight="1" ht="22">
       <c r="A543" s="1" t="inlineStr"/>
       <c r="B543" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALMIR GOMES RIBEIRO</t>
+            <t xml:space="preserve">VALERIANO ALEX VIEIRA DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -43021,7 +43021,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.463.326-63</t>
+            <t xml:space="preserve">086.507.656-10</t>
           </r>
         </is>
       </c>
@@ -43031,7 +43031,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04922140128</t>
+            <t xml:space="preserve">04705449109</t>
           </r>
         </is>
       </c>
@@ -43042,7 +43042,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/01/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -43090,7 +43090,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALQUIRIA SANTOS COUTO</t>
+            <t xml:space="preserve">VALMIR GOMES RIBEIRO</t>
           </r>
         </is>
       </c>
@@ -43100,7 +43100,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">077.378.626-09</t>
+            <t xml:space="preserve">065.463.326-63</t>
           </r>
         </is>
       </c>
@@ -43110,7 +43110,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05442378859</t>
+            <t xml:space="preserve">04922140128</t>
           </r>
         </is>
       </c>
@@ -43121,7 +43121,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/02/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -43169,7 +43169,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALTER DOMINGOS MEIRELES  </t>
+            <t xml:space="preserve">VALQUIRIA SANTOS COUTO</t>
           </r>
         </is>
       </c>
@@ -43179,7 +43179,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">040.666.886-83</t>
+            <t xml:space="preserve">077.378.626-09</t>
           </r>
         </is>
       </c>
@@ -43189,7 +43189,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02232141549</t>
+            <t xml:space="preserve">05442378859</t>
           </r>
         </is>
       </c>
@@ -43200,7 +43200,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2026</t>
+            <t xml:space="preserve">13/02/2026</t>
           </r>
         </is>
       </c>
@@ -43248,7 +43248,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VALTER RAMOS DE LIMA</t>
+            <t xml:space="preserve">VALTER DOMINGOS MEIRELES  </t>
           </r>
         </is>
       </c>
@@ -43258,7 +43258,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">832.376.746-72</t>
+            <t xml:space="preserve">040.666.886-83</t>
           </r>
         </is>
       </c>
@@ -43268,7 +43268,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01110738309</t>
+            <t xml:space="preserve">02232141549</t>
           </r>
         </is>
       </c>
@@ -43279,7 +43279,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">07/10/2026</t>
           </r>
         </is>
       </c>
@@ -43320,14 +43320,14 @@
       <c r="T546" s="12" t="inlineStr"/>
       <c r="U546" s="1" t="inlineStr"/>
     </row>
-    <row r="547" customHeight="1" ht="22">
+    <row r="547" customHeight="1" ht="21">
       <c r="A547" s="1" t="inlineStr"/>
       <c r="B547" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANDERCI BATISTA LEANDRO DOS SANTOS</t>
+            <t xml:space="preserve">VALTER RAMOS DE LIMA</t>
           </r>
         </is>
       </c>
@@ -43337,7 +43337,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">939.681.836-49</t>
+            <t xml:space="preserve">832.376.746-72</t>
           </r>
         </is>
       </c>
@@ -43347,7 +43347,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02672395939</t>
+            <t xml:space="preserve">01110738309</t>
           </r>
         </is>
       </c>
@@ -43358,7 +43358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/11/2026</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -43399,14 +43399,14 @@
       <c r="T547" s="12" t="inlineStr"/>
       <c r="U547" s="1" t="inlineStr"/>
     </row>
-    <row r="548" customHeight="1" ht="21">
+    <row r="548" customHeight="1" ht="22">
       <c r="A548" s="1" t="inlineStr"/>
       <c r="B548" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANDERSON TELES NASCIMENTO</t>
+            <t xml:space="preserve">VANDERCI BATISTA LEANDRO DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -43416,7 +43416,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">819.675.435-34</t>
+            <t xml:space="preserve">939.681.836-49</t>
           </r>
         </is>
       </c>
@@ -43426,7 +43426,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01845793756</t>
+            <t xml:space="preserve">02672395939</t>
           </r>
         </is>
       </c>
@@ -43437,7 +43437,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/10/2026</t>
+            <t xml:space="preserve">26/11/2026</t>
           </r>
         </is>
       </c>
@@ -43485,7 +43485,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANEIALVES GUIMARAES</t>
+            <t xml:space="preserve">VANDERSON TELES NASCIMENTO</t>
           </r>
         </is>
       </c>
@@ -43495,7 +43495,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">026.859.956-41</t>
+            <t xml:space="preserve">819.675.435-34</t>
           </r>
         </is>
       </c>
@@ -43505,7 +43505,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03607821769</t>
+            <t xml:space="preserve">01845793756</t>
           </r>
         </is>
       </c>
@@ -43516,7 +43516,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/01/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -43564,7 +43564,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANESSA CAROLINNE GONÇALVES</t>
+            <t xml:space="preserve">VANEIALVES GUIMARAES</t>
           </r>
         </is>
       </c>
@@ -43574,7 +43574,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">120.868.326-80</t>
+            <t xml:space="preserve">026.859.956-41</t>
           </r>
         </is>
       </c>
@@ -43584,7 +43584,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06829001421</t>
+            <t xml:space="preserve">03607821769</t>
           </r>
         </is>
       </c>
@@ -43595,7 +43595,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">12/12/2026</t>
+            <t xml:space="preserve">15/01/2027</t>
           </r>
         </is>
       </c>
@@ -43643,7 +43643,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VANUSA ABADIA DE PAULA</t>
+            <t xml:space="preserve">VANESSA CAROLINNE GONÇALVES</t>
           </r>
         </is>
       </c>
@@ -43653,7 +43653,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">064.805.036-00</t>
+            <t xml:space="preserve">120.868.326-80</t>
           </r>
         </is>
       </c>
@@ -43663,7 +43663,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04811324603</t>
+            <t xml:space="preserve">06829001421</t>
           </r>
         </is>
       </c>
@@ -43674,7 +43674,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/10/2027</t>
+            <t xml:space="preserve">12/12/2026</t>
           </r>
         </is>
       </c>
@@ -43722,7 +43722,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE DE PAULO DA SILVA</t>
+            <t xml:space="preserve">VANUSA ABADIA DE PAULA</t>
           </r>
         </is>
       </c>
@@ -43732,7 +43732,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">731.778.146-00</t>
+            <t xml:space="preserve">064.805.036-00</t>
           </r>
         </is>
       </c>
@@ -43742,7 +43742,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02507810777</t>
+            <t xml:space="preserve">04811324603</t>
           </r>
         </is>
       </c>
@@ -43753,7 +43753,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/07/2027</t>
+            <t xml:space="preserve">06/10/2027</t>
           </r>
         </is>
       </c>
@@ -43801,7 +43801,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE DOS REIS GOMES</t>
+            <t xml:space="preserve">VICENTE DE PAULO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -43811,7 +43811,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">755.303.926-87</t>
+            <t xml:space="preserve">731.778.146-00</t>
           </r>
         </is>
       </c>
@@ -43821,7 +43821,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02525863238</t>
+            <t xml:space="preserve">02507810777</t>
           </r>
         </is>
       </c>
@@ -43832,7 +43832,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/08/2027</t>
+            <t xml:space="preserve">22/07/2027</t>
           </r>
         </is>
       </c>
@@ -43880,7 +43880,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VICENTE ROBERTO ANGELO</t>
+            <t xml:space="preserve">VICENTE DOS REIS GOMES</t>
           </r>
         </is>
       </c>
@@ -43890,7 +43890,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">399.263.546-53</t>
+            <t xml:space="preserve">755.303.926-87</t>
           </r>
         </is>
       </c>
@@ -43900,7 +43900,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01030510930</t>
+            <t xml:space="preserve">02525863238</t>
           </r>
         </is>
       </c>
@@ -43911,7 +43911,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">26/08/2027</t>
           </r>
         </is>
       </c>
@@ -43959,7 +43959,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VILEIDE VAZ MOREIRA </t>
+            <t xml:space="preserve">VICENTE ROBERTO ANGELO</t>
           </r>
         </is>
       </c>
@@ -43969,7 +43969,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">109.093.766-03</t>
+            <t xml:space="preserve">399.263.546-53</t>
           </r>
         </is>
       </c>
@@ -43979,7 +43979,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06087149441</t>
+            <t xml:space="preserve">01030510930</t>
           </r>
         </is>
       </c>
@@ -43990,7 +43990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">11/08/2027</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -44038,7 +44038,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VINICIO JOSE DOS SANTOS</t>
+            <t xml:space="preserve">VILEIDE VAZ MOREIRA </t>
           </r>
         </is>
       </c>
@@ -44048,7 +44048,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">048.389.316-11</t>
+            <t xml:space="preserve">109.093.766-03</t>
           </r>
         </is>
       </c>
@@ -44058,7 +44058,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01306809764</t>
+            <t xml:space="preserve">06087149441</t>
           </r>
         </is>
       </c>
@@ -44069,7 +44069,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/07/2027</t>
+            <t xml:space="preserve">11/08/2027</t>
           </r>
         </is>
       </c>
@@ -44117,7 +44117,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VINICIUS BORGES VALES</t>
+            <t xml:space="preserve">VINICIO JOSE DOS SANTOS</t>
           </r>
         </is>
       </c>
@@ -44127,7 +44127,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">086.215.466-98</t>
+            <t xml:space="preserve">048.389.316-11</t>
           </r>
         </is>
       </c>
@@ -44137,7 +44137,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04262664653</t>
+            <t xml:space="preserve">01306809764</t>
           </r>
         </is>
       </c>
@@ -44148,7 +44148,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">31/07/2024</t>
+            <t xml:space="preserve">23/07/2027</t>
           </r>
         </is>
       </c>
@@ -44196,7 +44196,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VITOR FERREIRA SANTOS</t>
+            <t xml:space="preserve">VINICIUS BORGES VALES</t>
           </r>
         </is>
       </c>
@@ -44206,7 +44206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">136.025.886-88</t>
+            <t xml:space="preserve">086.215.466-98</t>
           </r>
         </is>
       </c>
@@ -44216,7 +44216,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07186400700</t>
+            <t xml:space="preserve">04262664653</t>
           </r>
         </is>
       </c>
@@ -44227,7 +44227,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2027</t>
+            <t xml:space="preserve">31/07/2024</t>
           </r>
         </is>
       </c>
@@ -44275,7 +44275,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VITOR GABRIEL GOMES CORREIA </t>
+            <t xml:space="preserve">VITOR FERREIRA SANTOS</t>
           </r>
         </is>
       </c>
@@ -44285,7 +44285,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">019.705.576-13</t>
+            <t xml:space="preserve">136.025.886-88</t>
           </r>
         </is>
       </c>
@@ -44295,7 +44295,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06930599950</t>
+            <t xml:space="preserve">07186400700</t>
           </r>
         </is>
       </c>
@@ -44306,7 +44306,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">21/10/2027</t>
           </r>
         </is>
       </c>
@@ -44354,7 +44354,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WAGNER FERNANDES DA SILVA</t>
+            <t xml:space="preserve">VITOR GABRIEL GOMES CORREIA </t>
           </r>
         </is>
       </c>
@@ -44364,7 +44364,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">012.597.906-14</t>
+            <t xml:space="preserve">019.705.576-13</t>
           </r>
         </is>
       </c>
@@ -44374,7 +44374,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03780457127</t>
+            <t xml:space="preserve">06930599950</t>
           </r>
         </is>
       </c>
@@ -44385,7 +44385,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">21/10/2026</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -44426,14 +44426,14 @@
       <c r="T560" s="12" t="inlineStr"/>
       <c r="U560" s="1" t="inlineStr"/>
     </row>
-    <row r="561" customHeight="1" ht="22">
+    <row r="561" customHeight="1" ht="21">
       <c r="A561" s="1" t="inlineStr"/>
       <c r="B561" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WALBER EVANGELISTA LONGO DO NASCIMENTO</t>
+            <t xml:space="preserve">WAGNER FERNANDES DA SILVA</t>
           </r>
         </is>
       </c>
@@ -44443,7 +44443,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">072.851.686-10</t>
+            <t xml:space="preserve">012.597.906-14</t>
           </r>
         </is>
       </c>
@@ -44453,7 +44453,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03810941378</t>
+            <t xml:space="preserve">03780457127</t>
           </r>
         </is>
       </c>
@@ -44464,7 +44464,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/08/2027</t>
+            <t xml:space="preserve">21/10/2026</t>
           </r>
         </is>
       </c>
@@ -44505,14 +44505,14 @@
       <c r="T561" s="12" t="inlineStr"/>
       <c r="U561" s="1" t="inlineStr"/>
     </row>
-    <row r="562" customHeight="1" ht="21">
+    <row r="562" customHeight="1" ht="22">
       <c r="A562" s="1" t="inlineStr"/>
       <c r="B562" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WALLACE DE LIMA   </t>
+            <t xml:space="preserve">WALBER EVANGELISTA LONGO DO NASCIMENTO</t>
           </r>
         </is>
       </c>
@@ -44522,7 +44522,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.786.806-94</t>
+            <t xml:space="preserve">072.851.686-10</t>
           </r>
         </is>
       </c>
@@ -44532,7 +44532,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04928551509</t>
+            <t xml:space="preserve">03810941378</t>
           </r>
         </is>
       </c>
@@ -44543,7 +44543,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">27/08/2027</t>
           </r>
         </is>
       </c>
@@ -44591,7 +44591,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WALMIR ALVES MEIRELES   </t>
+            <t xml:space="preserve">WALLACE DE LIMA   </t>
           </r>
         </is>
       </c>
@@ -44601,7 +44601,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">001.214.386-35</t>
+            <t xml:space="preserve">061.786.806-94</t>
           </r>
         </is>
       </c>
@@ -44611,7 +44611,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00441481335</t>
+            <t xml:space="preserve">04928551509</t>
           </r>
         </is>
       </c>
@@ -44622,7 +44622,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/08/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -44670,7 +44670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WANDEIR HONORATO DE OLIVEIRA</t>
+            <t xml:space="preserve">WALMIR ALVES MEIRELES   </t>
           </r>
         </is>
       </c>
@@ -44680,7 +44680,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">824.616.866-53</t>
+            <t xml:space="preserve">001.214.386-35</t>
           </r>
         </is>
       </c>
@@ -44690,7 +44690,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02755705481</t>
+            <t xml:space="preserve">00441481335</t>
           </r>
         </is>
       </c>
@@ -44701,7 +44701,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">06/08/2027</t>
           </r>
         </is>
       </c>
@@ -44749,7 +44749,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WANDERSON HENRIQUE FARAH</t>
+            <t xml:space="preserve">WANDEIR HONORATO DE OLIVEIRA</t>
           </r>
         </is>
       </c>
@@ -44759,7 +44759,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">070.031.086-07</t>
+            <t xml:space="preserve">824.616.866-53</t>
           </r>
         </is>
       </c>
@@ -44769,7 +44769,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03551548436</t>
+            <t xml:space="preserve">02755705481</t>
           </r>
         </is>
       </c>
@@ -44780,7 +44780,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/05/2026</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -44828,7 +44828,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WARLEY TEODORO</t>
+            <t xml:space="preserve">WANDERSON HENRIQUE FARAH</t>
           </r>
         </is>
       </c>
@@ -44838,7 +44838,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">061.096.156-09</t>
+            <t xml:space="preserve">070.031.086-07</t>
           </r>
         </is>
       </c>
@@ -44848,7 +44848,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03946495186</t>
+            <t xml:space="preserve">03551548436</t>
           </r>
         </is>
       </c>
@@ -44859,7 +44859,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/09/2027</t>
+            <t xml:space="preserve">30/05/2026</t>
           </r>
         </is>
       </c>
@@ -44907,7 +44907,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON ANTONIO DE AVILA</t>
+            <t xml:space="preserve">WARLEY TEODORO</t>
           </r>
         </is>
       </c>
@@ -44917,7 +44917,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">913.901.686-20</t>
+            <t xml:space="preserve">061.096.156-09</t>
           </r>
         </is>
       </c>
@@ -44927,7 +44927,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00562356548</t>
+            <t xml:space="preserve">03946495186</t>
           </r>
         </is>
       </c>
@@ -44938,7 +44938,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/09/2027</t>
+            <t xml:space="preserve">23/09/2027</t>
           </r>
         </is>
       </c>
@@ -44986,7 +44986,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON BARBOSA VIEIRA</t>
+            <t xml:space="preserve">WASHINGTON ANTONIO DE AVILA</t>
           </r>
         </is>
       </c>
@@ -44996,7 +44996,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">094.176.466-48</t>
+            <t xml:space="preserve">913.901.686-20</t>
           </r>
         </is>
       </c>
@@ -45006,7 +45006,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">0412500611226</t>
+            <t xml:space="preserve">00562356548</t>
           </r>
         </is>
       </c>
@@ -45017,7 +45017,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/01/2027</t>
+            <t xml:space="preserve">04/09/2027</t>
           </r>
         </is>
       </c>
@@ -45065,7 +45065,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTON WELLINGTON PINTO</t>
+            <t xml:space="preserve">WASHINGTON BARBOSA VIEIRA</t>
           </r>
         </is>
       </c>
@@ -45075,7 +45075,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">092.920.176-08</t>
+            <t xml:space="preserve">094.176.466-48</t>
           </r>
         </is>
       </c>
@@ -45085,7 +45085,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04783305563</t>
+            <t xml:space="preserve">0412500611226</t>
           </r>
         </is>
       </c>
@@ -45096,7 +45096,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">23/01/2027</t>
           </r>
         </is>
       </c>
@@ -45137,14 +45137,14 @@
       <c r="T569" s="12" t="inlineStr"/>
       <c r="U569" s="1" t="inlineStr"/>
     </row>
-    <row r="570" customHeight="1" ht="22">
+    <row r="570" customHeight="1" ht="21">
       <c r="A570" s="1" t="inlineStr"/>
       <c r="B570" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WASHINGTONINACIO GOME DE REZENDE</t>
+            <t xml:space="preserve">WASHINGTON WELLINGTON PINTO</t>
           </r>
         </is>
       </c>
@@ -45154,7 +45154,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">125.555.806-70</t>
+            <t xml:space="preserve">092.920.176-08</t>
           </r>
         </is>
       </c>
@@ -45164,7 +45164,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06093566794</t>
+            <t xml:space="preserve">04783305563</t>
           </r>
         </is>
       </c>
@@ -45175,7 +45175,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/07/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -45223,7 +45223,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTHON FERNANDO FRANCISCO</t>
+            <t xml:space="preserve">WASHINGTONINACIO GOME DE REZENDE</t>
           </r>
         </is>
       </c>
@@ -45233,7 +45233,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">110.378.116-23</t>
+            <t xml:space="preserve">125.555.806-70</t>
           </r>
         </is>
       </c>
@@ -45243,7 +45243,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05042709980</t>
+            <t xml:space="preserve">06093566794</t>
           </r>
         </is>
       </c>
@@ -45254,7 +45254,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">06/07/2027</t>
+            <t xml:space="preserve">16/07/2027</t>
           </r>
         </is>
       </c>
@@ -45302,7 +45302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON APARECIDO DO NASCIMENTOS</t>
+            <t xml:space="preserve">WELLINGTHON FERNANDO FRANCISCO</t>
           </r>
         </is>
       </c>
@@ -45312,7 +45312,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">012.579.656-03</t>
+            <t xml:space="preserve">110.378.116-23</t>
           </r>
         </is>
       </c>
@@ -45322,7 +45322,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03357647398</t>
+            <t xml:space="preserve">05042709980</t>
           </r>
         </is>
       </c>
@@ -45333,7 +45333,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/07/2027</t>
+            <t xml:space="preserve">06/07/2027</t>
           </r>
         </is>
       </c>
@@ -45374,14 +45374,14 @@
       <c r="T572" s="12" t="inlineStr"/>
       <c r="U572" s="1" t="inlineStr"/>
     </row>
-    <row r="573" customHeight="1" ht="21">
+    <row r="573" customHeight="1" ht="22">
       <c r="A573" s="1" t="inlineStr"/>
       <c r="B573" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON PEREIRA SILVA</t>
+            <t xml:space="preserve">WELLINGTON APARECIDO DO NASCIMENTOS</t>
           </r>
         </is>
       </c>
@@ -45391,7 +45391,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">052.481.486-42</t>
+            <t xml:space="preserve">012.579.656-03</t>
           </r>
         </is>
       </c>
@@ -45401,7 +45401,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">02266389739</t>
+            <t xml:space="preserve">03357647398</t>
           </r>
         </is>
       </c>
@@ -45412,7 +45412,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">17/09/2027</t>
+            <t xml:space="preserve">15/07/2027</t>
           </r>
         </is>
       </c>
@@ -45460,7 +45460,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINGTON TERTULIANO</t>
+            <t xml:space="preserve">WELLINGTON PEREIRA SILVA</t>
           </r>
         </is>
       </c>
@@ -45470,7 +45470,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">084.518.494-66</t>
+            <t xml:space="preserve">052.481.486-42</t>
           </r>
         </is>
       </c>
@@ -45480,7 +45480,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04648920920</t>
+            <t xml:space="preserve">02266389739</t>
           </r>
         </is>
       </c>
@@ -45491,7 +45491,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/08/2027</t>
+            <t xml:space="preserve">17/09/2027</t>
           </r>
         </is>
       </c>
@@ -45539,7 +45539,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLINTON SOUSA NUNES</t>
+            <t xml:space="preserve">WELLINGTON TERTULIANO</t>
           </r>
         </is>
       </c>
@@ -45549,7 +45549,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.631.261-68</t>
+            <t xml:space="preserve">084.518.494-66</t>
           </r>
         </is>
       </c>
@@ -45559,7 +45559,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01601461581</t>
+            <t xml:space="preserve">04648920920</t>
           </r>
         </is>
       </c>
@@ -45570,7 +45570,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">24/09/2027</t>
+            <t xml:space="preserve">13/08/2027</t>
           </r>
         </is>
       </c>
@@ -45618,7 +45618,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELLISON FERREIRA RODRIGUES</t>
+            <t xml:space="preserve">WELLINTON SOUSA NUNES</t>
           </r>
         </is>
       </c>
@@ -45628,7 +45628,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">060.332.916-03</t>
+            <t xml:space="preserve">868.631.261-68</t>
           </r>
         </is>
       </c>
@@ -45638,7 +45638,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04203957932</t>
+            <t xml:space="preserve">01601461581</t>
           </r>
         </is>
       </c>
@@ -45649,7 +45649,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/07/2031</t>
+            <t xml:space="preserve">24/09/2027</t>
           </r>
         </is>
       </c>
@@ -45697,7 +45697,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELRERT VIETRA DOR HANTO</t>
+            <t xml:space="preserve">WELLISON FERREIRA RODRIGUES</t>
           </r>
         </is>
       </c>
@@ -45707,7 +45707,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.562.536-07</t>
+            <t xml:space="preserve">060.332.916-03</t>
           </r>
         </is>
       </c>
@@ -45717,7 +45717,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">03993707114</t>
+            <t xml:space="preserve">04203957932</t>
           </r>
         </is>
       </c>
@@ -45728,7 +45728,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">25/09/2027</t>
+            <t xml:space="preserve">29/07/2031</t>
           </r>
         </is>
       </c>
@@ -45769,14 +45769,14 @@
       <c r="T577" s="12" t="inlineStr"/>
       <c r="U577" s="1" t="inlineStr"/>
     </row>
-    <row r="578" customHeight="1" ht="22">
+    <row r="578" customHeight="1" ht="21">
       <c r="A578" s="1" t="inlineStr"/>
       <c r="B578" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WELSON ELIAS ARGUELLO TAVARES</t>
+            <t xml:space="preserve">WELRERT VIETRA DOR HANTO</t>
           </r>
         </is>
       </c>
@@ -45786,7 +45786,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">134.002.706-28</t>
+            <t xml:space="preserve">054.562.536-07</t>
           </r>
         </is>
       </c>
@@ -45796,7 +45796,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07495476705</t>
+            <t xml:space="preserve">03993707114</t>
           </r>
         </is>
       </c>
@@ -45807,7 +45807,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/10/2027</t>
+            <t xml:space="preserve">25/09/2027</t>
           </r>
         </is>
       </c>
@@ -45848,14 +45848,14 @@
       <c r="T578" s="12" t="inlineStr"/>
       <c r="U578" s="1" t="inlineStr"/>
     </row>
-    <row r="579" customHeight="1" ht="21">
+    <row r="579" customHeight="1" ht="22">
       <c r="A579" s="1" t="inlineStr"/>
       <c r="B579" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WEMERSON DE SOUZA PIRES</t>
+            <t xml:space="preserve">WELSON ELIAS ARGUELLO TAVARES</t>
           </r>
         </is>
       </c>
@@ -45865,7 +45865,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">085.948.536-61</t>
+            <t xml:space="preserve">134.002.706-28</t>
           </r>
         </is>
       </c>
@@ -45875,7 +45875,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04289760206</t>
+            <t xml:space="preserve">07495476705</t>
           </r>
         </is>
       </c>
@@ -45886,7 +45886,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/09/2027</t>
+            <t xml:space="preserve">15/10/2027</t>
           </r>
         </is>
       </c>
@@ -45934,7 +45934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEI FERNANDES DA COSTA</t>
+            <t xml:space="preserve">WEMERSON DE SOUZA PIRES</t>
           </r>
         </is>
       </c>
@@ -45944,7 +45944,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">054.289.656-73</t>
+            <t xml:space="preserve">085.948.536-61</t>
           </r>
         </is>
       </c>
@@ -45954,7 +45954,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01357310210</t>
+            <t xml:space="preserve">04289760206</t>
           </r>
         </is>
       </c>
@@ -45965,7 +45965,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">22/01/2027</t>
+            <t xml:space="preserve">18/09/2027</t>
           </r>
         </is>
       </c>
@@ -46013,7 +46013,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEY LARA DORNELAS VAZ</t>
+            <t xml:space="preserve">WESLEI FERNANDES DA COSTA</t>
           </r>
         </is>
       </c>
@@ -46023,7 +46023,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">051.926.946-20</t>
+            <t xml:space="preserve">054.289.656-73</t>
           </r>
         </is>
       </c>
@@ -46033,7 +46033,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01882616840</t>
+            <t xml:space="preserve">01357310210</t>
           </r>
         </is>
       </c>
@@ -46044,7 +46044,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">29/04/2027</t>
+            <t xml:space="preserve">22/01/2027</t>
           </r>
         </is>
       </c>
@@ -46092,7 +46092,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WESLEY PEREIRA DA SILVA</t>
+            <t xml:space="preserve">WESLEY LARA DORNELAS VAZ</t>
           </r>
         </is>
       </c>
@@ -46102,7 +46102,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">080.589.316-40</t>
+            <t xml:space="preserve">051.926.946-20</t>
           </r>
         </is>
       </c>
@@ -46112,7 +46112,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04884904684</t>
+            <t xml:space="preserve">01882616840</t>
           </r>
         </is>
       </c>
@@ -46123,7 +46123,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07/10/2027</t>
+            <t xml:space="preserve">29/04/2027</t>
           </r>
         </is>
       </c>
@@ -46164,14 +46164,14 @@
       <c r="T582" s="12" t="inlineStr"/>
       <c r="U582" s="1" t="inlineStr"/>
     </row>
-    <row r="583" customHeight="1" ht="22">
+    <row r="583" customHeight="1" ht="21">
       <c r="A583" s="1" t="inlineStr"/>
       <c r="B583" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILDENBERG DAYRELL BENEDITO DA SILVA</t>
+            <t xml:space="preserve">WESLEY PEREIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -46181,7 +46181,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">146.120.596-46</t>
+            <t xml:space="preserve">080.589.316-40</t>
           </r>
         </is>
       </c>
@@ -46191,7 +46191,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">07394414462</t>
+            <t xml:space="preserve">04884904684</t>
           </r>
         </is>
       </c>
@@ -46202,7 +46202,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">07/10/2027</t>
           </r>
         </is>
       </c>
@@ -46243,14 +46243,14 @@
       <c r="T583" s="12" t="inlineStr"/>
       <c r="U583" s="1" t="inlineStr"/>
     </row>
-    <row r="584" customHeight="1" ht="21">
+    <row r="584" customHeight="1" ht="22">
       <c r="A584" s="1" t="inlineStr"/>
       <c r="B584" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLER DIAS LADEIRA DA SILVA</t>
+            <t xml:space="preserve">WILDENBERG DAYRELL BENEDITO DA SILVA</t>
           </r>
         </is>
       </c>
@@ -46260,7 +46260,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">868.752.806-04</t>
+            <t xml:space="preserve">146.120.596-46</t>
           </r>
         </is>
       </c>
@@ -46270,7 +46270,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01225273506</t>
+            <t xml:space="preserve">07394414462</t>
           </r>
         </is>
       </c>
@@ -46281,7 +46281,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">05/10/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -46329,7 +46329,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLER RODRIGUES DUARTE   </t>
+            <t xml:space="preserve">WILLER DIAS LADEIRA DA SILVA</t>
           </r>
         </is>
       </c>
@@ -46339,7 +46339,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">842.137.796-53</t>
+            <t xml:space="preserve">868.752.806-04</t>
           </r>
         </is>
       </c>
@@ -46349,7 +46349,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">00718175645</t>
+            <t xml:space="preserve">01225273506</t>
           </r>
         </is>
       </c>
@@ -46360,7 +46360,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/10/2027</t>
+            <t xml:space="preserve">05/10/2027</t>
           </r>
         </is>
       </c>
@@ -46408,7 +46408,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILLIAN LOURENCO DA SILVA </t>
+            <t xml:space="preserve">WILLER RODRIGUES DUARTE   </t>
           </r>
         </is>
       </c>
@@ -46418,7 +46418,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">065.769.226-39</t>
+            <t xml:space="preserve">842.137.796-53</t>
           </r>
         </is>
       </c>
@@ -46428,7 +46428,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04158429281</t>
+            <t xml:space="preserve">00718175645</t>
           </r>
         </is>
       </c>
@@ -46439,7 +46439,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">15/09/2027</t>
+            <t xml:space="preserve">20/10/2027</t>
           </r>
         </is>
       </c>
@@ -46480,14 +46480,14 @@
       <c r="T586" s="12" t="inlineStr"/>
       <c r="U586" s="1" t="inlineStr"/>
     </row>
-    <row r="587" customHeight="1" ht="22">
+    <row r="587" customHeight="1" ht="21">
       <c r="A587" s="1" t="inlineStr"/>
       <c r="B587" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">WILSON FRANCISCO MARZANO SILVEIRA </t>
+            <t xml:space="preserve">WILLIAN LOURENCO DA SILVA </t>
           </r>
         </is>
       </c>
@@ -46497,7 +46497,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">049.781.696-23</t>
+            <t xml:space="preserve">065.769.226-39</t>
           </r>
         </is>
       </c>
@@ -46507,7 +46507,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01673877203</t>
+            <t xml:space="preserve">04158429281</t>
           </r>
         </is>
       </c>
@@ -46518,7 +46518,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/08/2027</t>
+            <t xml:space="preserve">15/09/2027</t>
           </r>
         </is>
       </c>
@@ -46566,7 +46566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ZENILSON MARCELINO DE CARVALHO</t>
+            <t xml:space="preserve">WILSON FRANCISCO MARZANO SILVEIRA </t>
           </r>
         </is>
       </c>
@@ -46576,7 +46576,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">039.291.734-33</t>
+            <t xml:space="preserve">049.781.696-23</t>
           </r>
         </is>
       </c>
@@ -46586,7 +46586,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04371720578</t>
+            <t xml:space="preserve">01673877203</t>
           </r>
         </is>
       </c>
@@ -46597,7 +46597,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/01/2027</t>
+            <t xml:space="preserve">10/08/2027</t>
           </r>
         </is>
       </c>
@@ -46638,35 +46638,83 @@
       <c r="T588" s="12" t="inlineStr"/>
       <c r="U588" s="1" t="inlineStr"/>
     </row>
-    <row r="589" customHeight="1" ht="15">
+    <row r="589" customHeight="1" ht="22">
       <c r="A589" s="1" t="inlineStr"/>
-      <c r="B589" s="1" t="inlineStr"/>
-      <c r="C589" s="14" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-       </rPr>
-            <t xml:space="preserve">Total Ativo: 582</t>
-          </r>
-        </is>
-      </c>
-      <c r="D589" s="15" t="inlineStr"/>
-      <c r="E589" s="1" t="inlineStr"/>
-      <c r="F589" s="1" t="inlineStr"/>
-      <c r="G589" s="1" t="inlineStr"/>
-      <c r="H589" s="1" t="inlineStr"/>
-      <c r="I589" s="1" t="inlineStr"/>
-      <c r="J589" s="1" t="inlineStr"/>
-      <c r="K589" s="1" t="inlineStr"/>
-      <c r="L589" s="1" t="inlineStr"/>
-      <c r="M589" s="1" t="inlineStr"/>
-      <c r="N589" s="1" t="inlineStr"/>
-      <c r="O589" s="1" t="inlineStr"/>
-      <c r="P589" s="1" t="inlineStr"/>
-      <c r="Q589" s="1" t="inlineStr"/>
-      <c r="R589" s="1" t="inlineStr"/>
-      <c r="S589" s="1" t="inlineStr"/>
-      <c r="T589" s="1" t="inlineStr"/>
+      <c r="B589" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">ZENILSON MARCELINO DE CARVALHO</t>
+          </r>
+        </is>
+      </c>
+      <c r="C589" s="10" t="inlineStr"/>
+      <c r="D589" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">039.291.734-33</t>
+          </r>
+        </is>
+      </c>
+      <c r="E589" s="12" t="inlineStr"/>
+      <c r="F589" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">04371720578</t>
+          </r>
+        </is>
+      </c>
+      <c r="G589" s="12" t="inlineStr"/>
+      <c r="H589" s="12" t="inlineStr"/>
+      <c r="I589" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">13/01/2027</t>
+          </r>
+        </is>
+      </c>
+      <c r="J589" s="12" t="inlineStr"/>
+      <c r="K589" s="12" t="inlineStr"/>
+      <c r="L589" s="12" t="inlineStr"/>
+      <c r="M589" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">87</t>
+          </r>
+        </is>
+      </c>
+      <c r="N589" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">VIACAO MINAS GERAIS LTDA</t>
+          </r>
+        </is>
+      </c>
+      <c r="O589" s="10" t="inlineStr"/>
+      <c r="P589" s="10" t="inlineStr"/>
+      <c r="Q589" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Ativo</t>
+          </r>
+        </is>
+      </c>
+      <c r="R589" s="12" t="inlineStr"/>
+      <c r="S589" s="12" t="inlineStr"/>
+      <c r="T589" s="12" t="inlineStr"/>
       <c r="U589" s="1" t="inlineStr"/>
     </row>
     <row r="590" customHeight="1" ht="15">
@@ -46677,7 +46725,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">Total Inativo: 0</t>
+            <t xml:space="preserve">Total Ativo: 583</t>
           </r>
         </is>
       </c>
@@ -46708,7 +46756,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">Total Geral: 582</t>
+            <t xml:space="preserve">Total Inativo: 0</t>
           </r>
         </is>
       </c>
@@ -46734,8 +46782,16 @@
     <row r="592" customHeight="1" ht="15">
       <c r="A592" s="1" t="inlineStr"/>
       <c r="B592" s="1" t="inlineStr"/>
-      <c r="C592" s="1" t="inlineStr"/>
-      <c r="D592" s="1" t="inlineStr"/>
+      <c r="C592" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">Total Geral: 583</t>
+          </r>
+        </is>
+      </c>
+      <c r="D592" s="15" t="inlineStr"/>
       <c r="E592" s="1" t="inlineStr"/>
       <c r="F592" s="1" t="inlineStr"/>
       <c r="G592" s="1" t="inlineStr"/>
@@ -46749,7 +46805,30 @@
       <c r="O592" s="1" t="inlineStr"/>
       <c r="P592" s="1" t="inlineStr"/>
       <c r="Q592" s="1" t="inlineStr"/>
-      <c r="R592" s="16" t="inlineStr">
+      <c r="R592" s="1" t="inlineStr"/>
+      <c r="S592" s="1" t="inlineStr"/>
+      <c r="T592" s="1" t="inlineStr"/>
+      <c r="U592" s="1" t="inlineStr"/>
+    </row>
+    <row r="593" customHeight="1" ht="15">
+      <c r="A593" s="1" t="inlineStr"/>
+      <c r="B593" s="1" t="inlineStr"/>
+      <c r="C593" s="1" t="inlineStr"/>
+      <c r="D593" s="1" t="inlineStr"/>
+      <c r="E593" s="1" t="inlineStr"/>
+      <c r="F593" s="1" t="inlineStr"/>
+      <c r="G593" s="1" t="inlineStr"/>
+      <c r="H593" s="1" t="inlineStr"/>
+      <c r="I593" s="1" t="inlineStr"/>
+      <c r="J593" s="1" t="inlineStr"/>
+      <c r="K593" s="1" t="inlineStr"/>
+      <c r="L593" s="1" t="inlineStr"/>
+      <c r="M593" s="1" t="inlineStr"/>
+      <c r="N593" s="1" t="inlineStr"/>
+      <c r="O593" s="1" t="inlineStr"/>
+      <c r="P593" s="1" t="inlineStr"/>
+      <c r="Q593" s="1" t="inlineStr"/>
+      <c r="R593" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46758,8 +46837,8 @@
           </r>
         </is>
       </c>
-      <c r="S592" s="17" t="inlineStr"/>
-      <c r="T592" s="16" t="inlineStr">
+      <c r="S593" s="17" t="inlineStr"/>
+      <c r="T593" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46768,7 +46847,7 @@
           </r>
         </is>
       </c>
-      <c r="U592" s="1" t="inlineStr"/>
+      <c r="U593" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -50277,10 +50356,16 @@
     <mergeCell ref="I588:L588"/>
     <mergeCell ref="N588:P588"/>
     <mergeCell ref="Q588:T588"/>
-    <mergeCell ref="C589:D589"/>
+    <mergeCell ref="B589:C589"/>
+    <mergeCell ref="D589:E589"/>
+    <mergeCell ref="F589:H589"/>
+    <mergeCell ref="I589:L589"/>
+    <mergeCell ref="N589:P589"/>
+    <mergeCell ref="Q589:T589"/>
     <mergeCell ref="C590:D590"/>
     <mergeCell ref="C591:D591"/>
-    <mergeCell ref="R592:S592"/>
+    <mergeCell ref="C592:D592"/>
+    <mergeCell ref="R593:S593"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rIdDr1"/>

--- a/relCondutores.xlsx
+++ b/relCondutores.xlsx
@@ -315,7 +315,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1065174443" name="Picture">
+        <xdr:cNvPr id="219128509" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
